--- a/Trading_PnL_Tracker.xlsx
+++ b/Trading_PnL_Tracker.xlsx
@@ -37,7 +37,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Provided by you: Day 1 = 25 Sep 2026. Each row is one calendar day.</t>
+          <t xml:space="preserve">Provided by you: you start trading tomorrow (26 Sep 2026). If this falls on a weekend, Day 1 moves to the next Monday. Only weekdays (Mon–Fri) get rows.</t>
         </r>
       </text>
     </comment>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Daily Trading P/L Tracker — ₹4,230 → ₹1,00,000 Goal</t>
   </si>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">DASHBOARD  (all calculated)</t>
   </si>
   <si>
-    <t xml:space="preserve">Start date (Day 1)</t>
+    <t xml:space="preserve">Start trading from</t>
   </si>
   <si>
     <t xml:space="preserve">Current balance</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Projected goal date*</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend:  Yellow cells with blue text = your inputs (Settings, Actual P/L, Done?, Notes).  All other cells are formulas — don't overwrite them.  Grey italic rows = Projection (target assumed met), white rows = Actual.   *Projection-based figures.</t>
+    <t xml:space="preserve">Rows = trading days only (Mon–Fri, weekends skipped).  Legend:  Yellow cells with blue text = your inputs (Settings, Actual P/L, Done?, Notes).  All other cells are formulas — don't overwrite them.  Grey italic rows = Projection (target assumed met), white rows = Actual.   *Projection-based figures.</t>
   </si>
   <si>
     <t xml:space="preserve">Day</t>
@@ -240,7 +240,7 @@
     <t xml:space="preserve">   • Rows marked "Projection" (grey italic) assume every daily profit target is hit. This is an illustration, not a prediction or guarantee.</t>
   </si>
   <si>
-    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹4,230 at 3%/day takes about 108 days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
+    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹4,230 at 3%/day takes about 108 trading days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
   </si>
   <si>
     <t xml:space="preserve">   • The table stops at the first day whose projected (or actual) close reaches the goal, and extends automatically after losses (up to 500 days).</t>
@@ -249,7 +249,13 @@
     <t xml:space="preserve">Other notes</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Dates are consecutive calendar days from 25-Sep-2026 (Day 1). Enter 0 for weekends/holidays you don't trade.</t>
+    <t xml:space="preserve">   • Only trading days (Monday–Friday) get rows — Saturdays and Sundays are skipped automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Start date is 26-Sep-2026 (Sat), so Day 1 is Monday 28-Sep-2026. Change the "Start trading from" setting to move everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Market holidays on weekdays still get a row — enter 0 on those days.</t>
   </si>
   <si>
     <t xml:space="preserve">   • Amounts are rounded to the paisa (2 decimals). Targets and limits = ROUND(opening capital × 3%, 2).</t>
@@ -1023,7 +1029,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>5</v>
@@ -1131,8 +1137,8 @@
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="14" t="n">
-        <f aca="false">$C$5+$J$6</f>
-        <v>46290</v>
+        <f aca="false">WORKDAY($C$5-1,$J$6+1)</f>
+        <v>46293</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>17</v>
@@ -1140,7 +1146,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="14" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",IF(AND($C$512&lt;&gt;"",N($F$512)&lt;$C$7),"Beyond 500 rows",MAX($B$13:$B$512)))</f>
-        <v>46397</v>
+        <v>46442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1199,8 +1205,8 @@
         <v>1</v>
       </c>
       <c r="B13" s="19" t="n">
-        <f aca="false">IF(C13="","",$C$5+A13-1)</f>
-        <v>46290</v>
+        <f aca="false">IF(C13="","",WORKDAY($C$5-1,A13))</f>
+        <v>46293</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">$C$6</f>
@@ -1236,8 +1242,8 @@
         <v>2</v>
       </c>
       <c r="B14" s="19" t="n">
-        <f aca="false">IF(C14="","",$C$5+A14-1)</f>
-        <v>46291</v>
+        <f aca="false">IF(C14="","",WORKDAY($C$5-1,A14))</f>
+        <v>46294</v>
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">IF(C13="","",IF(OR(IF(ISNUMBER(G13),H13,F13)&gt;=$C$7,IF(ISNUMBER(G13),H13,F13)&lt;=0),"",IF(ISNUMBER(G13),H13,F13)))</f>
@@ -1273,8 +1279,8 @@
         <v>3</v>
       </c>
       <c r="B15" s="19" t="n">
-        <f aca="false">IF(C15="","",$C$5+A15-1)</f>
-        <v>46292</v>
+        <f aca="false">IF(C15="","",WORKDAY($C$5-1,A15))</f>
+        <v>46295</v>
       </c>
       <c r="C15" s="20" t="n">
         <f aca="false">IF(C14="","",IF(OR(IF(ISNUMBER(G14),H14,F14)&gt;=$C$7,IF(ISNUMBER(G14),H14,F14)&lt;=0),"",IF(ISNUMBER(G14),H14,F14)))</f>
@@ -1310,8 +1316,8 @@
         <v>4</v>
       </c>
       <c r="B16" s="19" t="n">
-        <f aca="false">IF(C16="","",$C$5+A16-1)</f>
-        <v>46293</v>
+        <f aca="false">IF(C16="","",WORKDAY($C$5-1,A16))</f>
+        <v>46296</v>
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">IF(C15="","",IF(OR(IF(ISNUMBER(G15),H15,F15)&gt;=$C$7,IF(ISNUMBER(G15),H15,F15)&lt;=0),"",IF(ISNUMBER(G15),H15,F15)))</f>
@@ -1347,8 +1353,8 @@
         <v>5</v>
       </c>
       <c r="B17" s="19" t="n">
-        <f aca="false">IF(C17="","",$C$5+A17-1)</f>
-        <v>46294</v>
+        <f aca="false">IF(C17="","",WORKDAY($C$5-1,A17))</f>
+        <v>46297</v>
       </c>
       <c r="C17" s="20" t="n">
         <f aca="false">IF(C16="","",IF(OR(IF(ISNUMBER(G16),H16,F16)&gt;=$C$7,IF(ISNUMBER(G16),H16,F16)&lt;=0),"",IF(ISNUMBER(G16),H16,F16)))</f>
@@ -1384,8 +1390,8 @@
         <v>6</v>
       </c>
       <c r="B18" s="19" t="n">
-        <f aca="false">IF(C18="","",$C$5+A18-1)</f>
-        <v>46295</v>
+        <f aca="false">IF(C18="","",WORKDAY($C$5-1,A18))</f>
+        <v>46300</v>
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">IF(C17="","",IF(OR(IF(ISNUMBER(G17),H17,F17)&gt;=$C$7,IF(ISNUMBER(G17),H17,F17)&lt;=0),"",IF(ISNUMBER(G17),H17,F17)))</f>
@@ -1421,8 +1427,8 @@
         <v>7</v>
       </c>
       <c r="B19" s="19" t="n">
-        <f aca="false">IF(C19="","",$C$5+A19-1)</f>
-        <v>46296</v>
+        <f aca="false">IF(C19="","",WORKDAY($C$5-1,A19))</f>
+        <v>46301</v>
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">IF(C18="","",IF(OR(IF(ISNUMBER(G18),H18,F18)&gt;=$C$7,IF(ISNUMBER(G18),H18,F18)&lt;=0),"",IF(ISNUMBER(G18),H18,F18)))</f>
@@ -1458,8 +1464,8 @@
         <v>8</v>
       </c>
       <c r="B20" s="19" t="n">
-        <f aca="false">IF(C20="","",$C$5+A20-1)</f>
-        <v>46297</v>
+        <f aca="false">IF(C20="","",WORKDAY($C$5-1,A20))</f>
+        <v>46302</v>
       </c>
       <c r="C20" s="20" t="n">
         <f aca="false">IF(C19="","",IF(OR(IF(ISNUMBER(G19),H19,F19)&gt;=$C$7,IF(ISNUMBER(G19),H19,F19)&lt;=0),"",IF(ISNUMBER(G19),H19,F19)))</f>
@@ -1495,8 +1501,8 @@
         <v>9</v>
       </c>
       <c r="B21" s="19" t="n">
-        <f aca="false">IF(C21="","",$C$5+A21-1)</f>
-        <v>46298</v>
+        <f aca="false">IF(C21="","",WORKDAY($C$5-1,A21))</f>
+        <v>46303</v>
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">IF(C20="","",IF(OR(IF(ISNUMBER(G20),H20,F20)&gt;=$C$7,IF(ISNUMBER(G20),H20,F20)&lt;=0),"",IF(ISNUMBER(G20),H20,F20)))</f>
@@ -1532,8 +1538,8 @@
         <v>10</v>
       </c>
       <c r="B22" s="19" t="n">
-        <f aca="false">IF(C22="","",$C$5+A22-1)</f>
-        <v>46299</v>
+        <f aca="false">IF(C22="","",WORKDAY($C$5-1,A22))</f>
+        <v>46304</v>
       </c>
       <c r="C22" s="20" t="n">
         <f aca="false">IF(C21="","",IF(OR(IF(ISNUMBER(G21),H21,F21)&gt;=$C$7,IF(ISNUMBER(G21),H21,F21)&lt;=0),"",IF(ISNUMBER(G21),H21,F21)))</f>
@@ -1569,8 +1575,8 @@
         <v>11</v>
       </c>
       <c r="B23" s="19" t="n">
-        <f aca="false">IF(C23="","",$C$5+A23-1)</f>
-        <v>46300</v>
+        <f aca="false">IF(C23="","",WORKDAY($C$5-1,A23))</f>
+        <v>46307</v>
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">IF(C22="","",IF(OR(IF(ISNUMBER(G22),H22,F22)&gt;=$C$7,IF(ISNUMBER(G22),H22,F22)&lt;=0),"",IF(ISNUMBER(G22),H22,F22)))</f>
@@ -1606,8 +1612,8 @@
         <v>12</v>
       </c>
       <c r="B24" s="19" t="n">
-        <f aca="false">IF(C24="","",$C$5+A24-1)</f>
-        <v>46301</v>
+        <f aca="false">IF(C24="","",WORKDAY($C$5-1,A24))</f>
+        <v>46308</v>
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">IF(C23="","",IF(OR(IF(ISNUMBER(G23),H23,F23)&gt;=$C$7,IF(ISNUMBER(G23),H23,F23)&lt;=0),"",IF(ISNUMBER(G23),H23,F23)))</f>
@@ -1643,8 +1649,8 @@
         <v>13</v>
       </c>
       <c r="B25" s="19" t="n">
-        <f aca="false">IF(C25="","",$C$5+A25-1)</f>
-        <v>46302</v>
+        <f aca="false">IF(C25="","",WORKDAY($C$5-1,A25))</f>
+        <v>46309</v>
       </c>
       <c r="C25" s="20" t="n">
         <f aca="false">IF(C24="","",IF(OR(IF(ISNUMBER(G24),H24,F24)&gt;=$C$7,IF(ISNUMBER(G24),H24,F24)&lt;=0),"",IF(ISNUMBER(G24),H24,F24)))</f>
@@ -1680,8 +1686,8 @@
         <v>14</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">IF(C26="","",$C$5+A26-1)</f>
-        <v>46303</v>
+        <f aca="false">IF(C26="","",WORKDAY($C$5-1,A26))</f>
+        <v>46310</v>
       </c>
       <c r="C26" s="20" t="n">
         <f aca="false">IF(C25="","",IF(OR(IF(ISNUMBER(G25),H25,F25)&gt;=$C$7,IF(ISNUMBER(G25),H25,F25)&lt;=0),"",IF(ISNUMBER(G25),H25,F25)))</f>
@@ -1717,8 +1723,8 @@
         <v>15</v>
       </c>
       <c r="B27" s="19" t="n">
-        <f aca="false">IF(C27="","",$C$5+A27-1)</f>
-        <v>46304</v>
+        <f aca="false">IF(C27="","",WORKDAY($C$5-1,A27))</f>
+        <v>46311</v>
       </c>
       <c r="C27" s="20" t="n">
         <f aca="false">IF(C26="","",IF(OR(IF(ISNUMBER(G26),H26,F26)&gt;=$C$7,IF(ISNUMBER(G26),H26,F26)&lt;=0),"",IF(ISNUMBER(G26),H26,F26)))</f>
@@ -1754,8 +1760,8 @@
         <v>16</v>
       </c>
       <c r="B28" s="19" t="n">
-        <f aca="false">IF(C28="","",$C$5+A28-1)</f>
-        <v>46305</v>
+        <f aca="false">IF(C28="","",WORKDAY($C$5-1,A28))</f>
+        <v>46314</v>
       </c>
       <c r="C28" s="20" t="n">
         <f aca="false">IF(C27="","",IF(OR(IF(ISNUMBER(G27),H27,F27)&gt;=$C$7,IF(ISNUMBER(G27),H27,F27)&lt;=0),"",IF(ISNUMBER(G27),H27,F27)))</f>
@@ -1791,8 +1797,8 @@
         <v>17</v>
       </c>
       <c r="B29" s="19" t="n">
-        <f aca="false">IF(C29="","",$C$5+A29-1)</f>
-        <v>46306</v>
+        <f aca="false">IF(C29="","",WORKDAY($C$5-1,A29))</f>
+        <v>46315</v>
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">IF(C28="","",IF(OR(IF(ISNUMBER(G28),H28,F28)&gt;=$C$7,IF(ISNUMBER(G28),H28,F28)&lt;=0),"",IF(ISNUMBER(G28),H28,F28)))</f>
@@ -1828,8 +1834,8 @@
         <v>18</v>
       </c>
       <c r="B30" s="19" t="n">
-        <f aca="false">IF(C30="","",$C$5+A30-1)</f>
-        <v>46307</v>
+        <f aca="false">IF(C30="","",WORKDAY($C$5-1,A30))</f>
+        <v>46316</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">IF(C29="","",IF(OR(IF(ISNUMBER(G29),H29,F29)&gt;=$C$7,IF(ISNUMBER(G29),H29,F29)&lt;=0),"",IF(ISNUMBER(G29),H29,F29)))</f>
@@ -1865,8 +1871,8 @@
         <v>19</v>
       </c>
       <c r="B31" s="19" t="n">
-        <f aca="false">IF(C31="","",$C$5+A31-1)</f>
-        <v>46308</v>
+        <f aca="false">IF(C31="","",WORKDAY($C$5-1,A31))</f>
+        <v>46317</v>
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">IF(C30="","",IF(OR(IF(ISNUMBER(G30),H30,F30)&gt;=$C$7,IF(ISNUMBER(G30),H30,F30)&lt;=0),"",IF(ISNUMBER(G30),H30,F30)))</f>
@@ -1902,8 +1908,8 @@
         <v>20</v>
       </c>
       <c r="B32" s="19" t="n">
-        <f aca="false">IF(C32="","",$C$5+A32-1)</f>
-        <v>46309</v>
+        <f aca="false">IF(C32="","",WORKDAY($C$5-1,A32))</f>
+        <v>46318</v>
       </c>
       <c r="C32" s="20" t="n">
         <f aca="false">IF(C31="","",IF(OR(IF(ISNUMBER(G31),H31,F31)&gt;=$C$7,IF(ISNUMBER(G31),H31,F31)&lt;=0),"",IF(ISNUMBER(G31),H31,F31)))</f>
@@ -1939,8 +1945,8 @@
         <v>21</v>
       </c>
       <c r="B33" s="19" t="n">
-        <f aca="false">IF(C33="","",$C$5+A33-1)</f>
-        <v>46310</v>
+        <f aca="false">IF(C33="","",WORKDAY($C$5-1,A33))</f>
+        <v>46321</v>
       </c>
       <c r="C33" s="20" t="n">
         <f aca="false">IF(C32="","",IF(OR(IF(ISNUMBER(G32),H32,F32)&gt;=$C$7,IF(ISNUMBER(G32),H32,F32)&lt;=0),"",IF(ISNUMBER(G32),H32,F32)))</f>
@@ -1976,8 +1982,8 @@
         <v>22</v>
       </c>
       <c r="B34" s="19" t="n">
-        <f aca="false">IF(C34="","",$C$5+A34-1)</f>
-        <v>46311</v>
+        <f aca="false">IF(C34="","",WORKDAY($C$5-1,A34))</f>
+        <v>46322</v>
       </c>
       <c r="C34" s="20" t="n">
         <f aca="false">IF(C33="","",IF(OR(IF(ISNUMBER(G33),H33,F33)&gt;=$C$7,IF(ISNUMBER(G33),H33,F33)&lt;=0),"",IF(ISNUMBER(G33),H33,F33)))</f>
@@ -2013,8 +2019,8 @@
         <v>23</v>
       </c>
       <c r="B35" s="19" t="n">
-        <f aca="false">IF(C35="","",$C$5+A35-1)</f>
-        <v>46312</v>
+        <f aca="false">IF(C35="","",WORKDAY($C$5-1,A35))</f>
+        <v>46323</v>
       </c>
       <c r="C35" s="20" t="n">
         <f aca="false">IF(C34="","",IF(OR(IF(ISNUMBER(G34),H34,F34)&gt;=$C$7,IF(ISNUMBER(G34),H34,F34)&lt;=0),"",IF(ISNUMBER(G34),H34,F34)))</f>
@@ -2050,8 +2056,8 @@
         <v>24</v>
       </c>
       <c r="B36" s="19" t="n">
-        <f aca="false">IF(C36="","",$C$5+A36-1)</f>
-        <v>46313</v>
+        <f aca="false">IF(C36="","",WORKDAY($C$5-1,A36))</f>
+        <v>46324</v>
       </c>
       <c r="C36" s="20" t="n">
         <f aca="false">IF(C35="","",IF(OR(IF(ISNUMBER(G35),H35,F35)&gt;=$C$7,IF(ISNUMBER(G35),H35,F35)&lt;=0),"",IF(ISNUMBER(G35),H35,F35)))</f>
@@ -2087,8 +2093,8 @@
         <v>25</v>
       </c>
       <c r="B37" s="19" t="n">
-        <f aca="false">IF(C37="","",$C$5+A37-1)</f>
-        <v>46314</v>
+        <f aca="false">IF(C37="","",WORKDAY($C$5-1,A37))</f>
+        <v>46325</v>
       </c>
       <c r="C37" s="20" t="n">
         <f aca="false">IF(C36="","",IF(OR(IF(ISNUMBER(G36),H36,F36)&gt;=$C$7,IF(ISNUMBER(G36),H36,F36)&lt;=0),"",IF(ISNUMBER(G36),H36,F36)))</f>
@@ -2124,8 +2130,8 @@
         <v>26</v>
       </c>
       <c r="B38" s="19" t="n">
-        <f aca="false">IF(C38="","",$C$5+A38-1)</f>
-        <v>46315</v>
+        <f aca="false">IF(C38="","",WORKDAY($C$5-1,A38))</f>
+        <v>46328</v>
       </c>
       <c r="C38" s="20" t="n">
         <f aca="false">IF(C37="","",IF(OR(IF(ISNUMBER(G37),H37,F37)&gt;=$C$7,IF(ISNUMBER(G37),H37,F37)&lt;=0),"",IF(ISNUMBER(G37),H37,F37)))</f>
@@ -2161,8 +2167,8 @@
         <v>27</v>
       </c>
       <c r="B39" s="19" t="n">
-        <f aca="false">IF(C39="","",$C$5+A39-1)</f>
-        <v>46316</v>
+        <f aca="false">IF(C39="","",WORKDAY($C$5-1,A39))</f>
+        <v>46329</v>
       </c>
       <c r="C39" s="20" t="n">
         <f aca="false">IF(C38="","",IF(OR(IF(ISNUMBER(G38),H38,F38)&gt;=$C$7,IF(ISNUMBER(G38),H38,F38)&lt;=0),"",IF(ISNUMBER(G38),H38,F38)))</f>
@@ -2198,8 +2204,8 @@
         <v>28</v>
       </c>
       <c r="B40" s="19" t="n">
-        <f aca="false">IF(C40="","",$C$5+A40-1)</f>
-        <v>46317</v>
+        <f aca="false">IF(C40="","",WORKDAY($C$5-1,A40))</f>
+        <v>46330</v>
       </c>
       <c r="C40" s="20" t="n">
         <f aca="false">IF(C39="","",IF(OR(IF(ISNUMBER(G39),H39,F39)&gt;=$C$7,IF(ISNUMBER(G39),H39,F39)&lt;=0),"",IF(ISNUMBER(G39),H39,F39)))</f>
@@ -2235,8 +2241,8 @@
         <v>29</v>
       </c>
       <c r="B41" s="19" t="n">
-        <f aca="false">IF(C41="","",$C$5+A41-1)</f>
-        <v>46318</v>
+        <f aca="false">IF(C41="","",WORKDAY($C$5-1,A41))</f>
+        <v>46331</v>
       </c>
       <c r="C41" s="20" t="n">
         <f aca="false">IF(C40="","",IF(OR(IF(ISNUMBER(G40),H40,F40)&gt;=$C$7,IF(ISNUMBER(G40),H40,F40)&lt;=0),"",IF(ISNUMBER(G40),H40,F40)))</f>
@@ -2272,8 +2278,8 @@
         <v>30</v>
       </c>
       <c r="B42" s="19" t="n">
-        <f aca="false">IF(C42="","",$C$5+A42-1)</f>
-        <v>46319</v>
+        <f aca="false">IF(C42="","",WORKDAY($C$5-1,A42))</f>
+        <v>46332</v>
       </c>
       <c r="C42" s="20" t="n">
         <f aca="false">IF(C41="","",IF(OR(IF(ISNUMBER(G41),H41,F41)&gt;=$C$7,IF(ISNUMBER(G41),H41,F41)&lt;=0),"",IF(ISNUMBER(G41),H41,F41)))</f>
@@ -2309,8 +2315,8 @@
         <v>31</v>
       </c>
       <c r="B43" s="19" t="n">
-        <f aca="false">IF(C43="","",$C$5+A43-1)</f>
-        <v>46320</v>
+        <f aca="false">IF(C43="","",WORKDAY($C$5-1,A43))</f>
+        <v>46335</v>
       </c>
       <c r="C43" s="20" t="n">
         <f aca="false">IF(C42="","",IF(OR(IF(ISNUMBER(G42),H42,F42)&gt;=$C$7,IF(ISNUMBER(G42),H42,F42)&lt;=0),"",IF(ISNUMBER(G42),H42,F42)))</f>
@@ -2346,8 +2352,8 @@
         <v>32</v>
       </c>
       <c r="B44" s="19" t="n">
-        <f aca="false">IF(C44="","",$C$5+A44-1)</f>
-        <v>46321</v>
+        <f aca="false">IF(C44="","",WORKDAY($C$5-1,A44))</f>
+        <v>46336</v>
       </c>
       <c r="C44" s="20" t="n">
         <f aca="false">IF(C43="","",IF(OR(IF(ISNUMBER(G43),H43,F43)&gt;=$C$7,IF(ISNUMBER(G43),H43,F43)&lt;=0),"",IF(ISNUMBER(G43),H43,F43)))</f>
@@ -2383,8 +2389,8 @@
         <v>33</v>
       </c>
       <c r="B45" s="19" t="n">
-        <f aca="false">IF(C45="","",$C$5+A45-1)</f>
-        <v>46322</v>
+        <f aca="false">IF(C45="","",WORKDAY($C$5-1,A45))</f>
+        <v>46337</v>
       </c>
       <c r="C45" s="20" t="n">
         <f aca="false">IF(C44="","",IF(OR(IF(ISNUMBER(G44),H44,F44)&gt;=$C$7,IF(ISNUMBER(G44),H44,F44)&lt;=0),"",IF(ISNUMBER(G44),H44,F44)))</f>
@@ -2420,8 +2426,8 @@
         <v>34</v>
       </c>
       <c r="B46" s="19" t="n">
-        <f aca="false">IF(C46="","",$C$5+A46-1)</f>
-        <v>46323</v>
+        <f aca="false">IF(C46="","",WORKDAY($C$5-1,A46))</f>
+        <v>46338</v>
       </c>
       <c r="C46" s="20" t="n">
         <f aca="false">IF(C45="","",IF(OR(IF(ISNUMBER(G45),H45,F45)&gt;=$C$7,IF(ISNUMBER(G45),H45,F45)&lt;=0),"",IF(ISNUMBER(G45),H45,F45)))</f>
@@ -2457,8 +2463,8 @@
         <v>35</v>
       </c>
       <c r="B47" s="19" t="n">
-        <f aca="false">IF(C47="","",$C$5+A47-1)</f>
-        <v>46324</v>
+        <f aca="false">IF(C47="","",WORKDAY($C$5-1,A47))</f>
+        <v>46339</v>
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">IF(C46="","",IF(OR(IF(ISNUMBER(G46),H46,F46)&gt;=$C$7,IF(ISNUMBER(G46),H46,F46)&lt;=0),"",IF(ISNUMBER(G46),H46,F46)))</f>
@@ -2494,8 +2500,8 @@
         <v>36</v>
       </c>
       <c r="B48" s="19" t="n">
-        <f aca="false">IF(C48="","",$C$5+A48-1)</f>
-        <v>46325</v>
+        <f aca="false">IF(C48="","",WORKDAY($C$5-1,A48))</f>
+        <v>46342</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">IF(C47="","",IF(OR(IF(ISNUMBER(G47),H47,F47)&gt;=$C$7,IF(ISNUMBER(G47),H47,F47)&lt;=0),"",IF(ISNUMBER(G47),H47,F47)))</f>
@@ -2531,8 +2537,8 @@
         <v>37</v>
       </c>
       <c r="B49" s="19" t="n">
-        <f aca="false">IF(C49="","",$C$5+A49-1)</f>
-        <v>46326</v>
+        <f aca="false">IF(C49="","",WORKDAY($C$5-1,A49))</f>
+        <v>46343</v>
       </c>
       <c r="C49" s="20" t="n">
         <f aca="false">IF(C48="","",IF(OR(IF(ISNUMBER(G48),H48,F48)&gt;=$C$7,IF(ISNUMBER(G48),H48,F48)&lt;=0),"",IF(ISNUMBER(G48),H48,F48)))</f>
@@ -2568,8 +2574,8 @@
         <v>38</v>
       </c>
       <c r="B50" s="19" t="n">
-        <f aca="false">IF(C50="","",$C$5+A50-1)</f>
-        <v>46327</v>
+        <f aca="false">IF(C50="","",WORKDAY($C$5-1,A50))</f>
+        <v>46344</v>
       </c>
       <c r="C50" s="20" t="n">
         <f aca="false">IF(C49="","",IF(OR(IF(ISNUMBER(G49),H49,F49)&gt;=$C$7,IF(ISNUMBER(G49),H49,F49)&lt;=0),"",IF(ISNUMBER(G49),H49,F49)))</f>
@@ -2605,8 +2611,8 @@
         <v>39</v>
       </c>
       <c r="B51" s="19" t="n">
-        <f aca="false">IF(C51="","",$C$5+A51-1)</f>
-        <v>46328</v>
+        <f aca="false">IF(C51="","",WORKDAY($C$5-1,A51))</f>
+        <v>46345</v>
       </c>
       <c r="C51" s="20" t="n">
         <f aca="false">IF(C50="","",IF(OR(IF(ISNUMBER(G50),H50,F50)&gt;=$C$7,IF(ISNUMBER(G50),H50,F50)&lt;=0),"",IF(ISNUMBER(G50),H50,F50)))</f>
@@ -2642,8 +2648,8 @@
         <v>40</v>
       </c>
       <c r="B52" s="19" t="n">
-        <f aca="false">IF(C52="","",$C$5+A52-1)</f>
-        <v>46329</v>
+        <f aca="false">IF(C52="","",WORKDAY($C$5-1,A52))</f>
+        <v>46346</v>
       </c>
       <c r="C52" s="20" t="n">
         <f aca="false">IF(C51="","",IF(OR(IF(ISNUMBER(G51),H51,F51)&gt;=$C$7,IF(ISNUMBER(G51),H51,F51)&lt;=0),"",IF(ISNUMBER(G51),H51,F51)))</f>
@@ -2679,8 +2685,8 @@
         <v>41</v>
       </c>
       <c r="B53" s="19" t="n">
-        <f aca="false">IF(C53="","",$C$5+A53-1)</f>
-        <v>46330</v>
+        <f aca="false">IF(C53="","",WORKDAY($C$5-1,A53))</f>
+        <v>46349</v>
       </c>
       <c r="C53" s="20" t="n">
         <f aca="false">IF(C52="","",IF(OR(IF(ISNUMBER(G52),H52,F52)&gt;=$C$7,IF(ISNUMBER(G52),H52,F52)&lt;=0),"",IF(ISNUMBER(G52),H52,F52)))</f>
@@ -2716,8 +2722,8 @@
         <v>42</v>
       </c>
       <c r="B54" s="19" t="n">
-        <f aca="false">IF(C54="","",$C$5+A54-1)</f>
-        <v>46331</v>
+        <f aca="false">IF(C54="","",WORKDAY($C$5-1,A54))</f>
+        <v>46350</v>
       </c>
       <c r="C54" s="20" t="n">
         <f aca="false">IF(C53="","",IF(OR(IF(ISNUMBER(G53),H53,F53)&gt;=$C$7,IF(ISNUMBER(G53),H53,F53)&lt;=0),"",IF(ISNUMBER(G53),H53,F53)))</f>
@@ -2753,8 +2759,8 @@
         <v>43</v>
       </c>
       <c r="B55" s="19" t="n">
-        <f aca="false">IF(C55="","",$C$5+A55-1)</f>
-        <v>46332</v>
+        <f aca="false">IF(C55="","",WORKDAY($C$5-1,A55))</f>
+        <v>46351</v>
       </c>
       <c r="C55" s="20" t="n">
         <f aca="false">IF(C54="","",IF(OR(IF(ISNUMBER(G54),H54,F54)&gt;=$C$7,IF(ISNUMBER(G54),H54,F54)&lt;=0),"",IF(ISNUMBER(G54),H54,F54)))</f>
@@ -2790,8 +2796,8 @@
         <v>44</v>
       </c>
       <c r="B56" s="19" t="n">
-        <f aca="false">IF(C56="","",$C$5+A56-1)</f>
-        <v>46333</v>
+        <f aca="false">IF(C56="","",WORKDAY($C$5-1,A56))</f>
+        <v>46352</v>
       </c>
       <c r="C56" s="20" t="n">
         <f aca="false">IF(C55="","",IF(OR(IF(ISNUMBER(G55),H55,F55)&gt;=$C$7,IF(ISNUMBER(G55),H55,F55)&lt;=0),"",IF(ISNUMBER(G55),H55,F55)))</f>
@@ -2827,8 +2833,8 @@
         <v>45</v>
       </c>
       <c r="B57" s="19" t="n">
-        <f aca="false">IF(C57="","",$C$5+A57-1)</f>
-        <v>46334</v>
+        <f aca="false">IF(C57="","",WORKDAY($C$5-1,A57))</f>
+        <v>46353</v>
       </c>
       <c r="C57" s="20" t="n">
         <f aca="false">IF(C56="","",IF(OR(IF(ISNUMBER(G56),H56,F56)&gt;=$C$7,IF(ISNUMBER(G56),H56,F56)&lt;=0),"",IF(ISNUMBER(G56),H56,F56)))</f>
@@ -2864,8 +2870,8 @@
         <v>46</v>
       </c>
       <c r="B58" s="19" t="n">
-        <f aca="false">IF(C58="","",$C$5+A58-1)</f>
-        <v>46335</v>
+        <f aca="false">IF(C58="","",WORKDAY($C$5-1,A58))</f>
+        <v>46356</v>
       </c>
       <c r="C58" s="20" t="n">
         <f aca="false">IF(C57="","",IF(OR(IF(ISNUMBER(G57),H57,F57)&gt;=$C$7,IF(ISNUMBER(G57),H57,F57)&lt;=0),"",IF(ISNUMBER(G57),H57,F57)))</f>
@@ -2901,8 +2907,8 @@
         <v>47</v>
       </c>
       <c r="B59" s="19" t="n">
-        <f aca="false">IF(C59="","",$C$5+A59-1)</f>
-        <v>46336</v>
+        <f aca="false">IF(C59="","",WORKDAY($C$5-1,A59))</f>
+        <v>46357</v>
       </c>
       <c r="C59" s="20" t="n">
         <f aca="false">IF(C58="","",IF(OR(IF(ISNUMBER(G58),H58,F58)&gt;=$C$7,IF(ISNUMBER(G58),H58,F58)&lt;=0),"",IF(ISNUMBER(G58),H58,F58)))</f>
@@ -2938,8 +2944,8 @@
         <v>48</v>
       </c>
       <c r="B60" s="19" t="n">
-        <f aca="false">IF(C60="","",$C$5+A60-1)</f>
-        <v>46337</v>
+        <f aca="false">IF(C60="","",WORKDAY($C$5-1,A60))</f>
+        <v>46358</v>
       </c>
       <c r="C60" s="20" t="n">
         <f aca="false">IF(C59="","",IF(OR(IF(ISNUMBER(G59),H59,F59)&gt;=$C$7,IF(ISNUMBER(G59),H59,F59)&lt;=0),"",IF(ISNUMBER(G59),H59,F59)))</f>
@@ -2975,8 +2981,8 @@
         <v>49</v>
       </c>
       <c r="B61" s="19" t="n">
-        <f aca="false">IF(C61="","",$C$5+A61-1)</f>
-        <v>46338</v>
+        <f aca="false">IF(C61="","",WORKDAY($C$5-1,A61))</f>
+        <v>46359</v>
       </c>
       <c r="C61" s="20" t="n">
         <f aca="false">IF(C60="","",IF(OR(IF(ISNUMBER(G60),H60,F60)&gt;=$C$7,IF(ISNUMBER(G60),H60,F60)&lt;=0),"",IF(ISNUMBER(G60),H60,F60)))</f>
@@ -3012,8 +3018,8 @@
         <v>50</v>
       </c>
       <c r="B62" s="19" t="n">
-        <f aca="false">IF(C62="","",$C$5+A62-1)</f>
-        <v>46339</v>
+        <f aca="false">IF(C62="","",WORKDAY($C$5-1,A62))</f>
+        <v>46360</v>
       </c>
       <c r="C62" s="20" t="n">
         <f aca="false">IF(C61="","",IF(OR(IF(ISNUMBER(G61),H61,F61)&gt;=$C$7,IF(ISNUMBER(G61),H61,F61)&lt;=0),"",IF(ISNUMBER(G61),H61,F61)))</f>
@@ -3049,8 +3055,8 @@
         <v>51</v>
       </c>
       <c r="B63" s="19" t="n">
-        <f aca="false">IF(C63="","",$C$5+A63-1)</f>
-        <v>46340</v>
+        <f aca="false">IF(C63="","",WORKDAY($C$5-1,A63))</f>
+        <v>46363</v>
       </c>
       <c r="C63" s="20" t="n">
         <f aca="false">IF(C62="","",IF(OR(IF(ISNUMBER(G62),H62,F62)&gt;=$C$7,IF(ISNUMBER(G62),H62,F62)&lt;=0),"",IF(ISNUMBER(G62),H62,F62)))</f>
@@ -3086,8 +3092,8 @@
         <v>52</v>
       </c>
       <c r="B64" s="19" t="n">
-        <f aca="false">IF(C64="","",$C$5+A64-1)</f>
-        <v>46341</v>
+        <f aca="false">IF(C64="","",WORKDAY($C$5-1,A64))</f>
+        <v>46364</v>
       </c>
       <c r="C64" s="20" t="n">
         <f aca="false">IF(C63="","",IF(OR(IF(ISNUMBER(G63),H63,F63)&gt;=$C$7,IF(ISNUMBER(G63),H63,F63)&lt;=0),"",IF(ISNUMBER(G63),H63,F63)))</f>
@@ -3123,8 +3129,8 @@
         <v>53</v>
       </c>
       <c r="B65" s="19" t="n">
-        <f aca="false">IF(C65="","",$C$5+A65-1)</f>
-        <v>46342</v>
+        <f aca="false">IF(C65="","",WORKDAY($C$5-1,A65))</f>
+        <v>46365</v>
       </c>
       <c r="C65" s="20" t="n">
         <f aca="false">IF(C64="","",IF(OR(IF(ISNUMBER(G64),H64,F64)&gt;=$C$7,IF(ISNUMBER(G64),H64,F64)&lt;=0),"",IF(ISNUMBER(G64),H64,F64)))</f>
@@ -3160,8 +3166,8 @@
         <v>54</v>
       </c>
       <c r="B66" s="19" t="n">
-        <f aca="false">IF(C66="","",$C$5+A66-1)</f>
-        <v>46343</v>
+        <f aca="false">IF(C66="","",WORKDAY($C$5-1,A66))</f>
+        <v>46366</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">IF(C65="","",IF(OR(IF(ISNUMBER(G65),H65,F65)&gt;=$C$7,IF(ISNUMBER(G65),H65,F65)&lt;=0),"",IF(ISNUMBER(G65),H65,F65)))</f>
@@ -3197,8 +3203,8 @@
         <v>55</v>
       </c>
       <c r="B67" s="19" t="n">
-        <f aca="false">IF(C67="","",$C$5+A67-1)</f>
-        <v>46344</v>
+        <f aca="false">IF(C67="","",WORKDAY($C$5-1,A67))</f>
+        <v>46367</v>
       </c>
       <c r="C67" s="20" t="n">
         <f aca="false">IF(C66="","",IF(OR(IF(ISNUMBER(G66),H66,F66)&gt;=$C$7,IF(ISNUMBER(G66),H66,F66)&lt;=0),"",IF(ISNUMBER(G66),H66,F66)))</f>
@@ -3234,8 +3240,8 @@
         <v>56</v>
       </c>
       <c r="B68" s="19" t="n">
-        <f aca="false">IF(C68="","",$C$5+A68-1)</f>
-        <v>46345</v>
+        <f aca="false">IF(C68="","",WORKDAY($C$5-1,A68))</f>
+        <v>46370</v>
       </c>
       <c r="C68" s="20" t="n">
         <f aca="false">IF(C67="","",IF(OR(IF(ISNUMBER(G67),H67,F67)&gt;=$C$7,IF(ISNUMBER(G67),H67,F67)&lt;=0),"",IF(ISNUMBER(G67),H67,F67)))</f>
@@ -3271,8 +3277,8 @@
         <v>57</v>
       </c>
       <c r="B69" s="19" t="n">
-        <f aca="false">IF(C69="","",$C$5+A69-1)</f>
-        <v>46346</v>
+        <f aca="false">IF(C69="","",WORKDAY($C$5-1,A69))</f>
+        <v>46371</v>
       </c>
       <c r="C69" s="20" t="n">
         <f aca="false">IF(C68="","",IF(OR(IF(ISNUMBER(G68),H68,F68)&gt;=$C$7,IF(ISNUMBER(G68),H68,F68)&lt;=0),"",IF(ISNUMBER(G68),H68,F68)))</f>
@@ -3308,8 +3314,8 @@
         <v>58</v>
       </c>
       <c r="B70" s="19" t="n">
-        <f aca="false">IF(C70="","",$C$5+A70-1)</f>
-        <v>46347</v>
+        <f aca="false">IF(C70="","",WORKDAY($C$5-1,A70))</f>
+        <v>46372</v>
       </c>
       <c r="C70" s="20" t="n">
         <f aca="false">IF(C69="","",IF(OR(IF(ISNUMBER(G69),H69,F69)&gt;=$C$7,IF(ISNUMBER(G69),H69,F69)&lt;=0),"",IF(ISNUMBER(G69),H69,F69)))</f>
@@ -3345,8 +3351,8 @@
         <v>59</v>
       </c>
       <c r="B71" s="19" t="n">
-        <f aca="false">IF(C71="","",$C$5+A71-1)</f>
-        <v>46348</v>
+        <f aca="false">IF(C71="","",WORKDAY($C$5-1,A71))</f>
+        <v>46373</v>
       </c>
       <c r="C71" s="20" t="n">
         <f aca="false">IF(C70="","",IF(OR(IF(ISNUMBER(G70),H70,F70)&gt;=$C$7,IF(ISNUMBER(G70),H70,F70)&lt;=0),"",IF(ISNUMBER(G70),H70,F70)))</f>
@@ -3382,8 +3388,8 @@
         <v>60</v>
       </c>
       <c r="B72" s="19" t="n">
-        <f aca="false">IF(C72="","",$C$5+A72-1)</f>
-        <v>46349</v>
+        <f aca="false">IF(C72="","",WORKDAY($C$5-1,A72))</f>
+        <v>46374</v>
       </c>
       <c r="C72" s="20" t="n">
         <f aca="false">IF(C71="","",IF(OR(IF(ISNUMBER(G71),H71,F71)&gt;=$C$7,IF(ISNUMBER(G71),H71,F71)&lt;=0),"",IF(ISNUMBER(G71),H71,F71)))</f>
@@ -3419,8 +3425,8 @@
         <v>61</v>
       </c>
       <c r="B73" s="19" t="n">
-        <f aca="false">IF(C73="","",$C$5+A73-1)</f>
-        <v>46350</v>
+        <f aca="false">IF(C73="","",WORKDAY($C$5-1,A73))</f>
+        <v>46377</v>
       </c>
       <c r="C73" s="20" t="n">
         <f aca="false">IF(C72="","",IF(OR(IF(ISNUMBER(G72),H72,F72)&gt;=$C$7,IF(ISNUMBER(G72),H72,F72)&lt;=0),"",IF(ISNUMBER(G72),H72,F72)))</f>
@@ -3456,8 +3462,8 @@
         <v>62</v>
       </c>
       <c r="B74" s="19" t="n">
-        <f aca="false">IF(C74="","",$C$5+A74-1)</f>
-        <v>46351</v>
+        <f aca="false">IF(C74="","",WORKDAY($C$5-1,A74))</f>
+        <v>46378</v>
       </c>
       <c r="C74" s="20" t="n">
         <f aca="false">IF(C73="","",IF(OR(IF(ISNUMBER(G73),H73,F73)&gt;=$C$7,IF(ISNUMBER(G73),H73,F73)&lt;=0),"",IF(ISNUMBER(G73),H73,F73)))</f>
@@ -3493,8 +3499,8 @@
         <v>63</v>
       </c>
       <c r="B75" s="19" t="n">
-        <f aca="false">IF(C75="","",$C$5+A75-1)</f>
-        <v>46352</v>
+        <f aca="false">IF(C75="","",WORKDAY($C$5-1,A75))</f>
+        <v>46379</v>
       </c>
       <c r="C75" s="20" t="n">
         <f aca="false">IF(C74="","",IF(OR(IF(ISNUMBER(G74),H74,F74)&gt;=$C$7,IF(ISNUMBER(G74),H74,F74)&lt;=0),"",IF(ISNUMBER(G74),H74,F74)))</f>
@@ -3530,8 +3536,8 @@
         <v>64</v>
       </c>
       <c r="B76" s="19" t="n">
-        <f aca="false">IF(C76="","",$C$5+A76-1)</f>
-        <v>46353</v>
+        <f aca="false">IF(C76="","",WORKDAY($C$5-1,A76))</f>
+        <v>46380</v>
       </c>
       <c r="C76" s="20" t="n">
         <f aca="false">IF(C75="","",IF(OR(IF(ISNUMBER(G75),H75,F75)&gt;=$C$7,IF(ISNUMBER(G75),H75,F75)&lt;=0),"",IF(ISNUMBER(G75),H75,F75)))</f>
@@ -3567,8 +3573,8 @@
         <v>65</v>
       </c>
       <c r="B77" s="19" t="n">
-        <f aca="false">IF(C77="","",$C$5+A77-1)</f>
-        <v>46354</v>
+        <f aca="false">IF(C77="","",WORKDAY($C$5-1,A77))</f>
+        <v>46381</v>
       </c>
       <c r="C77" s="20" t="n">
         <f aca="false">IF(C76="","",IF(OR(IF(ISNUMBER(G76),H76,F76)&gt;=$C$7,IF(ISNUMBER(G76),H76,F76)&lt;=0),"",IF(ISNUMBER(G76),H76,F76)))</f>
@@ -3604,8 +3610,8 @@
         <v>66</v>
       </c>
       <c r="B78" s="19" t="n">
-        <f aca="false">IF(C78="","",$C$5+A78-1)</f>
-        <v>46355</v>
+        <f aca="false">IF(C78="","",WORKDAY($C$5-1,A78))</f>
+        <v>46384</v>
       </c>
       <c r="C78" s="20" t="n">
         <f aca="false">IF(C77="","",IF(OR(IF(ISNUMBER(G77),H77,F77)&gt;=$C$7,IF(ISNUMBER(G77),H77,F77)&lt;=0),"",IF(ISNUMBER(G77),H77,F77)))</f>
@@ -3641,8 +3647,8 @@
         <v>67</v>
       </c>
       <c r="B79" s="19" t="n">
-        <f aca="false">IF(C79="","",$C$5+A79-1)</f>
-        <v>46356</v>
+        <f aca="false">IF(C79="","",WORKDAY($C$5-1,A79))</f>
+        <v>46385</v>
       </c>
       <c r="C79" s="20" t="n">
         <f aca="false">IF(C78="","",IF(OR(IF(ISNUMBER(G78),H78,F78)&gt;=$C$7,IF(ISNUMBER(G78),H78,F78)&lt;=0),"",IF(ISNUMBER(G78),H78,F78)))</f>
@@ -3678,8 +3684,8 @@
         <v>68</v>
       </c>
       <c r="B80" s="19" t="n">
-        <f aca="false">IF(C80="","",$C$5+A80-1)</f>
-        <v>46357</v>
+        <f aca="false">IF(C80="","",WORKDAY($C$5-1,A80))</f>
+        <v>46386</v>
       </c>
       <c r="C80" s="20" t="n">
         <f aca="false">IF(C79="","",IF(OR(IF(ISNUMBER(G79),H79,F79)&gt;=$C$7,IF(ISNUMBER(G79),H79,F79)&lt;=0),"",IF(ISNUMBER(G79),H79,F79)))</f>
@@ -3715,8 +3721,8 @@
         <v>69</v>
       </c>
       <c r="B81" s="19" t="n">
-        <f aca="false">IF(C81="","",$C$5+A81-1)</f>
-        <v>46358</v>
+        <f aca="false">IF(C81="","",WORKDAY($C$5-1,A81))</f>
+        <v>46387</v>
       </c>
       <c r="C81" s="20" t="n">
         <f aca="false">IF(C80="","",IF(OR(IF(ISNUMBER(G80),H80,F80)&gt;=$C$7,IF(ISNUMBER(G80),H80,F80)&lt;=0),"",IF(ISNUMBER(G80),H80,F80)))</f>
@@ -3752,8 +3758,8 @@
         <v>70</v>
       </c>
       <c r="B82" s="19" t="n">
-        <f aca="false">IF(C82="","",$C$5+A82-1)</f>
-        <v>46359</v>
+        <f aca="false">IF(C82="","",WORKDAY($C$5-1,A82))</f>
+        <v>46388</v>
       </c>
       <c r="C82" s="20" t="n">
         <f aca="false">IF(C81="","",IF(OR(IF(ISNUMBER(G81),H81,F81)&gt;=$C$7,IF(ISNUMBER(G81),H81,F81)&lt;=0),"",IF(ISNUMBER(G81),H81,F81)))</f>
@@ -3789,8 +3795,8 @@
         <v>71</v>
       </c>
       <c r="B83" s="19" t="n">
-        <f aca="false">IF(C83="","",$C$5+A83-1)</f>
-        <v>46360</v>
+        <f aca="false">IF(C83="","",WORKDAY($C$5-1,A83))</f>
+        <v>46391</v>
       </c>
       <c r="C83" s="20" t="n">
         <f aca="false">IF(C82="","",IF(OR(IF(ISNUMBER(G82),H82,F82)&gt;=$C$7,IF(ISNUMBER(G82),H82,F82)&lt;=0),"",IF(ISNUMBER(G82),H82,F82)))</f>
@@ -3826,8 +3832,8 @@
         <v>72</v>
       </c>
       <c r="B84" s="19" t="n">
-        <f aca="false">IF(C84="","",$C$5+A84-1)</f>
-        <v>46361</v>
+        <f aca="false">IF(C84="","",WORKDAY($C$5-1,A84))</f>
+        <v>46392</v>
       </c>
       <c r="C84" s="20" t="n">
         <f aca="false">IF(C83="","",IF(OR(IF(ISNUMBER(G83),H83,F83)&gt;=$C$7,IF(ISNUMBER(G83),H83,F83)&lt;=0),"",IF(ISNUMBER(G83),H83,F83)))</f>
@@ -3863,8 +3869,8 @@
         <v>73</v>
       </c>
       <c r="B85" s="19" t="n">
-        <f aca="false">IF(C85="","",$C$5+A85-1)</f>
-        <v>46362</v>
+        <f aca="false">IF(C85="","",WORKDAY($C$5-1,A85))</f>
+        <v>46393</v>
       </c>
       <c r="C85" s="20" t="n">
         <f aca="false">IF(C84="","",IF(OR(IF(ISNUMBER(G84),H84,F84)&gt;=$C$7,IF(ISNUMBER(G84),H84,F84)&lt;=0),"",IF(ISNUMBER(G84),H84,F84)))</f>
@@ -3900,8 +3906,8 @@
         <v>74</v>
       </c>
       <c r="B86" s="19" t="n">
-        <f aca="false">IF(C86="","",$C$5+A86-1)</f>
-        <v>46363</v>
+        <f aca="false">IF(C86="","",WORKDAY($C$5-1,A86))</f>
+        <v>46394</v>
       </c>
       <c r="C86" s="20" t="n">
         <f aca="false">IF(C85="","",IF(OR(IF(ISNUMBER(G85),H85,F85)&gt;=$C$7,IF(ISNUMBER(G85),H85,F85)&lt;=0),"",IF(ISNUMBER(G85),H85,F85)))</f>
@@ -3937,8 +3943,8 @@
         <v>75</v>
       </c>
       <c r="B87" s="19" t="n">
-        <f aca="false">IF(C87="","",$C$5+A87-1)</f>
-        <v>46364</v>
+        <f aca="false">IF(C87="","",WORKDAY($C$5-1,A87))</f>
+        <v>46395</v>
       </c>
       <c r="C87" s="20" t="n">
         <f aca="false">IF(C86="","",IF(OR(IF(ISNUMBER(G86),H86,F86)&gt;=$C$7,IF(ISNUMBER(G86),H86,F86)&lt;=0),"",IF(ISNUMBER(G86),H86,F86)))</f>
@@ -3974,8 +3980,8 @@
         <v>76</v>
       </c>
       <c r="B88" s="19" t="n">
-        <f aca="false">IF(C88="","",$C$5+A88-1)</f>
-        <v>46365</v>
+        <f aca="false">IF(C88="","",WORKDAY($C$5-1,A88))</f>
+        <v>46398</v>
       </c>
       <c r="C88" s="20" t="n">
         <f aca="false">IF(C87="","",IF(OR(IF(ISNUMBER(G87),H87,F87)&gt;=$C$7,IF(ISNUMBER(G87),H87,F87)&lt;=0),"",IF(ISNUMBER(G87),H87,F87)))</f>
@@ -4011,8 +4017,8 @@
         <v>77</v>
       </c>
       <c r="B89" s="19" t="n">
-        <f aca="false">IF(C89="","",$C$5+A89-1)</f>
-        <v>46366</v>
+        <f aca="false">IF(C89="","",WORKDAY($C$5-1,A89))</f>
+        <v>46399</v>
       </c>
       <c r="C89" s="20" t="n">
         <f aca="false">IF(C88="","",IF(OR(IF(ISNUMBER(G88),H88,F88)&gt;=$C$7,IF(ISNUMBER(G88),H88,F88)&lt;=0),"",IF(ISNUMBER(G88),H88,F88)))</f>
@@ -4048,8 +4054,8 @@
         <v>78</v>
       </c>
       <c r="B90" s="19" t="n">
-        <f aca="false">IF(C90="","",$C$5+A90-1)</f>
-        <v>46367</v>
+        <f aca="false">IF(C90="","",WORKDAY($C$5-1,A90))</f>
+        <v>46400</v>
       </c>
       <c r="C90" s="20" t="n">
         <f aca="false">IF(C89="","",IF(OR(IF(ISNUMBER(G89),H89,F89)&gt;=$C$7,IF(ISNUMBER(G89),H89,F89)&lt;=0),"",IF(ISNUMBER(G89),H89,F89)))</f>
@@ -4085,8 +4091,8 @@
         <v>79</v>
       </c>
       <c r="B91" s="19" t="n">
-        <f aca="false">IF(C91="","",$C$5+A91-1)</f>
-        <v>46368</v>
+        <f aca="false">IF(C91="","",WORKDAY($C$5-1,A91))</f>
+        <v>46401</v>
       </c>
       <c r="C91" s="20" t="n">
         <f aca="false">IF(C90="","",IF(OR(IF(ISNUMBER(G90),H90,F90)&gt;=$C$7,IF(ISNUMBER(G90),H90,F90)&lt;=0),"",IF(ISNUMBER(G90),H90,F90)))</f>
@@ -4122,8 +4128,8 @@
         <v>80</v>
       </c>
       <c r="B92" s="19" t="n">
-        <f aca="false">IF(C92="","",$C$5+A92-1)</f>
-        <v>46369</v>
+        <f aca="false">IF(C92="","",WORKDAY($C$5-1,A92))</f>
+        <v>46402</v>
       </c>
       <c r="C92" s="20" t="n">
         <f aca="false">IF(C91="","",IF(OR(IF(ISNUMBER(G91),H91,F91)&gt;=$C$7,IF(ISNUMBER(G91),H91,F91)&lt;=0),"",IF(ISNUMBER(G91),H91,F91)))</f>
@@ -4159,8 +4165,8 @@
         <v>81</v>
       </c>
       <c r="B93" s="19" t="n">
-        <f aca="false">IF(C93="","",$C$5+A93-1)</f>
-        <v>46370</v>
+        <f aca="false">IF(C93="","",WORKDAY($C$5-1,A93))</f>
+        <v>46405</v>
       </c>
       <c r="C93" s="20" t="n">
         <f aca="false">IF(C92="","",IF(OR(IF(ISNUMBER(G92),H92,F92)&gt;=$C$7,IF(ISNUMBER(G92),H92,F92)&lt;=0),"",IF(ISNUMBER(G92),H92,F92)))</f>
@@ -4196,8 +4202,8 @@
         <v>82</v>
       </c>
       <c r="B94" s="19" t="n">
-        <f aca="false">IF(C94="","",$C$5+A94-1)</f>
-        <v>46371</v>
+        <f aca="false">IF(C94="","",WORKDAY($C$5-1,A94))</f>
+        <v>46406</v>
       </c>
       <c r="C94" s="20" t="n">
         <f aca="false">IF(C93="","",IF(OR(IF(ISNUMBER(G93),H93,F93)&gt;=$C$7,IF(ISNUMBER(G93),H93,F93)&lt;=0),"",IF(ISNUMBER(G93),H93,F93)))</f>
@@ -4233,8 +4239,8 @@
         <v>83</v>
       </c>
       <c r="B95" s="19" t="n">
-        <f aca="false">IF(C95="","",$C$5+A95-1)</f>
-        <v>46372</v>
+        <f aca="false">IF(C95="","",WORKDAY($C$5-1,A95))</f>
+        <v>46407</v>
       </c>
       <c r="C95" s="20" t="n">
         <f aca="false">IF(C94="","",IF(OR(IF(ISNUMBER(G94),H94,F94)&gt;=$C$7,IF(ISNUMBER(G94),H94,F94)&lt;=0),"",IF(ISNUMBER(G94),H94,F94)))</f>
@@ -4270,8 +4276,8 @@
         <v>84</v>
       </c>
       <c r="B96" s="19" t="n">
-        <f aca="false">IF(C96="","",$C$5+A96-1)</f>
-        <v>46373</v>
+        <f aca="false">IF(C96="","",WORKDAY($C$5-1,A96))</f>
+        <v>46408</v>
       </c>
       <c r="C96" s="20" t="n">
         <f aca="false">IF(C95="","",IF(OR(IF(ISNUMBER(G95),H95,F95)&gt;=$C$7,IF(ISNUMBER(G95),H95,F95)&lt;=0),"",IF(ISNUMBER(G95),H95,F95)))</f>
@@ -4307,8 +4313,8 @@
         <v>85</v>
       </c>
       <c r="B97" s="19" t="n">
-        <f aca="false">IF(C97="","",$C$5+A97-1)</f>
-        <v>46374</v>
+        <f aca="false">IF(C97="","",WORKDAY($C$5-1,A97))</f>
+        <v>46409</v>
       </c>
       <c r="C97" s="20" t="n">
         <f aca="false">IF(C96="","",IF(OR(IF(ISNUMBER(G96),H96,F96)&gt;=$C$7,IF(ISNUMBER(G96),H96,F96)&lt;=0),"",IF(ISNUMBER(G96),H96,F96)))</f>
@@ -4344,8 +4350,8 @@
         <v>86</v>
       </c>
       <c r="B98" s="19" t="n">
-        <f aca="false">IF(C98="","",$C$5+A98-1)</f>
-        <v>46375</v>
+        <f aca="false">IF(C98="","",WORKDAY($C$5-1,A98))</f>
+        <v>46412</v>
       </c>
       <c r="C98" s="20" t="n">
         <f aca="false">IF(C97="","",IF(OR(IF(ISNUMBER(G97),H97,F97)&gt;=$C$7,IF(ISNUMBER(G97),H97,F97)&lt;=0),"",IF(ISNUMBER(G97),H97,F97)))</f>
@@ -4381,8 +4387,8 @@
         <v>87</v>
       </c>
       <c r="B99" s="19" t="n">
-        <f aca="false">IF(C99="","",$C$5+A99-1)</f>
-        <v>46376</v>
+        <f aca="false">IF(C99="","",WORKDAY($C$5-1,A99))</f>
+        <v>46413</v>
       </c>
       <c r="C99" s="20" t="n">
         <f aca="false">IF(C98="","",IF(OR(IF(ISNUMBER(G98),H98,F98)&gt;=$C$7,IF(ISNUMBER(G98),H98,F98)&lt;=0),"",IF(ISNUMBER(G98),H98,F98)))</f>
@@ -4418,8 +4424,8 @@
         <v>88</v>
       </c>
       <c r="B100" s="19" t="n">
-        <f aca="false">IF(C100="","",$C$5+A100-1)</f>
-        <v>46377</v>
+        <f aca="false">IF(C100="","",WORKDAY($C$5-1,A100))</f>
+        <v>46414</v>
       </c>
       <c r="C100" s="20" t="n">
         <f aca="false">IF(C99="","",IF(OR(IF(ISNUMBER(G99),H99,F99)&gt;=$C$7,IF(ISNUMBER(G99),H99,F99)&lt;=0),"",IF(ISNUMBER(G99),H99,F99)))</f>
@@ -4455,8 +4461,8 @@
         <v>89</v>
       </c>
       <c r="B101" s="19" t="n">
-        <f aca="false">IF(C101="","",$C$5+A101-1)</f>
-        <v>46378</v>
+        <f aca="false">IF(C101="","",WORKDAY($C$5-1,A101))</f>
+        <v>46415</v>
       </c>
       <c r="C101" s="20" t="n">
         <f aca="false">IF(C100="","",IF(OR(IF(ISNUMBER(G100),H100,F100)&gt;=$C$7,IF(ISNUMBER(G100),H100,F100)&lt;=0),"",IF(ISNUMBER(G100),H100,F100)))</f>
@@ -4492,8 +4498,8 @@
         <v>90</v>
       </c>
       <c r="B102" s="19" t="n">
-        <f aca="false">IF(C102="","",$C$5+A102-1)</f>
-        <v>46379</v>
+        <f aca="false">IF(C102="","",WORKDAY($C$5-1,A102))</f>
+        <v>46416</v>
       </c>
       <c r="C102" s="20" t="n">
         <f aca="false">IF(C101="","",IF(OR(IF(ISNUMBER(G101),H101,F101)&gt;=$C$7,IF(ISNUMBER(G101),H101,F101)&lt;=0),"",IF(ISNUMBER(G101),H101,F101)))</f>
@@ -4529,8 +4535,8 @@
         <v>91</v>
       </c>
       <c r="B103" s="19" t="n">
-        <f aca="false">IF(C103="","",$C$5+A103-1)</f>
-        <v>46380</v>
+        <f aca="false">IF(C103="","",WORKDAY($C$5-1,A103))</f>
+        <v>46419</v>
       </c>
       <c r="C103" s="20" t="n">
         <f aca="false">IF(C102="","",IF(OR(IF(ISNUMBER(G102),H102,F102)&gt;=$C$7,IF(ISNUMBER(G102),H102,F102)&lt;=0),"",IF(ISNUMBER(G102),H102,F102)))</f>
@@ -4566,8 +4572,8 @@
         <v>92</v>
       </c>
       <c r="B104" s="19" t="n">
-        <f aca="false">IF(C104="","",$C$5+A104-1)</f>
-        <v>46381</v>
+        <f aca="false">IF(C104="","",WORKDAY($C$5-1,A104))</f>
+        <v>46420</v>
       </c>
       <c r="C104" s="20" t="n">
         <f aca="false">IF(C103="","",IF(OR(IF(ISNUMBER(G103),H103,F103)&gt;=$C$7,IF(ISNUMBER(G103),H103,F103)&lt;=0),"",IF(ISNUMBER(G103),H103,F103)))</f>
@@ -4603,8 +4609,8 @@
         <v>93</v>
       </c>
       <c r="B105" s="19" t="n">
-        <f aca="false">IF(C105="","",$C$5+A105-1)</f>
-        <v>46382</v>
+        <f aca="false">IF(C105="","",WORKDAY($C$5-1,A105))</f>
+        <v>46421</v>
       </c>
       <c r="C105" s="20" t="n">
         <f aca="false">IF(C104="","",IF(OR(IF(ISNUMBER(G104),H104,F104)&gt;=$C$7,IF(ISNUMBER(G104),H104,F104)&lt;=0),"",IF(ISNUMBER(G104),H104,F104)))</f>
@@ -4640,8 +4646,8 @@
         <v>94</v>
       </c>
       <c r="B106" s="19" t="n">
-        <f aca="false">IF(C106="","",$C$5+A106-1)</f>
-        <v>46383</v>
+        <f aca="false">IF(C106="","",WORKDAY($C$5-1,A106))</f>
+        <v>46422</v>
       </c>
       <c r="C106" s="20" t="n">
         <f aca="false">IF(C105="","",IF(OR(IF(ISNUMBER(G105),H105,F105)&gt;=$C$7,IF(ISNUMBER(G105),H105,F105)&lt;=0),"",IF(ISNUMBER(G105),H105,F105)))</f>
@@ -4677,8 +4683,8 @@
         <v>95</v>
       </c>
       <c r="B107" s="19" t="n">
-        <f aca="false">IF(C107="","",$C$5+A107-1)</f>
-        <v>46384</v>
+        <f aca="false">IF(C107="","",WORKDAY($C$5-1,A107))</f>
+        <v>46423</v>
       </c>
       <c r="C107" s="20" t="n">
         <f aca="false">IF(C106="","",IF(OR(IF(ISNUMBER(G106),H106,F106)&gt;=$C$7,IF(ISNUMBER(G106),H106,F106)&lt;=0),"",IF(ISNUMBER(G106),H106,F106)))</f>
@@ -4714,8 +4720,8 @@
         <v>96</v>
       </c>
       <c r="B108" s="19" t="n">
-        <f aca="false">IF(C108="","",$C$5+A108-1)</f>
-        <v>46385</v>
+        <f aca="false">IF(C108="","",WORKDAY($C$5-1,A108))</f>
+        <v>46426</v>
       </c>
       <c r="C108" s="20" t="n">
         <f aca="false">IF(C107="","",IF(OR(IF(ISNUMBER(G107),H107,F107)&gt;=$C$7,IF(ISNUMBER(G107),H107,F107)&lt;=0),"",IF(ISNUMBER(G107),H107,F107)))</f>
@@ -4751,8 +4757,8 @@
         <v>97</v>
       </c>
       <c r="B109" s="19" t="n">
-        <f aca="false">IF(C109="","",$C$5+A109-1)</f>
-        <v>46386</v>
+        <f aca="false">IF(C109="","",WORKDAY($C$5-1,A109))</f>
+        <v>46427</v>
       </c>
       <c r="C109" s="20" t="n">
         <f aca="false">IF(C108="","",IF(OR(IF(ISNUMBER(G108),H108,F108)&gt;=$C$7,IF(ISNUMBER(G108),H108,F108)&lt;=0),"",IF(ISNUMBER(G108),H108,F108)))</f>
@@ -4788,8 +4794,8 @@
         <v>98</v>
       </c>
       <c r="B110" s="19" t="n">
-        <f aca="false">IF(C110="","",$C$5+A110-1)</f>
-        <v>46387</v>
+        <f aca="false">IF(C110="","",WORKDAY($C$5-1,A110))</f>
+        <v>46428</v>
       </c>
       <c r="C110" s="20" t="n">
         <f aca="false">IF(C109="","",IF(OR(IF(ISNUMBER(G109),H109,F109)&gt;=$C$7,IF(ISNUMBER(G109),H109,F109)&lt;=0),"",IF(ISNUMBER(G109),H109,F109)))</f>
@@ -4825,8 +4831,8 @@
         <v>99</v>
       </c>
       <c r="B111" s="19" t="n">
-        <f aca="false">IF(C111="","",$C$5+A111-1)</f>
-        <v>46388</v>
+        <f aca="false">IF(C111="","",WORKDAY($C$5-1,A111))</f>
+        <v>46429</v>
       </c>
       <c r="C111" s="20" t="n">
         <f aca="false">IF(C110="","",IF(OR(IF(ISNUMBER(G110),H110,F110)&gt;=$C$7,IF(ISNUMBER(G110),H110,F110)&lt;=0),"",IF(ISNUMBER(G110),H110,F110)))</f>
@@ -4862,8 +4868,8 @@
         <v>100</v>
       </c>
       <c r="B112" s="19" t="n">
-        <f aca="false">IF(C112="","",$C$5+A112-1)</f>
-        <v>46389</v>
+        <f aca="false">IF(C112="","",WORKDAY($C$5-1,A112))</f>
+        <v>46430</v>
       </c>
       <c r="C112" s="20" t="n">
         <f aca="false">IF(C111="","",IF(OR(IF(ISNUMBER(G111),H111,F111)&gt;=$C$7,IF(ISNUMBER(G111),H111,F111)&lt;=0),"",IF(ISNUMBER(G111),H111,F111)))</f>
@@ -4899,8 +4905,8 @@
         <v>101</v>
       </c>
       <c r="B113" s="19" t="n">
-        <f aca="false">IF(C113="","",$C$5+A113-1)</f>
-        <v>46390</v>
+        <f aca="false">IF(C113="","",WORKDAY($C$5-1,A113))</f>
+        <v>46433</v>
       </c>
       <c r="C113" s="20" t="n">
         <f aca="false">IF(C112="","",IF(OR(IF(ISNUMBER(G112),H112,F112)&gt;=$C$7,IF(ISNUMBER(G112),H112,F112)&lt;=0),"",IF(ISNUMBER(G112),H112,F112)))</f>
@@ -4936,8 +4942,8 @@
         <v>102</v>
       </c>
       <c r="B114" s="19" t="n">
-        <f aca="false">IF(C114="","",$C$5+A114-1)</f>
-        <v>46391</v>
+        <f aca="false">IF(C114="","",WORKDAY($C$5-1,A114))</f>
+        <v>46434</v>
       </c>
       <c r="C114" s="20" t="n">
         <f aca="false">IF(C113="","",IF(OR(IF(ISNUMBER(G113),H113,F113)&gt;=$C$7,IF(ISNUMBER(G113),H113,F113)&lt;=0),"",IF(ISNUMBER(G113),H113,F113)))</f>
@@ -4973,8 +4979,8 @@
         <v>103</v>
       </c>
       <c r="B115" s="19" t="n">
-        <f aca="false">IF(C115="","",$C$5+A115-1)</f>
-        <v>46392</v>
+        <f aca="false">IF(C115="","",WORKDAY($C$5-1,A115))</f>
+        <v>46435</v>
       </c>
       <c r="C115" s="20" t="n">
         <f aca="false">IF(C114="","",IF(OR(IF(ISNUMBER(G114),H114,F114)&gt;=$C$7,IF(ISNUMBER(G114),H114,F114)&lt;=0),"",IF(ISNUMBER(G114),H114,F114)))</f>
@@ -5010,8 +5016,8 @@
         <v>104</v>
       </c>
       <c r="B116" s="19" t="n">
-        <f aca="false">IF(C116="","",$C$5+A116-1)</f>
-        <v>46393</v>
+        <f aca="false">IF(C116="","",WORKDAY($C$5-1,A116))</f>
+        <v>46436</v>
       </c>
       <c r="C116" s="20" t="n">
         <f aca="false">IF(C115="","",IF(OR(IF(ISNUMBER(G115),H115,F115)&gt;=$C$7,IF(ISNUMBER(G115),H115,F115)&lt;=0),"",IF(ISNUMBER(G115),H115,F115)))</f>
@@ -5047,8 +5053,8 @@
         <v>105</v>
       </c>
       <c r="B117" s="19" t="n">
-        <f aca="false">IF(C117="","",$C$5+A117-1)</f>
-        <v>46394</v>
+        <f aca="false">IF(C117="","",WORKDAY($C$5-1,A117))</f>
+        <v>46437</v>
       </c>
       <c r="C117" s="20" t="n">
         <f aca="false">IF(C116="","",IF(OR(IF(ISNUMBER(G116),H116,F116)&gt;=$C$7,IF(ISNUMBER(G116),H116,F116)&lt;=0),"",IF(ISNUMBER(G116),H116,F116)))</f>
@@ -5084,8 +5090,8 @@
         <v>106</v>
       </c>
       <c r="B118" s="19" t="n">
-        <f aca="false">IF(C118="","",$C$5+A118-1)</f>
-        <v>46395</v>
+        <f aca="false">IF(C118="","",WORKDAY($C$5-1,A118))</f>
+        <v>46440</v>
       </c>
       <c r="C118" s="20" t="n">
         <f aca="false">IF(C117="","",IF(OR(IF(ISNUMBER(G117),H117,F117)&gt;=$C$7,IF(ISNUMBER(G117),H117,F117)&lt;=0),"",IF(ISNUMBER(G117),H117,F117)))</f>
@@ -5121,8 +5127,8 @@
         <v>107</v>
       </c>
       <c r="B119" s="19" t="n">
-        <f aca="false">IF(C119="","",$C$5+A119-1)</f>
-        <v>46396</v>
+        <f aca="false">IF(C119="","",WORKDAY($C$5-1,A119))</f>
+        <v>46441</v>
       </c>
       <c r="C119" s="20" t="n">
         <f aca="false">IF(C118="","",IF(OR(IF(ISNUMBER(G118),H118,F118)&gt;=$C$7,IF(ISNUMBER(G118),H118,F118)&lt;=0),"",IF(ISNUMBER(G118),H118,F118)))</f>
@@ -5158,8 +5164,8 @@
         <v>108</v>
       </c>
       <c r="B120" s="19" t="n">
-        <f aca="false">IF(C120="","",$C$5+A120-1)</f>
-        <v>46397</v>
+        <f aca="false">IF(C120="","",WORKDAY($C$5-1,A120))</f>
+        <v>46442</v>
       </c>
       <c r="C120" s="20" t="n">
         <f aca="false">IF(C119="","",IF(OR(IF(ISNUMBER(G119),H119,F119)&gt;=$C$7,IF(ISNUMBER(G119),H119,F119)&lt;=0),"",IF(ISNUMBER(G119),H119,F119)))</f>
@@ -5195,7 +5201,7 @@
         <v/>
       </c>
       <c r="B121" s="19" t="str">
-        <f aca="false">IF(C121="","",$C$5+A121-1)</f>
+        <f aca="false">IF(C121="","",WORKDAY($C$5-1,A121))</f>
         <v/>
       </c>
       <c r="C121" s="20" t="str">
@@ -5232,7 +5238,7 @@
         <v/>
       </c>
       <c r="B122" s="19" t="str">
-        <f aca="false">IF(C122="","",$C$5+A122-1)</f>
+        <f aca="false">IF(C122="","",WORKDAY($C$5-1,A122))</f>
         <v/>
       </c>
       <c r="C122" s="20" t="str">
@@ -5269,7 +5275,7 @@
         <v/>
       </c>
       <c r="B123" s="19" t="str">
-        <f aca="false">IF(C123="","",$C$5+A123-1)</f>
+        <f aca="false">IF(C123="","",WORKDAY($C$5-1,A123))</f>
         <v/>
       </c>
       <c r="C123" s="20" t="str">
@@ -5306,7 +5312,7 @@
         <v/>
       </c>
       <c r="B124" s="19" t="str">
-        <f aca="false">IF(C124="","",$C$5+A124-1)</f>
+        <f aca="false">IF(C124="","",WORKDAY($C$5-1,A124))</f>
         <v/>
       </c>
       <c r="C124" s="20" t="str">
@@ -5343,7 +5349,7 @@
         <v/>
       </c>
       <c r="B125" s="19" t="str">
-        <f aca="false">IF(C125="","",$C$5+A125-1)</f>
+        <f aca="false">IF(C125="","",WORKDAY($C$5-1,A125))</f>
         <v/>
       </c>
       <c r="C125" s="20" t="str">
@@ -5380,7 +5386,7 @@
         <v/>
       </c>
       <c r="B126" s="19" t="str">
-        <f aca="false">IF(C126="","",$C$5+A126-1)</f>
+        <f aca="false">IF(C126="","",WORKDAY($C$5-1,A126))</f>
         <v/>
       </c>
       <c r="C126" s="20" t="str">
@@ -5417,7 +5423,7 @@
         <v/>
       </c>
       <c r="B127" s="19" t="str">
-        <f aca="false">IF(C127="","",$C$5+A127-1)</f>
+        <f aca="false">IF(C127="","",WORKDAY($C$5-1,A127))</f>
         <v/>
       </c>
       <c r="C127" s="20" t="str">
@@ -5454,7 +5460,7 @@
         <v/>
       </c>
       <c r="B128" s="19" t="str">
-        <f aca="false">IF(C128="","",$C$5+A128-1)</f>
+        <f aca="false">IF(C128="","",WORKDAY($C$5-1,A128))</f>
         <v/>
       </c>
       <c r="C128" s="20" t="str">
@@ -5491,7 +5497,7 @@
         <v/>
       </c>
       <c r="B129" s="19" t="str">
-        <f aca="false">IF(C129="","",$C$5+A129-1)</f>
+        <f aca="false">IF(C129="","",WORKDAY($C$5-1,A129))</f>
         <v/>
       </c>
       <c r="C129" s="20" t="str">
@@ -5528,7 +5534,7 @@
         <v/>
       </c>
       <c r="B130" s="19" t="str">
-        <f aca="false">IF(C130="","",$C$5+A130-1)</f>
+        <f aca="false">IF(C130="","",WORKDAY($C$5-1,A130))</f>
         <v/>
       </c>
       <c r="C130" s="20" t="str">
@@ -5565,7 +5571,7 @@
         <v/>
       </c>
       <c r="B131" s="19" t="str">
-        <f aca="false">IF(C131="","",$C$5+A131-1)</f>
+        <f aca="false">IF(C131="","",WORKDAY($C$5-1,A131))</f>
         <v/>
       </c>
       <c r="C131" s="20" t="str">
@@ -5602,7 +5608,7 @@
         <v/>
       </c>
       <c r="B132" s="19" t="str">
-        <f aca="false">IF(C132="","",$C$5+A132-1)</f>
+        <f aca="false">IF(C132="","",WORKDAY($C$5-1,A132))</f>
         <v/>
       </c>
       <c r="C132" s="20" t="str">
@@ -5639,7 +5645,7 @@
         <v/>
       </c>
       <c r="B133" s="19" t="str">
-        <f aca="false">IF(C133="","",$C$5+A133-1)</f>
+        <f aca="false">IF(C133="","",WORKDAY($C$5-1,A133))</f>
         <v/>
       </c>
       <c r="C133" s="20" t="str">
@@ -5676,7 +5682,7 @@
         <v/>
       </c>
       <c r="B134" s="19" t="str">
-        <f aca="false">IF(C134="","",$C$5+A134-1)</f>
+        <f aca="false">IF(C134="","",WORKDAY($C$5-1,A134))</f>
         <v/>
       </c>
       <c r="C134" s="20" t="str">
@@ -5713,7 +5719,7 @@
         <v/>
       </c>
       <c r="B135" s="19" t="str">
-        <f aca="false">IF(C135="","",$C$5+A135-1)</f>
+        <f aca="false">IF(C135="","",WORKDAY($C$5-1,A135))</f>
         <v/>
       </c>
       <c r="C135" s="20" t="str">
@@ -5750,7 +5756,7 @@
         <v/>
       </c>
       <c r="B136" s="19" t="str">
-        <f aca="false">IF(C136="","",$C$5+A136-1)</f>
+        <f aca="false">IF(C136="","",WORKDAY($C$5-1,A136))</f>
         <v/>
       </c>
       <c r="C136" s="20" t="str">
@@ -5787,7 +5793,7 @@
         <v/>
       </c>
       <c r="B137" s="19" t="str">
-        <f aca="false">IF(C137="","",$C$5+A137-1)</f>
+        <f aca="false">IF(C137="","",WORKDAY($C$5-1,A137))</f>
         <v/>
       </c>
       <c r="C137" s="20" t="str">
@@ -5824,7 +5830,7 @@
         <v/>
       </c>
       <c r="B138" s="19" t="str">
-        <f aca="false">IF(C138="","",$C$5+A138-1)</f>
+        <f aca="false">IF(C138="","",WORKDAY($C$5-1,A138))</f>
         <v/>
       </c>
       <c r="C138" s="20" t="str">
@@ -5861,7 +5867,7 @@
         <v/>
       </c>
       <c r="B139" s="19" t="str">
-        <f aca="false">IF(C139="","",$C$5+A139-1)</f>
+        <f aca="false">IF(C139="","",WORKDAY($C$5-1,A139))</f>
         <v/>
       </c>
       <c r="C139" s="20" t="str">
@@ -5898,7 +5904,7 @@
         <v/>
       </c>
       <c r="B140" s="19" t="str">
-        <f aca="false">IF(C140="","",$C$5+A140-1)</f>
+        <f aca="false">IF(C140="","",WORKDAY($C$5-1,A140))</f>
         <v/>
       </c>
       <c r="C140" s="20" t="str">
@@ -5935,7 +5941,7 @@
         <v/>
       </c>
       <c r="B141" s="19" t="str">
-        <f aca="false">IF(C141="","",$C$5+A141-1)</f>
+        <f aca="false">IF(C141="","",WORKDAY($C$5-1,A141))</f>
         <v/>
       </c>
       <c r="C141" s="20" t="str">
@@ -5972,7 +5978,7 @@
         <v/>
       </c>
       <c r="B142" s="19" t="str">
-        <f aca="false">IF(C142="","",$C$5+A142-1)</f>
+        <f aca="false">IF(C142="","",WORKDAY($C$5-1,A142))</f>
         <v/>
       </c>
       <c r="C142" s="20" t="str">
@@ -6009,7 +6015,7 @@
         <v/>
       </c>
       <c r="B143" s="19" t="str">
-        <f aca="false">IF(C143="","",$C$5+A143-1)</f>
+        <f aca="false">IF(C143="","",WORKDAY($C$5-1,A143))</f>
         <v/>
       </c>
       <c r="C143" s="20" t="str">
@@ -6046,7 +6052,7 @@
         <v/>
       </c>
       <c r="B144" s="19" t="str">
-        <f aca="false">IF(C144="","",$C$5+A144-1)</f>
+        <f aca="false">IF(C144="","",WORKDAY($C$5-1,A144))</f>
         <v/>
       </c>
       <c r="C144" s="20" t="str">
@@ -6083,7 +6089,7 @@
         <v/>
       </c>
       <c r="B145" s="19" t="str">
-        <f aca="false">IF(C145="","",$C$5+A145-1)</f>
+        <f aca="false">IF(C145="","",WORKDAY($C$5-1,A145))</f>
         <v/>
       </c>
       <c r="C145" s="20" t="str">
@@ -6120,7 +6126,7 @@
         <v/>
       </c>
       <c r="B146" s="19" t="str">
-        <f aca="false">IF(C146="","",$C$5+A146-1)</f>
+        <f aca="false">IF(C146="","",WORKDAY($C$5-1,A146))</f>
         <v/>
       </c>
       <c r="C146" s="20" t="str">
@@ -6157,7 +6163,7 @@
         <v/>
       </c>
       <c r="B147" s="19" t="str">
-        <f aca="false">IF(C147="","",$C$5+A147-1)</f>
+        <f aca="false">IF(C147="","",WORKDAY($C$5-1,A147))</f>
         <v/>
       </c>
       <c r="C147" s="20" t="str">
@@ -6194,7 +6200,7 @@
         <v/>
       </c>
       <c r="B148" s="19" t="str">
-        <f aca="false">IF(C148="","",$C$5+A148-1)</f>
+        <f aca="false">IF(C148="","",WORKDAY($C$5-1,A148))</f>
         <v/>
       </c>
       <c r="C148" s="20" t="str">
@@ -6231,7 +6237,7 @@
         <v/>
       </c>
       <c r="B149" s="19" t="str">
-        <f aca="false">IF(C149="","",$C$5+A149-1)</f>
+        <f aca="false">IF(C149="","",WORKDAY($C$5-1,A149))</f>
         <v/>
       </c>
       <c r="C149" s="20" t="str">
@@ -6268,7 +6274,7 @@
         <v/>
       </c>
       <c r="B150" s="19" t="str">
-        <f aca="false">IF(C150="","",$C$5+A150-1)</f>
+        <f aca="false">IF(C150="","",WORKDAY($C$5-1,A150))</f>
         <v/>
       </c>
       <c r="C150" s="20" t="str">
@@ -6305,7 +6311,7 @@
         <v/>
       </c>
       <c r="B151" s="19" t="str">
-        <f aca="false">IF(C151="","",$C$5+A151-1)</f>
+        <f aca="false">IF(C151="","",WORKDAY($C$5-1,A151))</f>
         <v/>
       </c>
       <c r="C151" s="20" t="str">
@@ -6342,7 +6348,7 @@
         <v/>
       </c>
       <c r="B152" s="19" t="str">
-        <f aca="false">IF(C152="","",$C$5+A152-1)</f>
+        <f aca="false">IF(C152="","",WORKDAY($C$5-1,A152))</f>
         <v/>
       </c>
       <c r="C152" s="20" t="str">
@@ -6379,7 +6385,7 @@
         <v/>
       </c>
       <c r="B153" s="19" t="str">
-        <f aca="false">IF(C153="","",$C$5+A153-1)</f>
+        <f aca="false">IF(C153="","",WORKDAY($C$5-1,A153))</f>
         <v/>
       </c>
       <c r="C153" s="20" t="str">
@@ -6416,7 +6422,7 @@
         <v/>
       </c>
       <c r="B154" s="19" t="str">
-        <f aca="false">IF(C154="","",$C$5+A154-1)</f>
+        <f aca="false">IF(C154="","",WORKDAY($C$5-1,A154))</f>
         <v/>
       </c>
       <c r="C154" s="20" t="str">
@@ -6453,7 +6459,7 @@
         <v/>
       </c>
       <c r="B155" s="19" t="str">
-        <f aca="false">IF(C155="","",$C$5+A155-1)</f>
+        <f aca="false">IF(C155="","",WORKDAY($C$5-1,A155))</f>
         <v/>
       </c>
       <c r="C155" s="20" t="str">
@@ -6490,7 +6496,7 @@
         <v/>
       </c>
       <c r="B156" s="19" t="str">
-        <f aca="false">IF(C156="","",$C$5+A156-1)</f>
+        <f aca="false">IF(C156="","",WORKDAY($C$5-1,A156))</f>
         <v/>
       </c>
       <c r="C156" s="20" t="str">
@@ -6527,7 +6533,7 @@
         <v/>
       </c>
       <c r="B157" s="19" t="str">
-        <f aca="false">IF(C157="","",$C$5+A157-1)</f>
+        <f aca="false">IF(C157="","",WORKDAY($C$5-1,A157))</f>
         <v/>
       </c>
       <c r="C157" s="20" t="str">
@@ -6564,7 +6570,7 @@
         <v/>
       </c>
       <c r="B158" s="19" t="str">
-        <f aca="false">IF(C158="","",$C$5+A158-1)</f>
+        <f aca="false">IF(C158="","",WORKDAY($C$5-1,A158))</f>
         <v/>
       </c>
       <c r="C158" s="20" t="str">
@@ -6601,7 +6607,7 @@
         <v/>
       </c>
       <c r="B159" s="19" t="str">
-        <f aca="false">IF(C159="","",$C$5+A159-1)</f>
+        <f aca="false">IF(C159="","",WORKDAY($C$5-1,A159))</f>
         <v/>
       </c>
       <c r="C159" s="20" t="str">
@@ -6638,7 +6644,7 @@
         <v/>
       </c>
       <c r="B160" s="19" t="str">
-        <f aca="false">IF(C160="","",$C$5+A160-1)</f>
+        <f aca="false">IF(C160="","",WORKDAY($C$5-1,A160))</f>
         <v/>
       </c>
       <c r="C160" s="20" t="str">
@@ -6675,7 +6681,7 @@
         <v/>
       </c>
       <c r="B161" s="19" t="str">
-        <f aca="false">IF(C161="","",$C$5+A161-1)</f>
+        <f aca="false">IF(C161="","",WORKDAY($C$5-1,A161))</f>
         <v/>
       </c>
       <c r="C161" s="20" t="str">
@@ -6712,7 +6718,7 @@
         <v/>
       </c>
       <c r="B162" s="19" t="str">
-        <f aca="false">IF(C162="","",$C$5+A162-1)</f>
+        <f aca="false">IF(C162="","",WORKDAY($C$5-1,A162))</f>
         <v/>
       </c>
       <c r="C162" s="20" t="str">
@@ -6749,7 +6755,7 @@
         <v/>
       </c>
       <c r="B163" s="19" t="str">
-        <f aca="false">IF(C163="","",$C$5+A163-1)</f>
+        <f aca="false">IF(C163="","",WORKDAY($C$5-1,A163))</f>
         <v/>
       </c>
       <c r="C163" s="20" t="str">
@@ -6786,7 +6792,7 @@
         <v/>
       </c>
       <c r="B164" s="19" t="str">
-        <f aca="false">IF(C164="","",$C$5+A164-1)</f>
+        <f aca="false">IF(C164="","",WORKDAY($C$5-1,A164))</f>
         <v/>
       </c>
       <c r="C164" s="20" t="str">
@@ -6823,7 +6829,7 @@
         <v/>
       </c>
       <c r="B165" s="19" t="str">
-        <f aca="false">IF(C165="","",$C$5+A165-1)</f>
+        <f aca="false">IF(C165="","",WORKDAY($C$5-1,A165))</f>
         <v/>
       </c>
       <c r="C165" s="20" t="str">
@@ -6860,7 +6866,7 @@
         <v/>
       </c>
       <c r="B166" s="19" t="str">
-        <f aca="false">IF(C166="","",$C$5+A166-1)</f>
+        <f aca="false">IF(C166="","",WORKDAY($C$5-1,A166))</f>
         <v/>
       </c>
       <c r="C166" s="20" t="str">
@@ -6897,7 +6903,7 @@
         <v/>
       </c>
       <c r="B167" s="19" t="str">
-        <f aca="false">IF(C167="","",$C$5+A167-1)</f>
+        <f aca="false">IF(C167="","",WORKDAY($C$5-1,A167))</f>
         <v/>
       </c>
       <c r="C167" s="20" t="str">
@@ -6934,7 +6940,7 @@
         <v/>
       </c>
       <c r="B168" s="19" t="str">
-        <f aca="false">IF(C168="","",$C$5+A168-1)</f>
+        <f aca="false">IF(C168="","",WORKDAY($C$5-1,A168))</f>
         <v/>
       </c>
       <c r="C168" s="20" t="str">
@@ -6971,7 +6977,7 @@
         <v/>
       </c>
       <c r="B169" s="19" t="str">
-        <f aca="false">IF(C169="","",$C$5+A169-1)</f>
+        <f aca="false">IF(C169="","",WORKDAY($C$5-1,A169))</f>
         <v/>
       </c>
       <c r="C169" s="20" t="str">
@@ -7008,7 +7014,7 @@
         <v/>
       </c>
       <c r="B170" s="19" t="str">
-        <f aca="false">IF(C170="","",$C$5+A170-1)</f>
+        <f aca="false">IF(C170="","",WORKDAY($C$5-1,A170))</f>
         <v/>
       </c>
       <c r="C170" s="20" t="str">
@@ -7045,7 +7051,7 @@
         <v/>
       </c>
       <c r="B171" s="19" t="str">
-        <f aca="false">IF(C171="","",$C$5+A171-1)</f>
+        <f aca="false">IF(C171="","",WORKDAY($C$5-1,A171))</f>
         <v/>
       </c>
       <c r="C171" s="20" t="str">
@@ -7082,7 +7088,7 @@
         <v/>
       </c>
       <c r="B172" s="19" t="str">
-        <f aca="false">IF(C172="","",$C$5+A172-1)</f>
+        <f aca="false">IF(C172="","",WORKDAY($C$5-1,A172))</f>
         <v/>
       </c>
       <c r="C172" s="20" t="str">
@@ -7119,7 +7125,7 @@
         <v/>
       </c>
       <c r="B173" s="19" t="str">
-        <f aca="false">IF(C173="","",$C$5+A173-1)</f>
+        <f aca="false">IF(C173="","",WORKDAY($C$5-1,A173))</f>
         <v/>
       </c>
       <c r="C173" s="20" t="str">
@@ -7156,7 +7162,7 @@
         <v/>
       </c>
       <c r="B174" s="19" t="str">
-        <f aca="false">IF(C174="","",$C$5+A174-1)</f>
+        <f aca="false">IF(C174="","",WORKDAY($C$5-1,A174))</f>
         <v/>
       </c>
       <c r="C174" s="20" t="str">
@@ -7193,7 +7199,7 @@
         <v/>
       </c>
       <c r="B175" s="19" t="str">
-        <f aca="false">IF(C175="","",$C$5+A175-1)</f>
+        <f aca="false">IF(C175="","",WORKDAY($C$5-1,A175))</f>
         <v/>
       </c>
       <c r="C175" s="20" t="str">
@@ -7230,7 +7236,7 @@
         <v/>
       </c>
       <c r="B176" s="19" t="str">
-        <f aca="false">IF(C176="","",$C$5+A176-1)</f>
+        <f aca="false">IF(C176="","",WORKDAY($C$5-1,A176))</f>
         <v/>
       </c>
       <c r="C176" s="20" t="str">
@@ -7267,7 +7273,7 @@
         <v/>
       </c>
       <c r="B177" s="19" t="str">
-        <f aca="false">IF(C177="","",$C$5+A177-1)</f>
+        <f aca="false">IF(C177="","",WORKDAY($C$5-1,A177))</f>
         <v/>
       </c>
       <c r="C177" s="20" t="str">
@@ -7304,7 +7310,7 @@
         <v/>
       </c>
       <c r="B178" s="19" t="str">
-        <f aca="false">IF(C178="","",$C$5+A178-1)</f>
+        <f aca="false">IF(C178="","",WORKDAY($C$5-1,A178))</f>
         <v/>
       </c>
       <c r="C178" s="20" t="str">
@@ -7341,7 +7347,7 @@
         <v/>
       </c>
       <c r="B179" s="19" t="str">
-        <f aca="false">IF(C179="","",$C$5+A179-1)</f>
+        <f aca="false">IF(C179="","",WORKDAY($C$5-1,A179))</f>
         <v/>
       </c>
       <c r="C179" s="20" t="str">
@@ -7378,7 +7384,7 @@
         <v/>
       </c>
       <c r="B180" s="19" t="str">
-        <f aca="false">IF(C180="","",$C$5+A180-1)</f>
+        <f aca="false">IF(C180="","",WORKDAY($C$5-1,A180))</f>
         <v/>
       </c>
       <c r="C180" s="20" t="str">
@@ -7415,7 +7421,7 @@
         <v/>
       </c>
       <c r="B181" s="19" t="str">
-        <f aca="false">IF(C181="","",$C$5+A181-1)</f>
+        <f aca="false">IF(C181="","",WORKDAY($C$5-1,A181))</f>
         <v/>
       </c>
       <c r="C181" s="20" t="str">
@@ -7452,7 +7458,7 @@
         <v/>
       </c>
       <c r="B182" s="19" t="str">
-        <f aca="false">IF(C182="","",$C$5+A182-1)</f>
+        <f aca="false">IF(C182="","",WORKDAY($C$5-1,A182))</f>
         <v/>
       </c>
       <c r="C182" s="20" t="str">
@@ -7489,7 +7495,7 @@
         <v/>
       </c>
       <c r="B183" s="19" t="str">
-        <f aca="false">IF(C183="","",$C$5+A183-1)</f>
+        <f aca="false">IF(C183="","",WORKDAY($C$5-1,A183))</f>
         <v/>
       </c>
       <c r="C183" s="20" t="str">
@@ -7526,7 +7532,7 @@
         <v/>
       </c>
       <c r="B184" s="19" t="str">
-        <f aca="false">IF(C184="","",$C$5+A184-1)</f>
+        <f aca="false">IF(C184="","",WORKDAY($C$5-1,A184))</f>
         <v/>
       </c>
       <c r="C184" s="20" t="str">
@@ -7563,7 +7569,7 @@
         <v/>
       </c>
       <c r="B185" s="19" t="str">
-        <f aca="false">IF(C185="","",$C$5+A185-1)</f>
+        <f aca="false">IF(C185="","",WORKDAY($C$5-1,A185))</f>
         <v/>
       </c>
       <c r="C185" s="20" t="str">
@@ -7600,7 +7606,7 @@
         <v/>
       </c>
       <c r="B186" s="19" t="str">
-        <f aca="false">IF(C186="","",$C$5+A186-1)</f>
+        <f aca="false">IF(C186="","",WORKDAY($C$5-1,A186))</f>
         <v/>
       </c>
       <c r="C186" s="20" t="str">
@@ -7637,7 +7643,7 @@
         <v/>
       </c>
       <c r="B187" s="19" t="str">
-        <f aca="false">IF(C187="","",$C$5+A187-1)</f>
+        <f aca="false">IF(C187="","",WORKDAY($C$5-1,A187))</f>
         <v/>
       </c>
       <c r="C187" s="20" t="str">
@@ -7674,7 +7680,7 @@
         <v/>
       </c>
       <c r="B188" s="19" t="str">
-        <f aca="false">IF(C188="","",$C$5+A188-1)</f>
+        <f aca="false">IF(C188="","",WORKDAY($C$5-1,A188))</f>
         <v/>
       </c>
       <c r="C188" s="20" t="str">
@@ -7711,7 +7717,7 @@
         <v/>
       </c>
       <c r="B189" s="19" t="str">
-        <f aca="false">IF(C189="","",$C$5+A189-1)</f>
+        <f aca="false">IF(C189="","",WORKDAY($C$5-1,A189))</f>
         <v/>
       </c>
       <c r="C189" s="20" t="str">
@@ -7748,7 +7754,7 @@
         <v/>
       </c>
       <c r="B190" s="19" t="str">
-        <f aca="false">IF(C190="","",$C$5+A190-1)</f>
+        <f aca="false">IF(C190="","",WORKDAY($C$5-1,A190))</f>
         <v/>
       </c>
       <c r="C190" s="20" t="str">
@@ -7785,7 +7791,7 @@
         <v/>
       </c>
       <c r="B191" s="19" t="str">
-        <f aca="false">IF(C191="","",$C$5+A191-1)</f>
+        <f aca="false">IF(C191="","",WORKDAY($C$5-1,A191))</f>
         <v/>
       </c>
       <c r="C191" s="20" t="str">
@@ -7822,7 +7828,7 @@
         <v/>
       </c>
       <c r="B192" s="19" t="str">
-        <f aca="false">IF(C192="","",$C$5+A192-1)</f>
+        <f aca="false">IF(C192="","",WORKDAY($C$5-1,A192))</f>
         <v/>
       </c>
       <c r="C192" s="20" t="str">
@@ -7859,7 +7865,7 @@
         <v/>
       </c>
       <c r="B193" s="19" t="str">
-        <f aca="false">IF(C193="","",$C$5+A193-1)</f>
+        <f aca="false">IF(C193="","",WORKDAY($C$5-1,A193))</f>
         <v/>
       </c>
       <c r="C193" s="20" t="str">
@@ -7896,7 +7902,7 @@
         <v/>
       </c>
       <c r="B194" s="19" t="str">
-        <f aca="false">IF(C194="","",$C$5+A194-1)</f>
+        <f aca="false">IF(C194="","",WORKDAY($C$5-1,A194))</f>
         <v/>
       </c>
       <c r="C194" s="20" t="str">
@@ -7933,7 +7939,7 @@
         <v/>
       </c>
       <c r="B195" s="19" t="str">
-        <f aca="false">IF(C195="","",$C$5+A195-1)</f>
+        <f aca="false">IF(C195="","",WORKDAY($C$5-1,A195))</f>
         <v/>
       </c>
       <c r="C195" s="20" t="str">
@@ -7970,7 +7976,7 @@
         <v/>
       </c>
       <c r="B196" s="19" t="str">
-        <f aca="false">IF(C196="","",$C$5+A196-1)</f>
+        <f aca="false">IF(C196="","",WORKDAY($C$5-1,A196))</f>
         <v/>
       </c>
       <c r="C196" s="20" t="str">
@@ -8007,7 +8013,7 @@
         <v/>
       </c>
       <c r="B197" s="19" t="str">
-        <f aca="false">IF(C197="","",$C$5+A197-1)</f>
+        <f aca="false">IF(C197="","",WORKDAY($C$5-1,A197))</f>
         <v/>
       </c>
       <c r="C197" s="20" t="str">
@@ -8044,7 +8050,7 @@
         <v/>
       </c>
       <c r="B198" s="19" t="str">
-        <f aca="false">IF(C198="","",$C$5+A198-1)</f>
+        <f aca="false">IF(C198="","",WORKDAY($C$5-1,A198))</f>
         <v/>
       </c>
       <c r="C198" s="20" t="str">
@@ -8081,7 +8087,7 @@
         <v/>
       </c>
       <c r="B199" s="19" t="str">
-        <f aca="false">IF(C199="","",$C$5+A199-1)</f>
+        <f aca="false">IF(C199="","",WORKDAY($C$5-1,A199))</f>
         <v/>
       </c>
       <c r="C199" s="20" t="str">
@@ -8118,7 +8124,7 @@
         <v/>
       </c>
       <c r="B200" s="19" t="str">
-        <f aca="false">IF(C200="","",$C$5+A200-1)</f>
+        <f aca="false">IF(C200="","",WORKDAY($C$5-1,A200))</f>
         <v/>
       </c>
       <c r="C200" s="20" t="str">
@@ -8155,7 +8161,7 @@
         <v/>
       </c>
       <c r="B201" s="19" t="str">
-        <f aca="false">IF(C201="","",$C$5+A201-1)</f>
+        <f aca="false">IF(C201="","",WORKDAY($C$5-1,A201))</f>
         <v/>
       </c>
       <c r="C201" s="20" t="str">
@@ -8192,7 +8198,7 @@
         <v/>
       </c>
       <c r="B202" s="19" t="str">
-        <f aca="false">IF(C202="","",$C$5+A202-1)</f>
+        <f aca="false">IF(C202="","",WORKDAY($C$5-1,A202))</f>
         <v/>
       </c>
       <c r="C202" s="20" t="str">
@@ -8229,7 +8235,7 @@
         <v/>
       </c>
       <c r="B203" s="19" t="str">
-        <f aca="false">IF(C203="","",$C$5+A203-1)</f>
+        <f aca="false">IF(C203="","",WORKDAY($C$5-1,A203))</f>
         <v/>
       </c>
       <c r="C203" s="20" t="str">
@@ -8266,7 +8272,7 @@
         <v/>
       </c>
       <c r="B204" s="19" t="str">
-        <f aca="false">IF(C204="","",$C$5+A204-1)</f>
+        <f aca="false">IF(C204="","",WORKDAY($C$5-1,A204))</f>
         <v/>
       </c>
       <c r="C204" s="20" t="str">
@@ -8303,7 +8309,7 @@
         <v/>
       </c>
       <c r="B205" s="19" t="str">
-        <f aca="false">IF(C205="","",$C$5+A205-1)</f>
+        <f aca="false">IF(C205="","",WORKDAY($C$5-1,A205))</f>
         <v/>
       </c>
       <c r="C205" s="20" t="str">
@@ -8340,7 +8346,7 @@
         <v/>
       </c>
       <c r="B206" s="19" t="str">
-        <f aca="false">IF(C206="","",$C$5+A206-1)</f>
+        <f aca="false">IF(C206="","",WORKDAY($C$5-1,A206))</f>
         <v/>
       </c>
       <c r="C206" s="20" t="str">
@@ -8377,7 +8383,7 @@
         <v/>
       </c>
       <c r="B207" s="19" t="str">
-        <f aca="false">IF(C207="","",$C$5+A207-1)</f>
+        <f aca="false">IF(C207="","",WORKDAY($C$5-1,A207))</f>
         <v/>
       </c>
       <c r="C207" s="20" t="str">
@@ -8414,7 +8420,7 @@
         <v/>
       </c>
       <c r="B208" s="19" t="str">
-        <f aca="false">IF(C208="","",$C$5+A208-1)</f>
+        <f aca="false">IF(C208="","",WORKDAY($C$5-1,A208))</f>
         <v/>
       </c>
       <c r="C208" s="20" t="str">
@@ -8451,7 +8457,7 @@
         <v/>
       </c>
       <c r="B209" s="19" t="str">
-        <f aca="false">IF(C209="","",$C$5+A209-1)</f>
+        <f aca="false">IF(C209="","",WORKDAY($C$5-1,A209))</f>
         <v/>
       </c>
       <c r="C209" s="20" t="str">
@@ -8488,7 +8494,7 @@
         <v/>
       </c>
       <c r="B210" s="19" t="str">
-        <f aca="false">IF(C210="","",$C$5+A210-1)</f>
+        <f aca="false">IF(C210="","",WORKDAY($C$5-1,A210))</f>
         <v/>
       </c>
       <c r="C210" s="20" t="str">
@@ -8525,7 +8531,7 @@
         <v/>
       </c>
       <c r="B211" s="19" t="str">
-        <f aca="false">IF(C211="","",$C$5+A211-1)</f>
+        <f aca="false">IF(C211="","",WORKDAY($C$5-1,A211))</f>
         <v/>
       </c>
       <c r="C211" s="20" t="str">
@@ -8562,7 +8568,7 @@
         <v/>
       </c>
       <c r="B212" s="19" t="str">
-        <f aca="false">IF(C212="","",$C$5+A212-1)</f>
+        <f aca="false">IF(C212="","",WORKDAY($C$5-1,A212))</f>
         <v/>
       </c>
       <c r="C212" s="20" t="str">
@@ -8599,7 +8605,7 @@
         <v/>
       </c>
       <c r="B213" s="19" t="str">
-        <f aca="false">IF(C213="","",$C$5+A213-1)</f>
+        <f aca="false">IF(C213="","",WORKDAY($C$5-1,A213))</f>
         <v/>
       </c>
       <c r="C213" s="20" t="str">
@@ -8636,7 +8642,7 @@
         <v/>
       </c>
       <c r="B214" s="19" t="str">
-        <f aca="false">IF(C214="","",$C$5+A214-1)</f>
+        <f aca="false">IF(C214="","",WORKDAY($C$5-1,A214))</f>
         <v/>
       </c>
       <c r="C214" s="20" t="str">
@@ -8673,7 +8679,7 @@
         <v/>
       </c>
       <c r="B215" s="19" t="str">
-        <f aca="false">IF(C215="","",$C$5+A215-1)</f>
+        <f aca="false">IF(C215="","",WORKDAY($C$5-1,A215))</f>
         <v/>
       </c>
       <c r="C215" s="20" t="str">
@@ -8710,7 +8716,7 @@
         <v/>
       </c>
       <c r="B216" s="19" t="str">
-        <f aca="false">IF(C216="","",$C$5+A216-1)</f>
+        <f aca="false">IF(C216="","",WORKDAY($C$5-1,A216))</f>
         <v/>
       </c>
       <c r="C216" s="20" t="str">
@@ -8747,7 +8753,7 @@
         <v/>
       </c>
       <c r="B217" s="19" t="str">
-        <f aca="false">IF(C217="","",$C$5+A217-1)</f>
+        <f aca="false">IF(C217="","",WORKDAY($C$5-1,A217))</f>
         <v/>
       </c>
       <c r="C217" s="20" t="str">
@@ -8784,7 +8790,7 @@
         <v/>
       </c>
       <c r="B218" s="19" t="str">
-        <f aca="false">IF(C218="","",$C$5+A218-1)</f>
+        <f aca="false">IF(C218="","",WORKDAY($C$5-1,A218))</f>
         <v/>
       </c>
       <c r="C218" s="20" t="str">
@@ -8821,7 +8827,7 @@
         <v/>
       </c>
       <c r="B219" s="19" t="str">
-        <f aca="false">IF(C219="","",$C$5+A219-1)</f>
+        <f aca="false">IF(C219="","",WORKDAY($C$5-1,A219))</f>
         <v/>
       </c>
       <c r="C219" s="20" t="str">
@@ -8858,7 +8864,7 @@
         <v/>
       </c>
       <c r="B220" s="19" t="str">
-        <f aca="false">IF(C220="","",$C$5+A220-1)</f>
+        <f aca="false">IF(C220="","",WORKDAY($C$5-1,A220))</f>
         <v/>
       </c>
       <c r="C220" s="20" t="str">
@@ -8895,7 +8901,7 @@
         <v/>
       </c>
       <c r="B221" s="19" t="str">
-        <f aca="false">IF(C221="","",$C$5+A221-1)</f>
+        <f aca="false">IF(C221="","",WORKDAY($C$5-1,A221))</f>
         <v/>
       </c>
       <c r="C221" s="20" t="str">
@@ -8932,7 +8938,7 @@
         <v/>
       </c>
       <c r="B222" s="19" t="str">
-        <f aca="false">IF(C222="","",$C$5+A222-1)</f>
+        <f aca="false">IF(C222="","",WORKDAY($C$5-1,A222))</f>
         <v/>
       </c>
       <c r="C222" s="20" t="str">
@@ -8969,7 +8975,7 @@
         <v/>
       </c>
       <c r="B223" s="19" t="str">
-        <f aca="false">IF(C223="","",$C$5+A223-1)</f>
+        <f aca="false">IF(C223="","",WORKDAY($C$5-1,A223))</f>
         <v/>
       </c>
       <c r="C223" s="20" t="str">
@@ -9006,7 +9012,7 @@
         <v/>
       </c>
       <c r="B224" s="19" t="str">
-        <f aca="false">IF(C224="","",$C$5+A224-1)</f>
+        <f aca="false">IF(C224="","",WORKDAY($C$5-1,A224))</f>
         <v/>
       </c>
       <c r="C224" s="20" t="str">
@@ -9043,7 +9049,7 @@
         <v/>
       </c>
       <c r="B225" s="19" t="str">
-        <f aca="false">IF(C225="","",$C$5+A225-1)</f>
+        <f aca="false">IF(C225="","",WORKDAY($C$5-1,A225))</f>
         <v/>
       </c>
       <c r="C225" s="20" t="str">
@@ -9080,7 +9086,7 @@
         <v/>
       </c>
       <c r="B226" s="19" t="str">
-        <f aca="false">IF(C226="","",$C$5+A226-1)</f>
+        <f aca="false">IF(C226="","",WORKDAY($C$5-1,A226))</f>
         <v/>
       </c>
       <c r="C226" s="20" t="str">
@@ -9117,7 +9123,7 @@
         <v/>
       </c>
       <c r="B227" s="19" t="str">
-        <f aca="false">IF(C227="","",$C$5+A227-1)</f>
+        <f aca="false">IF(C227="","",WORKDAY($C$5-1,A227))</f>
         <v/>
       </c>
       <c r="C227" s="20" t="str">
@@ -9154,7 +9160,7 @@
         <v/>
       </c>
       <c r="B228" s="19" t="str">
-        <f aca="false">IF(C228="","",$C$5+A228-1)</f>
+        <f aca="false">IF(C228="","",WORKDAY($C$5-1,A228))</f>
         <v/>
       </c>
       <c r="C228" s="20" t="str">
@@ -9191,7 +9197,7 @@
         <v/>
       </c>
       <c r="B229" s="19" t="str">
-        <f aca="false">IF(C229="","",$C$5+A229-1)</f>
+        <f aca="false">IF(C229="","",WORKDAY($C$5-1,A229))</f>
         <v/>
       </c>
       <c r="C229" s="20" t="str">
@@ -9228,7 +9234,7 @@
         <v/>
       </c>
       <c r="B230" s="19" t="str">
-        <f aca="false">IF(C230="","",$C$5+A230-1)</f>
+        <f aca="false">IF(C230="","",WORKDAY($C$5-1,A230))</f>
         <v/>
       </c>
       <c r="C230" s="20" t="str">
@@ -9265,7 +9271,7 @@
         <v/>
       </c>
       <c r="B231" s="19" t="str">
-        <f aca="false">IF(C231="","",$C$5+A231-1)</f>
+        <f aca="false">IF(C231="","",WORKDAY($C$5-1,A231))</f>
         <v/>
       </c>
       <c r="C231" s="20" t="str">
@@ -9302,7 +9308,7 @@
         <v/>
       </c>
       <c r="B232" s="19" t="str">
-        <f aca="false">IF(C232="","",$C$5+A232-1)</f>
+        <f aca="false">IF(C232="","",WORKDAY($C$5-1,A232))</f>
         <v/>
       </c>
       <c r="C232" s="20" t="str">
@@ -9339,7 +9345,7 @@
         <v/>
       </c>
       <c r="B233" s="19" t="str">
-        <f aca="false">IF(C233="","",$C$5+A233-1)</f>
+        <f aca="false">IF(C233="","",WORKDAY($C$5-1,A233))</f>
         <v/>
       </c>
       <c r="C233" s="20" t="str">
@@ -9376,7 +9382,7 @@
         <v/>
       </c>
       <c r="B234" s="19" t="str">
-        <f aca="false">IF(C234="","",$C$5+A234-1)</f>
+        <f aca="false">IF(C234="","",WORKDAY($C$5-1,A234))</f>
         <v/>
       </c>
       <c r="C234" s="20" t="str">
@@ -9413,7 +9419,7 @@
         <v/>
       </c>
       <c r="B235" s="19" t="str">
-        <f aca="false">IF(C235="","",$C$5+A235-1)</f>
+        <f aca="false">IF(C235="","",WORKDAY($C$5-1,A235))</f>
         <v/>
       </c>
       <c r="C235" s="20" t="str">
@@ -9450,7 +9456,7 @@
         <v/>
       </c>
       <c r="B236" s="19" t="str">
-        <f aca="false">IF(C236="","",$C$5+A236-1)</f>
+        <f aca="false">IF(C236="","",WORKDAY($C$5-1,A236))</f>
         <v/>
       </c>
       <c r="C236" s="20" t="str">
@@ -9487,7 +9493,7 @@
         <v/>
       </c>
       <c r="B237" s="19" t="str">
-        <f aca="false">IF(C237="","",$C$5+A237-1)</f>
+        <f aca="false">IF(C237="","",WORKDAY($C$5-1,A237))</f>
         <v/>
       </c>
       <c r="C237" s="20" t="str">
@@ -9524,7 +9530,7 @@
         <v/>
       </c>
       <c r="B238" s="19" t="str">
-        <f aca="false">IF(C238="","",$C$5+A238-1)</f>
+        <f aca="false">IF(C238="","",WORKDAY($C$5-1,A238))</f>
         <v/>
       </c>
       <c r="C238" s="20" t="str">
@@ -9561,7 +9567,7 @@
         <v/>
       </c>
       <c r="B239" s="19" t="str">
-        <f aca="false">IF(C239="","",$C$5+A239-1)</f>
+        <f aca="false">IF(C239="","",WORKDAY($C$5-1,A239))</f>
         <v/>
       </c>
       <c r="C239" s="20" t="str">
@@ -9598,7 +9604,7 @@
         <v/>
       </c>
       <c r="B240" s="19" t="str">
-        <f aca="false">IF(C240="","",$C$5+A240-1)</f>
+        <f aca="false">IF(C240="","",WORKDAY($C$5-1,A240))</f>
         <v/>
       </c>
       <c r="C240" s="20" t="str">
@@ -9635,7 +9641,7 @@
         <v/>
       </c>
       <c r="B241" s="19" t="str">
-        <f aca="false">IF(C241="","",$C$5+A241-1)</f>
+        <f aca="false">IF(C241="","",WORKDAY($C$5-1,A241))</f>
         <v/>
       </c>
       <c r="C241" s="20" t="str">
@@ -9672,7 +9678,7 @@
         <v/>
       </c>
       <c r="B242" s="19" t="str">
-        <f aca="false">IF(C242="","",$C$5+A242-1)</f>
+        <f aca="false">IF(C242="","",WORKDAY($C$5-1,A242))</f>
         <v/>
       </c>
       <c r="C242" s="20" t="str">
@@ -9709,7 +9715,7 @@
         <v/>
       </c>
       <c r="B243" s="19" t="str">
-        <f aca="false">IF(C243="","",$C$5+A243-1)</f>
+        <f aca="false">IF(C243="","",WORKDAY($C$5-1,A243))</f>
         <v/>
       </c>
       <c r="C243" s="20" t="str">
@@ -9746,7 +9752,7 @@
         <v/>
       </c>
       <c r="B244" s="19" t="str">
-        <f aca="false">IF(C244="","",$C$5+A244-1)</f>
+        <f aca="false">IF(C244="","",WORKDAY($C$5-1,A244))</f>
         <v/>
       </c>
       <c r="C244" s="20" t="str">
@@ -9783,7 +9789,7 @@
         <v/>
       </c>
       <c r="B245" s="19" t="str">
-        <f aca="false">IF(C245="","",$C$5+A245-1)</f>
+        <f aca="false">IF(C245="","",WORKDAY($C$5-1,A245))</f>
         <v/>
       </c>
       <c r="C245" s="20" t="str">
@@ -9820,7 +9826,7 @@
         <v/>
       </c>
       <c r="B246" s="19" t="str">
-        <f aca="false">IF(C246="","",$C$5+A246-1)</f>
+        <f aca="false">IF(C246="","",WORKDAY($C$5-1,A246))</f>
         <v/>
       </c>
       <c r="C246" s="20" t="str">
@@ -9857,7 +9863,7 @@
         <v/>
       </c>
       <c r="B247" s="19" t="str">
-        <f aca="false">IF(C247="","",$C$5+A247-1)</f>
+        <f aca="false">IF(C247="","",WORKDAY($C$5-1,A247))</f>
         <v/>
       </c>
       <c r="C247" s="20" t="str">
@@ -9894,7 +9900,7 @@
         <v/>
       </c>
       <c r="B248" s="19" t="str">
-        <f aca="false">IF(C248="","",$C$5+A248-1)</f>
+        <f aca="false">IF(C248="","",WORKDAY($C$5-1,A248))</f>
         <v/>
       </c>
       <c r="C248" s="20" t="str">
@@ -9931,7 +9937,7 @@
         <v/>
       </c>
       <c r="B249" s="19" t="str">
-        <f aca="false">IF(C249="","",$C$5+A249-1)</f>
+        <f aca="false">IF(C249="","",WORKDAY($C$5-1,A249))</f>
         <v/>
       </c>
       <c r="C249" s="20" t="str">
@@ -9968,7 +9974,7 @@
         <v/>
       </c>
       <c r="B250" s="19" t="str">
-        <f aca="false">IF(C250="","",$C$5+A250-1)</f>
+        <f aca="false">IF(C250="","",WORKDAY($C$5-1,A250))</f>
         <v/>
       </c>
       <c r="C250" s="20" t="str">
@@ -10005,7 +10011,7 @@
         <v/>
       </c>
       <c r="B251" s="19" t="str">
-        <f aca="false">IF(C251="","",$C$5+A251-1)</f>
+        <f aca="false">IF(C251="","",WORKDAY($C$5-1,A251))</f>
         <v/>
       </c>
       <c r="C251" s="20" t="str">
@@ -10042,7 +10048,7 @@
         <v/>
       </c>
       <c r="B252" s="19" t="str">
-        <f aca="false">IF(C252="","",$C$5+A252-1)</f>
+        <f aca="false">IF(C252="","",WORKDAY($C$5-1,A252))</f>
         <v/>
       </c>
       <c r="C252" s="20" t="str">
@@ -10079,7 +10085,7 @@
         <v/>
       </c>
       <c r="B253" s="19" t="str">
-        <f aca="false">IF(C253="","",$C$5+A253-1)</f>
+        <f aca="false">IF(C253="","",WORKDAY($C$5-1,A253))</f>
         <v/>
       </c>
       <c r="C253" s="20" t="str">
@@ -10116,7 +10122,7 @@
         <v/>
       </c>
       <c r="B254" s="19" t="str">
-        <f aca="false">IF(C254="","",$C$5+A254-1)</f>
+        <f aca="false">IF(C254="","",WORKDAY($C$5-1,A254))</f>
         <v/>
       </c>
       <c r="C254" s="20" t="str">
@@ -10153,7 +10159,7 @@
         <v/>
       </c>
       <c r="B255" s="19" t="str">
-        <f aca="false">IF(C255="","",$C$5+A255-1)</f>
+        <f aca="false">IF(C255="","",WORKDAY($C$5-1,A255))</f>
         <v/>
       </c>
       <c r="C255" s="20" t="str">
@@ -10190,7 +10196,7 @@
         <v/>
       </c>
       <c r="B256" s="19" t="str">
-        <f aca="false">IF(C256="","",$C$5+A256-1)</f>
+        <f aca="false">IF(C256="","",WORKDAY($C$5-1,A256))</f>
         <v/>
       </c>
       <c r="C256" s="20" t="str">
@@ -10227,7 +10233,7 @@
         <v/>
       </c>
       <c r="B257" s="19" t="str">
-        <f aca="false">IF(C257="","",$C$5+A257-1)</f>
+        <f aca="false">IF(C257="","",WORKDAY($C$5-1,A257))</f>
         <v/>
       </c>
       <c r="C257" s="20" t="str">
@@ -10264,7 +10270,7 @@
         <v/>
       </c>
       <c r="B258" s="19" t="str">
-        <f aca="false">IF(C258="","",$C$5+A258-1)</f>
+        <f aca="false">IF(C258="","",WORKDAY($C$5-1,A258))</f>
         <v/>
       </c>
       <c r="C258" s="20" t="str">
@@ -10301,7 +10307,7 @@
         <v/>
       </c>
       <c r="B259" s="19" t="str">
-        <f aca="false">IF(C259="","",$C$5+A259-1)</f>
+        <f aca="false">IF(C259="","",WORKDAY($C$5-1,A259))</f>
         <v/>
       </c>
       <c r="C259" s="20" t="str">
@@ -10338,7 +10344,7 @@
         <v/>
       </c>
       <c r="B260" s="19" t="str">
-        <f aca="false">IF(C260="","",$C$5+A260-1)</f>
+        <f aca="false">IF(C260="","",WORKDAY($C$5-1,A260))</f>
         <v/>
       </c>
       <c r="C260" s="20" t="str">
@@ -10375,7 +10381,7 @@
         <v/>
       </c>
       <c r="B261" s="19" t="str">
-        <f aca="false">IF(C261="","",$C$5+A261-1)</f>
+        <f aca="false">IF(C261="","",WORKDAY($C$5-1,A261))</f>
         <v/>
       </c>
       <c r="C261" s="20" t="str">
@@ -10412,7 +10418,7 @@
         <v/>
       </c>
       <c r="B262" s="19" t="str">
-        <f aca="false">IF(C262="","",$C$5+A262-1)</f>
+        <f aca="false">IF(C262="","",WORKDAY($C$5-1,A262))</f>
         <v/>
       </c>
       <c r="C262" s="20" t="str">
@@ -10449,7 +10455,7 @@
         <v/>
       </c>
       <c r="B263" s="19" t="str">
-        <f aca="false">IF(C263="","",$C$5+A263-1)</f>
+        <f aca="false">IF(C263="","",WORKDAY($C$5-1,A263))</f>
         <v/>
       </c>
       <c r="C263" s="20" t="str">
@@ -10486,7 +10492,7 @@
         <v/>
       </c>
       <c r="B264" s="19" t="str">
-        <f aca="false">IF(C264="","",$C$5+A264-1)</f>
+        <f aca="false">IF(C264="","",WORKDAY($C$5-1,A264))</f>
         <v/>
       </c>
       <c r="C264" s="20" t="str">
@@ -10523,7 +10529,7 @@
         <v/>
       </c>
       <c r="B265" s="19" t="str">
-        <f aca="false">IF(C265="","",$C$5+A265-1)</f>
+        <f aca="false">IF(C265="","",WORKDAY($C$5-1,A265))</f>
         <v/>
       </c>
       <c r="C265" s="20" t="str">
@@ -10560,7 +10566,7 @@
         <v/>
       </c>
       <c r="B266" s="19" t="str">
-        <f aca="false">IF(C266="","",$C$5+A266-1)</f>
+        <f aca="false">IF(C266="","",WORKDAY($C$5-1,A266))</f>
         <v/>
       </c>
       <c r="C266" s="20" t="str">
@@ -10597,7 +10603,7 @@
         <v/>
       </c>
       <c r="B267" s="19" t="str">
-        <f aca="false">IF(C267="","",$C$5+A267-1)</f>
+        <f aca="false">IF(C267="","",WORKDAY($C$5-1,A267))</f>
         <v/>
       </c>
       <c r="C267" s="20" t="str">
@@ -10634,7 +10640,7 @@
         <v/>
       </c>
       <c r="B268" s="19" t="str">
-        <f aca="false">IF(C268="","",$C$5+A268-1)</f>
+        <f aca="false">IF(C268="","",WORKDAY($C$5-1,A268))</f>
         <v/>
       </c>
       <c r="C268" s="20" t="str">
@@ -10671,7 +10677,7 @@
         <v/>
       </c>
       <c r="B269" s="19" t="str">
-        <f aca="false">IF(C269="","",$C$5+A269-1)</f>
+        <f aca="false">IF(C269="","",WORKDAY($C$5-1,A269))</f>
         <v/>
       </c>
       <c r="C269" s="20" t="str">
@@ -10708,7 +10714,7 @@
         <v/>
       </c>
       <c r="B270" s="19" t="str">
-        <f aca="false">IF(C270="","",$C$5+A270-1)</f>
+        <f aca="false">IF(C270="","",WORKDAY($C$5-1,A270))</f>
         <v/>
       </c>
       <c r="C270" s="20" t="str">
@@ -10745,7 +10751,7 @@
         <v/>
       </c>
       <c r="B271" s="19" t="str">
-        <f aca="false">IF(C271="","",$C$5+A271-1)</f>
+        <f aca="false">IF(C271="","",WORKDAY($C$5-1,A271))</f>
         <v/>
       </c>
       <c r="C271" s="20" t="str">
@@ -10782,7 +10788,7 @@
         <v/>
       </c>
       <c r="B272" s="19" t="str">
-        <f aca="false">IF(C272="","",$C$5+A272-1)</f>
+        <f aca="false">IF(C272="","",WORKDAY($C$5-1,A272))</f>
         <v/>
       </c>
       <c r="C272" s="20" t="str">
@@ -10819,7 +10825,7 @@
         <v/>
       </c>
       <c r="B273" s="19" t="str">
-        <f aca="false">IF(C273="","",$C$5+A273-1)</f>
+        <f aca="false">IF(C273="","",WORKDAY($C$5-1,A273))</f>
         <v/>
       </c>
       <c r="C273" s="20" t="str">
@@ -10856,7 +10862,7 @@
         <v/>
       </c>
       <c r="B274" s="19" t="str">
-        <f aca="false">IF(C274="","",$C$5+A274-1)</f>
+        <f aca="false">IF(C274="","",WORKDAY($C$5-1,A274))</f>
         <v/>
       </c>
       <c r="C274" s="20" t="str">
@@ -10893,7 +10899,7 @@
         <v/>
       </c>
       <c r="B275" s="19" t="str">
-        <f aca="false">IF(C275="","",$C$5+A275-1)</f>
+        <f aca="false">IF(C275="","",WORKDAY($C$5-1,A275))</f>
         <v/>
       </c>
       <c r="C275" s="20" t="str">
@@ -10930,7 +10936,7 @@
         <v/>
       </c>
       <c r="B276" s="19" t="str">
-        <f aca="false">IF(C276="","",$C$5+A276-1)</f>
+        <f aca="false">IF(C276="","",WORKDAY($C$5-1,A276))</f>
         <v/>
       </c>
       <c r="C276" s="20" t="str">
@@ -10967,7 +10973,7 @@
         <v/>
       </c>
       <c r="B277" s="19" t="str">
-        <f aca="false">IF(C277="","",$C$5+A277-1)</f>
+        <f aca="false">IF(C277="","",WORKDAY($C$5-1,A277))</f>
         <v/>
       </c>
       <c r="C277" s="20" t="str">
@@ -11004,7 +11010,7 @@
         <v/>
       </c>
       <c r="B278" s="19" t="str">
-        <f aca="false">IF(C278="","",$C$5+A278-1)</f>
+        <f aca="false">IF(C278="","",WORKDAY($C$5-1,A278))</f>
         <v/>
       </c>
       <c r="C278" s="20" t="str">
@@ -11041,7 +11047,7 @@
         <v/>
       </c>
       <c r="B279" s="19" t="str">
-        <f aca="false">IF(C279="","",$C$5+A279-1)</f>
+        <f aca="false">IF(C279="","",WORKDAY($C$5-1,A279))</f>
         <v/>
       </c>
       <c r="C279" s="20" t="str">
@@ -11078,7 +11084,7 @@
         <v/>
       </c>
       <c r="B280" s="19" t="str">
-        <f aca="false">IF(C280="","",$C$5+A280-1)</f>
+        <f aca="false">IF(C280="","",WORKDAY($C$5-1,A280))</f>
         <v/>
       </c>
       <c r="C280" s="20" t="str">
@@ -11115,7 +11121,7 @@
         <v/>
       </c>
       <c r="B281" s="19" t="str">
-        <f aca="false">IF(C281="","",$C$5+A281-1)</f>
+        <f aca="false">IF(C281="","",WORKDAY($C$5-1,A281))</f>
         <v/>
       </c>
       <c r="C281" s="20" t="str">
@@ -11152,7 +11158,7 @@
         <v/>
       </c>
       <c r="B282" s="19" t="str">
-        <f aca="false">IF(C282="","",$C$5+A282-1)</f>
+        <f aca="false">IF(C282="","",WORKDAY($C$5-1,A282))</f>
         <v/>
       </c>
       <c r="C282" s="20" t="str">
@@ -11189,7 +11195,7 @@
         <v/>
       </c>
       <c r="B283" s="19" t="str">
-        <f aca="false">IF(C283="","",$C$5+A283-1)</f>
+        <f aca="false">IF(C283="","",WORKDAY($C$5-1,A283))</f>
         <v/>
       </c>
       <c r="C283" s="20" t="str">
@@ -11226,7 +11232,7 @@
         <v/>
       </c>
       <c r="B284" s="19" t="str">
-        <f aca="false">IF(C284="","",$C$5+A284-1)</f>
+        <f aca="false">IF(C284="","",WORKDAY($C$5-1,A284))</f>
         <v/>
       </c>
       <c r="C284" s="20" t="str">
@@ -11263,7 +11269,7 @@
         <v/>
       </c>
       <c r="B285" s="19" t="str">
-        <f aca="false">IF(C285="","",$C$5+A285-1)</f>
+        <f aca="false">IF(C285="","",WORKDAY($C$5-1,A285))</f>
         <v/>
       </c>
       <c r="C285" s="20" t="str">
@@ -11300,7 +11306,7 @@
         <v/>
       </c>
       <c r="B286" s="19" t="str">
-        <f aca="false">IF(C286="","",$C$5+A286-1)</f>
+        <f aca="false">IF(C286="","",WORKDAY($C$5-1,A286))</f>
         <v/>
       </c>
       <c r="C286" s="20" t="str">
@@ -11337,7 +11343,7 @@
         <v/>
       </c>
       <c r="B287" s="19" t="str">
-        <f aca="false">IF(C287="","",$C$5+A287-1)</f>
+        <f aca="false">IF(C287="","",WORKDAY($C$5-1,A287))</f>
         <v/>
       </c>
       <c r="C287" s="20" t="str">
@@ -11374,7 +11380,7 @@
         <v/>
       </c>
       <c r="B288" s="19" t="str">
-        <f aca="false">IF(C288="","",$C$5+A288-1)</f>
+        <f aca="false">IF(C288="","",WORKDAY($C$5-1,A288))</f>
         <v/>
       </c>
       <c r="C288" s="20" t="str">
@@ -11411,7 +11417,7 @@
         <v/>
       </c>
       <c r="B289" s="19" t="str">
-        <f aca="false">IF(C289="","",$C$5+A289-1)</f>
+        <f aca="false">IF(C289="","",WORKDAY($C$5-1,A289))</f>
         <v/>
       </c>
       <c r="C289" s="20" t="str">
@@ -11448,7 +11454,7 @@
         <v/>
       </c>
       <c r="B290" s="19" t="str">
-        <f aca="false">IF(C290="","",$C$5+A290-1)</f>
+        <f aca="false">IF(C290="","",WORKDAY($C$5-1,A290))</f>
         <v/>
       </c>
       <c r="C290" s="20" t="str">
@@ -11485,7 +11491,7 @@
         <v/>
       </c>
       <c r="B291" s="19" t="str">
-        <f aca="false">IF(C291="","",$C$5+A291-1)</f>
+        <f aca="false">IF(C291="","",WORKDAY($C$5-1,A291))</f>
         <v/>
       </c>
       <c r="C291" s="20" t="str">
@@ -11522,7 +11528,7 @@
         <v/>
       </c>
       <c r="B292" s="19" t="str">
-        <f aca="false">IF(C292="","",$C$5+A292-1)</f>
+        <f aca="false">IF(C292="","",WORKDAY($C$5-1,A292))</f>
         <v/>
       </c>
       <c r="C292" s="20" t="str">
@@ -11559,7 +11565,7 @@
         <v/>
       </c>
       <c r="B293" s="19" t="str">
-        <f aca="false">IF(C293="","",$C$5+A293-1)</f>
+        <f aca="false">IF(C293="","",WORKDAY($C$5-1,A293))</f>
         <v/>
       </c>
       <c r="C293" s="20" t="str">
@@ -11596,7 +11602,7 @@
         <v/>
       </c>
       <c r="B294" s="19" t="str">
-        <f aca="false">IF(C294="","",$C$5+A294-1)</f>
+        <f aca="false">IF(C294="","",WORKDAY($C$5-1,A294))</f>
         <v/>
       </c>
       <c r="C294" s="20" t="str">
@@ -11633,7 +11639,7 @@
         <v/>
       </c>
       <c r="B295" s="19" t="str">
-        <f aca="false">IF(C295="","",$C$5+A295-1)</f>
+        <f aca="false">IF(C295="","",WORKDAY($C$5-1,A295))</f>
         <v/>
       </c>
       <c r="C295" s="20" t="str">
@@ -11670,7 +11676,7 @@
         <v/>
       </c>
       <c r="B296" s="19" t="str">
-        <f aca="false">IF(C296="","",$C$5+A296-1)</f>
+        <f aca="false">IF(C296="","",WORKDAY($C$5-1,A296))</f>
         <v/>
       </c>
       <c r="C296" s="20" t="str">
@@ -11707,7 +11713,7 @@
         <v/>
       </c>
       <c r="B297" s="19" t="str">
-        <f aca="false">IF(C297="","",$C$5+A297-1)</f>
+        <f aca="false">IF(C297="","",WORKDAY($C$5-1,A297))</f>
         <v/>
       </c>
       <c r="C297" s="20" t="str">
@@ -11744,7 +11750,7 @@
         <v/>
       </c>
       <c r="B298" s="19" t="str">
-        <f aca="false">IF(C298="","",$C$5+A298-1)</f>
+        <f aca="false">IF(C298="","",WORKDAY($C$5-1,A298))</f>
         <v/>
       </c>
       <c r="C298" s="20" t="str">
@@ -11781,7 +11787,7 @@
         <v/>
       </c>
       <c r="B299" s="19" t="str">
-        <f aca="false">IF(C299="","",$C$5+A299-1)</f>
+        <f aca="false">IF(C299="","",WORKDAY($C$5-1,A299))</f>
         <v/>
       </c>
       <c r="C299" s="20" t="str">
@@ -11818,7 +11824,7 @@
         <v/>
       </c>
       <c r="B300" s="19" t="str">
-        <f aca="false">IF(C300="","",$C$5+A300-1)</f>
+        <f aca="false">IF(C300="","",WORKDAY($C$5-1,A300))</f>
         <v/>
       </c>
       <c r="C300" s="20" t="str">
@@ -11855,7 +11861,7 @@
         <v/>
       </c>
       <c r="B301" s="19" t="str">
-        <f aca="false">IF(C301="","",$C$5+A301-1)</f>
+        <f aca="false">IF(C301="","",WORKDAY($C$5-1,A301))</f>
         <v/>
       </c>
       <c r="C301" s="20" t="str">
@@ -11892,7 +11898,7 @@
         <v/>
       </c>
       <c r="B302" s="19" t="str">
-        <f aca="false">IF(C302="","",$C$5+A302-1)</f>
+        <f aca="false">IF(C302="","",WORKDAY($C$5-1,A302))</f>
         <v/>
       </c>
       <c r="C302" s="20" t="str">
@@ -11929,7 +11935,7 @@
         <v/>
       </c>
       <c r="B303" s="19" t="str">
-        <f aca="false">IF(C303="","",$C$5+A303-1)</f>
+        <f aca="false">IF(C303="","",WORKDAY($C$5-1,A303))</f>
         <v/>
       </c>
       <c r="C303" s="20" t="str">
@@ -11966,7 +11972,7 @@
         <v/>
       </c>
       <c r="B304" s="19" t="str">
-        <f aca="false">IF(C304="","",$C$5+A304-1)</f>
+        <f aca="false">IF(C304="","",WORKDAY($C$5-1,A304))</f>
         <v/>
       </c>
       <c r="C304" s="20" t="str">
@@ -12003,7 +12009,7 @@
         <v/>
       </c>
       <c r="B305" s="19" t="str">
-        <f aca="false">IF(C305="","",$C$5+A305-1)</f>
+        <f aca="false">IF(C305="","",WORKDAY($C$5-1,A305))</f>
         <v/>
       </c>
       <c r="C305" s="20" t="str">
@@ -12040,7 +12046,7 @@
         <v/>
       </c>
       <c r="B306" s="19" t="str">
-        <f aca="false">IF(C306="","",$C$5+A306-1)</f>
+        <f aca="false">IF(C306="","",WORKDAY($C$5-1,A306))</f>
         <v/>
       </c>
       <c r="C306" s="20" t="str">
@@ -12077,7 +12083,7 @@
         <v/>
       </c>
       <c r="B307" s="19" t="str">
-        <f aca="false">IF(C307="","",$C$5+A307-1)</f>
+        <f aca="false">IF(C307="","",WORKDAY($C$5-1,A307))</f>
         <v/>
       </c>
       <c r="C307" s="20" t="str">
@@ -12114,7 +12120,7 @@
         <v/>
       </c>
       <c r="B308" s="19" t="str">
-        <f aca="false">IF(C308="","",$C$5+A308-1)</f>
+        <f aca="false">IF(C308="","",WORKDAY($C$5-1,A308))</f>
         <v/>
       </c>
       <c r="C308" s="20" t="str">
@@ -12151,7 +12157,7 @@
         <v/>
       </c>
       <c r="B309" s="19" t="str">
-        <f aca="false">IF(C309="","",$C$5+A309-1)</f>
+        <f aca="false">IF(C309="","",WORKDAY($C$5-1,A309))</f>
         <v/>
       </c>
       <c r="C309" s="20" t="str">
@@ -12188,7 +12194,7 @@
         <v/>
       </c>
       <c r="B310" s="19" t="str">
-        <f aca="false">IF(C310="","",$C$5+A310-1)</f>
+        <f aca="false">IF(C310="","",WORKDAY($C$5-1,A310))</f>
         <v/>
       </c>
       <c r="C310" s="20" t="str">
@@ -12225,7 +12231,7 @@
         <v/>
       </c>
       <c r="B311" s="19" t="str">
-        <f aca="false">IF(C311="","",$C$5+A311-1)</f>
+        <f aca="false">IF(C311="","",WORKDAY($C$5-1,A311))</f>
         <v/>
       </c>
       <c r="C311" s="20" t="str">
@@ -12262,7 +12268,7 @@
         <v/>
       </c>
       <c r="B312" s="19" t="str">
-        <f aca="false">IF(C312="","",$C$5+A312-1)</f>
+        <f aca="false">IF(C312="","",WORKDAY($C$5-1,A312))</f>
         <v/>
       </c>
       <c r="C312" s="20" t="str">
@@ -12299,7 +12305,7 @@
         <v/>
       </c>
       <c r="B313" s="19" t="str">
-        <f aca="false">IF(C313="","",$C$5+A313-1)</f>
+        <f aca="false">IF(C313="","",WORKDAY($C$5-1,A313))</f>
         <v/>
       </c>
       <c r="C313" s="20" t="str">
@@ -12336,7 +12342,7 @@
         <v/>
       </c>
       <c r="B314" s="19" t="str">
-        <f aca="false">IF(C314="","",$C$5+A314-1)</f>
+        <f aca="false">IF(C314="","",WORKDAY($C$5-1,A314))</f>
         <v/>
       </c>
       <c r="C314" s="20" t="str">
@@ -12373,7 +12379,7 @@
         <v/>
       </c>
       <c r="B315" s="19" t="str">
-        <f aca="false">IF(C315="","",$C$5+A315-1)</f>
+        <f aca="false">IF(C315="","",WORKDAY($C$5-1,A315))</f>
         <v/>
       </c>
       <c r="C315" s="20" t="str">
@@ -12410,7 +12416,7 @@
         <v/>
       </c>
       <c r="B316" s="19" t="str">
-        <f aca="false">IF(C316="","",$C$5+A316-1)</f>
+        <f aca="false">IF(C316="","",WORKDAY($C$5-1,A316))</f>
         <v/>
       </c>
       <c r="C316" s="20" t="str">
@@ -12447,7 +12453,7 @@
         <v/>
       </c>
       <c r="B317" s="19" t="str">
-        <f aca="false">IF(C317="","",$C$5+A317-1)</f>
+        <f aca="false">IF(C317="","",WORKDAY($C$5-1,A317))</f>
         <v/>
       </c>
       <c r="C317" s="20" t="str">
@@ -12484,7 +12490,7 @@
         <v/>
       </c>
       <c r="B318" s="19" t="str">
-        <f aca="false">IF(C318="","",$C$5+A318-1)</f>
+        <f aca="false">IF(C318="","",WORKDAY($C$5-1,A318))</f>
         <v/>
       </c>
       <c r="C318" s="20" t="str">
@@ -12521,7 +12527,7 @@
         <v/>
       </c>
       <c r="B319" s="19" t="str">
-        <f aca="false">IF(C319="","",$C$5+A319-1)</f>
+        <f aca="false">IF(C319="","",WORKDAY($C$5-1,A319))</f>
         <v/>
       </c>
       <c r="C319" s="20" t="str">
@@ -12558,7 +12564,7 @@
         <v/>
       </c>
       <c r="B320" s="19" t="str">
-        <f aca="false">IF(C320="","",$C$5+A320-1)</f>
+        <f aca="false">IF(C320="","",WORKDAY($C$5-1,A320))</f>
         <v/>
       </c>
       <c r="C320" s="20" t="str">
@@ -12595,7 +12601,7 @@
         <v/>
       </c>
       <c r="B321" s="19" t="str">
-        <f aca="false">IF(C321="","",$C$5+A321-1)</f>
+        <f aca="false">IF(C321="","",WORKDAY($C$5-1,A321))</f>
         <v/>
       </c>
       <c r="C321" s="20" t="str">
@@ -12632,7 +12638,7 @@
         <v/>
       </c>
       <c r="B322" s="19" t="str">
-        <f aca="false">IF(C322="","",$C$5+A322-1)</f>
+        <f aca="false">IF(C322="","",WORKDAY($C$5-1,A322))</f>
         <v/>
       </c>
       <c r="C322" s="20" t="str">
@@ -12669,7 +12675,7 @@
         <v/>
       </c>
       <c r="B323" s="19" t="str">
-        <f aca="false">IF(C323="","",$C$5+A323-1)</f>
+        <f aca="false">IF(C323="","",WORKDAY($C$5-1,A323))</f>
         <v/>
       </c>
       <c r="C323" s="20" t="str">
@@ -12706,7 +12712,7 @@
         <v/>
       </c>
       <c r="B324" s="19" t="str">
-        <f aca="false">IF(C324="","",$C$5+A324-1)</f>
+        <f aca="false">IF(C324="","",WORKDAY($C$5-1,A324))</f>
         <v/>
       </c>
       <c r="C324" s="20" t="str">
@@ -12743,7 +12749,7 @@
         <v/>
       </c>
       <c r="B325" s="19" t="str">
-        <f aca="false">IF(C325="","",$C$5+A325-1)</f>
+        <f aca="false">IF(C325="","",WORKDAY($C$5-1,A325))</f>
         <v/>
       </c>
       <c r="C325" s="20" t="str">
@@ -12780,7 +12786,7 @@
         <v/>
       </c>
       <c r="B326" s="19" t="str">
-        <f aca="false">IF(C326="","",$C$5+A326-1)</f>
+        <f aca="false">IF(C326="","",WORKDAY($C$5-1,A326))</f>
         <v/>
       </c>
       <c r="C326" s="20" t="str">
@@ -12817,7 +12823,7 @@
         <v/>
       </c>
       <c r="B327" s="19" t="str">
-        <f aca="false">IF(C327="","",$C$5+A327-1)</f>
+        <f aca="false">IF(C327="","",WORKDAY($C$5-1,A327))</f>
         <v/>
       </c>
       <c r="C327" s="20" t="str">
@@ -12854,7 +12860,7 @@
         <v/>
       </c>
       <c r="B328" s="19" t="str">
-        <f aca="false">IF(C328="","",$C$5+A328-1)</f>
+        <f aca="false">IF(C328="","",WORKDAY($C$5-1,A328))</f>
         <v/>
       </c>
       <c r="C328" s="20" t="str">
@@ -12891,7 +12897,7 @@
         <v/>
       </c>
       <c r="B329" s="19" t="str">
-        <f aca="false">IF(C329="","",$C$5+A329-1)</f>
+        <f aca="false">IF(C329="","",WORKDAY($C$5-1,A329))</f>
         <v/>
       </c>
       <c r="C329" s="20" t="str">
@@ -12928,7 +12934,7 @@
         <v/>
       </c>
       <c r="B330" s="19" t="str">
-        <f aca="false">IF(C330="","",$C$5+A330-1)</f>
+        <f aca="false">IF(C330="","",WORKDAY($C$5-1,A330))</f>
         <v/>
       </c>
       <c r="C330" s="20" t="str">
@@ -12965,7 +12971,7 @@
         <v/>
       </c>
       <c r="B331" s="19" t="str">
-        <f aca="false">IF(C331="","",$C$5+A331-1)</f>
+        <f aca="false">IF(C331="","",WORKDAY($C$5-1,A331))</f>
         <v/>
       </c>
       <c r="C331" s="20" t="str">
@@ -13002,7 +13008,7 @@
         <v/>
       </c>
       <c r="B332" s="19" t="str">
-        <f aca="false">IF(C332="","",$C$5+A332-1)</f>
+        <f aca="false">IF(C332="","",WORKDAY($C$5-1,A332))</f>
         <v/>
       </c>
       <c r="C332" s="20" t="str">
@@ -13039,7 +13045,7 @@
         <v/>
       </c>
       <c r="B333" s="19" t="str">
-        <f aca="false">IF(C333="","",$C$5+A333-1)</f>
+        <f aca="false">IF(C333="","",WORKDAY($C$5-1,A333))</f>
         <v/>
       </c>
       <c r="C333" s="20" t="str">
@@ -13076,7 +13082,7 @@
         <v/>
       </c>
       <c r="B334" s="19" t="str">
-        <f aca="false">IF(C334="","",$C$5+A334-1)</f>
+        <f aca="false">IF(C334="","",WORKDAY($C$5-1,A334))</f>
         <v/>
       </c>
       <c r="C334" s="20" t="str">
@@ -13113,7 +13119,7 @@
         <v/>
       </c>
       <c r="B335" s="19" t="str">
-        <f aca="false">IF(C335="","",$C$5+A335-1)</f>
+        <f aca="false">IF(C335="","",WORKDAY($C$5-1,A335))</f>
         <v/>
       </c>
       <c r="C335" s="20" t="str">
@@ -13150,7 +13156,7 @@
         <v/>
       </c>
       <c r="B336" s="19" t="str">
-        <f aca="false">IF(C336="","",$C$5+A336-1)</f>
+        <f aca="false">IF(C336="","",WORKDAY($C$5-1,A336))</f>
         <v/>
       </c>
       <c r="C336" s="20" t="str">
@@ -13187,7 +13193,7 @@
         <v/>
       </c>
       <c r="B337" s="19" t="str">
-        <f aca="false">IF(C337="","",$C$5+A337-1)</f>
+        <f aca="false">IF(C337="","",WORKDAY($C$5-1,A337))</f>
         <v/>
       </c>
       <c r="C337" s="20" t="str">
@@ -13224,7 +13230,7 @@
         <v/>
       </c>
       <c r="B338" s="19" t="str">
-        <f aca="false">IF(C338="","",$C$5+A338-1)</f>
+        <f aca="false">IF(C338="","",WORKDAY($C$5-1,A338))</f>
         <v/>
       </c>
       <c r="C338" s="20" t="str">
@@ -13261,7 +13267,7 @@
         <v/>
       </c>
       <c r="B339" s="19" t="str">
-        <f aca="false">IF(C339="","",$C$5+A339-1)</f>
+        <f aca="false">IF(C339="","",WORKDAY($C$5-1,A339))</f>
         <v/>
       </c>
       <c r="C339" s="20" t="str">
@@ -13298,7 +13304,7 @@
         <v/>
       </c>
       <c r="B340" s="19" t="str">
-        <f aca="false">IF(C340="","",$C$5+A340-1)</f>
+        <f aca="false">IF(C340="","",WORKDAY($C$5-1,A340))</f>
         <v/>
       </c>
       <c r="C340" s="20" t="str">
@@ -13335,7 +13341,7 @@
         <v/>
       </c>
       <c r="B341" s="19" t="str">
-        <f aca="false">IF(C341="","",$C$5+A341-1)</f>
+        <f aca="false">IF(C341="","",WORKDAY($C$5-1,A341))</f>
         <v/>
       </c>
       <c r="C341" s="20" t="str">
@@ -13372,7 +13378,7 @@
         <v/>
       </c>
       <c r="B342" s="19" t="str">
-        <f aca="false">IF(C342="","",$C$5+A342-1)</f>
+        <f aca="false">IF(C342="","",WORKDAY($C$5-1,A342))</f>
         <v/>
       </c>
       <c r="C342" s="20" t="str">
@@ -13409,7 +13415,7 @@
         <v/>
       </c>
       <c r="B343" s="19" t="str">
-        <f aca="false">IF(C343="","",$C$5+A343-1)</f>
+        <f aca="false">IF(C343="","",WORKDAY($C$5-1,A343))</f>
         <v/>
       </c>
       <c r="C343" s="20" t="str">
@@ -13446,7 +13452,7 @@
         <v/>
       </c>
       <c r="B344" s="19" t="str">
-        <f aca="false">IF(C344="","",$C$5+A344-1)</f>
+        <f aca="false">IF(C344="","",WORKDAY($C$5-1,A344))</f>
         <v/>
       </c>
       <c r="C344" s="20" t="str">
@@ -13483,7 +13489,7 @@
         <v/>
       </c>
       <c r="B345" s="19" t="str">
-        <f aca="false">IF(C345="","",$C$5+A345-1)</f>
+        <f aca="false">IF(C345="","",WORKDAY($C$5-1,A345))</f>
         <v/>
       </c>
       <c r="C345" s="20" t="str">
@@ -13520,7 +13526,7 @@
         <v/>
       </c>
       <c r="B346" s="19" t="str">
-        <f aca="false">IF(C346="","",$C$5+A346-1)</f>
+        <f aca="false">IF(C346="","",WORKDAY($C$5-1,A346))</f>
         <v/>
       </c>
       <c r="C346" s="20" t="str">
@@ -13557,7 +13563,7 @@
         <v/>
       </c>
       <c r="B347" s="19" t="str">
-        <f aca="false">IF(C347="","",$C$5+A347-1)</f>
+        <f aca="false">IF(C347="","",WORKDAY($C$5-1,A347))</f>
         <v/>
       </c>
       <c r="C347" s="20" t="str">
@@ -13594,7 +13600,7 @@
         <v/>
       </c>
       <c r="B348" s="19" t="str">
-        <f aca="false">IF(C348="","",$C$5+A348-1)</f>
+        <f aca="false">IF(C348="","",WORKDAY($C$5-1,A348))</f>
         <v/>
       </c>
       <c r="C348" s="20" t="str">
@@ -13631,7 +13637,7 @@
         <v/>
       </c>
       <c r="B349" s="19" t="str">
-        <f aca="false">IF(C349="","",$C$5+A349-1)</f>
+        <f aca="false">IF(C349="","",WORKDAY($C$5-1,A349))</f>
         <v/>
       </c>
       <c r="C349" s="20" t="str">
@@ -13668,7 +13674,7 @@
         <v/>
       </c>
       <c r="B350" s="19" t="str">
-        <f aca="false">IF(C350="","",$C$5+A350-1)</f>
+        <f aca="false">IF(C350="","",WORKDAY($C$5-1,A350))</f>
         <v/>
       </c>
       <c r="C350" s="20" t="str">
@@ -13705,7 +13711,7 @@
         <v/>
       </c>
       <c r="B351" s="19" t="str">
-        <f aca="false">IF(C351="","",$C$5+A351-1)</f>
+        <f aca="false">IF(C351="","",WORKDAY($C$5-1,A351))</f>
         <v/>
       </c>
       <c r="C351" s="20" t="str">
@@ -13742,7 +13748,7 @@
         <v/>
       </c>
       <c r="B352" s="19" t="str">
-        <f aca="false">IF(C352="","",$C$5+A352-1)</f>
+        <f aca="false">IF(C352="","",WORKDAY($C$5-1,A352))</f>
         <v/>
       </c>
       <c r="C352" s="20" t="str">
@@ -13779,7 +13785,7 @@
         <v/>
       </c>
       <c r="B353" s="19" t="str">
-        <f aca="false">IF(C353="","",$C$5+A353-1)</f>
+        <f aca="false">IF(C353="","",WORKDAY($C$5-1,A353))</f>
         <v/>
       </c>
       <c r="C353" s="20" t="str">
@@ -13816,7 +13822,7 @@
         <v/>
       </c>
       <c r="B354" s="19" t="str">
-        <f aca="false">IF(C354="","",$C$5+A354-1)</f>
+        <f aca="false">IF(C354="","",WORKDAY($C$5-1,A354))</f>
         <v/>
       </c>
       <c r="C354" s="20" t="str">
@@ -13853,7 +13859,7 @@
         <v/>
       </c>
       <c r="B355" s="19" t="str">
-        <f aca="false">IF(C355="","",$C$5+A355-1)</f>
+        <f aca="false">IF(C355="","",WORKDAY($C$5-1,A355))</f>
         <v/>
       </c>
       <c r="C355" s="20" t="str">
@@ -13890,7 +13896,7 @@
         <v/>
       </c>
       <c r="B356" s="19" t="str">
-        <f aca="false">IF(C356="","",$C$5+A356-1)</f>
+        <f aca="false">IF(C356="","",WORKDAY($C$5-1,A356))</f>
         <v/>
       </c>
       <c r="C356" s="20" t="str">
@@ -13927,7 +13933,7 @@
         <v/>
       </c>
       <c r="B357" s="19" t="str">
-        <f aca="false">IF(C357="","",$C$5+A357-1)</f>
+        <f aca="false">IF(C357="","",WORKDAY($C$5-1,A357))</f>
         <v/>
       </c>
       <c r="C357" s="20" t="str">
@@ -13964,7 +13970,7 @@
         <v/>
       </c>
       <c r="B358" s="19" t="str">
-        <f aca="false">IF(C358="","",$C$5+A358-1)</f>
+        <f aca="false">IF(C358="","",WORKDAY($C$5-1,A358))</f>
         <v/>
       </c>
       <c r="C358" s="20" t="str">
@@ -14001,7 +14007,7 @@
         <v/>
       </c>
       <c r="B359" s="19" t="str">
-        <f aca="false">IF(C359="","",$C$5+A359-1)</f>
+        <f aca="false">IF(C359="","",WORKDAY($C$5-1,A359))</f>
         <v/>
       </c>
       <c r="C359" s="20" t="str">
@@ -14038,7 +14044,7 @@
         <v/>
       </c>
       <c r="B360" s="19" t="str">
-        <f aca="false">IF(C360="","",$C$5+A360-1)</f>
+        <f aca="false">IF(C360="","",WORKDAY($C$5-1,A360))</f>
         <v/>
       </c>
       <c r="C360" s="20" t="str">
@@ -14075,7 +14081,7 @@
         <v/>
       </c>
       <c r="B361" s="19" t="str">
-        <f aca="false">IF(C361="","",$C$5+A361-1)</f>
+        <f aca="false">IF(C361="","",WORKDAY($C$5-1,A361))</f>
         <v/>
       </c>
       <c r="C361" s="20" t="str">
@@ -14112,7 +14118,7 @@
         <v/>
       </c>
       <c r="B362" s="19" t="str">
-        <f aca="false">IF(C362="","",$C$5+A362-1)</f>
+        <f aca="false">IF(C362="","",WORKDAY($C$5-1,A362))</f>
         <v/>
       </c>
       <c r="C362" s="20" t="str">
@@ -14149,7 +14155,7 @@
         <v/>
       </c>
       <c r="B363" s="19" t="str">
-        <f aca="false">IF(C363="","",$C$5+A363-1)</f>
+        <f aca="false">IF(C363="","",WORKDAY($C$5-1,A363))</f>
         <v/>
       </c>
       <c r="C363" s="20" t="str">
@@ -14186,7 +14192,7 @@
         <v/>
       </c>
       <c r="B364" s="19" t="str">
-        <f aca="false">IF(C364="","",$C$5+A364-1)</f>
+        <f aca="false">IF(C364="","",WORKDAY($C$5-1,A364))</f>
         <v/>
       </c>
       <c r="C364" s="20" t="str">
@@ -14223,7 +14229,7 @@
         <v/>
       </c>
       <c r="B365" s="19" t="str">
-        <f aca="false">IF(C365="","",$C$5+A365-1)</f>
+        <f aca="false">IF(C365="","",WORKDAY($C$5-1,A365))</f>
         <v/>
       </c>
       <c r="C365" s="20" t="str">
@@ -14260,7 +14266,7 @@
         <v/>
       </c>
       <c r="B366" s="19" t="str">
-        <f aca="false">IF(C366="","",$C$5+A366-1)</f>
+        <f aca="false">IF(C366="","",WORKDAY($C$5-1,A366))</f>
         <v/>
       </c>
       <c r="C366" s="20" t="str">
@@ -14297,7 +14303,7 @@
         <v/>
       </c>
       <c r="B367" s="19" t="str">
-        <f aca="false">IF(C367="","",$C$5+A367-1)</f>
+        <f aca="false">IF(C367="","",WORKDAY($C$5-1,A367))</f>
         <v/>
       </c>
       <c r="C367" s="20" t="str">
@@ -14334,7 +14340,7 @@
         <v/>
       </c>
       <c r="B368" s="19" t="str">
-        <f aca="false">IF(C368="","",$C$5+A368-1)</f>
+        <f aca="false">IF(C368="","",WORKDAY($C$5-1,A368))</f>
         <v/>
       </c>
       <c r="C368" s="20" t="str">
@@ -14371,7 +14377,7 @@
         <v/>
       </c>
       <c r="B369" s="19" t="str">
-        <f aca="false">IF(C369="","",$C$5+A369-1)</f>
+        <f aca="false">IF(C369="","",WORKDAY($C$5-1,A369))</f>
         <v/>
       </c>
       <c r="C369" s="20" t="str">
@@ -14408,7 +14414,7 @@
         <v/>
       </c>
       <c r="B370" s="19" t="str">
-        <f aca="false">IF(C370="","",$C$5+A370-1)</f>
+        <f aca="false">IF(C370="","",WORKDAY($C$5-1,A370))</f>
         <v/>
       </c>
       <c r="C370" s="20" t="str">
@@ -14445,7 +14451,7 @@
         <v/>
       </c>
       <c r="B371" s="19" t="str">
-        <f aca="false">IF(C371="","",$C$5+A371-1)</f>
+        <f aca="false">IF(C371="","",WORKDAY($C$5-1,A371))</f>
         <v/>
       </c>
       <c r="C371" s="20" t="str">
@@ -14482,7 +14488,7 @@
         <v/>
       </c>
       <c r="B372" s="19" t="str">
-        <f aca="false">IF(C372="","",$C$5+A372-1)</f>
+        <f aca="false">IF(C372="","",WORKDAY($C$5-1,A372))</f>
         <v/>
       </c>
       <c r="C372" s="20" t="str">
@@ -14519,7 +14525,7 @@
         <v/>
       </c>
       <c r="B373" s="19" t="str">
-        <f aca="false">IF(C373="","",$C$5+A373-1)</f>
+        <f aca="false">IF(C373="","",WORKDAY($C$5-1,A373))</f>
         <v/>
       </c>
       <c r="C373" s="20" t="str">
@@ -14556,7 +14562,7 @@
         <v/>
       </c>
       <c r="B374" s="19" t="str">
-        <f aca="false">IF(C374="","",$C$5+A374-1)</f>
+        <f aca="false">IF(C374="","",WORKDAY($C$5-1,A374))</f>
         <v/>
       </c>
       <c r="C374" s="20" t="str">
@@ -14593,7 +14599,7 @@
         <v/>
       </c>
       <c r="B375" s="19" t="str">
-        <f aca="false">IF(C375="","",$C$5+A375-1)</f>
+        <f aca="false">IF(C375="","",WORKDAY($C$5-1,A375))</f>
         <v/>
       </c>
       <c r="C375" s="20" t="str">
@@ -14630,7 +14636,7 @@
         <v/>
       </c>
       <c r="B376" s="19" t="str">
-        <f aca="false">IF(C376="","",$C$5+A376-1)</f>
+        <f aca="false">IF(C376="","",WORKDAY($C$5-1,A376))</f>
         <v/>
       </c>
       <c r="C376" s="20" t="str">
@@ -14667,7 +14673,7 @@
         <v/>
       </c>
       <c r="B377" s="19" t="str">
-        <f aca="false">IF(C377="","",$C$5+A377-1)</f>
+        <f aca="false">IF(C377="","",WORKDAY($C$5-1,A377))</f>
         <v/>
       </c>
       <c r="C377" s="20" t="str">
@@ -14704,7 +14710,7 @@
         <v/>
       </c>
       <c r="B378" s="19" t="str">
-        <f aca="false">IF(C378="","",$C$5+A378-1)</f>
+        <f aca="false">IF(C378="","",WORKDAY($C$5-1,A378))</f>
         <v/>
       </c>
       <c r="C378" s="20" t="str">
@@ -14741,7 +14747,7 @@
         <v/>
       </c>
       <c r="B379" s="19" t="str">
-        <f aca="false">IF(C379="","",$C$5+A379-1)</f>
+        <f aca="false">IF(C379="","",WORKDAY($C$5-1,A379))</f>
         <v/>
       </c>
       <c r="C379" s="20" t="str">
@@ -14778,7 +14784,7 @@
         <v/>
       </c>
       <c r="B380" s="19" t="str">
-        <f aca="false">IF(C380="","",$C$5+A380-1)</f>
+        <f aca="false">IF(C380="","",WORKDAY($C$5-1,A380))</f>
         <v/>
       </c>
       <c r="C380" s="20" t="str">
@@ -14815,7 +14821,7 @@
         <v/>
       </c>
       <c r="B381" s="19" t="str">
-        <f aca="false">IF(C381="","",$C$5+A381-1)</f>
+        <f aca="false">IF(C381="","",WORKDAY($C$5-1,A381))</f>
         <v/>
       </c>
       <c r="C381" s="20" t="str">
@@ -14852,7 +14858,7 @@
         <v/>
       </c>
       <c r="B382" s="19" t="str">
-        <f aca="false">IF(C382="","",$C$5+A382-1)</f>
+        <f aca="false">IF(C382="","",WORKDAY($C$5-1,A382))</f>
         <v/>
       </c>
       <c r="C382" s="20" t="str">
@@ -14889,7 +14895,7 @@
         <v/>
       </c>
       <c r="B383" s="19" t="str">
-        <f aca="false">IF(C383="","",$C$5+A383-1)</f>
+        <f aca="false">IF(C383="","",WORKDAY($C$5-1,A383))</f>
         <v/>
       </c>
       <c r="C383" s="20" t="str">
@@ -14926,7 +14932,7 @@
         <v/>
       </c>
       <c r="B384" s="19" t="str">
-        <f aca="false">IF(C384="","",$C$5+A384-1)</f>
+        <f aca="false">IF(C384="","",WORKDAY($C$5-1,A384))</f>
         <v/>
       </c>
       <c r="C384" s="20" t="str">
@@ -14963,7 +14969,7 @@
         <v/>
       </c>
       <c r="B385" s="19" t="str">
-        <f aca="false">IF(C385="","",$C$5+A385-1)</f>
+        <f aca="false">IF(C385="","",WORKDAY($C$5-1,A385))</f>
         <v/>
       </c>
       <c r="C385" s="20" t="str">
@@ -15000,7 +15006,7 @@
         <v/>
       </c>
       <c r="B386" s="19" t="str">
-        <f aca="false">IF(C386="","",$C$5+A386-1)</f>
+        <f aca="false">IF(C386="","",WORKDAY($C$5-1,A386))</f>
         <v/>
       </c>
       <c r="C386" s="20" t="str">
@@ -15037,7 +15043,7 @@
         <v/>
       </c>
       <c r="B387" s="19" t="str">
-        <f aca="false">IF(C387="","",$C$5+A387-1)</f>
+        <f aca="false">IF(C387="","",WORKDAY($C$5-1,A387))</f>
         <v/>
       </c>
       <c r="C387" s="20" t="str">
@@ -15074,7 +15080,7 @@
         <v/>
       </c>
       <c r="B388" s="19" t="str">
-        <f aca="false">IF(C388="","",$C$5+A388-1)</f>
+        <f aca="false">IF(C388="","",WORKDAY($C$5-1,A388))</f>
         <v/>
       </c>
       <c r="C388" s="20" t="str">
@@ -15111,7 +15117,7 @@
         <v/>
       </c>
       <c r="B389" s="19" t="str">
-        <f aca="false">IF(C389="","",$C$5+A389-1)</f>
+        <f aca="false">IF(C389="","",WORKDAY($C$5-1,A389))</f>
         <v/>
       </c>
       <c r="C389" s="20" t="str">
@@ -15148,7 +15154,7 @@
         <v/>
       </c>
       <c r="B390" s="19" t="str">
-        <f aca="false">IF(C390="","",$C$5+A390-1)</f>
+        <f aca="false">IF(C390="","",WORKDAY($C$5-1,A390))</f>
         <v/>
       </c>
       <c r="C390" s="20" t="str">
@@ -15185,7 +15191,7 @@
         <v/>
       </c>
       <c r="B391" s="19" t="str">
-        <f aca="false">IF(C391="","",$C$5+A391-1)</f>
+        <f aca="false">IF(C391="","",WORKDAY($C$5-1,A391))</f>
         <v/>
       </c>
       <c r="C391" s="20" t="str">
@@ -15222,7 +15228,7 @@
         <v/>
       </c>
       <c r="B392" s="19" t="str">
-        <f aca="false">IF(C392="","",$C$5+A392-1)</f>
+        <f aca="false">IF(C392="","",WORKDAY($C$5-1,A392))</f>
         <v/>
       </c>
       <c r="C392" s="20" t="str">
@@ -15259,7 +15265,7 @@
         <v/>
       </c>
       <c r="B393" s="19" t="str">
-        <f aca="false">IF(C393="","",$C$5+A393-1)</f>
+        <f aca="false">IF(C393="","",WORKDAY($C$5-1,A393))</f>
         <v/>
       </c>
       <c r="C393" s="20" t="str">
@@ -15296,7 +15302,7 @@
         <v/>
       </c>
       <c r="B394" s="19" t="str">
-        <f aca="false">IF(C394="","",$C$5+A394-1)</f>
+        <f aca="false">IF(C394="","",WORKDAY($C$5-1,A394))</f>
         <v/>
       </c>
       <c r="C394" s="20" t="str">
@@ -15333,7 +15339,7 @@
         <v/>
       </c>
       <c r="B395" s="19" t="str">
-        <f aca="false">IF(C395="","",$C$5+A395-1)</f>
+        <f aca="false">IF(C395="","",WORKDAY($C$5-1,A395))</f>
         <v/>
       </c>
       <c r="C395" s="20" t="str">
@@ -15370,7 +15376,7 @@
         <v/>
       </c>
       <c r="B396" s="19" t="str">
-        <f aca="false">IF(C396="","",$C$5+A396-1)</f>
+        <f aca="false">IF(C396="","",WORKDAY($C$5-1,A396))</f>
         <v/>
       </c>
       <c r="C396" s="20" t="str">
@@ -15407,7 +15413,7 @@
         <v/>
       </c>
       <c r="B397" s="19" t="str">
-        <f aca="false">IF(C397="","",$C$5+A397-1)</f>
+        <f aca="false">IF(C397="","",WORKDAY($C$5-1,A397))</f>
         <v/>
       </c>
       <c r="C397" s="20" t="str">
@@ -15444,7 +15450,7 @@
         <v/>
       </c>
       <c r="B398" s="19" t="str">
-        <f aca="false">IF(C398="","",$C$5+A398-1)</f>
+        <f aca="false">IF(C398="","",WORKDAY($C$5-1,A398))</f>
         <v/>
       </c>
       <c r="C398" s="20" t="str">
@@ -15481,7 +15487,7 @@
         <v/>
       </c>
       <c r="B399" s="19" t="str">
-        <f aca="false">IF(C399="","",$C$5+A399-1)</f>
+        <f aca="false">IF(C399="","",WORKDAY($C$5-1,A399))</f>
         <v/>
       </c>
       <c r="C399" s="20" t="str">
@@ -15518,7 +15524,7 @@
         <v/>
       </c>
       <c r="B400" s="19" t="str">
-        <f aca="false">IF(C400="","",$C$5+A400-1)</f>
+        <f aca="false">IF(C400="","",WORKDAY($C$5-1,A400))</f>
         <v/>
       </c>
       <c r="C400" s="20" t="str">
@@ -15555,7 +15561,7 @@
         <v/>
       </c>
       <c r="B401" s="19" t="str">
-        <f aca="false">IF(C401="","",$C$5+A401-1)</f>
+        <f aca="false">IF(C401="","",WORKDAY($C$5-1,A401))</f>
         <v/>
       </c>
       <c r="C401" s="20" t="str">
@@ -15592,7 +15598,7 @@
         <v/>
       </c>
       <c r="B402" s="19" t="str">
-        <f aca="false">IF(C402="","",$C$5+A402-1)</f>
+        <f aca="false">IF(C402="","",WORKDAY($C$5-1,A402))</f>
         <v/>
       </c>
       <c r="C402" s="20" t="str">
@@ -15629,7 +15635,7 @@
         <v/>
       </c>
       <c r="B403" s="19" t="str">
-        <f aca="false">IF(C403="","",$C$5+A403-1)</f>
+        <f aca="false">IF(C403="","",WORKDAY($C$5-1,A403))</f>
         <v/>
       </c>
       <c r="C403" s="20" t="str">
@@ -15666,7 +15672,7 @@
         <v/>
       </c>
       <c r="B404" s="19" t="str">
-        <f aca="false">IF(C404="","",$C$5+A404-1)</f>
+        <f aca="false">IF(C404="","",WORKDAY($C$5-1,A404))</f>
         <v/>
       </c>
       <c r="C404" s="20" t="str">
@@ -15703,7 +15709,7 @@
         <v/>
       </c>
       <c r="B405" s="19" t="str">
-        <f aca="false">IF(C405="","",$C$5+A405-1)</f>
+        <f aca="false">IF(C405="","",WORKDAY($C$5-1,A405))</f>
         <v/>
       </c>
       <c r="C405" s="20" t="str">
@@ -15740,7 +15746,7 @@
         <v/>
       </c>
       <c r="B406" s="19" t="str">
-        <f aca="false">IF(C406="","",$C$5+A406-1)</f>
+        <f aca="false">IF(C406="","",WORKDAY($C$5-1,A406))</f>
         <v/>
       </c>
       <c r="C406" s="20" t="str">
@@ -15777,7 +15783,7 @@
         <v/>
       </c>
       <c r="B407" s="19" t="str">
-        <f aca="false">IF(C407="","",$C$5+A407-1)</f>
+        <f aca="false">IF(C407="","",WORKDAY($C$5-1,A407))</f>
         <v/>
       </c>
       <c r="C407" s="20" t="str">
@@ -15814,7 +15820,7 @@
         <v/>
       </c>
       <c r="B408" s="19" t="str">
-        <f aca="false">IF(C408="","",$C$5+A408-1)</f>
+        <f aca="false">IF(C408="","",WORKDAY($C$5-1,A408))</f>
         <v/>
       </c>
       <c r="C408" s="20" t="str">
@@ -15851,7 +15857,7 @@
         <v/>
       </c>
       <c r="B409" s="19" t="str">
-        <f aca="false">IF(C409="","",$C$5+A409-1)</f>
+        <f aca="false">IF(C409="","",WORKDAY($C$5-1,A409))</f>
         <v/>
       </c>
       <c r="C409" s="20" t="str">
@@ -15888,7 +15894,7 @@
         <v/>
       </c>
       <c r="B410" s="19" t="str">
-        <f aca="false">IF(C410="","",$C$5+A410-1)</f>
+        <f aca="false">IF(C410="","",WORKDAY($C$5-1,A410))</f>
         <v/>
       </c>
       <c r="C410" s="20" t="str">
@@ -15925,7 +15931,7 @@
         <v/>
       </c>
       <c r="B411" s="19" t="str">
-        <f aca="false">IF(C411="","",$C$5+A411-1)</f>
+        <f aca="false">IF(C411="","",WORKDAY($C$5-1,A411))</f>
         <v/>
       </c>
       <c r="C411" s="20" t="str">
@@ -15962,7 +15968,7 @@
         <v/>
       </c>
       <c r="B412" s="19" t="str">
-        <f aca="false">IF(C412="","",$C$5+A412-1)</f>
+        <f aca="false">IF(C412="","",WORKDAY($C$5-1,A412))</f>
         <v/>
       </c>
       <c r="C412" s="20" t="str">
@@ -15999,7 +16005,7 @@
         <v/>
       </c>
       <c r="B413" s="19" t="str">
-        <f aca="false">IF(C413="","",$C$5+A413-1)</f>
+        <f aca="false">IF(C413="","",WORKDAY($C$5-1,A413))</f>
         <v/>
       </c>
       <c r="C413" s="20" t="str">
@@ -16036,7 +16042,7 @@
         <v/>
       </c>
       <c r="B414" s="19" t="str">
-        <f aca="false">IF(C414="","",$C$5+A414-1)</f>
+        <f aca="false">IF(C414="","",WORKDAY($C$5-1,A414))</f>
         <v/>
       </c>
       <c r="C414" s="20" t="str">
@@ -16073,7 +16079,7 @@
         <v/>
       </c>
       <c r="B415" s="19" t="str">
-        <f aca="false">IF(C415="","",$C$5+A415-1)</f>
+        <f aca="false">IF(C415="","",WORKDAY($C$5-1,A415))</f>
         <v/>
       </c>
       <c r="C415" s="20" t="str">
@@ -16110,7 +16116,7 @@
         <v/>
       </c>
       <c r="B416" s="19" t="str">
-        <f aca="false">IF(C416="","",$C$5+A416-1)</f>
+        <f aca="false">IF(C416="","",WORKDAY($C$5-1,A416))</f>
         <v/>
       </c>
       <c r="C416" s="20" t="str">
@@ -16147,7 +16153,7 @@
         <v/>
       </c>
       <c r="B417" s="19" t="str">
-        <f aca="false">IF(C417="","",$C$5+A417-1)</f>
+        <f aca="false">IF(C417="","",WORKDAY($C$5-1,A417))</f>
         <v/>
       </c>
       <c r="C417" s="20" t="str">
@@ -16184,7 +16190,7 @@
         <v/>
       </c>
       <c r="B418" s="19" t="str">
-        <f aca="false">IF(C418="","",$C$5+A418-1)</f>
+        <f aca="false">IF(C418="","",WORKDAY($C$5-1,A418))</f>
         <v/>
       </c>
       <c r="C418" s="20" t="str">
@@ -16221,7 +16227,7 @@
         <v/>
       </c>
       <c r="B419" s="19" t="str">
-        <f aca="false">IF(C419="","",$C$5+A419-1)</f>
+        <f aca="false">IF(C419="","",WORKDAY($C$5-1,A419))</f>
         <v/>
       </c>
       <c r="C419" s="20" t="str">
@@ -16258,7 +16264,7 @@
         <v/>
       </c>
       <c r="B420" s="19" t="str">
-        <f aca="false">IF(C420="","",$C$5+A420-1)</f>
+        <f aca="false">IF(C420="","",WORKDAY($C$5-1,A420))</f>
         <v/>
       </c>
       <c r="C420" s="20" t="str">
@@ -16295,7 +16301,7 @@
         <v/>
       </c>
       <c r="B421" s="19" t="str">
-        <f aca="false">IF(C421="","",$C$5+A421-1)</f>
+        <f aca="false">IF(C421="","",WORKDAY($C$5-1,A421))</f>
         <v/>
       </c>
       <c r="C421" s="20" t="str">
@@ -16332,7 +16338,7 @@
         <v/>
       </c>
       <c r="B422" s="19" t="str">
-        <f aca="false">IF(C422="","",$C$5+A422-1)</f>
+        <f aca="false">IF(C422="","",WORKDAY($C$5-1,A422))</f>
         <v/>
       </c>
       <c r="C422" s="20" t="str">
@@ -16369,7 +16375,7 @@
         <v/>
       </c>
       <c r="B423" s="19" t="str">
-        <f aca="false">IF(C423="","",$C$5+A423-1)</f>
+        <f aca="false">IF(C423="","",WORKDAY($C$5-1,A423))</f>
         <v/>
       </c>
       <c r="C423" s="20" t="str">
@@ -16406,7 +16412,7 @@
         <v/>
       </c>
       <c r="B424" s="19" t="str">
-        <f aca="false">IF(C424="","",$C$5+A424-1)</f>
+        <f aca="false">IF(C424="","",WORKDAY($C$5-1,A424))</f>
         <v/>
       </c>
       <c r="C424" s="20" t="str">
@@ -16443,7 +16449,7 @@
         <v/>
       </c>
       <c r="B425" s="19" t="str">
-        <f aca="false">IF(C425="","",$C$5+A425-1)</f>
+        <f aca="false">IF(C425="","",WORKDAY($C$5-1,A425))</f>
         <v/>
       </c>
       <c r="C425" s="20" t="str">
@@ -16480,7 +16486,7 @@
         <v/>
       </c>
       <c r="B426" s="19" t="str">
-        <f aca="false">IF(C426="","",$C$5+A426-1)</f>
+        <f aca="false">IF(C426="","",WORKDAY($C$5-1,A426))</f>
         <v/>
       </c>
       <c r="C426" s="20" t="str">
@@ -16517,7 +16523,7 @@
         <v/>
       </c>
       <c r="B427" s="19" t="str">
-        <f aca="false">IF(C427="","",$C$5+A427-1)</f>
+        <f aca="false">IF(C427="","",WORKDAY($C$5-1,A427))</f>
         <v/>
       </c>
       <c r="C427" s="20" t="str">
@@ -16554,7 +16560,7 @@
         <v/>
       </c>
       <c r="B428" s="19" t="str">
-        <f aca="false">IF(C428="","",$C$5+A428-1)</f>
+        <f aca="false">IF(C428="","",WORKDAY($C$5-1,A428))</f>
         <v/>
       </c>
       <c r="C428" s="20" t="str">
@@ -16591,7 +16597,7 @@
         <v/>
       </c>
       <c r="B429" s="19" t="str">
-        <f aca="false">IF(C429="","",$C$5+A429-1)</f>
+        <f aca="false">IF(C429="","",WORKDAY($C$5-1,A429))</f>
         <v/>
       </c>
       <c r="C429" s="20" t="str">
@@ -16628,7 +16634,7 @@
         <v/>
       </c>
       <c r="B430" s="19" t="str">
-        <f aca="false">IF(C430="","",$C$5+A430-1)</f>
+        <f aca="false">IF(C430="","",WORKDAY($C$5-1,A430))</f>
         <v/>
       </c>
       <c r="C430" s="20" t="str">
@@ -16665,7 +16671,7 @@
         <v/>
       </c>
       <c r="B431" s="19" t="str">
-        <f aca="false">IF(C431="","",$C$5+A431-1)</f>
+        <f aca="false">IF(C431="","",WORKDAY($C$5-1,A431))</f>
         <v/>
       </c>
       <c r="C431" s="20" t="str">
@@ -16702,7 +16708,7 @@
         <v/>
       </c>
       <c r="B432" s="19" t="str">
-        <f aca="false">IF(C432="","",$C$5+A432-1)</f>
+        <f aca="false">IF(C432="","",WORKDAY($C$5-1,A432))</f>
         <v/>
       </c>
       <c r="C432" s="20" t="str">
@@ -16739,7 +16745,7 @@
         <v/>
       </c>
       <c r="B433" s="19" t="str">
-        <f aca="false">IF(C433="","",$C$5+A433-1)</f>
+        <f aca="false">IF(C433="","",WORKDAY($C$5-1,A433))</f>
         <v/>
       </c>
       <c r="C433" s="20" t="str">
@@ -16776,7 +16782,7 @@
         <v/>
       </c>
       <c r="B434" s="19" t="str">
-        <f aca="false">IF(C434="","",$C$5+A434-1)</f>
+        <f aca="false">IF(C434="","",WORKDAY($C$5-1,A434))</f>
         <v/>
       </c>
       <c r="C434" s="20" t="str">
@@ -16813,7 +16819,7 @@
         <v/>
       </c>
       <c r="B435" s="19" t="str">
-        <f aca="false">IF(C435="","",$C$5+A435-1)</f>
+        <f aca="false">IF(C435="","",WORKDAY($C$5-1,A435))</f>
         <v/>
       </c>
       <c r="C435" s="20" t="str">
@@ -16850,7 +16856,7 @@
         <v/>
       </c>
       <c r="B436" s="19" t="str">
-        <f aca="false">IF(C436="","",$C$5+A436-1)</f>
+        <f aca="false">IF(C436="","",WORKDAY($C$5-1,A436))</f>
         <v/>
       </c>
       <c r="C436" s="20" t="str">
@@ -16887,7 +16893,7 @@
         <v/>
       </c>
       <c r="B437" s="19" t="str">
-        <f aca="false">IF(C437="","",$C$5+A437-1)</f>
+        <f aca="false">IF(C437="","",WORKDAY($C$5-1,A437))</f>
         <v/>
       </c>
       <c r="C437" s="20" t="str">
@@ -16924,7 +16930,7 @@
         <v/>
       </c>
       <c r="B438" s="19" t="str">
-        <f aca="false">IF(C438="","",$C$5+A438-1)</f>
+        <f aca="false">IF(C438="","",WORKDAY($C$5-1,A438))</f>
         <v/>
       </c>
       <c r="C438" s="20" t="str">
@@ -16961,7 +16967,7 @@
         <v/>
       </c>
       <c r="B439" s="19" t="str">
-        <f aca="false">IF(C439="","",$C$5+A439-1)</f>
+        <f aca="false">IF(C439="","",WORKDAY($C$5-1,A439))</f>
         <v/>
       </c>
       <c r="C439" s="20" t="str">
@@ -16998,7 +17004,7 @@
         <v/>
       </c>
       <c r="B440" s="19" t="str">
-        <f aca="false">IF(C440="","",$C$5+A440-1)</f>
+        <f aca="false">IF(C440="","",WORKDAY($C$5-1,A440))</f>
         <v/>
       </c>
       <c r="C440" s="20" t="str">
@@ -17035,7 +17041,7 @@
         <v/>
       </c>
       <c r="B441" s="19" t="str">
-        <f aca="false">IF(C441="","",$C$5+A441-1)</f>
+        <f aca="false">IF(C441="","",WORKDAY($C$5-1,A441))</f>
         <v/>
       </c>
       <c r="C441" s="20" t="str">
@@ -17072,7 +17078,7 @@
         <v/>
       </c>
       <c r="B442" s="19" t="str">
-        <f aca="false">IF(C442="","",$C$5+A442-1)</f>
+        <f aca="false">IF(C442="","",WORKDAY($C$5-1,A442))</f>
         <v/>
       </c>
       <c r="C442" s="20" t="str">
@@ -17109,7 +17115,7 @@
         <v/>
       </c>
       <c r="B443" s="19" t="str">
-        <f aca="false">IF(C443="","",$C$5+A443-1)</f>
+        <f aca="false">IF(C443="","",WORKDAY($C$5-1,A443))</f>
         <v/>
       </c>
       <c r="C443" s="20" t="str">
@@ -17146,7 +17152,7 @@
         <v/>
       </c>
       <c r="B444" s="19" t="str">
-        <f aca="false">IF(C444="","",$C$5+A444-1)</f>
+        <f aca="false">IF(C444="","",WORKDAY($C$5-1,A444))</f>
         <v/>
       </c>
       <c r="C444" s="20" t="str">
@@ -17183,7 +17189,7 @@
         <v/>
       </c>
       <c r="B445" s="19" t="str">
-        <f aca="false">IF(C445="","",$C$5+A445-1)</f>
+        <f aca="false">IF(C445="","",WORKDAY($C$5-1,A445))</f>
         <v/>
       </c>
       <c r="C445" s="20" t="str">
@@ -17220,7 +17226,7 @@
         <v/>
       </c>
       <c r="B446" s="19" t="str">
-        <f aca="false">IF(C446="","",$C$5+A446-1)</f>
+        <f aca="false">IF(C446="","",WORKDAY($C$5-1,A446))</f>
         <v/>
       </c>
       <c r="C446" s="20" t="str">
@@ -17257,7 +17263,7 @@
         <v/>
       </c>
       <c r="B447" s="19" t="str">
-        <f aca="false">IF(C447="","",$C$5+A447-1)</f>
+        <f aca="false">IF(C447="","",WORKDAY($C$5-1,A447))</f>
         <v/>
       </c>
       <c r="C447" s="20" t="str">
@@ -17294,7 +17300,7 @@
         <v/>
       </c>
       <c r="B448" s="19" t="str">
-        <f aca="false">IF(C448="","",$C$5+A448-1)</f>
+        <f aca="false">IF(C448="","",WORKDAY($C$5-1,A448))</f>
         <v/>
       </c>
       <c r="C448" s="20" t="str">
@@ -17331,7 +17337,7 @@
         <v/>
       </c>
       <c r="B449" s="19" t="str">
-        <f aca="false">IF(C449="","",$C$5+A449-1)</f>
+        <f aca="false">IF(C449="","",WORKDAY($C$5-1,A449))</f>
         <v/>
       </c>
       <c r="C449" s="20" t="str">
@@ -17368,7 +17374,7 @@
         <v/>
       </c>
       <c r="B450" s="19" t="str">
-        <f aca="false">IF(C450="","",$C$5+A450-1)</f>
+        <f aca="false">IF(C450="","",WORKDAY($C$5-1,A450))</f>
         <v/>
       </c>
       <c r="C450" s="20" t="str">
@@ -17405,7 +17411,7 @@
         <v/>
       </c>
       <c r="B451" s="19" t="str">
-        <f aca="false">IF(C451="","",$C$5+A451-1)</f>
+        <f aca="false">IF(C451="","",WORKDAY($C$5-1,A451))</f>
         <v/>
       </c>
       <c r="C451" s="20" t="str">
@@ -17442,7 +17448,7 @@
         <v/>
       </c>
       <c r="B452" s="19" t="str">
-        <f aca="false">IF(C452="","",$C$5+A452-1)</f>
+        <f aca="false">IF(C452="","",WORKDAY($C$5-1,A452))</f>
         <v/>
       </c>
       <c r="C452" s="20" t="str">
@@ -17479,7 +17485,7 @@
         <v/>
       </c>
       <c r="B453" s="19" t="str">
-        <f aca="false">IF(C453="","",$C$5+A453-1)</f>
+        <f aca="false">IF(C453="","",WORKDAY($C$5-1,A453))</f>
         <v/>
       </c>
       <c r="C453" s="20" t="str">
@@ -17516,7 +17522,7 @@
         <v/>
       </c>
       <c r="B454" s="19" t="str">
-        <f aca="false">IF(C454="","",$C$5+A454-1)</f>
+        <f aca="false">IF(C454="","",WORKDAY($C$5-1,A454))</f>
         <v/>
       </c>
       <c r="C454" s="20" t="str">
@@ -17553,7 +17559,7 @@
         <v/>
       </c>
       <c r="B455" s="19" t="str">
-        <f aca="false">IF(C455="","",$C$5+A455-1)</f>
+        <f aca="false">IF(C455="","",WORKDAY($C$5-1,A455))</f>
         <v/>
       </c>
       <c r="C455" s="20" t="str">
@@ -17590,7 +17596,7 @@
         <v/>
       </c>
       <c r="B456" s="19" t="str">
-        <f aca="false">IF(C456="","",$C$5+A456-1)</f>
+        <f aca="false">IF(C456="","",WORKDAY($C$5-1,A456))</f>
         <v/>
       </c>
       <c r="C456" s="20" t="str">
@@ -17627,7 +17633,7 @@
         <v/>
       </c>
       <c r="B457" s="19" t="str">
-        <f aca="false">IF(C457="","",$C$5+A457-1)</f>
+        <f aca="false">IF(C457="","",WORKDAY($C$5-1,A457))</f>
         <v/>
       </c>
       <c r="C457" s="20" t="str">
@@ -17664,7 +17670,7 @@
         <v/>
       </c>
       <c r="B458" s="19" t="str">
-        <f aca="false">IF(C458="","",$C$5+A458-1)</f>
+        <f aca="false">IF(C458="","",WORKDAY($C$5-1,A458))</f>
         <v/>
       </c>
       <c r="C458" s="20" t="str">
@@ -17701,7 +17707,7 @@
         <v/>
       </c>
       <c r="B459" s="19" t="str">
-        <f aca="false">IF(C459="","",$C$5+A459-1)</f>
+        <f aca="false">IF(C459="","",WORKDAY($C$5-1,A459))</f>
         <v/>
       </c>
       <c r="C459" s="20" t="str">
@@ -17738,7 +17744,7 @@
         <v/>
       </c>
       <c r="B460" s="19" t="str">
-        <f aca="false">IF(C460="","",$C$5+A460-1)</f>
+        <f aca="false">IF(C460="","",WORKDAY($C$5-1,A460))</f>
         <v/>
       </c>
       <c r="C460" s="20" t="str">
@@ -17775,7 +17781,7 @@
         <v/>
       </c>
       <c r="B461" s="19" t="str">
-        <f aca="false">IF(C461="","",$C$5+A461-1)</f>
+        <f aca="false">IF(C461="","",WORKDAY($C$5-1,A461))</f>
         <v/>
       </c>
       <c r="C461" s="20" t="str">
@@ -17812,7 +17818,7 @@
         <v/>
       </c>
       <c r="B462" s="19" t="str">
-        <f aca="false">IF(C462="","",$C$5+A462-1)</f>
+        <f aca="false">IF(C462="","",WORKDAY($C$5-1,A462))</f>
         <v/>
       </c>
       <c r="C462" s="20" t="str">
@@ -17849,7 +17855,7 @@
         <v/>
       </c>
       <c r="B463" s="19" t="str">
-        <f aca="false">IF(C463="","",$C$5+A463-1)</f>
+        <f aca="false">IF(C463="","",WORKDAY($C$5-1,A463))</f>
         <v/>
       </c>
       <c r="C463" s="20" t="str">
@@ -17886,7 +17892,7 @@
         <v/>
       </c>
       <c r="B464" s="19" t="str">
-        <f aca="false">IF(C464="","",$C$5+A464-1)</f>
+        <f aca="false">IF(C464="","",WORKDAY($C$5-1,A464))</f>
         <v/>
       </c>
       <c r="C464" s="20" t="str">
@@ -17923,7 +17929,7 @@
         <v/>
       </c>
       <c r="B465" s="19" t="str">
-        <f aca="false">IF(C465="","",$C$5+A465-1)</f>
+        <f aca="false">IF(C465="","",WORKDAY($C$5-1,A465))</f>
         <v/>
       </c>
       <c r="C465" s="20" t="str">
@@ -17960,7 +17966,7 @@
         <v/>
       </c>
       <c r="B466" s="19" t="str">
-        <f aca="false">IF(C466="","",$C$5+A466-1)</f>
+        <f aca="false">IF(C466="","",WORKDAY($C$5-1,A466))</f>
         <v/>
       </c>
       <c r="C466" s="20" t="str">
@@ -17997,7 +18003,7 @@
         <v/>
       </c>
       <c r="B467" s="19" t="str">
-        <f aca="false">IF(C467="","",$C$5+A467-1)</f>
+        <f aca="false">IF(C467="","",WORKDAY($C$5-1,A467))</f>
         <v/>
       </c>
       <c r="C467" s="20" t="str">
@@ -18034,7 +18040,7 @@
         <v/>
       </c>
       <c r="B468" s="19" t="str">
-        <f aca="false">IF(C468="","",$C$5+A468-1)</f>
+        <f aca="false">IF(C468="","",WORKDAY($C$5-1,A468))</f>
         <v/>
       </c>
       <c r="C468" s="20" t="str">
@@ -18071,7 +18077,7 @@
         <v/>
       </c>
       <c r="B469" s="19" t="str">
-        <f aca="false">IF(C469="","",$C$5+A469-1)</f>
+        <f aca="false">IF(C469="","",WORKDAY($C$5-1,A469))</f>
         <v/>
       </c>
       <c r="C469" s="20" t="str">
@@ -18108,7 +18114,7 @@
         <v/>
       </c>
       <c r="B470" s="19" t="str">
-        <f aca="false">IF(C470="","",$C$5+A470-1)</f>
+        <f aca="false">IF(C470="","",WORKDAY($C$5-1,A470))</f>
         <v/>
       </c>
       <c r="C470" s="20" t="str">
@@ -18145,7 +18151,7 @@
         <v/>
       </c>
       <c r="B471" s="19" t="str">
-        <f aca="false">IF(C471="","",$C$5+A471-1)</f>
+        <f aca="false">IF(C471="","",WORKDAY($C$5-1,A471))</f>
         <v/>
       </c>
       <c r="C471" s="20" t="str">
@@ -18182,7 +18188,7 @@
         <v/>
       </c>
       <c r="B472" s="19" t="str">
-        <f aca="false">IF(C472="","",$C$5+A472-1)</f>
+        <f aca="false">IF(C472="","",WORKDAY($C$5-1,A472))</f>
         <v/>
       </c>
       <c r="C472" s="20" t="str">
@@ -18219,7 +18225,7 @@
         <v/>
       </c>
       <c r="B473" s="19" t="str">
-        <f aca="false">IF(C473="","",$C$5+A473-1)</f>
+        <f aca="false">IF(C473="","",WORKDAY($C$5-1,A473))</f>
         <v/>
       </c>
       <c r="C473" s="20" t="str">
@@ -18256,7 +18262,7 @@
         <v/>
       </c>
       <c r="B474" s="19" t="str">
-        <f aca="false">IF(C474="","",$C$5+A474-1)</f>
+        <f aca="false">IF(C474="","",WORKDAY($C$5-1,A474))</f>
         <v/>
       </c>
       <c r="C474" s="20" t="str">
@@ -18293,7 +18299,7 @@
         <v/>
       </c>
       <c r="B475" s="19" t="str">
-        <f aca="false">IF(C475="","",$C$5+A475-1)</f>
+        <f aca="false">IF(C475="","",WORKDAY($C$5-1,A475))</f>
         <v/>
       </c>
       <c r="C475" s="20" t="str">
@@ -18330,7 +18336,7 @@
         <v/>
       </c>
       <c r="B476" s="19" t="str">
-        <f aca="false">IF(C476="","",$C$5+A476-1)</f>
+        <f aca="false">IF(C476="","",WORKDAY($C$5-1,A476))</f>
         <v/>
       </c>
       <c r="C476" s="20" t="str">
@@ -18367,7 +18373,7 @@
         <v/>
       </c>
       <c r="B477" s="19" t="str">
-        <f aca="false">IF(C477="","",$C$5+A477-1)</f>
+        <f aca="false">IF(C477="","",WORKDAY($C$5-1,A477))</f>
         <v/>
       </c>
       <c r="C477" s="20" t="str">
@@ -18404,7 +18410,7 @@
         <v/>
       </c>
       <c r="B478" s="19" t="str">
-        <f aca="false">IF(C478="","",$C$5+A478-1)</f>
+        <f aca="false">IF(C478="","",WORKDAY($C$5-1,A478))</f>
         <v/>
       </c>
       <c r="C478" s="20" t="str">
@@ -18441,7 +18447,7 @@
         <v/>
       </c>
       <c r="B479" s="19" t="str">
-        <f aca="false">IF(C479="","",$C$5+A479-1)</f>
+        <f aca="false">IF(C479="","",WORKDAY($C$5-1,A479))</f>
         <v/>
       </c>
       <c r="C479" s="20" t="str">
@@ -18478,7 +18484,7 @@
         <v/>
       </c>
       <c r="B480" s="19" t="str">
-        <f aca="false">IF(C480="","",$C$5+A480-1)</f>
+        <f aca="false">IF(C480="","",WORKDAY($C$5-1,A480))</f>
         <v/>
       </c>
       <c r="C480" s="20" t="str">
@@ -18515,7 +18521,7 @@
         <v/>
       </c>
       <c r="B481" s="19" t="str">
-        <f aca="false">IF(C481="","",$C$5+A481-1)</f>
+        <f aca="false">IF(C481="","",WORKDAY($C$5-1,A481))</f>
         <v/>
       </c>
       <c r="C481" s="20" t="str">
@@ -18552,7 +18558,7 @@
         <v/>
       </c>
       <c r="B482" s="19" t="str">
-        <f aca="false">IF(C482="","",$C$5+A482-1)</f>
+        <f aca="false">IF(C482="","",WORKDAY($C$5-1,A482))</f>
         <v/>
       </c>
       <c r="C482" s="20" t="str">
@@ -18589,7 +18595,7 @@
         <v/>
       </c>
       <c r="B483" s="19" t="str">
-        <f aca="false">IF(C483="","",$C$5+A483-1)</f>
+        <f aca="false">IF(C483="","",WORKDAY($C$5-1,A483))</f>
         <v/>
       </c>
       <c r="C483" s="20" t="str">
@@ -18626,7 +18632,7 @@
         <v/>
       </c>
       <c r="B484" s="19" t="str">
-        <f aca="false">IF(C484="","",$C$5+A484-1)</f>
+        <f aca="false">IF(C484="","",WORKDAY($C$5-1,A484))</f>
         <v/>
       </c>
       <c r="C484" s="20" t="str">
@@ -18663,7 +18669,7 @@
         <v/>
       </c>
       <c r="B485" s="19" t="str">
-        <f aca="false">IF(C485="","",$C$5+A485-1)</f>
+        <f aca="false">IF(C485="","",WORKDAY($C$5-1,A485))</f>
         <v/>
       </c>
       <c r="C485" s="20" t="str">
@@ -18700,7 +18706,7 @@
         <v/>
       </c>
       <c r="B486" s="19" t="str">
-        <f aca="false">IF(C486="","",$C$5+A486-1)</f>
+        <f aca="false">IF(C486="","",WORKDAY($C$5-1,A486))</f>
         <v/>
       </c>
       <c r="C486" s="20" t="str">
@@ -18737,7 +18743,7 @@
         <v/>
       </c>
       <c r="B487" s="19" t="str">
-        <f aca="false">IF(C487="","",$C$5+A487-1)</f>
+        <f aca="false">IF(C487="","",WORKDAY($C$5-1,A487))</f>
         <v/>
       </c>
       <c r="C487" s="20" t="str">
@@ -18774,7 +18780,7 @@
         <v/>
       </c>
       <c r="B488" s="19" t="str">
-        <f aca="false">IF(C488="","",$C$5+A488-1)</f>
+        <f aca="false">IF(C488="","",WORKDAY($C$5-1,A488))</f>
         <v/>
       </c>
       <c r="C488" s="20" t="str">
@@ -18811,7 +18817,7 @@
         <v/>
       </c>
       <c r="B489" s="19" t="str">
-        <f aca="false">IF(C489="","",$C$5+A489-1)</f>
+        <f aca="false">IF(C489="","",WORKDAY($C$5-1,A489))</f>
         <v/>
       </c>
       <c r="C489" s="20" t="str">
@@ -18848,7 +18854,7 @@
         <v/>
       </c>
       <c r="B490" s="19" t="str">
-        <f aca="false">IF(C490="","",$C$5+A490-1)</f>
+        <f aca="false">IF(C490="","",WORKDAY($C$5-1,A490))</f>
         <v/>
       </c>
       <c r="C490" s="20" t="str">
@@ -18885,7 +18891,7 @@
         <v/>
       </c>
       <c r="B491" s="19" t="str">
-        <f aca="false">IF(C491="","",$C$5+A491-1)</f>
+        <f aca="false">IF(C491="","",WORKDAY($C$5-1,A491))</f>
         <v/>
       </c>
       <c r="C491" s="20" t="str">
@@ -18922,7 +18928,7 @@
         <v/>
       </c>
       <c r="B492" s="19" t="str">
-        <f aca="false">IF(C492="","",$C$5+A492-1)</f>
+        <f aca="false">IF(C492="","",WORKDAY($C$5-1,A492))</f>
         <v/>
       </c>
       <c r="C492" s="20" t="str">
@@ -18959,7 +18965,7 @@
         <v/>
       </c>
       <c r="B493" s="19" t="str">
-        <f aca="false">IF(C493="","",$C$5+A493-1)</f>
+        <f aca="false">IF(C493="","",WORKDAY($C$5-1,A493))</f>
         <v/>
       </c>
       <c r="C493" s="20" t="str">
@@ -18996,7 +19002,7 @@
         <v/>
       </c>
       <c r="B494" s="19" t="str">
-        <f aca="false">IF(C494="","",$C$5+A494-1)</f>
+        <f aca="false">IF(C494="","",WORKDAY($C$5-1,A494))</f>
         <v/>
       </c>
       <c r="C494" s="20" t="str">
@@ -19033,7 +19039,7 @@
         <v/>
       </c>
       <c r="B495" s="19" t="str">
-        <f aca="false">IF(C495="","",$C$5+A495-1)</f>
+        <f aca="false">IF(C495="","",WORKDAY($C$5-1,A495))</f>
         <v/>
       </c>
       <c r="C495" s="20" t="str">
@@ -19070,7 +19076,7 @@
         <v/>
       </c>
       <c r="B496" s="19" t="str">
-        <f aca="false">IF(C496="","",$C$5+A496-1)</f>
+        <f aca="false">IF(C496="","",WORKDAY($C$5-1,A496))</f>
         <v/>
       </c>
       <c r="C496" s="20" t="str">
@@ -19107,7 +19113,7 @@
         <v/>
       </c>
       <c r="B497" s="19" t="str">
-        <f aca="false">IF(C497="","",$C$5+A497-1)</f>
+        <f aca="false">IF(C497="","",WORKDAY($C$5-1,A497))</f>
         <v/>
       </c>
       <c r="C497" s="20" t="str">
@@ -19144,7 +19150,7 @@
         <v/>
       </c>
       <c r="B498" s="19" t="str">
-        <f aca="false">IF(C498="","",$C$5+A498-1)</f>
+        <f aca="false">IF(C498="","",WORKDAY($C$5-1,A498))</f>
         <v/>
       </c>
       <c r="C498" s="20" t="str">
@@ -19181,7 +19187,7 @@
         <v/>
       </c>
       <c r="B499" s="19" t="str">
-        <f aca="false">IF(C499="","",$C$5+A499-1)</f>
+        <f aca="false">IF(C499="","",WORKDAY($C$5-1,A499))</f>
         <v/>
       </c>
       <c r="C499" s="20" t="str">
@@ -19218,7 +19224,7 @@
         <v/>
       </c>
       <c r="B500" s="19" t="str">
-        <f aca="false">IF(C500="","",$C$5+A500-1)</f>
+        <f aca="false">IF(C500="","",WORKDAY($C$5-1,A500))</f>
         <v/>
       </c>
       <c r="C500" s="20" t="str">
@@ -19255,7 +19261,7 @@
         <v/>
       </c>
       <c r="B501" s="19" t="str">
-        <f aca="false">IF(C501="","",$C$5+A501-1)</f>
+        <f aca="false">IF(C501="","",WORKDAY($C$5-1,A501))</f>
         <v/>
       </c>
       <c r="C501" s="20" t="str">
@@ -19292,7 +19298,7 @@
         <v/>
       </c>
       <c r="B502" s="19" t="str">
-        <f aca="false">IF(C502="","",$C$5+A502-1)</f>
+        <f aca="false">IF(C502="","",WORKDAY($C$5-1,A502))</f>
         <v/>
       </c>
       <c r="C502" s="20" t="str">
@@ -19329,7 +19335,7 @@
         <v/>
       </c>
       <c r="B503" s="19" t="str">
-        <f aca="false">IF(C503="","",$C$5+A503-1)</f>
+        <f aca="false">IF(C503="","",WORKDAY($C$5-1,A503))</f>
         <v/>
       </c>
       <c r="C503" s="20" t="str">
@@ -19366,7 +19372,7 @@
         <v/>
       </c>
       <c r="B504" s="19" t="str">
-        <f aca="false">IF(C504="","",$C$5+A504-1)</f>
+        <f aca="false">IF(C504="","",WORKDAY($C$5-1,A504))</f>
         <v/>
       </c>
       <c r="C504" s="20" t="str">
@@ -19403,7 +19409,7 @@
         <v/>
       </c>
       <c r="B505" s="19" t="str">
-        <f aca="false">IF(C505="","",$C$5+A505-1)</f>
+        <f aca="false">IF(C505="","",WORKDAY($C$5-1,A505))</f>
         <v/>
       </c>
       <c r="C505" s="20" t="str">
@@ -19440,7 +19446,7 @@
         <v/>
       </c>
       <c r="B506" s="19" t="str">
-        <f aca="false">IF(C506="","",$C$5+A506-1)</f>
+        <f aca="false">IF(C506="","",WORKDAY($C$5-1,A506))</f>
         <v/>
       </c>
       <c r="C506" s="20" t="str">
@@ -19477,7 +19483,7 @@
         <v/>
       </c>
       <c r="B507" s="19" t="str">
-        <f aca="false">IF(C507="","",$C$5+A507-1)</f>
+        <f aca="false">IF(C507="","",WORKDAY($C$5-1,A507))</f>
         <v/>
       </c>
       <c r="C507" s="20" t="str">
@@ -19514,7 +19520,7 @@
         <v/>
       </c>
       <c r="B508" s="19" t="str">
-        <f aca="false">IF(C508="","",$C$5+A508-1)</f>
+        <f aca="false">IF(C508="","",WORKDAY($C$5-1,A508))</f>
         <v/>
       </c>
       <c r="C508" s="20" t="str">
@@ -19551,7 +19557,7 @@
         <v/>
       </c>
       <c r="B509" s="19" t="str">
-        <f aca="false">IF(C509="","",$C$5+A509-1)</f>
+        <f aca="false">IF(C509="","",WORKDAY($C$5-1,A509))</f>
         <v/>
       </c>
       <c r="C509" s="20" t="str">
@@ -19588,7 +19594,7 @@
         <v/>
       </c>
       <c r="B510" s="19" t="str">
-        <f aca="false">IF(C510="","",$C$5+A510-1)</f>
+        <f aca="false">IF(C510="","",WORKDAY($C$5-1,A510))</f>
         <v/>
       </c>
       <c r="C510" s="20" t="str">
@@ -19625,7 +19631,7 @@
         <v/>
       </c>
       <c r="B511" s="19" t="str">
-        <f aca="false">IF(C511="","",$C$5+A511-1)</f>
+        <f aca="false">IF(C511="","",WORKDAY($C$5-1,A511))</f>
         <v/>
       </c>
       <c r="C511" s="20" t="str">
@@ -19662,7 +19668,7 @@
         <v/>
       </c>
       <c r="B512" s="19" t="str">
-        <f aca="false">IF(C512="","",$C$5+A512-1)</f>
+        <f aca="false">IF(C512="","",WORKDAY($C$5-1,A512))</f>
         <v/>
       </c>
       <c r="C512" s="20" t="str">
@@ -19760,7 +19766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C6F4AB1B-E09F-47F2-9F7E-CE3043892DC8}</x14:id>
+          <x14:id>{596ABDFB-8924-4732-8F3B-D97075E9C277}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -19791,7 +19797,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C6F4AB1B-E09F-47F2-9F7E-CE3043892DC8}">
+          <x14:cfRule type="dataBar" id="{596ABDFB-8924-4732-8F3B-D97075E9C277}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -19816,7 +19822,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -19937,6 +19943,16 @@
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Trading_PnL_Tracker.xlsx
+++ b/Trading_PnL_Tracker.xlsx
@@ -9,7 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="How to Use" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="NSE Holidays" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="How to Use" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Tracker!$12:$12</definedName>
@@ -37,7 +38,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Provided by you: you start trading tomorrow (26 Sep 2026). If this falls on a weekend, Day 1 moves to the next Monday. Only weekdays (Mon–Fri) get rows.</t>
+          <t xml:space="preserve">Provided by you: you start trading tomorrow (26 Sep 2026). If this is a weekend or NSE holiday, Day 1 moves to the next trading day. Only NSE trading days get rows.</t>
         </r>
       </text>
     </comment>
@@ -106,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t xml:space="preserve">Daily Trading P/L Tracker — ₹4,230 → ₹1,00,000 Goal</t>
   </si>
@@ -162,7 +163,7 @@
     <t xml:space="preserve">Projected goal date*</t>
   </si>
   <si>
-    <t xml:space="preserve">Rows = trading days only (Mon–Fri, weekends skipped).  Legend:  Yellow cells with blue text = your inputs (Settings, Actual P/L, Done?, Notes).  All other cells are formulas — don't overwrite them.  Grey italic rows = Projection (target assumed met), white rows = Actual.   *Projection-based figures.</t>
+    <t xml:space="preserve">Rows = NSE trading days only (weekends and holidays on the 'NSE Holidays' sheet are skipped).  Legend:  Yellow cells with blue text = your inputs (Settings, Actual P/L, Done?, Notes).  All other cells are formulas — don't overwrite them.  Grey italic rows = Projection (target assumed met), white rows = Actual.   *Projection-based figures.</t>
   </si>
   <si>
     <t xml:space="preserve">Day</t>
@@ -199,6 +200,72 @@
   <si>
     <t xml:space="preserve">Notes
 (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSE Trading Holidays (Equity segment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekday market holidays only (weekends are skipped anyway). Source: NSE circular CMTR71775 (12-Dec-2025) as reported by news/broker sites — confirm at nseindia.com &gt; Market Timings &amp; Holidays. Yellow cells are editable: add 2027 holidays in the empty rows when NSE publishes them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holiday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shri Ram Navami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shri Mahavir Jayanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Friday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Baba Saheb Ambedkar Jayanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maharashtra Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bakri Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muharram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganesh Chaturthi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahatma Gandhi Jayanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dussehra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diwali Balipratipada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diwali Laxmi Pujan (Sun 8-Nov) has a 1-hour Muhurat session; not a tracker row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guru Nanak Jayanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christmas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic Day (expected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 list not yet published by NSE — confirm and add the rest</t>
   </si>
   <si>
     <t xml:space="preserve">How to use this tracker</t>
@@ -249,13 +316,13 @@
     <t xml:space="preserve">Other notes</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Only trading days (Monday–Friday) get rows — Saturdays and Sundays are skipped automatically.</t>
+    <t xml:space="preserve">   • Only NSE trading days get rows — Saturdays, Sundays and listed NSE holidays are skipped automatically.</t>
   </si>
   <si>
     <t xml:space="preserve">   • Start date is 26-Sep-2026 (Sat), so Day 1 is Monday 28-Sep-2026. Change the "Start trading from" setting to move everything.</t>
   </si>
   <si>
-    <t xml:space="preserve">   • Market holidays on weekdays still get a row — enter 0 on those days.</t>
+    <t xml:space="preserve">   • NSE trading holidays listed on the 'NSE Holidays' sheet are skipped too. Add 2027 dates there once NSE publishes them (usually in December).</t>
   </si>
   <si>
     <t xml:space="preserve">   • Amounts are rounded to the paisa (2 decimals). Targets and limits = ROUND(opening capital × 3%, 2).</t>
@@ -274,7 +341,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy&quot; (&quot;ddd\)"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100000]\₹#\,##\,##0.00;\₹#,##0.00"/>
@@ -282,8 +349,10 @@
     <numFmt numFmtId="168" formatCode="0;\-0;&quot;None yet&quot;"/>
     <numFmt numFmtId="169" formatCode="0"/>
     <numFmt numFmtId="170" formatCode="\₹#,##0.00;[RED]&quot;-₹&quot;#,##0.00;\₹0.00"/>
+    <numFmt numFmtId="171" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="172" formatCode="ddd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +471,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
@@ -491,7 +575,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -592,6 +676,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -608,7 +720,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1137,7 +1249,7 @@
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="14" t="n">
-        <f aca="false">WORKDAY($C$5-1,$J$6+1)</f>
+        <f aca="false">WORKDAY($C$5-1,$J$6+1,'NSE Holidays'!$A$5:$A$64)</f>
         <v>46293</v>
       </c>
       <c r="H9" s="6" t="s">
@@ -1146,7 +1258,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="14" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",IF(AND($C$512&lt;&gt;"",N($F$512)&lt;$C$7),"Beyond 500 rows",MAX($B$13:$B$512)))</f>
-        <v>46442</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1205,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="19" t="n">
-        <f aca="false">IF(C13="","",WORKDAY($C$5-1,A13))</f>
+        <f aca="false">IF(C13="","",WORKDAY($C$5-1,A13,'NSE Holidays'!$A$5:$A$64))</f>
         <v>46293</v>
       </c>
       <c r="C13" s="20" t="n">
@@ -1242,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="19" t="n">
-        <f aca="false">IF(C14="","",WORKDAY($C$5-1,A14))</f>
+        <f aca="false">IF(C14="","",WORKDAY($C$5-1,A14,'NSE Holidays'!$A$5:$A$64))</f>
         <v>46294</v>
       </c>
       <c r="C14" s="20" t="n">
@@ -1279,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="19" t="n">
-        <f aca="false">IF(C15="","",WORKDAY($C$5-1,A15))</f>
+        <f aca="false">IF(C15="","",WORKDAY($C$5-1,A15,'NSE Holidays'!$A$5:$A$64))</f>
         <v>46295</v>
       </c>
       <c r="C15" s="20" t="n">
@@ -1316,7 +1428,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="19" t="n">
-        <f aca="false">IF(C16="","",WORKDAY($C$5-1,A16))</f>
+        <f aca="false">IF(C16="","",WORKDAY($C$5-1,A16,'NSE Holidays'!$A$5:$A$64))</f>
         <v>46296</v>
       </c>
       <c r="C16" s="20" t="n">
@@ -1353,8 +1465,8 @@
         <v>5</v>
       </c>
       <c r="B17" s="19" t="n">
-        <f aca="false">IF(C17="","",WORKDAY($C$5-1,A17))</f>
-        <v>46297</v>
+        <f aca="false">IF(C17="","",WORKDAY($C$5-1,A17,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46300</v>
       </c>
       <c r="C17" s="20" t="n">
         <f aca="false">IF(C16="","",IF(OR(IF(ISNUMBER(G16),H16,F16)&gt;=$C$7,IF(ISNUMBER(G16),H16,F16)&lt;=0),"",IF(ISNUMBER(G16),H16,F16)))</f>
@@ -1390,8 +1502,8 @@
         <v>6</v>
       </c>
       <c r="B18" s="19" t="n">
-        <f aca="false">IF(C18="","",WORKDAY($C$5-1,A18))</f>
-        <v>46300</v>
+        <f aca="false">IF(C18="","",WORKDAY($C$5-1,A18,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46301</v>
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">IF(C17="","",IF(OR(IF(ISNUMBER(G17),H17,F17)&gt;=$C$7,IF(ISNUMBER(G17),H17,F17)&lt;=0),"",IF(ISNUMBER(G17),H17,F17)))</f>
@@ -1427,8 +1539,8 @@
         <v>7</v>
       </c>
       <c r="B19" s="19" t="n">
-        <f aca="false">IF(C19="","",WORKDAY($C$5-1,A19))</f>
-        <v>46301</v>
+        <f aca="false">IF(C19="","",WORKDAY($C$5-1,A19,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46302</v>
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">IF(C18="","",IF(OR(IF(ISNUMBER(G18),H18,F18)&gt;=$C$7,IF(ISNUMBER(G18),H18,F18)&lt;=0),"",IF(ISNUMBER(G18),H18,F18)))</f>
@@ -1464,8 +1576,8 @@
         <v>8</v>
       </c>
       <c r="B20" s="19" t="n">
-        <f aca="false">IF(C20="","",WORKDAY($C$5-1,A20))</f>
-        <v>46302</v>
+        <f aca="false">IF(C20="","",WORKDAY($C$5-1,A20,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46303</v>
       </c>
       <c r="C20" s="20" t="n">
         <f aca="false">IF(C19="","",IF(OR(IF(ISNUMBER(G19),H19,F19)&gt;=$C$7,IF(ISNUMBER(G19),H19,F19)&lt;=0),"",IF(ISNUMBER(G19),H19,F19)))</f>
@@ -1501,8 +1613,8 @@
         <v>9</v>
       </c>
       <c r="B21" s="19" t="n">
-        <f aca="false">IF(C21="","",WORKDAY($C$5-1,A21))</f>
-        <v>46303</v>
+        <f aca="false">IF(C21="","",WORKDAY($C$5-1,A21,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46304</v>
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">IF(C20="","",IF(OR(IF(ISNUMBER(G20),H20,F20)&gt;=$C$7,IF(ISNUMBER(G20),H20,F20)&lt;=0),"",IF(ISNUMBER(G20),H20,F20)))</f>
@@ -1538,8 +1650,8 @@
         <v>10</v>
       </c>
       <c r="B22" s="19" t="n">
-        <f aca="false">IF(C22="","",WORKDAY($C$5-1,A22))</f>
-        <v>46304</v>
+        <f aca="false">IF(C22="","",WORKDAY($C$5-1,A22,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46307</v>
       </c>
       <c r="C22" s="20" t="n">
         <f aca="false">IF(C21="","",IF(OR(IF(ISNUMBER(G21),H21,F21)&gt;=$C$7,IF(ISNUMBER(G21),H21,F21)&lt;=0),"",IF(ISNUMBER(G21),H21,F21)))</f>
@@ -1575,8 +1687,8 @@
         <v>11</v>
       </c>
       <c r="B23" s="19" t="n">
-        <f aca="false">IF(C23="","",WORKDAY($C$5-1,A23))</f>
-        <v>46307</v>
+        <f aca="false">IF(C23="","",WORKDAY($C$5-1,A23,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46308</v>
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">IF(C22="","",IF(OR(IF(ISNUMBER(G22),H22,F22)&gt;=$C$7,IF(ISNUMBER(G22),H22,F22)&lt;=0),"",IF(ISNUMBER(G22),H22,F22)))</f>
@@ -1612,8 +1724,8 @@
         <v>12</v>
       </c>
       <c r="B24" s="19" t="n">
-        <f aca="false">IF(C24="","",WORKDAY($C$5-1,A24))</f>
-        <v>46308</v>
+        <f aca="false">IF(C24="","",WORKDAY($C$5-1,A24,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46309</v>
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">IF(C23="","",IF(OR(IF(ISNUMBER(G23),H23,F23)&gt;=$C$7,IF(ISNUMBER(G23),H23,F23)&lt;=0),"",IF(ISNUMBER(G23),H23,F23)))</f>
@@ -1649,8 +1761,8 @@
         <v>13</v>
       </c>
       <c r="B25" s="19" t="n">
-        <f aca="false">IF(C25="","",WORKDAY($C$5-1,A25))</f>
-        <v>46309</v>
+        <f aca="false">IF(C25="","",WORKDAY($C$5-1,A25,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46310</v>
       </c>
       <c r="C25" s="20" t="n">
         <f aca="false">IF(C24="","",IF(OR(IF(ISNUMBER(G24),H24,F24)&gt;=$C$7,IF(ISNUMBER(G24),H24,F24)&lt;=0),"",IF(ISNUMBER(G24),H24,F24)))</f>
@@ -1686,8 +1798,8 @@
         <v>14</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">IF(C26="","",WORKDAY($C$5-1,A26))</f>
-        <v>46310</v>
+        <f aca="false">IF(C26="","",WORKDAY($C$5-1,A26,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46311</v>
       </c>
       <c r="C26" s="20" t="n">
         <f aca="false">IF(C25="","",IF(OR(IF(ISNUMBER(G25),H25,F25)&gt;=$C$7,IF(ISNUMBER(G25),H25,F25)&lt;=0),"",IF(ISNUMBER(G25),H25,F25)))</f>
@@ -1723,8 +1835,8 @@
         <v>15</v>
       </c>
       <c r="B27" s="19" t="n">
-        <f aca="false">IF(C27="","",WORKDAY($C$5-1,A27))</f>
-        <v>46311</v>
+        <f aca="false">IF(C27="","",WORKDAY($C$5-1,A27,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46314</v>
       </c>
       <c r="C27" s="20" t="n">
         <f aca="false">IF(C26="","",IF(OR(IF(ISNUMBER(G26),H26,F26)&gt;=$C$7,IF(ISNUMBER(G26),H26,F26)&lt;=0),"",IF(ISNUMBER(G26),H26,F26)))</f>
@@ -1760,8 +1872,8 @@
         <v>16</v>
       </c>
       <c r="B28" s="19" t="n">
-        <f aca="false">IF(C28="","",WORKDAY($C$5-1,A28))</f>
-        <v>46314</v>
+        <f aca="false">IF(C28="","",WORKDAY($C$5-1,A28,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46316</v>
       </c>
       <c r="C28" s="20" t="n">
         <f aca="false">IF(C27="","",IF(OR(IF(ISNUMBER(G27),H27,F27)&gt;=$C$7,IF(ISNUMBER(G27),H27,F27)&lt;=0),"",IF(ISNUMBER(G27),H27,F27)))</f>
@@ -1797,8 +1909,8 @@
         <v>17</v>
       </c>
       <c r="B29" s="19" t="n">
-        <f aca="false">IF(C29="","",WORKDAY($C$5-1,A29))</f>
-        <v>46315</v>
+        <f aca="false">IF(C29="","",WORKDAY($C$5-1,A29,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46317</v>
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">IF(C28="","",IF(OR(IF(ISNUMBER(G28),H28,F28)&gt;=$C$7,IF(ISNUMBER(G28),H28,F28)&lt;=0),"",IF(ISNUMBER(G28),H28,F28)))</f>
@@ -1834,8 +1946,8 @@
         <v>18</v>
       </c>
       <c r="B30" s="19" t="n">
-        <f aca="false">IF(C30="","",WORKDAY($C$5-1,A30))</f>
-        <v>46316</v>
+        <f aca="false">IF(C30="","",WORKDAY($C$5-1,A30,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46318</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">IF(C29="","",IF(OR(IF(ISNUMBER(G29),H29,F29)&gt;=$C$7,IF(ISNUMBER(G29),H29,F29)&lt;=0),"",IF(ISNUMBER(G29),H29,F29)))</f>
@@ -1871,8 +1983,8 @@
         <v>19</v>
       </c>
       <c r="B31" s="19" t="n">
-        <f aca="false">IF(C31="","",WORKDAY($C$5-1,A31))</f>
-        <v>46317</v>
+        <f aca="false">IF(C31="","",WORKDAY($C$5-1,A31,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46321</v>
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">IF(C30="","",IF(OR(IF(ISNUMBER(G30),H30,F30)&gt;=$C$7,IF(ISNUMBER(G30),H30,F30)&lt;=0),"",IF(ISNUMBER(G30),H30,F30)))</f>
@@ -1908,8 +2020,8 @@
         <v>20</v>
       </c>
       <c r="B32" s="19" t="n">
-        <f aca="false">IF(C32="","",WORKDAY($C$5-1,A32))</f>
-        <v>46318</v>
+        <f aca="false">IF(C32="","",WORKDAY($C$5-1,A32,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46322</v>
       </c>
       <c r="C32" s="20" t="n">
         <f aca="false">IF(C31="","",IF(OR(IF(ISNUMBER(G31),H31,F31)&gt;=$C$7,IF(ISNUMBER(G31),H31,F31)&lt;=0),"",IF(ISNUMBER(G31),H31,F31)))</f>
@@ -1945,8 +2057,8 @@
         <v>21</v>
       </c>
       <c r="B33" s="19" t="n">
-        <f aca="false">IF(C33="","",WORKDAY($C$5-1,A33))</f>
-        <v>46321</v>
+        <f aca="false">IF(C33="","",WORKDAY($C$5-1,A33,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46323</v>
       </c>
       <c r="C33" s="20" t="n">
         <f aca="false">IF(C32="","",IF(OR(IF(ISNUMBER(G32),H32,F32)&gt;=$C$7,IF(ISNUMBER(G32),H32,F32)&lt;=0),"",IF(ISNUMBER(G32),H32,F32)))</f>
@@ -1982,8 +2094,8 @@
         <v>22</v>
       </c>
       <c r="B34" s="19" t="n">
-        <f aca="false">IF(C34="","",WORKDAY($C$5-1,A34))</f>
-        <v>46322</v>
+        <f aca="false">IF(C34="","",WORKDAY($C$5-1,A34,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46324</v>
       </c>
       <c r="C34" s="20" t="n">
         <f aca="false">IF(C33="","",IF(OR(IF(ISNUMBER(G33),H33,F33)&gt;=$C$7,IF(ISNUMBER(G33),H33,F33)&lt;=0),"",IF(ISNUMBER(G33),H33,F33)))</f>
@@ -2019,8 +2131,8 @@
         <v>23</v>
       </c>
       <c r="B35" s="19" t="n">
-        <f aca="false">IF(C35="","",WORKDAY($C$5-1,A35))</f>
-        <v>46323</v>
+        <f aca="false">IF(C35="","",WORKDAY($C$5-1,A35,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46325</v>
       </c>
       <c r="C35" s="20" t="n">
         <f aca="false">IF(C34="","",IF(OR(IF(ISNUMBER(G34),H34,F34)&gt;=$C$7,IF(ISNUMBER(G34),H34,F34)&lt;=0),"",IF(ISNUMBER(G34),H34,F34)))</f>
@@ -2056,8 +2168,8 @@
         <v>24</v>
       </c>
       <c r="B36" s="19" t="n">
-        <f aca="false">IF(C36="","",WORKDAY($C$5-1,A36))</f>
-        <v>46324</v>
+        <f aca="false">IF(C36="","",WORKDAY($C$5-1,A36,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46328</v>
       </c>
       <c r="C36" s="20" t="n">
         <f aca="false">IF(C35="","",IF(OR(IF(ISNUMBER(G35),H35,F35)&gt;=$C$7,IF(ISNUMBER(G35),H35,F35)&lt;=0),"",IF(ISNUMBER(G35),H35,F35)))</f>
@@ -2093,8 +2205,8 @@
         <v>25</v>
       </c>
       <c r="B37" s="19" t="n">
-        <f aca="false">IF(C37="","",WORKDAY($C$5-1,A37))</f>
-        <v>46325</v>
+        <f aca="false">IF(C37="","",WORKDAY($C$5-1,A37,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46329</v>
       </c>
       <c r="C37" s="20" t="n">
         <f aca="false">IF(C36="","",IF(OR(IF(ISNUMBER(G36),H36,F36)&gt;=$C$7,IF(ISNUMBER(G36),H36,F36)&lt;=0),"",IF(ISNUMBER(G36),H36,F36)))</f>
@@ -2130,8 +2242,8 @@
         <v>26</v>
       </c>
       <c r="B38" s="19" t="n">
-        <f aca="false">IF(C38="","",WORKDAY($C$5-1,A38))</f>
-        <v>46328</v>
+        <f aca="false">IF(C38="","",WORKDAY($C$5-1,A38,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46330</v>
       </c>
       <c r="C38" s="20" t="n">
         <f aca="false">IF(C37="","",IF(OR(IF(ISNUMBER(G37),H37,F37)&gt;=$C$7,IF(ISNUMBER(G37),H37,F37)&lt;=0),"",IF(ISNUMBER(G37),H37,F37)))</f>
@@ -2167,8 +2279,8 @@
         <v>27</v>
       </c>
       <c r="B39" s="19" t="n">
-        <f aca="false">IF(C39="","",WORKDAY($C$5-1,A39))</f>
-        <v>46329</v>
+        <f aca="false">IF(C39="","",WORKDAY($C$5-1,A39,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46331</v>
       </c>
       <c r="C39" s="20" t="n">
         <f aca="false">IF(C38="","",IF(OR(IF(ISNUMBER(G38),H38,F38)&gt;=$C$7,IF(ISNUMBER(G38),H38,F38)&lt;=0),"",IF(ISNUMBER(G38),H38,F38)))</f>
@@ -2204,8 +2316,8 @@
         <v>28</v>
       </c>
       <c r="B40" s="19" t="n">
-        <f aca="false">IF(C40="","",WORKDAY($C$5-1,A40))</f>
-        <v>46330</v>
+        <f aca="false">IF(C40="","",WORKDAY($C$5-1,A40,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46332</v>
       </c>
       <c r="C40" s="20" t="n">
         <f aca="false">IF(C39="","",IF(OR(IF(ISNUMBER(G39),H39,F39)&gt;=$C$7,IF(ISNUMBER(G39),H39,F39)&lt;=0),"",IF(ISNUMBER(G39),H39,F39)))</f>
@@ -2241,8 +2353,8 @@
         <v>29</v>
       </c>
       <c r="B41" s="19" t="n">
-        <f aca="false">IF(C41="","",WORKDAY($C$5-1,A41))</f>
-        <v>46331</v>
+        <f aca="false">IF(C41="","",WORKDAY($C$5-1,A41,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46335</v>
       </c>
       <c r="C41" s="20" t="n">
         <f aca="false">IF(C40="","",IF(OR(IF(ISNUMBER(G40),H40,F40)&gt;=$C$7,IF(ISNUMBER(G40),H40,F40)&lt;=0),"",IF(ISNUMBER(G40),H40,F40)))</f>
@@ -2278,8 +2390,8 @@
         <v>30</v>
       </c>
       <c r="B42" s="19" t="n">
-        <f aca="false">IF(C42="","",WORKDAY($C$5-1,A42))</f>
-        <v>46332</v>
+        <f aca="false">IF(C42="","",WORKDAY($C$5-1,A42,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46337</v>
       </c>
       <c r="C42" s="20" t="n">
         <f aca="false">IF(C41="","",IF(OR(IF(ISNUMBER(G41),H41,F41)&gt;=$C$7,IF(ISNUMBER(G41),H41,F41)&lt;=0),"",IF(ISNUMBER(G41),H41,F41)))</f>
@@ -2315,8 +2427,8 @@
         <v>31</v>
       </c>
       <c r="B43" s="19" t="n">
-        <f aca="false">IF(C43="","",WORKDAY($C$5-1,A43))</f>
-        <v>46335</v>
+        <f aca="false">IF(C43="","",WORKDAY($C$5-1,A43,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46338</v>
       </c>
       <c r="C43" s="20" t="n">
         <f aca="false">IF(C42="","",IF(OR(IF(ISNUMBER(G42),H42,F42)&gt;=$C$7,IF(ISNUMBER(G42),H42,F42)&lt;=0),"",IF(ISNUMBER(G42),H42,F42)))</f>
@@ -2352,8 +2464,8 @@
         <v>32</v>
       </c>
       <c r="B44" s="19" t="n">
-        <f aca="false">IF(C44="","",WORKDAY($C$5-1,A44))</f>
-        <v>46336</v>
+        <f aca="false">IF(C44="","",WORKDAY($C$5-1,A44,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46339</v>
       </c>
       <c r="C44" s="20" t="n">
         <f aca="false">IF(C43="","",IF(OR(IF(ISNUMBER(G43),H43,F43)&gt;=$C$7,IF(ISNUMBER(G43),H43,F43)&lt;=0),"",IF(ISNUMBER(G43),H43,F43)))</f>
@@ -2389,8 +2501,8 @@
         <v>33</v>
       </c>
       <c r="B45" s="19" t="n">
-        <f aca="false">IF(C45="","",WORKDAY($C$5-1,A45))</f>
-        <v>46337</v>
+        <f aca="false">IF(C45="","",WORKDAY($C$5-1,A45,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46342</v>
       </c>
       <c r="C45" s="20" t="n">
         <f aca="false">IF(C44="","",IF(OR(IF(ISNUMBER(G44),H44,F44)&gt;=$C$7,IF(ISNUMBER(G44),H44,F44)&lt;=0),"",IF(ISNUMBER(G44),H44,F44)))</f>
@@ -2426,8 +2538,8 @@
         <v>34</v>
       </c>
       <c r="B46" s="19" t="n">
-        <f aca="false">IF(C46="","",WORKDAY($C$5-1,A46))</f>
-        <v>46338</v>
+        <f aca="false">IF(C46="","",WORKDAY($C$5-1,A46,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46343</v>
       </c>
       <c r="C46" s="20" t="n">
         <f aca="false">IF(C45="","",IF(OR(IF(ISNUMBER(G45),H45,F45)&gt;=$C$7,IF(ISNUMBER(G45),H45,F45)&lt;=0),"",IF(ISNUMBER(G45),H45,F45)))</f>
@@ -2463,8 +2575,8 @@
         <v>35</v>
       </c>
       <c r="B47" s="19" t="n">
-        <f aca="false">IF(C47="","",WORKDAY($C$5-1,A47))</f>
-        <v>46339</v>
+        <f aca="false">IF(C47="","",WORKDAY($C$5-1,A47,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46344</v>
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">IF(C46="","",IF(OR(IF(ISNUMBER(G46),H46,F46)&gt;=$C$7,IF(ISNUMBER(G46),H46,F46)&lt;=0),"",IF(ISNUMBER(G46),H46,F46)))</f>
@@ -2500,8 +2612,8 @@
         <v>36</v>
       </c>
       <c r="B48" s="19" t="n">
-        <f aca="false">IF(C48="","",WORKDAY($C$5-1,A48))</f>
-        <v>46342</v>
+        <f aca="false">IF(C48="","",WORKDAY($C$5-1,A48,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46345</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">IF(C47="","",IF(OR(IF(ISNUMBER(G47),H47,F47)&gt;=$C$7,IF(ISNUMBER(G47),H47,F47)&lt;=0),"",IF(ISNUMBER(G47),H47,F47)))</f>
@@ -2537,8 +2649,8 @@
         <v>37</v>
       </c>
       <c r="B49" s="19" t="n">
-        <f aca="false">IF(C49="","",WORKDAY($C$5-1,A49))</f>
-        <v>46343</v>
+        <f aca="false">IF(C49="","",WORKDAY($C$5-1,A49,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46346</v>
       </c>
       <c r="C49" s="20" t="n">
         <f aca="false">IF(C48="","",IF(OR(IF(ISNUMBER(G48),H48,F48)&gt;=$C$7,IF(ISNUMBER(G48),H48,F48)&lt;=0),"",IF(ISNUMBER(G48),H48,F48)))</f>
@@ -2574,8 +2686,8 @@
         <v>38</v>
       </c>
       <c r="B50" s="19" t="n">
-        <f aca="false">IF(C50="","",WORKDAY($C$5-1,A50))</f>
-        <v>46344</v>
+        <f aca="false">IF(C50="","",WORKDAY($C$5-1,A50,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46349</v>
       </c>
       <c r="C50" s="20" t="n">
         <f aca="false">IF(C49="","",IF(OR(IF(ISNUMBER(G49),H49,F49)&gt;=$C$7,IF(ISNUMBER(G49),H49,F49)&lt;=0),"",IF(ISNUMBER(G49),H49,F49)))</f>
@@ -2611,8 +2723,8 @@
         <v>39</v>
       </c>
       <c r="B51" s="19" t="n">
-        <f aca="false">IF(C51="","",WORKDAY($C$5-1,A51))</f>
-        <v>46345</v>
+        <f aca="false">IF(C51="","",WORKDAY($C$5-1,A51,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46351</v>
       </c>
       <c r="C51" s="20" t="n">
         <f aca="false">IF(C50="","",IF(OR(IF(ISNUMBER(G50),H50,F50)&gt;=$C$7,IF(ISNUMBER(G50),H50,F50)&lt;=0),"",IF(ISNUMBER(G50),H50,F50)))</f>
@@ -2648,8 +2760,8 @@
         <v>40</v>
       </c>
       <c r="B52" s="19" t="n">
-        <f aca="false">IF(C52="","",WORKDAY($C$5-1,A52))</f>
-        <v>46346</v>
+        <f aca="false">IF(C52="","",WORKDAY($C$5-1,A52,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46352</v>
       </c>
       <c r="C52" s="20" t="n">
         <f aca="false">IF(C51="","",IF(OR(IF(ISNUMBER(G51),H51,F51)&gt;=$C$7,IF(ISNUMBER(G51),H51,F51)&lt;=0),"",IF(ISNUMBER(G51),H51,F51)))</f>
@@ -2685,8 +2797,8 @@
         <v>41</v>
       </c>
       <c r="B53" s="19" t="n">
-        <f aca="false">IF(C53="","",WORKDAY($C$5-1,A53))</f>
-        <v>46349</v>
+        <f aca="false">IF(C53="","",WORKDAY($C$5-1,A53,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46353</v>
       </c>
       <c r="C53" s="20" t="n">
         <f aca="false">IF(C52="","",IF(OR(IF(ISNUMBER(G52),H52,F52)&gt;=$C$7,IF(ISNUMBER(G52),H52,F52)&lt;=0),"",IF(ISNUMBER(G52),H52,F52)))</f>
@@ -2722,8 +2834,8 @@
         <v>42</v>
       </c>
       <c r="B54" s="19" t="n">
-        <f aca="false">IF(C54="","",WORKDAY($C$5-1,A54))</f>
-        <v>46350</v>
+        <f aca="false">IF(C54="","",WORKDAY($C$5-1,A54,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46356</v>
       </c>
       <c r="C54" s="20" t="n">
         <f aca="false">IF(C53="","",IF(OR(IF(ISNUMBER(G53),H53,F53)&gt;=$C$7,IF(ISNUMBER(G53),H53,F53)&lt;=0),"",IF(ISNUMBER(G53),H53,F53)))</f>
@@ -2759,8 +2871,8 @@
         <v>43</v>
       </c>
       <c r="B55" s="19" t="n">
-        <f aca="false">IF(C55="","",WORKDAY($C$5-1,A55))</f>
-        <v>46351</v>
+        <f aca="false">IF(C55="","",WORKDAY($C$5-1,A55,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46357</v>
       </c>
       <c r="C55" s="20" t="n">
         <f aca="false">IF(C54="","",IF(OR(IF(ISNUMBER(G54),H54,F54)&gt;=$C$7,IF(ISNUMBER(G54),H54,F54)&lt;=0),"",IF(ISNUMBER(G54),H54,F54)))</f>
@@ -2796,8 +2908,8 @@
         <v>44</v>
       </c>
       <c r="B56" s="19" t="n">
-        <f aca="false">IF(C56="","",WORKDAY($C$5-1,A56))</f>
-        <v>46352</v>
+        <f aca="false">IF(C56="","",WORKDAY($C$5-1,A56,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46358</v>
       </c>
       <c r="C56" s="20" t="n">
         <f aca="false">IF(C55="","",IF(OR(IF(ISNUMBER(G55),H55,F55)&gt;=$C$7,IF(ISNUMBER(G55),H55,F55)&lt;=0),"",IF(ISNUMBER(G55),H55,F55)))</f>
@@ -2833,8 +2945,8 @@
         <v>45</v>
       </c>
       <c r="B57" s="19" t="n">
-        <f aca="false">IF(C57="","",WORKDAY($C$5-1,A57))</f>
-        <v>46353</v>
+        <f aca="false">IF(C57="","",WORKDAY($C$5-1,A57,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46359</v>
       </c>
       <c r="C57" s="20" t="n">
         <f aca="false">IF(C56="","",IF(OR(IF(ISNUMBER(G56),H56,F56)&gt;=$C$7,IF(ISNUMBER(G56),H56,F56)&lt;=0),"",IF(ISNUMBER(G56),H56,F56)))</f>
@@ -2870,8 +2982,8 @@
         <v>46</v>
       </c>
       <c r="B58" s="19" t="n">
-        <f aca="false">IF(C58="","",WORKDAY($C$5-1,A58))</f>
-        <v>46356</v>
+        <f aca="false">IF(C58="","",WORKDAY($C$5-1,A58,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46360</v>
       </c>
       <c r="C58" s="20" t="n">
         <f aca="false">IF(C57="","",IF(OR(IF(ISNUMBER(G57),H57,F57)&gt;=$C$7,IF(ISNUMBER(G57),H57,F57)&lt;=0),"",IF(ISNUMBER(G57),H57,F57)))</f>
@@ -2907,8 +3019,8 @@
         <v>47</v>
       </c>
       <c r="B59" s="19" t="n">
-        <f aca="false">IF(C59="","",WORKDAY($C$5-1,A59))</f>
-        <v>46357</v>
+        <f aca="false">IF(C59="","",WORKDAY($C$5-1,A59,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46363</v>
       </c>
       <c r="C59" s="20" t="n">
         <f aca="false">IF(C58="","",IF(OR(IF(ISNUMBER(G58),H58,F58)&gt;=$C$7,IF(ISNUMBER(G58),H58,F58)&lt;=0),"",IF(ISNUMBER(G58),H58,F58)))</f>
@@ -2944,8 +3056,8 @@
         <v>48</v>
       </c>
       <c r="B60" s="19" t="n">
-        <f aca="false">IF(C60="","",WORKDAY($C$5-1,A60))</f>
-        <v>46358</v>
+        <f aca="false">IF(C60="","",WORKDAY($C$5-1,A60,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46364</v>
       </c>
       <c r="C60" s="20" t="n">
         <f aca="false">IF(C59="","",IF(OR(IF(ISNUMBER(G59),H59,F59)&gt;=$C$7,IF(ISNUMBER(G59),H59,F59)&lt;=0),"",IF(ISNUMBER(G59),H59,F59)))</f>
@@ -2981,8 +3093,8 @@
         <v>49</v>
       </c>
       <c r="B61" s="19" t="n">
-        <f aca="false">IF(C61="","",WORKDAY($C$5-1,A61))</f>
-        <v>46359</v>
+        <f aca="false">IF(C61="","",WORKDAY($C$5-1,A61,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46365</v>
       </c>
       <c r="C61" s="20" t="n">
         <f aca="false">IF(C60="","",IF(OR(IF(ISNUMBER(G60),H60,F60)&gt;=$C$7,IF(ISNUMBER(G60),H60,F60)&lt;=0),"",IF(ISNUMBER(G60),H60,F60)))</f>
@@ -3018,8 +3130,8 @@
         <v>50</v>
       </c>
       <c r="B62" s="19" t="n">
-        <f aca="false">IF(C62="","",WORKDAY($C$5-1,A62))</f>
-        <v>46360</v>
+        <f aca="false">IF(C62="","",WORKDAY($C$5-1,A62,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46366</v>
       </c>
       <c r="C62" s="20" t="n">
         <f aca="false">IF(C61="","",IF(OR(IF(ISNUMBER(G61),H61,F61)&gt;=$C$7,IF(ISNUMBER(G61),H61,F61)&lt;=0),"",IF(ISNUMBER(G61),H61,F61)))</f>
@@ -3055,8 +3167,8 @@
         <v>51</v>
       </c>
       <c r="B63" s="19" t="n">
-        <f aca="false">IF(C63="","",WORKDAY($C$5-1,A63))</f>
-        <v>46363</v>
+        <f aca="false">IF(C63="","",WORKDAY($C$5-1,A63,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46367</v>
       </c>
       <c r="C63" s="20" t="n">
         <f aca="false">IF(C62="","",IF(OR(IF(ISNUMBER(G62),H62,F62)&gt;=$C$7,IF(ISNUMBER(G62),H62,F62)&lt;=0),"",IF(ISNUMBER(G62),H62,F62)))</f>
@@ -3092,8 +3204,8 @@
         <v>52</v>
       </c>
       <c r="B64" s="19" t="n">
-        <f aca="false">IF(C64="","",WORKDAY($C$5-1,A64))</f>
-        <v>46364</v>
+        <f aca="false">IF(C64="","",WORKDAY($C$5-1,A64,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46370</v>
       </c>
       <c r="C64" s="20" t="n">
         <f aca="false">IF(C63="","",IF(OR(IF(ISNUMBER(G63),H63,F63)&gt;=$C$7,IF(ISNUMBER(G63),H63,F63)&lt;=0),"",IF(ISNUMBER(G63),H63,F63)))</f>
@@ -3129,8 +3241,8 @@
         <v>53</v>
       </c>
       <c r="B65" s="19" t="n">
-        <f aca="false">IF(C65="","",WORKDAY($C$5-1,A65))</f>
-        <v>46365</v>
+        <f aca="false">IF(C65="","",WORKDAY($C$5-1,A65,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46371</v>
       </c>
       <c r="C65" s="20" t="n">
         <f aca="false">IF(C64="","",IF(OR(IF(ISNUMBER(G64),H64,F64)&gt;=$C$7,IF(ISNUMBER(G64),H64,F64)&lt;=0),"",IF(ISNUMBER(G64),H64,F64)))</f>
@@ -3166,8 +3278,8 @@
         <v>54</v>
       </c>
       <c r="B66" s="19" t="n">
-        <f aca="false">IF(C66="","",WORKDAY($C$5-1,A66))</f>
-        <v>46366</v>
+        <f aca="false">IF(C66="","",WORKDAY($C$5-1,A66,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46372</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">IF(C65="","",IF(OR(IF(ISNUMBER(G65),H65,F65)&gt;=$C$7,IF(ISNUMBER(G65),H65,F65)&lt;=0),"",IF(ISNUMBER(G65),H65,F65)))</f>
@@ -3203,8 +3315,8 @@
         <v>55</v>
       </c>
       <c r="B67" s="19" t="n">
-        <f aca="false">IF(C67="","",WORKDAY($C$5-1,A67))</f>
-        <v>46367</v>
+        <f aca="false">IF(C67="","",WORKDAY($C$5-1,A67,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46373</v>
       </c>
       <c r="C67" s="20" t="n">
         <f aca="false">IF(C66="","",IF(OR(IF(ISNUMBER(G66),H66,F66)&gt;=$C$7,IF(ISNUMBER(G66),H66,F66)&lt;=0),"",IF(ISNUMBER(G66),H66,F66)))</f>
@@ -3240,8 +3352,8 @@
         <v>56</v>
       </c>
       <c r="B68" s="19" t="n">
-        <f aca="false">IF(C68="","",WORKDAY($C$5-1,A68))</f>
-        <v>46370</v>
+        <f aca="false">IF(C68="","",WORKDAY($C$5-1,A68,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46374</v>
       </c>
       <c r="C68" s="20" t="n">
         <f aca="false">IF(C67="","",IF(OR(IF(ISNUMBER(G67),H67,F67)&gt;=$C$7,IF(ISNUMBER(G67),H67,F67)&lt;=0),"",IF(ISNUMBER(G67),H67,F67)))</f>
@@ -3277,8 +3389,8 @@
         <v>57</v>
       </c>
       <c r="B69" s="19" t="n">
-        <f aca="false">IF(C69="","",WORKDAY($C$5-1,A69))</f>
-        <v>46371</v>
+        <f aca="false">IF(C69="","",WORKDAY($C$5-1,A69,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46377</v>
       </c>
       <c r="C69" s="20" t="n">
         <f aca="false">IF(C68="","",IF(OR(IF(ISNUMBER(G68),H68,F68)&gt;=$C$7,IF(ISNUMBER(G68),H68,F68)&lt;=0),"",IF(ISNUMBER(G68),H68,F68)))</f>
@@ -3314,8 +3426,8 @@
         <v>58</v>
       </c>
       <c r="B70" s="19" t="n">
-        <f aca="false">IF(C70="","",WORKDAY($C$5-1,A70))</f>
-        <v>46372</v>
+        <f aca="false">IF(C70="","",WORKDAY($C$5-1,A70,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46378</v>
       </c>
       <c r="C70" s="20" t="n">
         <f aca="false">IF(C69="","",IF(OR(IF(ISNUMBER(G69),H69,F69)&gt;=$C$7,IF(ISNUMBER(G69),H69,F69)&lt;=0),"",IF(ISNUMBER(G69),H69,F69)))</f>
@@ -3351,8 +3463,8 @@
         <v>59</v>
       </c>
       <c r="B71" s="19" t="n">
-        <f aca="false">IF(C71="","",WORKDAY($C$5-1,A71))</f>
-        <v>46373</v>
+        <f aca="false">IF(C71="","",WORKDAY($C$5-1,A71,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46379</v>
       </c>
       <c r="C71" s="20" t="n">
         <f aca="false">IF(C70="","",IF(OR(IF(ISNUMBER(G70),H70,F70)&gt;=$C$7,IF(ISNUMBER(G70),H70,F70)&lt;=0),"",IF(ISNUMBER(G70),H70,F70)))</f>
@@ -3388,8 +3500,8 @@
         <v>60</v>
       </c>
       <c r="B72" s="19" t="n">
-        <f aca="false">IF(C72="","",WORKDAY($C$5-1,A72))</f>
-        <v>46374</v>
+        <f aca="false">IF(C72="","",WORKDAY($C$5-1,A72,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46380</v>
       </c>
       <c r="C72" s="20" t="n">
         <f aca="false">IF(C71="","",IF(OR(IF(ISNUMBER(G71),H71,F71)&gt;=$C$7,IF(ISNUMBER(G71),H71,F71)&lt;=0),"",IF(ISNUMBER(G71),H71,F71)))</f>
@@ -3425,8 +3537,8 @@
         <v>61</v>
       </c>
       <c r="B73" s="19" t="n">
-        <f aca="false">IF(C73="","",WORKDAY($C$5-1,A73))</f>
-        <v>46377</v>
+        <f aca="false">IF(C73="","",WORKDAY($C$5-1,A73,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46384</v>
       </c>
       <c r="C73" s="20" t="n">
         <f aca="false">IF(C72="","",IF(OR(IF(ISNUMBER(G72),H72,F72)&gt;=$C$7,IF(ISNUMBER(G72),H72,F72)&lt;=0),"",IF(ISNUMBER(G72),H72,F72)))</f>
@@ -3462,8 +3574,8 @@
         <v>62</v>
       </c>
       <c r="B74" s="19" t="n">
-        <f aca="false">IF(C74="","",WORKDAY($C$5-1,A74))</f>
-        <v>46378</v>
+        <f aca="false">IF(C74="","",WORKDAY($C$5-1,A74,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46385</v>
       </c>
       <c r="C74" s="20" t="n">
         <f aca="false">IF(C73="","",IF(OR(IF(ISNUMBER(G73),H73,F73)&gt;=$C$7,IF(ISNUMBER(G73),H73,F73)&lt;=0),"",IF(ISNUMBER(G73),H73,F73)))</f>
@@ -3499,8 +3611,8 @@
         <v>63</v>
       </c>
       <c r="B75" s="19" t="n">
-        <f aca="false">IF(C75="","",WORKDAY($C$5-1,A75))</f>
-        <v>46379</v>
+        <f aca="false">IF(C75="","",WORKDAY($C$5-1,A75,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46386</v>
       </c>
       <c r="C75" s="20" t="n">
         <f aca="false">IF(C74="","",IF(OR(IF(ISNUMBER(G74),H74,F74)&gt;=$C$7,IF(ISNUMBER(G74),H74,F74)&lt;=0),"",IF(ISNUMBER(G74),H74,F74)))</f>
@@ -3536,8 +3648,8 @@
         <v>64</v>
       </c>
       <c r="B76" s="19" t="n">
-        <f aca="false">IF(C76="","",WORKDAY($C$5-1,A76))</f>
-        <v>46380</v>
+        <f aca="false">IF(C76="","",WORKDAY($C$5-1,A76,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46387</v>
       </c>
       <c r="C76" s="20" t="n">
         <f aca="false">IF(C75="","",IF(OR(IF(ISNUMBER(G75),H75,F75)&gt;=$C$7,IF(ISNUMBER(G75),H75,F75)&lt;=0),"",IF(ISNUMBER(G75),H75,F75)))</f>
@@ -3573,8 +3685,8 @@
         <v>65</v>
       </c>
       <c r="B77" s="19" t="n">
-        <f aca="false">IF(C77="","",WORKDAY($C$5-1,A77))</f>
-        <v>46381</v>
+        <f aca="false">IF(C77="","",WORKDAY($C$5-1,A77,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46388</v>
       </c>
       <c r="C77" s="20" t="n">
         <f aca="false">IF(C76="","",IF(OR(IF(ISNUMBER(G76),H76,F76)&gt;=$C$7,IF(ISNUMBER(G76),H76,F76)&lt;=0),"",IF(ISNUMBER(G76),H76,F76)))</f>
@@ -3610,8 +3722,8 @@
         <v>66</v>
       </c>
       <c r="B78" s="19" t="n">
-        <f aca="false">IF(C78="","",WORKDAY($C$5-1,A78))</f>
-        <v>46384</v>
+        <f aca="false">IF(C78="","",WORKDAY($C$5-1,A78,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46391</v>
       </c>
       <c r="C78" s="20" t="n">
         <f aca="false">IF(C77="","",IF(OR(IF(ISNUMBER(G77),H77,F77)&gt;=$C$7,IF(ISNUMBER(G77),H77,F77)&lt;=0),"",IF(ISNUMBER(G77),H77,F77)))</f>
@@ -3647,8 +3759,8 @@
         <v>67</v>
       </c>
       <c r="B79" s="19" t="n">
-        <f aca="false">IF(C79="","",WORKDAY($C$5-1,A79))</f>
-        <v>46385</v>
+        <f aca="false">IF(C79="","",WORKDAY($C$5-1,A79,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46392</v>
       </c>
       <c r="C79" s="20" t="n">
         <f aca="false">IF(C78="","",IF(OR(IF(ISNUMBER(G78),H78,F78)&gt;=$C$7,IF(ISNUMBER(G78),H78,F78)&lt;=0),"",IF(ISNUMBER(G78),H78,F78)))</f>
@@ -3684,8 +3796,8 @@
         <v>68</v>
       </c>
       <c r="B80" s="19" t="n">
-        <f aca="false">IF(C80="","",WORKDAY($C$5-1,A80))</f>
-        <v>46386</v>
+        <f aca="false">IF(C80="","",WORKDAY($C$5-1,A80,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46393</v>
       </c>
       <c r="C80" s="20" t="n">
         <f aca="false">IF(C79="","",IF(OR(IF(ISNUMBER(G79),H79,F79)&gt;=$C$7,IF(ISNUMBER(G79),H79,F79)&lt;=0),"",IF(ISNUMBER(G79),H79,F79)))</f>
@@ -3721,8 +3833,8 @@
         <v>69</v>
       </c>
       <c r="B81" s="19" t="n">
-        <f aca="false">IF(C81="","",WORKDAY($C$5-1,A81))</f>
-        <v>46387</v>
+        <f aca="false">IF(C81="","",WORKDAY($C$5-1,A81,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46394</v>
       </c>
       <c r="C81" s="20" t="n">
         <f aca="false">IF(C80="","",IF(OR(IF(ISNUMBER(G80),H80,F80)&gt;=$C$7,IF(ISNUMBER(G80),H80,F80)&lt;=0),"",IF(ISNUMBER(G80),H80,F80)))</f>
@@ -3758,8 +3870,8 @@
         <v>70</v>
       </c>
       <c r="B82" s="19" t="n">
-        <f aca="false">IF(C82="","",WORKDAY($C$5-1,A82))</f>
-        <v>46388</v>
+        <f aca="false">IF(C82="","",WORKDAY($C$5-1,A82,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46395</v>
       </c>
       <c r="C82" s="20" t="n">
         <f aca="false">IF(C81="","",IF(OR(IF(ISNUMBER(G81),H81,F81)&gt;=$C$7,IF(ISNUMBER(G81),H81,F81)&lt;=0),"",IF(ISNUMBER(G81),H81,F81)))</f>
@@ -3795,8 +3907,8 @@
         <v>71</v>
       </c>
       <c r="B83" s="19" t="n">
-        <f aca="false">IF(C83="","",WORKDAY($C$5-1,A83))</f>
-        <v>46391</v>
+        <f aca="false">IF(C83="","",WORKDAY($C$5-1,A83,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46398</v>
       </c>
       <c r="C83" s="20" t="n">
         <f aca="false">IF(C82="","",IF(OR(IF(ISNUMBER(G82),H82,F82)&gt;=$C$7,IF(ISNUMBER(G82),H82,F82)&lt;=0),"",IF(ISNUMBER(G82),H82,F82)))</f>
@@ -3832,8 +3944,8 @@
         <v>72</v>
       </c>
       <c r="B84" s="19" t="n">
-        <f aca="false">IF(C84="","",WORKDAY($C$5-1,A84))</f>
-        <v>46392</v>
+        <f aca="false">IF(C84="","",WORKDAY($C$5-1,A84,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46399</v>
       </c>
       <c r="C84" s="20" t="n">
         <f aca="false">IF(C83="","",IF(OR(IF(ISNUMBER(G83),H83,F83)&gt;=$C$7,IF(ISNUMBER(G83),H83,F83)&lt;=0),"",IF(ISNUMBER(G83),H83,F83)))</f>
@@ -3869,8 +3981,8 @@
         <v>73</v>
       </c>
       <c r="B85" s="19" t="n">
-        <f aca="false">IF(C85="","",WORKDAY($C$5-1,A85))</f>
-        <v>46393</v>
+        <f aca="false">IF(C85="","",WORKDAY($C$5-1,A85,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46400</v>
       </c>
       <c r="C85" s="20" t="n">
         <f aca="false">IF(C84="","",IF(OR(IF(ISNUMBER(G84),H84,F84)&gt;=$C$7,IF(ISNUMBER(G84),H84,F84)&lt;=0),"",IF(ISNUMBER(G84),H84,F84)))</f>
@@ -3906,8 +4018,8 @@
         <v>74</v>
       </c>
       <c r="B86" s="19" t="n">
-        <f aca="false">IF(C86="","",WORKDAY($C$5-1,A86))</f>
-        <v>46394</v>
+        <f aca="false">IF(C86="","",WORKDAY($C$5-1,A86,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46401</v>
       </c>
       <c r="C86" s="20" t="n">
         <f aca="false">IF(C85="","",IF(OR(IF(ISNUMBER(G85),H85,F85)&gt;=$C$7,IF(ISNUMBER(G85),H85,F85)&lt;=0),"",IF(ISNUMBER(G85),H85,F85)))</f>
@@ -3943,8 +4055,8 @@
         <v>75</v>
       </c>
       <c r="B87" s="19" t="n">
-        <f aca="false">IF(C87="","",WORKDAY($C$5-1,A87))</f>
-        <v>46395</v>
+        <f aca="false">IF(C87="","",WORKDAY($C$5-1,A87,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46402</v>
       </c>
       <c r="C87" s="20" t="n">
         <f aca="false">IF(C86="","",IF(OR(IF(ISNUMBER(G86),H86,F86)&gt;=$C$7,IF(ISNUMBER(G86),H86,F86)&lt;=0),"",IF(ISNUMBER(G86),H86,F86)))</f>
@@ -3980,8 +4092,8 @@
         <v>76</v>
       </c>
       <c r="B88" s="19" t="n">
-        <f aca="false">IF(C88="","",WORKDAY($C$5-1,A88))</f>
-        <v>46398</v>
+        <f aca="false">IF(C88="","",WORKDAY($C$5-1,A88,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46405</v>
       </c>
       <c r="C88" s="20" t="n">
         <f aca="false">IF(C87="","",IF(OR(IF(ISNUMBER(G87),H87,F87)&gt;=$C$7,IF(ISNUMBER(G87),H87,F87)&lt;=0),"",IF(ISNUMBER(G87),H87,F87)))</f>
@@ -4017,8 +4129,8 @@
         <v>77</v>
       </c>
       <c r="B89" s="19" t="n">
-        <f aca="false">IF(C89="","",WORKDAY($C$5-1,A89))</f>
-        <v>46399</v>
+        <f aca="false">IF(C89="","",WORKDAY($C$5-1,A89,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46406</v>
       </c>
       <c r="C89" s="20" t="n">
         <f aca="false">IF(C88="","",IF(OR(IF(ISNUMBER(G88),H88,F88)&gt;=$C$7,IF(ISNUMBER(G88),H88,F88)&lt;=0),"",IF(ISNUMBER(G88),H88,F88)))</f>
@@ -4054,8 +4166,8 @@
         <v>78</v>
       </c>
       <c r="B90" s="19" t="n">
-        <f aca="false">IF(C90="","",WORKDAY($C$5-1,A90))</f>
-        <v>46400</v>
+        <f aca="false">IF(C90="","",WORKDAY($C$5-1,A90,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46407</v>
       </c>
       <c r="C90" s="20" t="n">
         <f aca="false">IF(C89="","",IF(OR(IF(ISNUMBER(G89),H89,F89)&gt;=$C$7,IF(ISNUMBER(G89),H89,F89)&lt;=0),"",IF(ISNUMBER(G89),H89,F89)))</f>
@@ -4091,8 +4203,8 @@
         <v>79</v>
       </c>
       <c r="B91" s="19" t="n">
-        <f aca="false">IF(C91="","",WORKDAY($C$5-1,A91))</f>
-        <v>46401</v>
+        <f aca="false">IF(C91="","",WORKDAY($C$5-1,A91,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46408</v>
       </c>
       <c r="C91" s="20" t="n">
         <f aca="false">IF(C90="","",IF(OR(IF(ISNUMBER(G90),H90,F90)&gt;=$C$7,IF(ISNUMBER(G90),H90,F90)&lt;=0),"",IF(ISNUMBER(G90),H90,F90)))</f>
@@ -4128,8 +4240,8 @@
         <v>80</v>
       </c>
       <c r="B92" s="19" t="n">
-        <f aca="false">IF(C92="","",WORKDAY($C$5-1,A92))</f>
-        <v>46402</v>
+        <f aca="false">IF(C92="","",WORKDAY($C$5-1,A92,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46409</v>
       </c>
       <c r="C92" s="20" t="n">
         <f aca="false">IF(C91="","",IF(OR(IF(ISNUMBER(G91),H91,F91)&gt;=$C$7,IF(ISNUMBER(G91),H91,F91)&lt;=0),"",IF(ISNUMBER(G91),H91,F91)))</f>
@@ -4165,8 +4277,8 @@
         <v>81</v>
       </c>
       <c r="B93" s="19" t="n">
-        <f aca="false">IF(C93="","",WORKDAY($C$5-1,A93))</f>
-        <v>46405</v>
+        <f aca="false">IF(C93="","",WORKDAY($C$5-1,A93,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46412</v>
       </c>
       <c r="C93" s="20" t="n">
         <f aca="false">IF(C92="","",IF(OR(IF(ISNUMBER(G92),H92,F92)&gt;=$C$7,IF(ISNUMBER(G92),H92,F92)&lt;=0),"",IF(ISNUMBER(G92),H92,F92)))</f>
@@ -4202,8 +4314,8 @@
         <v>82</v>
       </c>
       <c r="B94" s="19" t="n">
-        <f aca="false">IF(C94="","",WORKDAY($C$5-1,A94))</f>
-        <v>46406</v>
+        <f aca="false">IF(C94="","",WORKDAY($C$5-1,A94,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46414</v>
       </c>
       <c r="C94" s="20" t="n">
         <f aca="false">IF(C93="","",IF(OR(IF(ISNUMBER(G93),H93,F93)&gt;=$C$7,IF(ISNUMBER(G93),H93,F93)&lt;=0),"",IF(ISNUMBER(G93),H93,F93)))</f>
@@ -4239,8 +4351,8 @@
         <v>83</v>
       </c>
       <c r="B95" s="19" t="n">
-        <f aca="false">IF(C95="","",WORKDAY($C$5-1,A95))</f>
-        <v>46407</v>
+        <f aca="false">IF(C95="","",WORKDAY($C$5-1,A95,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46415</v>
       </c>
       <c r="C95" s="20" t="n">
         <f aca="false">IF(C94="","",IF(OR(IF(ISNUMBER(G94),H94,F94)&gt;=$C$7,IF(ISNUMBER(G94),H94,F94)&lt;=0),"",IF(ISNUMBER(G94),H94,F94)))</f>
@@ -4276,8 +4388,8 @@
         <v>84</v>
       </c>
       <c r="B96" s="19" t="n">
-        <f aca="false">IF(C96="","",WORKDAY($C$5-1,A96))</f>
-        <v>46408</v>
+        <f aca="false">IF(C96="","",WORKDAY($C$5-1,A96,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46416</v>
       </c>
       <c r="C96" s="20" t="n">
         <f aca="false">IF(C95="","",IF(OR(IF(ISNUMBER(G95),H95,F95)&gt;=$C$7,IF(ISNUMBER(G95),H95,F95)&lt;=0),"",IF(ISNUMBER(G95),H95,F95)))</f>
@@ -4313,8 +4425,8 @@
         <v>85</v>
       </c>
       <c r="B97" s="19" t="n">
-        <f aca="false">IF(C97="","",WORKDAY($C$5-1,A97))</f>
-        <v>46409</v>
+        <f aca="false">IF(C97="","",WORKDAY($C$5-1,A97,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46419</v>
       </c>
       <c r="C97" s="20" t="n">
         <f aca="false">IF(C96="","",IF(OR(IF(ISNUMBER(G96),H96,F96)&gt;=$C$7,IF(ISNUMBER(G96),H96,F96)&lt;=0),"",IF(ISNUMBER(G96),H96,F96)))</f>
@@ -4350,8 +4462,8 @@
         <v>86</v>
       </c>
       <c r="B98" s="19" t="n">
-        <f aca="false">IF(C98="","",WORKDAY($C$5-1,A98))</f>
-        <v>46412</v>
+        <f aca="false">IF(C98="","",WORKDAY($C$5-1,A98,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46420</v>
       </c>
       <c r="C98" s="20" t="n">
         <f aca="false">IF(C97="","",IF(OR(IF(ISNUMBER(G97),H97,F97)&gt;=$C$7,IF(ISNUMBER(G97),H97,F97)&lt;=0),"",IF(ISNUMBER(G97),H97,F97)))</f>
@@ -4387,8 +4499,8 @@
         <v>87</v>
       </c>
       <c r="B99" s="19" t="n">
-        <f aca="false">IF(C99="","",WORKDAY($C$5-1,A99))</f>
-        <v>46413</v>
+        <f aca="false">IF(C99="","",WORKDAY($C$5-1,A99,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46421</v>
       </c>
       <c r="C99" s="20" t="n">
         <f aca="false">IF(C98="","",IF(OR(IF(ISNUMBER(G98),H98,F98)&gt;=$C$7,IF(ISNUMBER(G98),H98,F98)&lt;=0),"",IF(ISNUMBER(G98),H98,F98)))</f>
@@ -4424,8 +4536,8 @@
         <v>88</v>
       </c>
       <c r="B100" s="19" t="n">
-        <f aca="false">IF(C100="","",WORKDAY($C$5-1,A100))</f>
-        <v>46414</v>
+        <f aca="false">IF(C100="","",WORKDAY($C$5-1,A100,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46422</v>
       </c>
       <c r="C100" s="20" t="n">
         <f aca="false">IF(C99="","",IF(OR(IF(ISNUMBER(G99),H99,F99)&gt;=$C$7,IF(ISNUMBER(G99),H99,F99)&lt;=0),"",IF(ISNUMBER(G99),H99,F99)))</f>
@@ -4461,8 +4573,8 @@
         <v>89</v>
       </c>
       <c r="B101" s="19" t="n">
-        <f aca="false">IF(C101="","",WORKDAY($C$5-1,A101))</f>
-        <v>46415</v>
+        <f aca="false">IF(C101="","",WORKDAY($C$5-1,A101,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46423</v>
       </c>
       <c r="C101" s="20" t="n">
         <f aca="false">IF(C100="","",IF(OR(IF(ISNUMBER(G100),H100,F100)&gt;=$C$7,IF(ISNUMBER(G100),H100,F100)&lt;=0),"",IF(ISNUMBER(G100),H100,F100)))</f>
@@ -4498,8 +4610,8 @@
         <v>90</v>
       </c>
       <c r="B102" s="19" t="n">
-        <f aca="false">IF(C102="","",WORKDAY($C$5-1,A102))</f>
-        <v>46416</v>
+        <f aca="false">IF(C102="","",WORKDAY($C$5-1,A102,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46426</v>
       </c>
       <c r="C102" s="20" t="n">
         <f aca="false">IF(C101="","",IF(OR(IF(ISNUMBER(G101),H101,F101)&gt;=$C$7,IF(ISNUMBER(G101),H101,F101)&lt;=0),"",IF(ISNUMBER(G101),H101,F101)))</f>
@@ -4535,8 +4647,8 @@
         <v>91</v>
       </c>
       <c r="B103" s="19" t="n">
-        <f aca="false">IF(C103="","",WORKDAY($C$5-1,A103))</f>
-        <v>46419</v>
+        <f aca="false">IF(C103="","",WORKDAY($C$5-1,A103,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46427</v>
       </c>
       <c r="C103" s="20" t="n">
         <f aca="false">IF(C102="","",IF(OR(IF(ISNUMBER(G102),H102,F102)&gt;=$C$7,IF(ISNUMBER(G102),H102,F102)&lt;=0),"",IF(ISNUMBER(G102),H102,F102)))</f>
@@ -4572,8 +4684,8 @@
         <v>92</v>
       </c>
       <c r="B104" s="19" t="n">
-        <f aca="false">IF(C104="","",WORKDAY($C$5-1,A104))</f>
-        <v>46420</v>
+        <f aca="false">IF(C104="","",WORKDAY($C$5-1,A104,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46428</v>
       </c>
       <c r="C104" s="20" t="n">
         <f aca="false">IF(C103="","",IF(OR(IF(ISNUMBER(G103),H103,F103)&gt;=$C$7,IF(ISNUMBER(G103),H103,F103)&lt;=0),"",IF(ISNUMBER(G103),H103,F103)))</f>
@@ -4609,8 +4721,8 @@
         <v>93</v>
       </c>
       <c r="B105" s="19" t="n">
-        <f aca="false">IF(C105="","",WORKDAY($C$5-1,A105))</f>
-        <v>46421</v>
+        <f aca="false">IF(C105="","",WORKDAY($C$5-1,A105,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46429</v>
       </c>
       <c r="C105" s="20" t="n">
         <f aca="false">IF(C104="","",IF(OR(IF(ISNUMBER(G104),H104,F104)&gt;=$C$7,IF(ISNUMBER(G104),H104,F104)&lt;=0),"",IF(ISNUMBER(G104),H104,F104)))</f>
@@ -4646,8 +4758,8 @@
         <v>94</v>
       </c>
       <c r="B106" s="19" t="n">
-        <f aca="false">IF(C106="","",WORKDAY($C$5-1,A106))</f>
-        <v>46422</v>
+        <f aca="false">IF(C106="","",WORKDAY($C$5-1,A106,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46430</v>
       </c>
       <c r="C106" s="20" t="n">
         <f aca="false">IF(C105="","",IF(OR(IF(ISNUMBER(G105),H105,F105)&gt;=$C$7,IF(ISNUMBER(G105),H105,F105)&lt;=0),"",IF(ISNUMBER(G105),H105,F105)))</f>
@@ -4683,8 +4795,8 @@
         <v>95</v>
       </c>
       <c r="B107" s="19" t="n">
-        <f aca="false">IF(C107="","",WORKDAY($C$5-1,A107))</f>
-        <v>46423</v>
+        <f aca="false">IF(C107="","",WORKDAY($C$5-1,A107,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46433</v>
       </c>
       <c r="C107" s="20" t="n">
         <f aca="false">IF(C106="","",IF(OR(IF(ISNUMBER(G106),H106,F106)&gt;=$C$7,IF(ISNUMBER(G106),H106,F106)&lt;=0),"",IF(ISNUMBER(G106),H106,F106)))</f>
@@ -4720,8 +4832,8 @@
         <v>96</v>
       </c>
       <c r="B108" s="19" t="n">
-        <f aca="false">IF(C108="","",WORKDAY($C$5-1,A108))</f>
-        <v>46426</v>
+        <f aca="false">IF(C108="","",WORKDAY($C$5-1,A108,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46434</v>
       </c>
       <c r="C108" s="20" t="n">
         <f aca="false">IF(C107="","",IF(OR(IF(ISNUMBER(G107),H107,F107)&gt;=$C$7,IF(ISNUMBER(G107),H107,F107)&lt;=0),"",IF(ISNUMBER(G107),H107,F107)))</f>
@@ -4757,8 +4869,8 @@
         <v>97</v>
       </c>
       <c r="B109" s="19" t="n">
-        <f aca="false">IF(C109="","",WORKDAY($C$5-1,A109))</f>
-        <v>46427</v>
+        <f aca="false">IF(C109="","",WORKDAY($C$5-1,A109,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46435</v>
       </c>
       <c r="C109" s="20" t="n">
         <f aca="false">IF(C108="","",IF(OR(IF(ISNUMBER(G108),H108,F108)&gt;=$C$7,IF(ISNUMBER(G108),H108,F108)&lt;=0),"",IF(ISNUMBER(G108),H108,F108)))</f>
@@ -4794,8 +4906,8 @@
         <v>98</v>
       </c>
       <c r="B110" s="19" t="n">
-        <f aca="false">IF(C110="","",WORKDAY($C$5-1,A110))</f>
-        <v>46428</v>
+        <f aca="false">IF(C110="","",WORKDAY($C$5-1,A110,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46436</v>
       </c>
       <c r="C110" s="20" t="n">
         <f aca="false">IF(C109="","",IF(OR(IF(ISNUMBER(G109),H109,F109)&gt;=$C$7,IF(ISNUMBER(G109),H109,F109)&lt;=0),"",IF(ISNUMBER(G109),H109,F109)))</f>
@@ -4831,8 +4943,8 @@
         <v>99</v>
       </c>
       <c r="B111" s="19" t="n">
-        <f aca="false">IF(C111="","",WORKDAY($C$5-1,A111))</f>
-        <v>46429</v>
+        <f aca="false">IF(C111="","",WORKDAY($C$5-1,A111,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46437</v>
       </c>
       <c r="C111" s="20" t="n">
         <f aca="false">IF(C110="","",IF(OR(IF(ISNUMBER(G110),H110,F110)&gt;=$C$7,IF(ISNUMBER(G110),H110,F110)&lt;=0),"",IF(ISNUMBER(G110),H110,F110)))</f>
@@ -4868,8 +4980,8 @@
         <v>100</v>
       </c>
       <c r="B112" s="19" t="n">
-        <f aca="false">IF(C112="","",WORKDAY($C$5-1,A112))</f>
-        <v>46430</v>
+        <f aca="false">IF(C112="","",WORKDAY($C$5-1,A112,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46440</v>
       </c>
       <c r="C112" s="20" t="n">
         <f aca="false">IF(C111="","",IF(OR(IF(ISNUMBER(G111),H111,F111)&gt;=$C$7,IF(ISNUMBER(G111),H111,F111)&lt;=0),"",IF(ISNUMBER(G111),H111,F111)))</f>
@@ -4905,8 +5017,8 @@
         <v>101</v>
       </c>
       <c r="B113" s="19" t="n">
-        <f aca="false">IF(C113="","",WORKDAY($C$5-1,A113))</f>
-        <v>46433</v>
+        <f aca="false">IF(C113="","",WORKDAY($C$5-1,A113,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46441</v>
       </c>
       <c r="C113" s="20" t="n">
         <f aca="false">IF(C112="","",IF(OR(IF(ISNUMBER(G112),H112,F112)&gt;=$C$7,IF(ISNUMBER(G112),H112,F112)&lt;=0),"",IF(ISNUMBER(G112),H112,F112)))</f>
@@ -4942,8 +5054,8 @@
         <v>102</v>
       </c>
       <c r="B114" s="19" t="n">
-        <f aca="false">IF(C114="","",WORKDAY($C$5-1,A114))</f>
-        <v>46434</v>
+        <f aca="false">IF(C114="","",WORKDAY($C$5-1,A114,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46442</v>
       </c>
       <c r="C114" s="20" t="n">
         <f aca="false">IF(C113="","",IF(OR(IF(ISNUMBER(G113),H113,F113)&gt;=$C$7,IF(ISNUMBER(G113),H113,F113)&lt;=0),"",IF(ISNUMBER(G113),H113,F113)))</f>
@@ -4979,8 +5091,8 @@
         <v>103</v>
       </c>
       <c r="B115" s="19" t="n">
-        <f aca="false">IF(C115="","",WORKDAY($C$5-1,A115))</f>
-        <v>46435</v>
+        <f aca="false">IF(C115="","",WORKDAY($C$5-1,A115,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46443</v>
       </c>
       <c r="C115" s="20" t="n">
         <f aca="false">IF(C114="","",IF(OR(IF(ISNUMBER(G114),H114,F114)&gt;=$C$7,IF(ISNUMBER(G114),H114,F114)&lt;=0),"",IF(ISNUMBER(G114),H114,F114)))</f>
@@ -5016,8 +5128,8 @@
         <v>104</v>
       </c>
       <c r="B116" s="19" t="n">
-        <f aca="false">IF(C116="","",WORKDAY($C$5-1,A116))</f>
-        <v>46436</v>
+        <f aca="false">IF(C116="","",WORKDAY($C$5-1,A116,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46444</v>
       </c>
       <c r="C116" s="20" t="n">
         <f aca="false">IF(C115="","",IF(OR(IF(ISNUMBER(G115),H115,F115)&gt;=$C$7,IF(ISNUMBER(G115),H115,F115)&lt;=0),"",IF(ISNUMBER(G115),H115,F115)))</f>
@@ -5053,8 +5165,8 @@
         <v>105</v>
       </c>
       <c r="B117" s="19" t="n">
-        <f aca="false">IF(C117="","",WORKDAY($C$5-1,A117))</f>
-        <v>46437</v>
+        <f aca="false">IF(C117="","",WORKDAY($C$5-1,A117,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46447</v>
       </c>
       <c r="C117" s="20" t="n">
         <f aca="false">IF(C116="","",IF(OR(IF(ISNUMBER(G116),H116,F116)&gt;=$C$7,IF(ISNUMBER(G116),H116,F116)&lt;=0),"",IF(ISNUMBER(G116),H116,F116)))</f>
@@ -5090,8 +5202,8 @@
         <v>106</v>
       </c>
       <c r="B118" s="19" t="n">
-        <f aca="false">IF(C118="","",WORKDAY($C$5-1,A118))</f>
-        <v>46440</v>
+        <f aca="false">IF(C118="","",WORKDAY($C$5-1,A118,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46448</v>
       </c>
       <c r="C118" s="20" t="n">
         <f aca="false">IF(C117="","",IF(OR(IF(ISNUMBER(G117),H117,F117)&gt;=$C$7,IF(ISNUMBER(G117),H117,F117)&lt;=0),"",IF(ISNUMBER(G117),H117,F117)))</f>
@@ -5127,8 +5239,8 @@
         <v>107</v>
       </c>
       <c r="B119" s="19" t="n">
-        <f aca="false">IF(C119="","",WORKDAY($C$5-1,A119))</f>
-        <v>46441</v>
+        <f aca="false">IF(C119="","",WORKDAY($C$5-1,A119,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46449</v>
       </c>
       <c r="C119" s="20" t="n">
         <f aca="false">IF(C118="","",IF(OR(IF(ISNUMBER(G118),H118,F118)&gt;=$C$7,IF(ISNUMBER(G118),H118,F118)&lt;=0),"",IF(ISNUMBER(G118),H118,F118)))</f>
@@ -5164,8 +5276,8 @@
         <v>108</v>
       </c>
       <c r="B120" s="19" t="n">
-        <f aca="false">IF(C120="","",WORKDAY($C$5-1,A120))</f>
-        <v>46442</v>
+        <f aca="false">IF(C120="","",WORKDAY($C$5-1,A120,'NSE Holidays'!$A$5:$A$64))</f>
+        <v>46450</v>
       </c>
       <c r="C120" s="20" t="n">
         <f aca="false">IF(C119="","",IF(OR(IF(ISNUMBER(G119),H119,F119)&gt;=$C$7,IF(ISNUMBER(G119),H119,F119)&lt;=0),"",IF(ISNUMBER(G119),H119,F119)))</f>
@@ -5201,7 +5313,7 @@
         <v/>
       </c>
       <c r="B121" s="19" t="str">
-        <f aca="false">IF(C121="","",WORKDAY($C$5-1,A121))</f>
+        <f aca="false">IF(C121="","",WORKDAY($C$5-1,A121,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C121" s="20" t="str">
@@ -5238,7 +5350,7 @@
         <v/>
       </c>
       <c r="B122" s="19" t="str">
-        <f aca="false">IF(C122="","",WORKDAY($C$5-1,A122))</f>
+        <f aca="false">IF(C122="","",WORKDAY($C$5-1,A122,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C122" s="20" t="str">
@@ -5275,7 +5387,7 @@
         <v/>
       </c>
       <c r="B123" s="19" t="str">
-        <f aca="false">IF(C123="","",WORKDAY($C$5-1,A123))</f>
+        <f aca="false">IF(C123="","",WORKDAY($C$5-1,A123,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C123" s="20" t="str">
@@ -5312,7 +5424,7 @@
         <v/>
       </c>
       <c r="B124" s="19" t="str">
-        <f aca="false">IF(C124="","",WORKDAY($C$5-1,A124))</f>
+        <f aca="false">IF(C124="","",WORKDAY($C$5-1,A124,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C124" s="20" t="str">
@@ -5349,7 +5461,7 @@
         <v/>
       </c>
       <c r="B125" s="19" t="str">
-        <f aca="false">IF(C125="","",WORKDAY($C$5-1,A125))</f>
+        <f aca="false">IF(C125="","",WORKDAY($C$5-1,A125,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C125" s="20" t="str">
@@ -5386,7 +5498,7 @@
         <v/>
       </c>
       <c r="B126" s="19" t="str">
-        <f aca="false">IF(C126="","",WORKDAY($C$5-1,A126))</f>
+        <f aca="false">IF(C126="","",WORKDAY($C$5-1,A126,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C126" s="20" t="str">
@@ -5423,7 +5535,7 @@
         <v/>
       </c>
       <c r="B127" s="19" t="str">
-        <f aca="false">IF(C127="","",WORKDAY($C$5-1,A127))</f>
+        <f aca="false">IF(C127="","",WORKDAY($C$5-1,A127,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C127" s="20" t="str">
@@ -5460,7 +5572,7 @@
         <v/>
       </c>
       <c r="B128" s="19" t="str">
-        <f aca="false">IF(C128="","",WORKDAY($C$5-1,A128))</f>
+        <f aca="false">IF(C128="","",WORKDAY($C$5-1,A128,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C128" s="20" t="str">
@@ -5497,7 +5609,7 @@
         <v/>
       </c>
       <c r="B129" s="19" t="str">
-        <f aca="false">IF(C129="","",WORKDAY($C$5-1,A129))</f>
+        <f aca="false">IF(C129="","",WORKDAY($C$5-1,A129,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C129" s="20" t="str">
@@ -5534,7 +5646,7 @@
         <v/>
       </c>
       <c r="B130" s="19" t="str">
-        <f aca="false">IF(C130="","",WORKDAY($C$5-1,A130))</f>
+        <f aca="false">IF(C130="","",WORKDAY($C$5-1,A130,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C130" s="20" t="str">
@@ -5571,7 +5683,7 @@
         <v/>
       </c>
       <c r="B131" s="19" t="str">
-        <f aca="false">IF(C131="","",WORKDAY($C$5-1,A131))</f>
+        <f aca="false">IF(C131="","",WORKDAY($C$5-1,A131,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C131" s="20" t="str">
@@ -5608,7 +5720,7 @@
         <v/>
       </c>
       <c r="B132" s="19" t="str">
-        <f aca="false">IF(C132="","",WORKDAY($C$5-1,A132))</f>
+        <f aca="false">IF(C132="","",WORKDAY($C$5-1,A132,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C132" s="20" t="str">
@@ -5645,7 +5757,7 @@
         <v/>
       </c>
       <c r="B133" s="19" t="str">
-        <f aca="false">IF(C133="","",WORKDAY($C$5-1,A133))</f>
+        <f aca="false">IF(C133="","",WORKDAY($C$5-1,A133,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C133" s="20" t="str">
@@ -5682,7 +5794,7 @@
         <v/>
       </c>
       <c r="B134" s="19" t="str">
-        <f aca="false">IF(C134="","",WORKDAY($C$5-1,A134))</f>
+        <f aca="false">IF(C134="","",WORKDAY($C$5-1,A134,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C134" s="20" t="str">
@@ -5719,7 +5831,7 @@
         <v/>
       </c>
       <c r="B135" s="19" t="str">
-        <f aca="false">IF(C135="","",WORKDAY($C$5-1,A135))</f>
+        <f aca="false">IF(C135="","",WORKDAY($C$5-1,A135,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C135" s="20" t="str">
@@ -5756,7 +5868,7 @@
         <v/>
       </c>
       <c r="B136" s="19" t="str">
-        <f aca="false">IF(C136="","",WORKDAY($C$5-1,A136))</f>
+        <f aca="false">IF(C136="","",WORKDAY($C$5-1,A136,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C136" s="20" t="str">
@@ -5793,7 +5905,7 @@
         <v/>
       </c>
       <c r="B137" s="19" t="str">
-        <f aca="false">IF(C137="","",WORKDAY($C$5-1,A137))</f>
+        <f aca="false">IF(C137="","",WORKDAY($C$5-1,A137,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C137" s="20" t="str">
@@ -5830,7 +5942,7 @@
         <v/>
       </c>
       <c r="B138" s="19" t="str">
-        <f aca="false">IF(C138="","",WORKDAY($C$5-1,A138))</f>
+        <f aca="false">IF(C138="","",WORKDAY($C$5-1,A138,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C138" s="20" t="str">
@@ -5867,7 +5979,7 @@
         <v/>
       </c>
       <c r="B139" s="19" t="str">
-        <f aca="false">IF(C139="","",WORKDAY($C$5-1,A139))</f>
+        <f aca="false">IF(C139="","",WORKDAY($C$5-1,A139,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C139" s="20" t="str">
@@ -5904,7 +6016,7 @@
         <v/>
       </c>
       <c r="B140" s="19" t="str">
-        <f aca="false">IF(C140="","",WORKDAY($C$5-1,A140))</f>
+        <f aca="false">IF(C140="","",WORKDAY($C$5-1,A140,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C140" s="20" t="str">
@@ -5941,7 +6053,7 @@
         <v/>
       </c>
       <c r="B141" s="19" t="str">
-        <f aca="false">IF(C141="","",WORKDAY($C$5-1,A141))</f>
+        <f aca="false">IF(C141="","",WORKDAY($C$5-1,A141,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C141" s="20" t="str">
@@ -5978,7 +6090,7 @@
         <v/>
       </c>
       <c r="B142" s="19" t="str">
-        <f aca="false">IF(C142="","",WORKDAY($C$5-1,A142))</f>
+        <f aca="false">IF(C142="","",WORKDAY($C$5-1,A142,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C142" s="20" t="str">
@@ -6015,7 +6127,7 @@
         <v/>
       </c>
       <c r="B143" s="19" t="str">
-        <f aca="false">IF(C143="","",WORKDAY($C$5-1,A143))</f>
+        <f aca="false">IF(C143="","",WORKDAY($C$5-1,A143,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C143" s="20" t="str">
@@ -6052,7 +6164,7 @@
         <v/>
       </c>
       <c r="B144" s="19" t="str">
-        <f aca="false">IF(C144="","",WORKDAY($C$5-1,A144))</f>
+        <f aca="false">IF(C144="","",WORKDAY($C$5-1,A144,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C144" s="20" t="str">
@@ -6089,7 +6201,7 @@
         <v/>
       </c>
       <c r="B145" s="19" t="str">
-        <f aca="false">IF(C145="","",WORKDAY($C$5-1,A145))</f>
+        <f aca="false">IF(C145="","",WORKDAY($C$5-1,A145,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C145" s="20" t="str">
@@ -6126,7 +6238,7 @@
         <v/>
       </c>
       <c r="B146" s="19" t="str">
-        <f aca="false">IF(C146="","",WORKDAY($C$5-1,A146))</f>
+        <f aca="false">IF(C146="","",WORKDAY($C$5-1,A146,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C146" s="20" t="str">
@@ -6163,7 +6275,7 @@
         <v/>
       </c>
       <c r="B147" s="19" t="str">
-        <f aca="false">IF(C147="","",WORKDAY($C$5-1,A147))</f>
+        <f aca="false">IF(C147="","",WORKDAY($C$5-1,A147,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C147" s="20" t="str">
@@ -6200,7 +6312,7 @@
         <v/>
       </c>
       <c r="B148" s="19" t="str">
-        <f aca="false">IF(C148="","",WORKDAY($C$5-1,A148))</f>
+        <f aca="false">IF(C148="","",WORKDAY($C$5-1,A148,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C148" s="20" t="str">
@@ -6237,7 +6349,7 @@
         <v/>
       </c>
       <c r="B149" s="19" t="str">
-        <f aca="false">IF(C149="","",WORKDAY($C$5-1,A149))</f>
+        <f aca="false">IF(C149="","",WORKDAY($C$5-1,A149,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C149" s="20" t="str">
@@ -6274,7 +6386,7 @@
         <v/>
       </c>
       <c r="B150" s="19" t="str">
-        <f aca="false">IF(C150="","",WORKDAY($C$5-1,A150))</f>
+        <f aca="false">IF(C150="","",WORKDAY($C$5-1,A150,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C150" s="20" t="str">
@@ -6311,7 +6423,7 @@
         <v/>
       </c>
       <c r="B151" s="19" t="str">
-        <f aca="false">IF(C151="","",WORKDAY($C$5-1,A151))</f>
+        <f aca="false">IF(C151="","",WORKDAY($C$5-1,A151,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C151" s="20" t="str">
@@ -6348,7 +6460,7 @@
         <v/>
       </c>
       <c r="B152" s="19" t="str">
-        <f aca="false">IF(C152="","",WORKDAY($C$5-1,A152))</f>
+        <f aca="false">IF(C152="","",WORKDAY($C$5-1,A152,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C152" s="20" t="str">
@@ -6385,7 +6497,7 @@
         <v/>
       </c>
       <c r="B153" s="19" t="str">
-        <f aca="false">IF(C153="","",WORKDAY($C$5-1,A153))</f>
+        <f aca="false">IF(C153="","",WORKDAY($C$5-1,A153,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C153" s="20" t="str">
@@ -6422,7 +6534,7 @@
         <v/>
       </c>
       <c r="B154" s="19" t="str">
-        <f aca="false">IF(C154="","",WORKDAY($C$5-1,A154))</f>
+        <f aca="false">IF(C154="","",WORKDAY($C$5-1,A154,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C154" s="20" t="str">
@@ -6459,7 +6571,7 @@
         <v/>
       </c>
       <c r="B155" s="19" t="str">
-        <f aca="false">IF(C155="","",WORKDAY($C$5-1,A155))</f>
+        <f aca="false">IF(C155="","",WORKDAY($C$5-1,A155,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C155" s="20" t="str">
@@ -6496,7 +6608,7 @@
         <v/>
       </c>
       <c r="B156" s="19" t="str">
-        <f aca="false">IF(C156="","",WORKDAY($C$5-1,A156))</f>
+        <f aca="false">IF(C156="","",WORKDAY($C$5-1,A156,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C156" s="20" t="str">
@@ -6533,7 +6645,7 @@
         <v/>
       </c>
       <c r="B157" s="19" t="str">
-        <f aca="false">IF(C157="","",WORKDAY($C$5-1,A157))</f>
+        <f aca="false">IF(C157="","",WORKDAY($C$5-1,A157,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C157" s="20" t="str">
@@ -6570,7 +6682,7 @@
         <v/>
       </c>
       <c r="B158" s="19" t="str">
-        <f aca="false">IF(C158="","",WORKDAY($C$5-1,A158))</f>
+        <f aca="false">IF(C158="","",WORKDAY($C$5-1,A158,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C158" s="20" t="str">
@@ -6607,7 +6719,7 @@
         <v/>
       </c>
       <c r="B159" s="19" t="str">
-        <f aca="false">IF(C159="","",WORKDAY($C$5-1,A159))</f>
+        <f aca="false">IF(C159="","",WORKDAY($C$5-1,A159,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C159" s="20" t="str">
@@ -6644,7 +6756,7 @@
         <v/>
       </c>
       <c r="B160" s="19" t="str">
-        <f aca="false">IF(C160="","",WORKDAY($C$5-1,A160))</f>
+        <f aca="false">IF(C160="","",WORKDAY($C$5-1,A160,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C160" s="20" t="str">
@@ -6681,7 +6793,7 @@
         <v/>
       </c>
       <c r="B161" s="19" t="str">
-        <f aca="false">IF(C161="","",WORKDAY($C$5-1,A161))</f>
+        <f aca="false">IF(C161="","",WORKDAY($C$5-1,A161,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C161" s="20" t="str">
@@ -6718,7 +6830,7 @@
         <v/>
       </c>
       <c r="B162" s="19" t="str">
-        <f aca="false">IF(C162="","",WORKDAY($C$5-1,A162))</f>
+        <f aca="false">IF(C162="","",WORKDAY($C$5-1,A162,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C162" s="20" t="str">
@@ -6755,7 +6867,7 @@
         <v/>
       </c>
       <c r="B163" s="19" t="str">
-        <f aca="false">IF(C163="","",WORKDAY($C$5-1,A163))</f>
+        <f aca="false">IF(C163="","",WORKDAY($C$5-1,A163,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C163" s="20" t="str">
@@ -6792,7 +6904,7 @@
         <v/>
       </c>
       <c r="B164" s="19" t="str">
-        <f aca="false">IF(C164="","",WORKDAY($C$5-1,A164))</f>
+        <f aca="false">IF(C164="","",WORKDAY($C$5-1,A164,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C164" s="20" t="str">
@@ -6829,7 +6941,7 @@
         <v/>
       </c>
       <c r="B165" s="19" t="str">
-        <f aca="false">IF(C165="","",WORKDAY($C$5-1,A165))</f>
+        <f aca="false">IF(C165="","",WORKDAY($C$5-1,A165,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C165" s="20" t="str">
@@ -6866,7 +6978,7 @@
         <v/>
       </c>
       <c r="B166" s="19" t="str">
-        <f aca="false">IF(C166="","",WORKDAY($C$5-1,A166))</f>
+        <f aca="false">IF(C166="","",WORKDAY($C$5-1,A166,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C166" s="20" t="str">
@@ -6903,7 +7015,7 @@
         <v/>
       </c>
       <c r="B167" s="19" t="str">
-        <f aca="false">IF(C167="","",WORKDAY($C$5-1,A167))</f>
+        <f aca="false">IF(C167="","",WORKDAY($C$5-1,A167,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C167" s="20" t="str">
@@ -6940,7 +7052,7 @@
         <v/>
       </c>
       <c r="B168" s="19" t="str">
-        <f aca="false">IF(C168="","",WORKDAY($C$5-1,A168))</f>
+        <f aca="false">IF(C168="","",WORKDAY($C$5-1,A168,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C168" s="20" t="str">
@@ -6977,7 +7089,7 @@
         <v/>
       </c>
       <c r="B169" s="19" t="str">
-        <f aca="false">IF(C169="","",WORKDAY($C$5-1,A169))</f>
+        <f aca="false">IF(C169="","",WORKDAY($C$5-1,A169,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C169" s="20" t="str">
@@ -7014,7 +7126,7 @@
         <v/>
       </c>
       <c r="B170" s="19" t="str">
-        <f aca="false">IF(C170="","",WORKDAY($C$5-1,A170))</f>
+        <f aca="false">IF(C170="","",WORKDAY($C$5-1,A170,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C170" s="20" t="str">
@@ -7051,7 +7163,7 @@
         <v/>
       </c>
       <c r="B171" s="19" t="str">
-        <f aca="false">IF(C171="","",WORKDAY($C$5-1,A171))</f>
+        <f aca="false">IF(C171="","",WORKDAY($C$5-1,A171,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C171" s="20" t="str">
@@ -7088,7 +7200,7 @@
         <v/>
       </c>
       <c r="B172" s="19" t="str">
-        <f aca="false">IF(C172="","",WORKDAY($C$5-1,A172))</f>
+        <f aca="false">IF(C172="","",WORKDAY($C$5-1,A172,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C172" s="20" t="str">
@@ -7125,7 +7237,7 @@
         <v/>
       </c>
       <c r="B173" s="19" t="str">
-        <f aca="false">IF(C173="","",WORKDAY($C$5-1,A173))</f>
+        <f aca="false">IF(C173="","",WORKDAY($C$5-1,A173,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C173" s="20" t="str">
@@ -7162,7 +7274,7 @@
         <v/>
       </c>
       <c r="B174" s="19" t="str">
-        <f aca="false">IF(C174="","",WORKDAY($C$5-1,A174))</f>
+        <f aca="false">IF(C174="","",WORKDAY($C$5-1,A174,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C174" s="20" t="str">
@@ -7199,7 +7311,7 @@
         <v/>
       </c>
       <c r="B175" s="19" t="str">
-        <f aca="false">IF(C175="","",WORKDAY($C$5-1,A175))</f>
+        <f aca="false">IF(C175="","",WORKDAY($C$5-1,A175,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C175" s="20" t="str">
@@ -7236,7 +7348,7 @@
         <v/>
       </c>
       <c r="B176" s="19" t="str">
-        <f aca="false">IF(C176="","",WORKDAY($C$5-1,A176))</f>
+        <f aca="false">IF(C176="","",WORKDAY($C$5-1,A176,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C176" s="20" t="str">
@@ -7273,7 +7385,7 @@
         <v/>
       </c>
       <c r="B177" s="19" t="str">
-        <f aca="false">IF(C177="","",WORKDAY($C$5-1,A177))</f>
+        <f aca="false">IF(C177="","",WORKDAY($C$5-1,A177,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C177" s="20" t="str">
@@ -7310,7 +7422,7 @@
         <v/>
       </c>
       <c r="B178" s="19" t="str">
-        <f aca="false">IF(C178="","",WORKDAY($C$5-1,A178))</f>
+        <f aca="false">IF(C178="","",WORKDAY($C$5-1,A178,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C178" s="20" t="str">
@@ -7347,7 +7459,7 @@
         <v/>
       </c>
       <c r="B179" s="19" t="str">
-        <f aca="false">IF(C179="","",WORKDAY($C$5-1,A179))</f>
+        <f aca="false">IF(C179="","",WORKDAY($C$5-1,A179,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C179" s="20" t="str">
@@ -7384,7 +7496,7 @@
         <v/>
       </c>
       <c r="B180" s="19" t="str">
-        <f aca="false">IF(C180="","",WORKDAY($C$5-1,A180))</f>
+        <f aca="false">IF(C180="","",WORKDAY($C$5-1,A180,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C180" s="20" t="str">
@@ -7421,7 +7533,7 @@
         <v/>
       </c>
       <c r="B181" s="19" t="str">
-        <f aca="false">IF(C181="","",WORKDAY($C$5-1,A181))</f>
+        <f aca="false">IF(C181="","",WORKDAY($C$5-1,A181,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C181" s="20" t="str">
@@ -7458,7 +7570,7 @@
         <v/>
       </c>
       <c r="B182" s="19" t="str">
-        <f aca="false">IF(C182="","",WORKDAY($C$5-1,A182))</f>
+        <f aca="false">IF(C182="","",WORKDAY($C$5-1,A182,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C182" s="20" t="str">
@@ -7495,7 +7607,7 @@
         <v/>
       </c>
       <c r="B183" s="19" t="str">
-        <f aca="false">IF(C183="","",WORKDAY($C$5-1,A183))</f>
+        <f aca="false">IF(C183="","",WORKDAY($C$5-1,A183,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C183" s="20" t="str">
@@ -7532,7 +7644,7 @@
         <v/>
       </c>
       <c r="B184" s="19" t="str">
-        <f aca="false">IF(C184="","",WORKDAY($C$5-1,A184))</f>
+        <f aca="false">IF(C184="","",WORKDAY($C$5-1,A184,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C184" s="20" t="str">
@@ -7569,7 +7681,7 @@
         <v/>
       </c>
       <c r="B185" s="19" t="str">
-        <f aca="false">IF(C185="","",WORKDAY($C$5-1,A185))</f>
+        <f aca="false">IF(C185="","",WORKDAY($C$5-1,A185,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C185" s="20" t="str">
@@ -7606,7 +7718,7 @@
         <v/>
       </c>
       <c r="B186" s="19" t="str">
-        <f aca="false">IF(C186="","",WORKDAY($C$5-1,A186))</f>
+        <f aca="false">IF(C186="","",WORKDAY($C$5-1,A186,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C186" s="20" t="str">
@@ -7643,7 +7755,7 @@
         <v/>
       </c>
       <c r="B187" s="19" t="str">
-        <f aca="false">IF(C187="","",WORKDAY($C$5-1,A187))</f>
+        <f aca="false">IF(C187="","",WORKDAY($C$5-1,A187,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C187" s="20" t="str">
@@ -7680,7 +7792,7 @@
         <v/>
       </c>
       <c r="B188" s="19" t="str">
-        <f aca="false">IF(C188="","",WORKDAY($C$5-1,A188))</f>
+        <f aca="false">IF(C188="","",WORKDAY($C$5-1,A188,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C188" s="20" t="str">
@@ -7717,7 +7829,7 @@
         <v/>
       </c>
       <c r="B189" s="19" t="str">
-        <f aca="false">IF(C189="","",WORKDAY($C$5-1,A189))</f>
+        <f aca="false">IF(C189="","",WORKDAY($C$5-1,A189,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C189" s="20" t="str">
@@ -7754,7 +7866,7 @@
         <v/>
       </c>
       <c r="B190" s="19" t="str">
-        <f aca="false">IF(C190="","",WORKDAY($C$5-1,A190))</f>
+        <f aca="false">IF(C190="","",WORKDAY($C$5-1,A190,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C190" s="20" t="str">
@@ -7791,7 +7903,7 @@
         <v/>
       </c>
       <c r="B191" s="19" t="str">
-        <f aca="false">IF(C191="","",WORKDAY($C$5-1,A191))</f>
+        <f aca="false">IF(C191="","",WORKDAY($C$5-1,A191,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C191" s="20" t="str">
@@ -7828,7 +7940,7 @@
         <v/>
       </c>
       <c r="B192" s="19" t="str">
-        <f aca="false">IF(C192="","",WORKDAY($C$5-1,A192))</f>
+        <f aca="false">IF(C192="","",WORKDAY($C$5-1,A192,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C192" s="20" t="str">
@@ -7865,7 +7977,7 @@
         <v/>
       </c>
       <c r="B193" s="19" t="str">
-        <f aca="false">IF(C193="","",WORKDAY($C$5-1,A193))</f>
+        <f aca="false">IF(C193="","",WORKDAY($C$5-1,A193,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C193" s="20" t="str">
@@ -7902,7 +8014,7 @@
         <v/>
       </c>
       <c r="B194" s="19" t="str">
-        <f aca="false">IF(C194="","",WORKDAY($C$5-1,A194))</f>
+        <f aca="false">IF(C194="","",WORKDAY($C$5-1,A194,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C194" s="20" t="str">
@@ -7939,7 +8051,7 @@
         <v/>
       </c>
       <c r="B195" s="19" t="str">
-        <f aca="false">IF(C195="","",WORKDAY($C$5-1,A195))</f>
+        <f aca="false">IF(C195="","",WORKDAY($C$5-1,A195,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C195" s="20" t="str">
@@ -7976,7 +8088,7 @@
         <v/>
       </c>
       <c r="B196" s="19" t="str">
-        <f aca="false">IF(C196="","",WORKDAY($C$5-1,A196))</f>
+        <f aca="false">IF(C196="","",WORKDAY($C$5-1,A196,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C196" s="20" t="str">
@@ -8013,7 +8125,7 @@
         <v/>
       </c>
       <c r="B197" s="19" t="str">
-        <f aca="false">IF(C197="","",WORKDAY($C$5-1,A197))</f>
+        <f aca="false">IF(C197="","",WORKDAY($C$5-1,A197,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C197" s="20" t="str">
@@ -8050,7 +8162,7 @@
         <v/>
       </c>
       <c r="B198" s="19" t="str">
-        <f aca="false">IF(C198="","",WORKDAY($C$5-1,A198))</f>
+        <f aca="false">IF(C198="","",WORKDAY($C$5-1,A198,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C198" s="20" t="str">
@@ -8087,7 +8199,7 @@
         <v/>
       </c>
       <c r="B199" s="19" t="str">
-        <f aca="false">IF(C199="","",WORKDAY($C$5-1,A199))</f>
+        <f aca="false">IF(C199="","",WORKDAY($C$5-1,A199,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C199" s="20" t="str">
@@ -8124,7 +8236,7 @@
         <v/>
       </c>
       <c r="B200" s="19" t="str">
-        <f aca="false">IF(C200="","",WORKDAY($C$5-1,A200))</f>
+        <f aca="false">IF(C200="","",WORKDAY($C$5-1,A200,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C200" s="20" t="str">
@@ -8161,7 +8273,7 @@
         <v/>
       </c>
       <c r="B201" s="19" t="str">
-        <f aca="false">IF(C201="","",WORKDAY($C$5-1,A201))</f>
+        <f aca="false">IF(C201="","",WORKDAY($C$5-1,A201,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C201" s="20" t="str">
@@ -8198,7 +8310,7 @@
         <v/>
       </c>
       <c r="B202" s="19" t="str">
-        <f aca="false">IF(C202="","",WORKDAY($C$5-1,A202))</f>
+        <f aca="false">IF(C202="","",WORKDAY($C$5-1,A202,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C202" s="20" t="str">
@@ -8235,7 +8347,7 @@
         <v/>
       </c>
       <c r="B203" s="19" t="str">
-        <f aca="false">IF(C203="","",WORKDAY($C$5-1,A203))</f>
+        <f aca="false">IF(C203="","",WORKDAY($C$5-1,A203,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C203" s="20" t="str">
@@ -8272,7 +8384,7 @@
         <v/>
       </c>
       <c r="B204" s="19" t="str">
-        <f aca="false">IF(C204="","",WORKDAY($C$5-1,A204))</f>
+        <f aca="false">IF(C204="","",WORKDAY($C$5-1,A204,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C204" s="20" t="str">
@@ -8309,7 +8421,7 @@
         <v/>
       </c>
       <c r="B205" s="19" t="str">
-        <f aca="false">IF(C205="","",WORKDAY($C$5-1,A205))</f>
+        <f aca="false">IF(C205="","",WORKDAY($C$5-1,A205,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C205" s="20" t="str">
@@ -8346,7 +8458,7 @@
         <v/>
       </c>
       <c r="B206" s="19" t="str">
-        <f aca="false">IF(C206="","",WORKDAY($C$5-1,A206))</f>
+        <f aca="false">IF(C206="","",WORKDAY($C$5-1,A206,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C206" s="20" t="str">
@@ -8383,7 +8495,7 @@
         <v/>
       </c>
       <c r="B207" s="19" t="str">
-        <f aca="false">IF(C207="","",WORKDAY($C$5-1,A207))</f>
+        <f aca="false">IF(C207="","",WORKDAY($C$5-1,A207,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C207" s="20" t="str">
@@ -8420,7 +8532,7 @@
         <v/>
       </c>
       <c r="B208" s="19" t="str">
-        <f aca="false">IF(C208="","",WORKDAY($C$5-1,A208))</f>
+        <f aca="false">IF(C208="","",WORKDAY($C$5-1,A208,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C208" s="20" t="str">
@@ -8457,7 +8569,7 @@
         <v/>
       </c>
       <c r="B209" s="19" t="str">
-        <f aca="false">IF(C209="","",WORKDAY($C$5-1,A209))</f>
+        <f aca="false">IF(C209="","",WORKDAY($C$5-1,A209,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C209" s="20" t="str">
@@ -8494,7 +8606,7 @@
         <v/>
       </c>
       <c r="B210" s="19" t="str">
-        <f aca="false">IF(C210="","",WORKDAY($C$5-1,A210))</f>
+        <f aca="false">IF(C210="","",WORKDAY($C$5-1,A210,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C210" s="20" t="str">
@@ -8531,7 +8643,7 @@
         <v/>
       </c>
       <c r="B211" s="19" t="str">
-        <f aca="false">IF(C211="","",WORKDAY($C$5-1,A211))</f>
+        <f aca="false">IF(C211="","",WORKDAY($C$5-1,A211,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C211" s="20" t="str">
@@ -8568,7 +8680,7 @@
         <v/>
       </c>
       <c r="B212" s="19" t="str">
-        <f aca="false">IF(C212="","",WORKDAY($C$5-1,A212))</f>
+        <f aca="false">IF(C212="","",WORKDAY($C$5-1,A212,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C212" s="20" t="str">
@@ -8605,7 +8717,7 @@
         <v/>
       </c>
       <c r="B213" s="19" t="str">
-        <f aca="false">IF(C213="","",WORKDAY($C$5-1,A213))</f>
+        <f aca="false">IF(C213="","",WORKDAY($C$5-1,A213,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C213" s="20" t="str">
@@ -8642,7 +8754,7 @@
         <v/>
       </c>
       <c r="B214" s="19" t="str">
-        <f aca="false">IF(C214="","",WORKDAY($C$5-1,A214))</f>
+        <f aca="false">IF(C214="","",WORKDAY($C$5-1,A214,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C214" s="20" t="str">
@@ -8679,7 +8791,7 @@
         <v/>
       </c>
       <c r="B215" s="19" t="str">
-        <f aca="false">IF(C215="","",WORKDAY($C$5-1,A215))</f>
+        <f aca="false">IF(C215="","",WORKDAY($C$5-1,A215,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C215" s="20" t="str">
@@ -8716,7 +8828,7 @@
         <v/>
       </c>
       <c r="B216" s="19" t="str">
-        <f aca="false">IF(C216="","",WORKDAY($C$5-1,A216))</f>
+        <f aca="false">IF(C216="","",WORKDAY($C$5-1,A216,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C216" s="20" t="str">
@@ -8753,7 +8865,7 @@
         <v/>
       </c>
       <c r="B217" s="19" t="str">
-        <f aca="false">IF(C217="","",WORKDAY($C$5-1,A217))</f>
+        <f aca="false">IF(C217="","",WORKDAY($C$5-1,A217,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C217" s="20" t="str">
@@ -8790,7 +8902,7 @@
         <v/>
       </c>
       <c r="B218" s="19" t="str">
-        <f aca="false">IF(C218="","",WORKDAY($C$5-1,A218))</f>
+        <f aca="false">IF(C218="","",WORKDAY($C$5-1,A218,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C218" s="20" t="str">
@@ -8827,7 +8939,7 @@
         <v/>
       </c>
       <c r="B219" s="19" t="str">
-        <f aca="false">IF(C219="","",WORKDAY($C$5-1,A219))</f>
+        <f aca="false">IF(C219="","",WORKDAY($C$5-1,A219,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C219" s="20" t="str">
@@ -8864,7 +8976,7 @@
         <v/>
       </c>
       <c r="B220" s="19" t="str">
-        <f aca="false">IF(C220="","",WORKDAY($C$5-1,A220))</f>
+        <f aca="false">IF(C220="","",WORKDAY($C$5-1,A220,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C220" s="20" t="str">
@@ -8901,7 +9013,7 @@
         <v/>
       </c>
       <c r="B221" s="19" t="str">
-        <f aca="false">IF(C221="","",WORKDAY($C$5-1,A221))</f>
+        <f aca="false">IF(C221="","",WORKDAY($C$5-1,A221,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C221" s="20" t="str">
@@ -8938,7 +9050,7 @@
         <v/>
       </c>
       <c r="B222" s="19" t="str">
-        <f aca="false">IF(C222="","",WORKDAY($C$5-1,A222))</f>
+        <f aca="false">IF(C222="","",WORKDAY($C$5-1,A222,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C222" s="20" t="str">
@@ -8975,7 +9087,7 @@
         <v/>
       </c>
       <c r="B223" s="19" t="str">
-        <f aca="false">IF(C223="","",WORKDAY($C$5-1,A223))</f>
+        <f aca="false">IF(C223="","",WORKDAY($C$5-1,A223,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C223" s="20" t="str">
@@ -9012,7 +9124,7 @@
         <v/>
       </c>
       <c r="B224" s="19" t="str">
-        <f aca="false">IF(C224="","",WORKDAY($C$5-1,A224))</f>
+        <f aca="false">IF(C224="","",WORKDAY($C$5-1,A224,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C224" s="20" t="str">
@@ -9049,7 +9161,7 @@
         <v/>
       </c>
       <c r="B225" s="19" t="str">
-        <f aca="false">IF(C225="","",WORKDAY($C$5-1,A225))</f>
+        <f aca="false">IF(C225="","",WORKDAY($C$5-1,A225,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C225" s="20" t="str">
@@ -9086,7 +9198,7 @@
         <v/>
       </c>
       <c r="B226" s="19" t="str">
-        <f aca="false">IF(C226="","",WORKDAY($C$5-1,A226))</f>
+        <f aca="false">IF(C226="","",WORKDAY($C$5-1,A226,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C226" s="20" t="str">
@@ -9123,7 +9235,7 @@
         <v/>
       </c>
       <c r="B227" s="19" t="str">
-        <f aca="false">IF(C227="","",WORKDAY($C$5-1,A227))</f>
+        <f aca="false">IF(C227="","",WORKDAY($C$5-1,A227,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C227" s="20" t="str">
@@ -9160,7 +9272,7 @@
         <v/>
       </c>
       <c r="B228" s="19" t="str">
-        <f aca="false">IF(C228="","",WORKDAY($C$5-1,A228))</f>
+        <f aca="false">IF(C228="","",WORKDAY($C$5-1,A228,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C228" s="20" t="str">
@@ -9197,7 +9309,7 @@
         <v/>
       </c>
       <c r="B229" s="19" t="str">
-        <f aca="false">IF(C229="","",WORKDAY($C$5-1,A229))</f>
+        <f aca="false">IF(C229="","",WORKDAY($C$5-1,A229,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C229" s="20" t="str">
@@ -9234,7 +9346,7 @@
         <v/>
       </c>
       <c r="B230" s="19" t="str">
-        <f aca="false">IF(C230="","",WORKDAY($C$5-1,A230))</f>
+        <f aca="false">IF(C230="","",WORKDAY($C$5-1,A230,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C230" s="20" t="str">
@@ -9271,7 +9383,7 @@
         <v/>
       </c>
       <c r="B231" s="19" t="str">
-        <f aca="false">IF(C231="","",WORKDAY($C$5-1,A231))</f>
+        <f aca="false">IF(C231="","",WORKDAY($C$5-1,A231,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C231" s="20" t="str">
@@ -9308,7 +9420,7 @@
         <v/>
       </c>
       <c r="B232" s="19" t="str">
-        <f aca="false">IF(C232="","",WORKDAY($C$5-1,A232))</f>
+        <f aca="false">IF(C232="","",WORKDAY($C$5-1,A232,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C232" s="20" t="str">
@@ -9345,7 +9457,7 @@
         <v/>
       </c>
       <c r="B233" s="19" t="str">
-        <f aca="false">IF(C233="","",WORKDAY($C$5-1,A233))</f>
+        <f aca="false">IF(C233="","",WORKDAY($C$5-1,A233,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C233" s="20" t="str">
@@ -9382,7 +9494,7 @@
         <v/>
       </c>
       <c r="B234" s="19" t="str">
-        <f aca="false">IF(C234="","",WORKDAY($C$5-1,A234))</f>
+        <f aca="false">IF(C234="","",WORKDAY($C$5-1,A234,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C234" s="20" t="str">
@@ -9419,7 +9531,7 @@
         <v/>
       </c>
       <c r="B235" s="19" t="str">
-        <f aca="false">IF(C235="","",WORKDAY($C$5-1,A235))</f>
+        <f aca="false">IF(C235="","",WORKDAY($C$5-1,A235,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C235" s="20" t="str">
@@ -9456,7 +9568,7 @@
         <v/>
       </c>
       <c r="B236" s="19" t="str">
-        <f aca="false">IF(C236="","",WORKDAY($C$5-1,A236))</f>
+        <f aca="false">IF(C236="","",WORKDAY($C$5-1,A236,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C236" s="20" t="str">
@@ -9493,7 +9605,7 @@
         <v/>
       </c>
       <c r="B237" s="19" t="str">
-        <f aca="false">IF(C237="","",WORKDAY($C$5-1,A237))</f>
+        <f aca="false">IF(C237="","",WORKDAY($C$5-1,A237,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C237" s="20" t="str">
@@ -9530,7 +9642,7 @@
         <v/>
       </c>
       <c r="B238" s="19" t="str">
-        <f aca="false">IF(C238="","",WORKDAY($C$5-1,A238))</f>
+        <f aca="false">IF(C238="","",WORKDAY($C$5-1,A238,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C238" s="20" t="str">
@@ -9567,7 +9679,7 @@
         <v/>
       </c>
       <c r="B239" s="19" t="str">
-        <f aca="false">IF(C239="","",WORKDAY($C$5-1,A239))</f>
+        <f aca="false">IF(C239="","",WORKDAY($C$5-1,A239,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C239" s="20" t="str">
@@ -9604,7 +9716,7 @@
         <v/>
       </c>
       <c r="B240" s="19" t="str">
-        <f aca="false">IF(C240="","",WORKDAY($C$5-1,A240))</f>
+        <f aca="false">IF(C240="","",WORKDAY($C$5-1,A240,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C240" s="20" t="str">
@@ -9641,7 +9753,7 @@
         <v/>
       </c>
       <c r="B241" s="19" t="str">
-        <f aca="false">IF(C241="","",WORKDAY($C$5-1,A241))</f>
+        <f aca="false">IF(C241="","",WORKDAY($C$5-1,A241,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C241" s="20" t="str">
@@ -9678,7 +9790,7 @@
         <v/>
       </c>
       <c r="B242" s="19" t="str">
-        <f aca="false">IF(C242="","",WORKDAY($C$5-1,A242))</f>
+        <f aca="false">IF(C242="","",WORKDAY($C$5-1,A242,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C242" s="20" t="str">
@@ -9715,7 +9827,7 @@
         <v/>
       </c>
       <c r="B243" s="19" t="str">
-        <f aca="false">IF(C243="","",WORKDAY($C$5-1,A243))</f>
+        <f aca="false">IF(C243="","",WORKDAY($C$5-1,A243,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C243" s="20" t="str">
@@ -9752,7 +9864,7 @@
         <v/>
       </c>
       <c r="B244" s="19" t="str">
-        <f aca="false">IF(C244="","",WORKDAY($C$5-1,A244))</f>
+        <f aca="false">IF(C244="","",WORKDAY($C$5-1,A244,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C244" s="20" t="str">
@@ -9789,7 +9901,7 @@
         <v/>
       </c>
       <c r="B245" s="19" t="str">
-        <f aca="false">IF(C245="","",WORKDAY($C$5-1,A245))</f>
+        <f aca="false">IF(C245="","",WORKDAY($C$5-1,A245,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C245" s="20" t="str">
@@ -9826,7 +9938,7 @@
         <v/>
       </c>
       <c r="B246" s="19" t="str">
-        <f aca="false">IF(C246="","",WORKDAY($C$5-1,A246))</f>
+        <f aca="false">IF(C246="","",WORKDAY($C$5-1,A246,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C246" s="20" t="str">
@@ -9863,7 +9975,7 @@
         <v/>
       </c>
       <c r="B247" s="19" t="str">
-        <f aca="false">IF(C247="","",WORKDAY($C$5-1,A247))</f>
+        <f aca="false">IF(C247="","",WORKDAY($C$5-1,A247,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C247" s="20" t="str">
@@ -9900,7 +10012,7 @@
         <v/>
       </c>
       <c r="B248" s="19" t="str">
-        <f aca="false">IF(C248="","",WORKDAY($C$5-1,A248))</f>
+        <f aca="false">IF(C248="","",WORKDAY($C$5-1,A248,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C248" s="20" t="str">
@@ -9937,7 +10049,7 @@
         <v/>
       </c>
       <c r="B249" s="19" t="str">
-        <f aca="false">IF(C249="","",WORKDAY($C$5-1,A249))</f>
+        <f aca="false">IF(C249="","",WORKDAY($C$5-1,A249,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C249" s="20" t="str">
@@ -9974,7 +10086,7 @@
         <v/>
       </c>
       <c r="B250" s="19" t="str">
-        <f aca="false">IF(C250="","",WORKDAY($C$5-1,A250))</f>
+        <f aca="false">IF(C250="","",WORKDAY($C$5-1,A250,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C250" s="20" t="str">
@@ -10011,7 +10123,7 @@
         <v/>
       </c>
       <c r="B251" s="19" t="str">
-        <f aca="false">IF(C251="","",WORKDAY($C$5-1,A251))</f>
+        <f aca="false">IF(C251="","",WORKDAY($C$5-1,A251,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C251" s="20" t="str">
@@ -10048,7 +10160,7 @@
         <v/>
       </c>
       <c r="B252" s="19" t="str">
-        <f aca="false">IF(C252="","",WORKDAY($C$5-1,A252))</f>
+        <f aca="false">IF(C252="","",WORKDAY($C$5-1,A252,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C252" s="20" t="str">
@@ -10085,7 +10197,7 @@
         <v/>
       </c>
       <c r="B253" s="19" t="str">
-        <f aca="false">IF(C253="","",WORKDAY($C$5-1,A253))</f>
+        <f aca="false">IF(C253="","",WORKDAY($C$5-1,A253,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C253" s="20" t="str">
@@ -10122,7 +10234,7 @@
         <v/>
       </c>
       <c r="B254" s="19" t="str">
-        <f aca="false">IF(C254="","",WORKDAY($C$5-1,A254))</f>
+        <f aca="false">IF(C254="","",WORKDAY($C$5-1,A254,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C254" s="20" t="str">
@@ -10159,7 +10271,7 @@
         <v/>
       </c>
       <c r="B255" s="19" t="str">
-        <f aca="false">IF(C255="","",WORKDAY($C$5-1,A255))</f>
+        <f aca="false">IF(C255="","",WORKDAY($C$5-1,A255,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C255" s="20" t="str">
@@ -10196,7 +10308,7 @@
         <v/>
       </c>
       <c r="B256" s="19" t="str">
-        <f aca="false">IF(C256="","",WORKDAY($C$5-1,A256))</f>
+        <f aca="false">IF(C256="","",WORKDAY($C$5-1,A256,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C256" s="20" t="str">
@@ -10233,7 +10345,7 @@
         <v/>
       </c>
       <c r="B257" s="19" t="str">
-        <f aca="false">IF(C257="","",WORKDAY($C$5-1,A257))</f>
+        <f aca="false">IF(C257="","",WORKDAY($C$5-1,A257,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C257" s="20" t="str">
@@ -10270,7 +10382,7 @@
         <v/>
       </c>
       <c r="B258" s="19" t="str">
-        <f aca="false">IF(C258="","",WORKDAY($C$5-1,A258))</f>
+        <f aca="false">IF(C258="","",WORKDAY($C$5-1,A258,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C258" s="20" t="str">
@@ -10307,7 +10419,7 @@
         <v/>
       </c>
       <c r="B259" s="19" t="str">
-        <f aca="false">IF(C259="","",WORKDAY($C$5-1,A259))</f>
+        <f aca="false">IF(C259="","",WORKDAY($C$5-1,A259,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C259" s="20" t="str">
@@ -10344,7 +10456,7 @@
         <v/>
       </c>
       <c r="B260" s="19" t="str">
-        <f aca="false">IF(C260="","",WORKDAY($C$5-1,A260))</f>
+        <f aca="false">IF(C260="","",WORKDAY($C$5-1,A260,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C260" s="20" t="str">
@@ -10381,7 +10493,7 @@
         <v/>
       </c>
       <c r="B261" s="19" t="str">
-        <f aca="false">IF(C261="","",WORKDAY($C$5-1,A261))</f>
+        <f aca="false">IF(C261="","",WORKDAY($C$5-1,A261,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C261" s="20" t="str">
@@ -10418,7 +10530,7 @@
         <v/>
       </c>
       <c r="B262" s="19" t="str">
-        <f aca="false">IF(C262="","",WORKDAY($C$5-1,A262))</f>
+        <f aca="false">IF(C262="","",WORKDAY($C$5-1,A262,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C262" s="20" t="str">
@@ -10455,7 +10567,7 @@
         <v/>
       </c>
       <c r="B263" s="19" t="str">
-        <f aca="false">IF(C263="","",WORKDAY($C$5-1,A263))</f>
+        <f aca="false">IF(C263="","",WORKDAY($C$5-1,A263,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C263" s="20" t="str">
@@ -10492,7 +10604,7 @@
         <v/>
       </c>
       <c r="B264" s="19" t="str">
-        <f aca="false">IF(C264="","",WORKDAY($C$5-1,A264))</f>
+        <f aca="false">IF(C264="","",WORKDAY($C$5-1,A264,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C264" s="20" t="str">
@@ -10529,7 +10641,7 @@
         <v/>
       </c>
       <c r="B265" s="19" t="str">
-        <f aca="false">IF(C265="","",WORKDAY($C$5-1,A265))</f>
+        <f aca="false">IF(C265="","",WORKDAY($C$5-1,A265,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C265" s="20" t="str">
@@ -10566,7 +10678,7 @@
         <v/>
       </c>
       <c r="B266" s="19" t="str">
-        <f aca="false">IF(C266="","",WORKDAY($C$5-1,A266))</f>
+        <f aca="false">IF(C266="","",WORKDAY($C$5-1,A266,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C266" s="20" t="str">
@@ -10603,7 +10715,7 @@
         <v/>
       </c>
       <c r="B267" s="19" t="str">
-        <f aca="false">IF(C267="","",WORKDAY($C$5-1,A267))</f>
+        <f aca="false">IF(C267="","",WORKDAY($C$5-1,A267,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C267" s="20" t="str">
@@ -10640,7 +10752,7 @@
         <v/>
       </c>
       <c r="B268" s="19" t="str">
-        <f aca="false">IF(C268="","",WORKDAY($C$5-1,A268))</f>
+        <f aca="false">IF(C268="","",WORKDAY($C$5-1,A268,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C268" s="20" t="str">
@@ -10677,7 +10789,7 @@
         <v/>
       </c>
       <c r="B269" s="19" t="str">
-        <f aca="false">IF(C269="","",WORKDAY($C$5-1,A269))</f>
+        <f aca="false">IF(C269="","",WORKDAY($C$5-1,A269,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C269" s="20" t="str">
@@ -10714,7 +10826,7 @@
         <v/>
       </c>
       <c r="B270" s="19" t="str">
-        <f aca="false">IF(C270="","",WORKDAY($C$5-1,A270))</f>
+        <f aca="false">IF(C270="","",WORKDAY($C$5-1,A270,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C270" s="20" t="str">
@@ -10751,7 +10863,7 @@
         <v/>
       </c>
       <c r="B271" s="19" t="str">
-        <f aca="false">IF(C271="","",WORKDAY($C$5-1,A271))</f>
+        <f aca="false">IF(C271="","",WORKDAY($C$5-1,A271,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C271" s="20" t="str">
@@ -10788,7 +10900,7 @@
         <v/>
       </c>
       <c r="B272" s="19" t="str">
-        <f aca="false">IF(C272="","",WORKDAY($C$5-1,A272))</f>
+        <f aca="false">IF(C272="","",WORKDAY($C$5-1,A272,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C272" s="20" t="str">
@@ -10825,7 +10937,7 @@
         <v/>
       </c>
       <c r="B273" s="19" t="str">
-        <f aca="false">IF(C273="","",WORKDAY($C$5-1,A273))</f>
+        <f aca="false">IF(C273="","",WORKDAY($C$5-1,A273,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C273" s="20" t="str">
@@ -10862,7 +10974,7 @@
         <v/>
       </c>
       <c r="B274" s="19" t="str">
-        <f aca="false">IF(C274="","",WORKDAY($C$5-1,A274))</f>
+        <f aca="false">IF(C274="","",WORKDAY($C$5-1,A274,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C274" s="20" t="str">
@@ -10899,7 +11011,7 @@
         <v/>
       </c>
       <c r="B275" s="19" t="str">
-        <f aca="false">IF(C275="","",WORKDAY($C$5-1,A275))</f>
+        <f aca="false">IF(C275="","",WORKDAY($C$5-1,A275,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C275" s="20" t="str">
@@ -10936,7 +11048,7 @@
         <v/>
       </c>
       <c r="B276" s="19" t="str">
-        <f aca="false">IF(C276="","",WORKDAY($C$5-1,A276))</f>
+        <f aca="false">IF(C276="","",WORKDAY($C$5-1,A276,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C276" s="20" t="str">
@@ -10973,7 +11085,7 @@
         <v/>
       </c>
       <c r="B277" s="19" t="str">
-        <f aca="false">IF(C277="","",WORKDAY($C$5-1,A277))</f>
+        <f aca="false">IF(C277="","",WORKDAY($C$5-1,A277,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C277" s="20" t="str">
@@ -11010,7 +11122,7 @@
         <v/>
       </c>
       <c r="B278" s="19" t="str">
-        <f aca="false">IF(C278="","",WORKDAY($C$5-1,A278))</f>
+        <f aca="false">IF(C278="","",WORKDAY($C$5-1,A278,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C278" s="20" t="str">
@@ -11047,7 +11159,7 @@
         <v/>
       </c>
       <c r="B279" s="19" t="str">
-        <f aca="false">IF(C279="","",WORKDAY($C$5-1,A279))</f>
+        <f aca="false">IF(C279="","",WORKDAY($C$5-1,A279,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C279" s="20" t="str">
@@ -11084,7 +11196,7 @@
         <v/>
       </c>
       <c r="B280" s="19" t="str">
-        <f aca="false">IF(C280="","",WORKDAY($C$5-1,A280))</f>
+        <f aca="false">IF(C280="","",WORKDAY($C$5-1,A280,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C280" s="20" t="str">
@@ -11121,7 +11233,7 @@
         <v/>
       </c>
       <c r="B281" s="19" t="str">
-        <f aca="false">IF(C281="","",WORKDAY($C$5-1,A281))</f>
+        <f aca="false">IF(C281="","",WORKDAY($C$5-1,A281,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C281" s="20" t="str">
@@ -11158,7 +11270,7 @@
         <v/>
       </c>
       <c r="B282" s="19" t="str">
-        <f aca="false">IF(C282="","",WORKDAY($C$5-1,A282))</f>
+        <f aca="false">IF(C282="","",WORKDAY($C$5-1,A282,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C282" s="20" t="str">
@@ -11195,7 +11307,7 @@
         <v/>
       </c>
       <c r="B283" s="19" t="str">
-        <f aca="false">IF(C283="","",WORKDAY($C$5-1,A283))</f>
+        <f aca="false">IF(C283="","",WORKDAY($C$5-1,A283,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C283" s="20" t="str">
@@ -11232,7 +11344,7 @@
         <v/>
       </c>
       <c r="B284" s="19" t="str">
-        <f aca="false">IF(C284="","",WORKDAY($C$5-1,A284))</f>
+        <f aca="false">IF(C284="","",WORKDAY($C$5-1,A284,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C284" s="20" t="str">
@@ -11269,7 +11381,7 @@
         <v/>
       </c>
       <c r="B285" s="19" t="str">
-        <f aca="false">IF(C285="","",WORKDAY($C$5-1,A285))</f>
+        <f aca="false">IF(C285="","",WORKDAY($C$5-1,A285,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C285" s="20" t="str">
@@ -11306,7 +11418,7 @@
         <v/>
       </c>
       <c r="B286" s="19" t="str">
-        <f aca="false">IF(C286="","",WORKDAY($C$5-1,A286))</f>
+        <f aca="false">IF(C286="","",WORKDAY($C$5-1,A286,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C286" s="20" t="str">
@@ -11343,7 +11455,7 @@
         <v/>
       </c>
       <c r="B287" s="19" t="str">
-        <f aca="false">IF(C287="","",WORKDAY($C$5-1,A287))</f>
+        <f aca="false">IF(C287="","",WORKDAY($C$5-1,A287,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C287" s="20" t="str">
@@ -11380,7 +11492,7 @@
         <v/>
       </c>
       <c r="B288" s="19" t="str">
-        <f aca="false">IF(C288="","",WORKDAY($C$5-1,A288))</f>
+        <f aca="false">IF(C288="","",WORKDAY($C$5-1,A288,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C288" s="20" t="str">
@@ -11417,7 +11529,7 @@
         <v/>
       </c>
       <c r="B289" s="19" t="str">
-        <f aca="false">IF(C289="","",WORKDAY($C$5-1,A289))</f>
+        <f aca="false">IF(C289="","",WORKDAY($C$5-1,A289,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C289" s="20" t="str">
@@ -11454,7 +11566,7 @@
         <v/>
       </c>
       <c r="B290" s="19" t="str">
-        <f aca="false">IF(C290="","",WORKDAY($C$5-1,A290))</f>
+        <f aca="false">IF(C290="","",WORKDAY($C$5-1,A290,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C290" s="20" t="str">
@@ -11491,7 +11603,7 @@
         <v/>
       </c>
       <c r="B291" s="19" t="str">
-        <f aca="false">IF(C291="","",WORKDAY($C$5-1,A291))</f>
+        <f aca="false">IF(C291="","",WORKDAY($C$5-1,A291,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C291" s="20" t="str">
@@ -11528,7 +11640,7 @@
         <v/>
       </c>
       <c r="B292" s="19" t="str">
-        <f aca="false">IF(C292="","",WORKDAY($C$5-1,A292))</f>
+        <f aca="false">IF(C292="","",WORKDAY($C$5-1,A292,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C292" s="20" t="str">
@@ -11565,7 +11677,7 @@
         <v/>
       </c>
       <c r="B293" s="19" t="str">
-        <f aca="false">IF(C293="","",WORKDAY($C$5-1,A293))</f>
+        <f aca="false">IF(C293="","",WORKDAY($C$5-1,A293,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C293" s="20" t="str">
@@ -11602,7 +11714,7 @@
         <v/>
       </c>
       <c r="B294" s="19" t="str">
-        <f aca="false">IF(C294="","",WORKDAY($C$5-1,A294))</f>
+        <f aca="false">IF(C294="","",WORKDAY($C$5-1,A294,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C294" s="20" t="str">
@@ -11639,7 +11751,7 @@
         <v/>
       </c>
       <c r="B295" s="19" t="str">
-        <f aca="false">IF(C295="","",WORKDAY($C$5-1,A295))</f>
+        <f aca="false">IF(C295="","",WORKDAY($C$5-1,A295,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C295" s="20" t="str">
@@ -11676,7 +11788,7 @@
         <v/>
       </c>
       <c r="B296" s="19" t="str">
-        <f aca="false">IF(C296="","",WORKDAY($C$5-1,A296))</f>
+        <f aca="false">IF(C296="","",WORKDAY($C$5-1,A296,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C296" s="20" t="str">
@@ -11713,7 +11825,7 @@
         <v/>
       </c>
       <c r="B297" s="19" t="str">
-        <f aca="false">IF(C297="","",WORKDAY($C$5-1,A297))</f>
+        <f aca="false">IF(C297="","",WORKDAY($C$5-1,A297,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C297" s="20" t="str">
@@ -11750,7 +11862,7 @@
         <v/>
       </c>
       <c r="B298" s="19" t="str">
-        <f aca="false">IF(C298="","",WORKDAY($C$5-1,A298))</f>
+        <f aca="false">IF(C298="","",WORKDAY($C$5-1,A298,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C298" s="20" t="str">
@@ -11787,7 +11899,7 @@
         <v/>
       </c>
       <c r="B299" s="19" t="str">
-        <f aca="false">IF(C299="","",WORKDAY($C$5-1,A299))</f>
+        <f aca="false">IF(C299="","",WORKDAY($C$5-1,A299,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C299" s="20" t="str">
@@ -11824,7 +11936,7 @@
         <v/>
       </c>
       <c r="B300" s="19" t="str">
-        <f aca="false">IF(C300="","",WORKDAY($C$5-1,A300))</f>
+        <f aca="false">IF(C300="","",WORKDAY($C$5-1,A300,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C300" s="20" t="str">
@@ -11861,7 +11973,7 @@
         <v/>
       </c>
       <c r="B301" s="19" t="str">
-        <f aca="false">IF(C301="","",WORKDAY($C$5-1,A301))</f>
+        <f aca="false">IF(C301="","",WORKDAY($C$5-1,A301,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C301" s="20" t="str">
@@ -11898,7 +12010,7 @@
         <v/>
       </c>
       <c r="B302" s="19" t="str">
-        <f aca="false">IF(C302="","",WORKDAY($C$5-1,A302))</f>
+        <f aca="false">IF(C302="","",WORKDAY($C$5-1,A302,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C302" s="20" t="str">
@@ -11935,7 +12047,7 @@
         <v/>
       </c>
       <c r="B303" s="19" t="str">
-        <f aca="false">IF(C303="","",WORKDAY($C$5-1,A303))</f>
+        <f aca="false">IF(C303="","",WORKDAY($C$5-1,A303,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C303" s="20" t="str">
@@ -11972,7 +12084,7 @@
         <v/>
       </c>
       <c r="B304" s="19" t="str">
-        <f aca="false">IF(C304="","",WORKDAY($C$5-1,A304))</f>
+        <f aca="false">IF(C304="","",WORKDAY($C$5-1,A304,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C304" s="20" t="str">
@@ -12009,7 +12121,7 @@
         <v/>
       </c>
       <c r="B305" s="19" t="str">
-        <f aca="false">IF(C305="","",WORKDAY($C$5-1,A305))</f>
+        <f aca="false">IF(C305="","",WORKDAY($C$5-1,A305,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C305" s="20" t="str">
@@ -12046,7 +12158,7 @@
         <v/>
       </c>
       <c r="B306" s="19" t="str">
-        <f aca="false">IF(C306="","",WORKDAY($C$5-1,A306))</f>
+        <f aca="false">IF(C306="","",WORKDAY($C$5-1,A306,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C306" s="20" t="str">
@@ -12083,7 +12195,7 @@
         <v/>
       </c>
       <c r="B307" s="19" t="str">
-        <f aca="false">IF(C307="","",WORKDAY($C$5-1,A307))</f>
+        <f aca="false">IF(C307="","",WORKDAY($C$5-1,A307,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C307" s="20" t="str">
@@ -12120,7 +12232,7 @@
         <v/>
       </c>
       <c r="B308" s="19" t="str">
-        <f aca="false">IF(C308="","",WORKDAY($C$5-1,A308))</f>
+        <f aca="false">IF(C308="","",WORKDAY($C$5-1,A308,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C308" s="20" t="str">
@@ -12157,7 +12269,7 @@
         <v/>
       </c>
       <c r="B309" s="19" t="str">
-        <f aca="false">IF(C309="","",WORKDAY($C$5-1,A309))</f>
+        <f aca="false">IF(C309="","",WORKDAY($C$5-1,A309,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C309" s="20" t="str">
@@ -12194,7 +12306,7 @@
         <v/>
       </c>
       <c r="B310" s="19" t="str">
-        <f aca="false">IF(C310="","",WORKDAY($C$5-1,A310))</f>
+        <f aca="false">IF(C310="","",WORKDAY($C$5-1,A310,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C310" s="20" t="str">
@@ -12231,7 +12343,7 @@
         <v/>
       </c>
       <c r="B311" s="19" t="str">
-        <f aca="false">IF(C311="","",WORKDAY($C$5-1,A311))</f>
+        <f aca="false">IF(C311="","",WORKDAY($C$5-1,A311,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C311" s="20" t="str">
@@ -12268,7 +12380,7 @@
         <v/>
       </c>
       <c r="B312" s="19" t="str">
-        <f aca="false">IF(C312="","",WORKDAY($C$5-1,A312))</f>
+        <f aca="false">IF(C312="","",WORKDAY($C$5-1,A312,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C312" s="20" t="str">
@@ -12305,7 +12417,7 @@
         <v/>
       </c>
       <c r="B313" s="19" t="str">
-        <f aca="false">IF(C313="","",WORKDAY($C$5-1,A313))</f>
+        <f aca="false">IF(C313="","",WORKDAY($C$5-1,A313,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C313" s="20" t="str">
@@ -12342,7 +12454,7 @@
         <v/>
       </c>
       <c r="B314" s="19" t="str">
-        <f aca="false">IF(C314="","",WORKDAY($C$5-1,A314))</f>
+        <f aca="false">IF(C314="","",WORKDAY($C$5-1,A314,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C314" s="20" t="str">
@@ -12379,7 +12491,7 @@
         <v/>
       </c>
       <c r="B315" s="19" t="str">
-        <f aca="false">IF(C315="","",WORKDAY($C$5-1,A315))</f>
+        <f aca="false">IF(C315="","",WORKDAY($C$5-1,A315,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C315" s="20" t="str">
@@ -12416,7 +12528,7 @@
         <v/>
       </c>
       <c r="B316" s="19" t="str">
-        <f aca="false">IF(C316="","",WORKDAY($C$5-1,A316))</f>
+        <f aca="false">IF(C316="","",WORKDAY($C$5-1,A316,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C316" s="20" t="str">
@@ -12453,7 +12565,7 @@
         <v/>
       </c>
       <c r="B317" s="19" t="str">
-        <f aca="false">IF(C317="","",WORKDAY($C$5-1,A317))</f>
+        <f aca="false">IF(C317="","",WORKDAY($C$5-1,A317,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C317" s="20" t="str">
@@ -12490,7 +12602,7 @@
         <v/>
       </c>
       <c r="B318" s="19" t="str">
-        <f aca="false">IF(C318="","",WORKDAY($C$5-1,A318))</f>
+        <f aca="false">IF(C318="","",WORKDAY($C$5-1,A318,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C318" s="20" t="str">
@@ -12527,7 +12639,7 @@
         <v/>
       </c>
       <c r="B319" s="19" t="str">
-        <f aca="false">IF(C319="","",WORKDAY($C$5-1,A319))</f>
+        <f aca="false">IF(C319="","",WORKDAY($C$5-1,A319,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C319" s="20" t="str">
@@ -12564,7 +12676,7 @@
         <v/>
       </c>
       <c r="B320" s="19" t="str">
-        <f aca="false">IF(C320="","",WORKDAY($C$5-1,A320))</f>
+        <f aca="false">IF(C320="","",WORKDAY($C$5-1,A320,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C320" s="20" t="str">
@@ -12601,7 +12713,7 @@
         <v/>
       </c>
       <c r="B321" s="19" t="str">
-        <f aca="false">IF(C321="","",WORKDAY($C$5-1,A321))</f>
+        <f aca="false">IF(C321="","",WORKDAY($C$5-1,A321,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C321" s="20" t="str">
@@ -12638,7 +12750,7 @@
         <v/>
       </c>
       <c r="B322" s="19" t="str">
-        <f aca="false">IF(C322="","",WORKDAY($C$5-1,A322))</f>
+        <f aca="false">IF(C322="","",WORKDAY($C$5-1,A322,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C322" s="20" t="str">
@@ -12675,7 +12787,7 @@
         <v/>
       </c>
       <c r="B323" s="19" t="str">
-        <f aca="false">IF(C323="","",WORKDAY($C$5-1,A323))</f>
+        <f aca="false">IF(C323="","",WORKDAY($C$5-1,A323,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C323" s="20" t="str">
@@ -12712,7 +12824,7 @@
         <v/>
       </c>
       <c r="B324" s="19" t="str">
-        <f aca="false">IF(C324="","",WORKDAY($C$5-1,A324))</f>
+        <f aca="false">IF(C324="","",WORKDAY($C$5-1,A324,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C324" s="20" t="str">
@@ -12749,7 +12861,7 @@
         <v/>
       </c>
       <c r="B325" s="19" t="str">
-        <f aca="false">IF(C325="","",WORKDAY($C$5-1,A325))</f>
+        <f aca="false">IF(C325="","",WORKDAY($C$5-1,A325,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C325" s="20" t="str">
@@ -12786,7 +12898,7 @@
         <v/>
       </c>
       <c r="B326" s="19" t="str">
-        <f aca="false">IF(C326="","",WORKDAY($C$5-1,A326))</f>
+        <f aca="false">IF(C326="","",WORKDAY($C$5-1,A326,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C326" s="20" t="str">
@@ -12823,7 +12935,7 @@
         <v/>
       </c>
       <c r="B327" s="19" t="str">
-        <f aca="false">IF(C327="","",WORKDAY($C$5-1,A327))</f>
+        <f aca="false">IF(C327="","",WORKDAY($C$5-1,A327,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C327" s="20" t="str">
@@ -12860,7 +12972,7 @@
         <v/>
       </c>
       <c r="B328" s="19" t="str">
-        <f aca="false">IF(C328="","",WORKDAY($C$5-1,A328))</f>
+        <f aca="false">IF(C328="","",WORKDAY($C$5-1,A328,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C328" s="20" t="str">
@@ -12897,7 +13009,7 @@
         <v/>
       </c>
       <c r="B329" s="19" t="str">
-        <f aca="false">IF(C329="","",WORKDAY($C$5-1,A329))</f>
+        <f aca="false">IF(C329="","",WORKDAY($C$5-1,A329,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C329" s="20" t="str">
@@ -12934,7 +13046,7 @@
         <v/>
       </c>
       <c r="B330" s="19" t="str">
-        <f aca="false">IF(C330="","",WORKDAY($C$5-1,A330))</f>
+        <f aca="false">IF(C330="","",WORKDAY($C$5-1,A330,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C330" s="20" t="str">
@@ -12971,7 +13083,7 @@
         <v/>
       </c>
       <c r="B331" s="19" t="str">
-        <f aca="false">IF(C331="","",WORKDAY($C$5-1,A331))</f>
+        <f aca="false">IF(C331="","",WORKDAY($C$5-1,A331,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C331" s="20" t="str">
@@ -13008,7 +13120,7 @@
         <v/>
       </c>
       <c r="B332" s="19" t="str">
-        <f aca="false">IF(C332="","",WORKDAY($C$5-1,A332))</f>
+        <f aca="false">IF(C332="","",WORKDAY($C$5-1,A332,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C332" s="20" t="str">
@@ -13045,7 +13157,7 @@
         <v/>
       </c>
       <c r="B333" s="19" t="str">
-        <f aca="false">IF(C333="","",WORKDAY($C$5-1,A333))</f>
+        <f aca="false">IF(C333="","",WORKDAY($C$5-1,A333,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C333" s="20" t="str">
@@ -13082,7 +13194,7 @@
         <v/>
       </c>
       <c r="B334" s="19" t="str">
-        <f aca="false">IF(C334="","",WORKDAY($C$5-1,A334))</f>
+        <f aca="false">IF(C334="","",WORKDAY($C$5-1,A334,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C334" s="20" t="str">
@@ -13119,7 +13231,7 @@
         <v/>
       </c>
       <c r="B335" s="19" t="str">
-        <f aca="false">IF(C335="","",WORKDAY($C$5-1,A335))</f>
+        <f aca="false">IF(C335="","",WORKDAY($C$5-1,A335,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C335" s="20" t="str">
@@ -13156,7 +13268,7 @@
         <v/>
       </c>
       <c r="B336" s="19" t="str">
-        <f aca="false">IF(C336="","",WORKDAY($C$5-1,A336))</f>
+        <f aca="false">IF(C336="","",WORKDAY($C$5-1,A336,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C336" s="20" t="str">
@@ -13193,7 +13305,7 @@
         <v/>
       </c>
       <c r="B337" s="19" t="str">
-        <f aca="false">IF(C337="","",WORKDAY($C$5-1,A337))</f>
+        <f aca="false">IF(C337="","",WORKDAY($C$5-1,A337,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C337" s="20" t="str">
@@ -13230,7 +13342,7 @@
         <v/>
       </c>
       <c r="B338" s="19" t="str">
-        <f aca="false">IF(C338="","",WORKDAY($C$5-1,A338))</f>
+        <f aca="false">IF(C338="","",WORKDAY($C$5-1,A338,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C338" s="20" t="str">
@@ -13267,7 +13379,7 @@
         <v/>
       </c>
       <c r="B339" s="19" t="str">
-        <f aca="false">IF(C339="","",WORKDAY($C$5-1,A339))</f>
+        <f aca="false">IF(C339="","",WORKDAY($C$5-1,A339,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C339" s="20" t="str">
@@ -13304,7 +13416,7 @@
         <v/>
       </c>
       <c r="B340" s="19" t="str">
-        <f aca="false">IF(C340="","",WORKDAY($C$5-1,A340))</f>
+        <f aca="false">IF(C340="","",WORKDAY($C$5-1,A340,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C340" s="20" t="str">
@@ -13341,7 +13453,7 @@
         <v/>
       </c>
       <c r="B341" s="19" t="str">
-        <f aca="false">IF(C341="","",WORKDAY($C$5-1,A341))</f>
+        <f aca="false">IF(C341="","",WORKDAY($C$5-1,A341,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C341" s="20" t="str">
@@ -13378,7 +13490,7 @@
         <v/>
       </c>
       <c r="B342" s="19" t="str">
-        <f aca="false">IF(C342="","",WORKDAY($C$5-1,A342))</f>
+        <f aca="false">IF(C342="","",WORKDAY($C$5-1,A342,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C342" s="20" t="str">
@@ -13415,7 +13527,7 @@
         <v/>
       </c>
       <c r="B343" s="19" t="str">
-        <f aca="false">IF(C343="","",WORKDAY($C$5-1,A343))</f>
+        <f aca="false">IF(C343="","",WORKDAY($C$5-1,A343,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C343" s="20" t="str">
@@ -13452,7 +13564,7 @@
         <v/>
       </c>
       <c r="B344" s="19" t="str">
-        <f aca="false">IF(C344="","",WORKDAY($C$5-1,A344))</f>
+        <f aca="false">IF(C344="","",WORKDAY($C$5-1,A344,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C344" s="20" t="str">
@@ -13489,7 +13601,7 @@
         <v/>
       </c>
       <c r="B345" s="19" t="str">
-        <f aca="false">IF(C345="","",WORKDAY($C$5-1,A345))</f>
+        <f aca="false">IF(C345="","",WORKDAY($C$5-1,A345,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C345" s="20" t="str">
@@ -13526,7 +13638,7 @@
         <v/>
       </c>
       <c r="B346" s="19" t="str">
-        <f aca="false">IF(C346="","",WORKDAY($C$5-1,A346))</f>
+        <f aca="false">IF(C346="","",WORKDAY($C$5-1,A346,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C346" s="20" t="str">
@@ -13563,7 +13675,7 @@
         <v/>
       </c>
       <c r="B347" s="19" t="str">
-        <f aca="false">IF(C347="","",WORKDAY($C$5-1,A347))</f>
+        <f aca="false">IF(C347="","",WORKDAY($C$5-1,A347,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C347" s="20" t="str">
@@ -13600,7 +13712,7 @@
         <v/>
       </c>
       <c r="B348" s="19" t="str">
-        <f aca="false">IF(C348="","",WORKDAY($C$5-1,A348))</f>
+        <f aca="false">IF(C348="","",WORKDAY($C$5-1,A348,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C348" s="20" t="str">
@@ -13637,7 +13749,7 @@
         <v/>
       </c>
       <c r="B349" s="19" t="str">
-        <f aca="false">IF(C349="","",WORKDAY($C$5-1,A349))</f>
+        <f aca="false">IF(C349="","",WORKDAY($C$5-1,A349,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C349" s="20" t="str">
@@ -13674,7 +13786,7 @@
         <v/>
       </c>
       <c r="B350" s="19" t="str">
-        <f aca="false">IF(C350="","",WORKDAY($C$5-1,A350))</f>
+        <f aca="false">IF(C350="","",WORKDAY($C$5-1,A350,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C350" s="20" t="str">
@@ -13711,7 +13823,7 @@
         <v/>
       </c>
       <c r="B351" s="19" t="str">
-        <f aca="false">IF(C351="","",WORKDAY($C$5-1,A351))</f>
+        <f aca="false">IF(C351="","",WORKDAY($C$5-1,A351,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C351" s="20" t="str">
@@ -13748,7 +13860,7 @@
         <v/>
       </c>
       <c r="B352" s="19" t="str">
-        <f aca="false">IF(C352="","",WORKDAY($C$5-1,A352))</f>
+        <f aca="false">IF(C352="","",WORKDAY($C$5-1,A352,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C352" s="20" t="str">
@@ -13785,7 +13897,7 @@
         <v/>
       </c>
       <c r="B353" s="19" t="str">
-        <f aca="false">IF(C353="","",WORKDAY($C$5-1,A353))</f>
+        <f aca="false">IF(C353="","",WORKDAY($C$5-1,A353,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C353" s="20" t="str">
@@ -13822,7 +13934,7 @@
         <v/>
       </c>
       <c r="B354" s="19" t="str">
-        <f aca="false">IF(C354="","",WORKDAY($C$5-1,A354))</f>
+        <f aca="false">IF(C354="","",WORKDAY($C$5-1,A354,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C354" s="20" t="str">
@@ -13859,7 +13971,7 @@
         <v/>
       </c>
       <c r="B355" s="19" t="str">
-        <f aca="false">IF(C355="","",WORKDAY($C$5-1,A355))</f>
+        <f aca="false">IF(C355="","",WORKDAY($C$5-1,A355,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C355" s="20" t="str">
@@ -13896,7 +14008,7 @@
         <v/>
       </c>
       <c r="B356" s="19" t="str">
-        <f aca="false">IF(C356="","",WORKDAY($C$5-1,A356))</f>
+        <f aca="false">IF(C356="","",WORKDAY($C$5-1,A356,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C356" s="20" t="str">
@@ -13933,7 +14045,7 @@
         <v/>
       </c>
       <c r="B357" s="19" t="str">
-        <f aca="false">IF(C357="","",WORKDAY($C$5-1,A357))</f>
+        <f aca="false">IF(C357="","",WORKDAY($C$5-1,A357,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C357" s="20" t="str">
@@ -13970,7 +14082,7 @@
         <v/>
       </c>
       <c r="B358" s="19" t="str">
-        <f aca="false">IF(C358="","",WORKDAY($C$5-1,A358))</f>
+        <f aca="false">IF(C358="","",WORKDAY($C$5-1,A358,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C358" s="20" t="str">
@@ -14007,7 +14119,7 @@
         <v/>
       </c>
       <c r="B359" s="19" t="str">
-        <f aca="false">IF(C359="","",WORKDAY($C$5-1,A359))</f>
+        <f aca="false">IF(C359="","",WORKDAY($C$5-1,A359,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C359" s="20" t="str">
@@ -14044,7 +14156,7 @@
         <v/>
       </c>
       <c r="B360" s="19" t="str">
-        <f aca="false">IF(C360="","",WORKDAY($C$5-1,A360))</f>
+        <f aca="false">IF(C360="","",WORKDAY($C$5-1,A360,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C360" s="20" t="str">
@@ -14081,7 +14193,7 @@
         <v/>
       </c>
       <c r="B361" s="19" t="str">
-        <f aca="false">IF(C361="","",WORKDAY($C$5-1,A361))</f>
+        <f aca="false">IF(C361="","",WORKDAY($C$5-1,A361,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C361" s="20" t="str">
@@ -14118,7 +14230,7 @@
         <v/>
       </c>
       <c r="B362" s="19" t="str">
-        <f aca="false">IF(C362="","",WORKDAY($C$5-1,A362))</f>
+        <f aca="false">IF(C362="","",WORKDAY($C$5-1,A362,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C362" s="20" t="str">
@@ -14155,7 +14267,7 @@
         <v/>
       </c>
       <c r="B363" s="19" t="str">
-        <f aca="false">IF(C363="","",WORKDAY($C$5-1,A363))</f>
+        <f aca="false">IF(C363="","",WORKDAY($C$5-1,A363,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C363" s="20" t="str">
@@ -14192,7 +14304,7 @@
         <v/>
       </c>
       <c r="B364" s="19" t="str">
-        <f aca="false">IF(C364="","",WORKDAY($C$5-1,A364))</f>
+        <f aca="false">IF(C364="","",WORKDAY($C$5-1,A364,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C364" s="20" t="str">
@@ -14229,7 +14341,7 @@
         <v/>
       </c>
       <c r="B365" s="19" t="str">
-        <f aca="false">IF(C365="","",WORKDAY($C$5-1,A365))</f>
+        <f aca="false">IF(C365="","",WORKDAY($C$5-1,A365,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C365" s="20" t="str">
@@ -14266,7 +14378,7 @@
         <v/>
       </c>
       <c r="B366" s="19" t="str">
-        <f aca="false">IF(C366="","",WORKDAY($C$5-1,A366))</f>
+        <f aca="false">IF(C366="","",WORKDAY($C$5-1,A366,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C366" s="20" t="str">
@@ -14303,7 +14415,7 @@
         <v/>
       </c>
       <c r="B367" s="19" t="str">
-        <f aca="false">IF(C367="","",WORKDAY($C$5-1,A367))</f>
+        <f aca="false">IF(C367="","",WORKDAY($C$5-1,A367,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C367" s="20" t="str">
@@ -14340,7 +14452,7 @@
         <v/>
       </c>
       <c r="B368" s="19" t="str">
-        <f aca="false">IF(C368="","",WORKDAY($C$5-1,A368))</f>
+        <f aca="false">IF(C368="","",WORKDAY($C$5-1,A368,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C368" s="20" t="str">
@@ -14377,7 +14489,7 @@
         <v/>
       </c>
       <c r="B369" s="19" t="str">
-        <f aca="false">IF(C369="","",WORKDAY($C$5-1,A369))</f>
+        <f aca="false">IF(C369="","",WORKDAY($C$5-1,A369,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C369" s="20" t="str">
@@ -14414,7 +14526,7 @@
         <v/>
       </c>
       <c r="B370" s="19" t="str">
-        <f aca="false">IF(C370="","",WORKDAY($C$5-1,A370))</f>
+        <f aca="false">IF(C370="","",WORKDAY($C$5-1,A370,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C370" s="20" t="str">
@@ -14451,7 +14563,7 @@
         <v/>
       </c>
       <c r="B371" s="19" t="str">
-        <f aca="false">IF(C371="","",WORKDAY($C$5-1,A371))</f>
+        <f aca="false">IF(C371="","",WORKDAY($C$5-1,A371,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C371" s="20" t="str">
@@ -14488,7 +14600,7 @@
         <v/>
       </c>
       <c r="B372" s="19" t="str">
-        <f aca="false">IF(C372="","",WORKDAY($C$5-1,A372))</f>
+        <f aca="false">IF(C372="","",WORKDAY($C$5-1,A372,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C372" s="20" t="str">
@@ -14525,7 +14637,7 @@
         <v/>
       </c>
       <c r="B373" s="19" t="str">
-        <f aca="false">IF(C373="","",WORKDAY($C$5-1,A373))</f>
+        <f aca="false">IF(C373="","",WORKDAY($C$5-1,A373,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C373" s="20" t="str">
@@ -14562,7 +14674,7 @@
         <v/>
       </c>
       <c r="B374" s="19" t="str">
-        <f aca="false">IF(C374="","",WORKDAY($C$5-1,A374))</f>
+        <f aca="false">IF(C374="","",WORKDAY($C$5-1,A374,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C374" s="20" t="str">
@@ -14599,7 +14711,7 @@
         <v/>
       </c>
       <c r="B375" s="19" t="str">
-        <f aca="false">IF(C375="","",WORKDAY($C$5-1,A375))</f>
+        <f aca="false">IF(C375="","",WORKDAY($C$5-1,A375,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C375" s="20" t="str">
@@ -14636,7 +14748,7 @@
         <v/>
       </c>
       <c r="B376" s="19" t="str">
-        <f aca="false">IF(C376="","",WORKDAY($C$5-1,A376))</f>
+        <f aca="false">IF(C376="","",WORKDAY($C$5-1,A376,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C376" s="20" t="str">
@@ -14673,7 +14785,7 @@
         <v/>
       </c>
       <c r="B377" s="19" t="str">
-        <f aca="false">IF(C377="","",WORKDAY($C$5-1,A377))</f>
+        <f aca="false">IF(C377="","",WORKDAY($C$5-1,A377,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C377" s="20" t="str">
@@ -14710,7 +14822,7 @@
         <v/>
       </c>
       <c r="B378" s="19" t="str">
-        <f aca="false">IF(C378="","",WORKDAY($C$5-1,A378))</f>
+        <f aca="false">IF(C378="","",WORKDAY($C$5-1,A378,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C378" s="20" t="str">
@@ -14747,7 +14859,7 @@
         <v/>
       </c>
       <c r="B379" s="19" t="str">
-        <f aca="false">IF(C379="","",WORKDAY($C$5-1,A379))</f>
+        <f aca="false">IF(C379="","",WORKDAY($C$5-1,A379,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C379" s="20" t="str">
@@ -14784,7 +14896,7 @@
         <v/>
       </c>
       <c r="B380" s="19" t="str">
-        <f aca="false">IF(C380="","",WORKDAY($C$5-1,A380))</f>
+        <f aca="false">IF(C380="","",WORKDAY($C$5-1,A380,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C380" s="20" t="str">
@@ -14821,7 +14933,7 @@
         <v/>
       </c>
       <c r="B381" s="19" t="str">
-        <f aca="false">IF(C381="","",WORKDAY($C$5-1,A381))</f>
+        <f aca="false">IF(C381="","",WORKDAY($C$5-1,A381,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C381" s="20" t="str">
@@ -14858,7 +14970,7 @@
         <v/>
       </c>
       <c r="B382" s="19" t="str">
-        <f aca="false">IF(C382="","",WORKDAY($C$5-1,A382))</f>
+        <f aca="false">IF(C382="","",WORKDAY($C$5-1,A382,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C382" s="20" t="str">
@@ -14895,7 +15007,7 @@
         <v/>
       </c>
       <c r="B383" s="19" t="str">
-        <f aca="false">IF(C383="","",WORKDAY($C$5-1,A383))</f>
+        <f aca="false">IF(C383="","",WORKDAY($C$5-1,A383,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C383" s="20" t="str">
@@ -14932,7 +15044,7 @@
         <v/>
       </c>
       <c r="B384" s="19" t="str">
-        <f aca="false">IF(C384="","",WORKDAY($C$5-1,A384))</f>
+        <f aca="false">IF(C384="","",WORKDAY($C$5-1,A384,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C384" s="20" t="str">
@@ -14969,7 +15081,7 @@
         <v/>
       </c>
       <c r="B385" s="19" t="str">
-        <f aca="false">IF(C385="","",WORKDAY($C$5-1,A385))</f>
+        <f aca="false">IF(C385="","",WORKDAY($C$5-1,A385,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C385" s="20" t="str">
@@ -15006,7 +15118,7 @@
         <v/>
       </c>
       <c r="B386" s="19" t="str">
-        <f aca="false">IF(C386="","",WORKDAY($C$5-1,A386))</f>
+        <f aca="false">IF(C386="","",WORKDAY($C$5-1,A386,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C386" s="20" t="str">
@@ -15043,7 +15155,7 @@
         <v/>
       </c>
       <c r="B387" s="19" t="str">
-        <f aca="false">IF(C387="","",WORKDAY($C$5-1,A387))</f>
+        <f aca="false">IF(C387="","",WORKDAY($C$5-1,A387,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C387" s="20" t="str">
@@ -15080,7 +15192,7 @@
         <v/>
       </c>
       <c r="B388" s="19" t="str">
-        <f aca="false">IF(C388="","",WORKDAY($C$5-1,A388))</f>
+        <f aca="false">IF(C388="","",WORKDAY($C$5-1,A388,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C388" s="20" t="str">
@@ -15117,7 +15229,7 @@
         <v/>
       </c>
       <c r="B389" s="19" t="str">
-        <f aca="false">IF(C389="","",WORKDAY($C$5-1,A389))</f>
+        <f aca="false">IF(C389="","",WORKDAY($C$5-1,A389,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C389" s="20" t="str">
@@ -15154,7 +15266,7 @@
         <v/>
       </c>
       <c r="B390" s="19" t="str">
-        <f aca="false">IF(C390="","",WORKDAY($C$5-1,A390))</f>
+        <f aca="false">IF(C390="","",WORKDAY($C$5-1,A390,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C390" s="20" t="str">
@@ -15191,7 +15303,7 @@
         <v/>
       </c>
       <c r="B391" s="19" t="str">
-        <f aca="false">IF(C391="","",WORKDAY($C$5-1,A391))</f>
+        <f aca="false">IF(C391="","",WORKDAY($C$5-1,A391,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C391" s="20" t="str">
@@ -15228,7 +15340,7 @@
         <v/>
       </c>
       <c r="B392" s="19" t="str">
-        <f aca="false">IF(C392="","",WORKDAY($C$5-1,A392))</f>
+        <f aca="false">IF(C392="","",WORKDAY($C$5-1,A392,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C392" s="20" t="str">
@@ -15265,7 +15377,7 @@
         <v/>
       </c>
       <c r="B393" s="19" t="str">
-        <f aca="false">IF(C393="","",WORKDAY($C$5-1,A393))</f>
+        <f aca="false">IF(C393="","",WORKDAY($C$5-1,A393,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C393" s="20" t="str">
@@ -15302,7 +15414,7 @@
         <v/>
       </c>
       <c r="B394" s="19" t="str">
-        <f aca="false">IF(C394="","",WORKDAY($C$5-1,A394))</f>
+        <f aca="false">IF(C394="","",WORKDAY($C$5-1,A394,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C394" s="20" t="str">
@@ -15339,7 +15451,7 @@
         <v/>
       </c>
       <c r="B395" s="19" t="str">
-        <f aca="false">IF(C395="","",WORKDAY($C$5-1,A395))</f>
+        <f aca="false">IF(C395="","",WORKDAY($C$5-1,A395,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C395" s="20" t="str">
@@ -15376,7 +15488,7 @@
         <v/>
       </c>
       <c r="B396" s="19" t="str">
-        <f aca="false">IF(C396="","",WORKDAY($C$5-1,A396))</f>
+        <f aca="false">IF(C396="","",WORKDAY($C$5-1,A396,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C396" s="20" t="str">
@@ -15413,7 +15525,7 @@
         <v/>
       </c>
       <c r="B397" s="19" t="str">
-        <f aca="false">IF(C397="","",WORKDAY($C$5-1,A397))</f>
+        <f aca="false">IF(C397="","",WORKDAY($C$5-1,A397,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C397" s="20" t="str">
@@ -15450,7 +15562,7 @@
         <v/>
       </c>
       <c r="B398" s="19" t="str">
-        <f aca="false">IF(C398="","",WORKDAY($C$5-1,A398))</f>
+        <f aca="false">IF(C398="","",WORKDAY($C$5-1,A398,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C398" s="20" t="str">
@@ -15487,7 +15599,7 @@
         <v/>
       </c>
       <c r="B399" s="19" t="str">
-        <f aca="false">IF(C399="","",WORKDAY($C$5-1,A399))</f>
+        <f aca="false">IF(C399="","",WORKDAY($C$5-1,A399,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C399" s="20" t="str">
@@ -15524,7 +15636,7 @@
         <v/>
       </c>
       <c r="B400" s="19" t="str">
-        <f aca="false">IF(C400="","",WORKDAY($C$5-1,A400))</f>
+        <f aca="false">IF(C400="","",WORKDAY($C$5-1,A400,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C400" s="20" t="str">
@@ -15561,7 +15673,7 @@
         <v/>
       </c>
       <c r="B401" s="19" t="str">
-        <f aca="false">IF(C401="","",WORKDAY($C$5-1,A401))</f>
+        <f aca="false">IF(C401="","",WORKDAY($C$5-1,A401,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C401" s="20" t="str">
@@ -15598,7 +15710,7 @@
         <v/>
       </c>
       <c r="B402" s="19" t="str">
-        <f aca="false">IF(C402="","",WORKDAY($C$5-1,A402))</f>
+        <f aca="false">IF(C402="","",WORKDAY($C$5-1,A402,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C402" s="20" t="str">
@@ -15635,7 +15747,7 @@
         <v/>
       </c>
       <c r="B403" s="19" t="str">
-        <f aca="false">IF(C403="","",WORKDAY($C$5-1,A403))</f>
+        <f aca="false">IF(C403="","",WORKDAY($C$5-1,A403,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C403" s="20" t="str">
@@ -15672,7 +15784,7 @@
         <v/>
       </c>
       <c r="B404" s="19" t="str">
-        <f aca="false">IF(C404="","",WORKDAY($C$5-1,A404))</f>
+        <f aca="false">IF(C404="","",WORKDAY($C$5-1,A404,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C404" s="20" t="str">
@@ -15709,7 +15821,7 @@
         <v/>
       </c>
       <c r="B405" s="19" t="str">
-        <f aca="false">IF(C405="","",WORKDAY($C$5-1,A405))</f>
+        <f aca="false">IF(C405="","",WORKDAY($C$5-1,A405,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C405" s="20" t="str">
@@ -15746,7 +15858,7 @@
         <v/>
       </c>
       <c r="B406" s="19" t="str">
-        <f aca="false">IF(C406="","",WORKDAY($C$5-1,A406))</f>
+        <f aca="false">IF(C406="","",WORKDAY($C$5-1,A406,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C406" s="20" t="str">
@@ -15783,7 +15895,7 @@
         <v/>
       </c>
       <c r="B407" s="19" t="str">
-        <f aca="false">IF(C407="","",WORKDAY($C$5-1,A407))</f>
+        <f aca="false">IF(C407="","",WORKDAY($C$5-1,A407,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C407" s="20" t="str">
@@ -15820,7 +15932,7 @@
         <v/>
       </c>
       <c r="B408" s="19" t="str">
-        <f aca="false">IF(C408="","",WORKDAY($C$5-1,A408))</f>
+        <f aca="false">IF(C408="","",WORKDAY($C$5-1,A408,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C408" s="20" t="str">
@@ -15857,7 +15969,7 @@
         <v/>
       </c>
       <c r="B409" s="19" t="str">
-        <f aca="false">IF(C409="","",WORKDAY($C$5-1,A409))</f>
+        <f aca="false">IF(C409="","",WORKDAY($C$5-1,A409,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C409" s="20" t="str">
@@ -15894,7 +16006,7 @@
         <v/>
       </c>
       <c r="B410" s="19" t="str">
-        <f aca="false">IF(C410="","",WORKDAY($C$5-1,A410))</f>
+        <f aca="false">IF(C410="","",WORKDAY($C$5-1,A410,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C410" s="20" t="str">
@@ -15931,7 +16043,7 @@
         <v/>
       </c>
       <c r="B411" s="19" t="str">
-        <f aca="false">IF(C411="","",WORKDAY($C$5-1,A411))</f>
+        <f aca="false">IF(C411="","",WORKDAY($C$5-1,A411,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C411" s="20" t="str">
@@ -15968,7 +16080,7 @@
         <v/>
       </c>
       <c r="B412" s="19" t="str">
-        <f aca="false">IF(C412="","",WORKDAY($C$5-1,A412))</f>
+        <f aca="false">IF(C412="","",WORKDAY($C$5-1,A412,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C412" s="20" t="str">
@@ -16005,7 +16117,7 @@
         <v/>
       </c>
       <c r="B413" s="19" t="str">
-        <f aca="false">IF(C413="","",WORKDAY($C$5-1,A413))</f>
+        <f aca="false">IF(C413="","",WORKDAY($C$5-1,A413,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C413" s="20" t="str">
@@ -16042,7 +16154,7 @@
         <v/>
       </c>
       <c r="B414" s="19" t="str">
-        <f aca="false">IF(C414="","",WORKDAY($C$5-1,A414))</f>
+        <f aca="false">IF(C414="","",WORKDAY($C$5-1,A414,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C414" s="20" t="str">
@@ -16079,7 +16191,7 @@
         <v/>
       </c>
       <c r="B415" s="19" t="str">
-        <f aca="false">IF(C415="","",WORKDAY($C$5-1,A415))</f>
+        <f aca="false">IF(C415="","",WORKDAY($C$5-1,A415,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C415" s="20" t="str">
@@ -16116,7 +16228,7 @@
         <v/>
       </c>
       <c r="B416" s="19" t="str">
-        <f aca="false">IF(C416="","",WORKDAY($C$5-1,A416))</f>
+        <f aca="false">IF(C416="","",WORKDAY($C$5-1,A416,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C416" s="20" t="str">
@@ -16153,7 +16265,7 @@
         <v/>
       </c>
       <c r="B417" s="19" t="str">
-        <f aca="false">IF(C417="","",WORKDAY($C$5-1,A417))</f>
+        <f aca="false">IF(C417="","",WORKDAY($C$5-1,A417,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C417" s="20" t="str">
@@ -16190,7 +16302,7 @@
         <v/>
       </c>
       <c r="B418" s="19" t="str">
-        <f aca="false">IF(C418="","",WORKDAY($C$5-1,A418))</f>
+        <f aca="false">IF(C418="","",WORKDAY($C$5-1,A418,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C418" s="20" t="str">
@@ -16227,7 +16339,7 @@
         <v/>
       </c>
       <c r="B419" s="19" t="str">
-        <f aca="false">IF(C419="","",WORKDAY($C$5-1,A419))</f>
+        <f aca="false">IF(C419="","",WORKDAY($C$5-1,A419,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C419" s="20" t="str">
@@ -16264,7 +16376,7 @@
         <v/>
       </c>
       <c r="B420" s="19" t="str">
-        <f aca="false">IF(C420="","",WORKDAY($C$5-1,A420))</f>
+        <f aca="false">IF(C420="","",WORKDAY($C$5-1,A420,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C420" s="20" t="str">
@@ -16301,7 +16413,7 @@
         <v/>
       </c>
       <c r="B421" s="19" t="str">
-        <f aca="false">IF(C421="","",WORKDAY($C$5-1,A421))</f>
+        <f aca="false">IF(C421="","",WORKDAY($C$5-1,A421,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C421" s="20" t="str">
@@ -16338,7 +16450,7 @@
         <v/>
       </c>
       <c r="B422" s="19" t="str">
-        <f aca="false">IF(C422="","",WORKDAY($C$5-1,A422))</f>
+        <f aca="false">IF(C422="","",WORKDAY($C$5-1,A422,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C422" s="20" t="str">
@@ -16375,7 +16487,7 @@
         <v/>
       </c>
       <c r="B423" s="19" t="str">
-        <f aca="false">IF(C423="","",WORKDAY($C$5-1,A423))</f>
+        <f aca="false">IF(C423="","",WORKDAY($C$5-1,A423,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C423" s="20" t="str">
@@ -16412,7 +16524,7 @@
         <v/>
       </c>
       <c r="B424" s="19" t="str">
-        <f aca="false">IF(C424="","",WORKDAY($C$5-1,A424))</f>
+        <f aca="false">IF(C424="","",WORKDAY($C$5-1,A424,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C424" s="20" t="str">
@@ -16449,7 +16561,7 @@
         <v/>
       </c>
       <c r="B425" s="19" t="str">
-        <f aca="false">IF(C425="","",WORKDAY($C$5-1,A425))</f>
+        <f aca="false">IF(C425="","",WORKDAY($C$5-1,A425,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C425" s="20" t="str">
@@ -16486,7 +16598,7 @@
         <v/>
       </c>
       <c r="B426" s="19" t="str">
-        <f aca="false">IF(C426="","",WORKDAY($C$5-1,A426))</f>
+        <f aca="false">IF(C426="","",WORKDAY($C$5-1,A426,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C426" s="20" t="str">
@@ -16523,7 +16635,7 @@
         <v/>
       </c>
       <c r="B427" s="19" t="str">
-        <f aca="false">IF(C427="","",WORKDAY($C$5-1,A427))</f>
+        <f aca="false">IF(C427="","",WORKDAY($C$5-1,A427,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C427" s="20" t="str">
@@ -16560,7 +16672,7 @@
         <v/>
       </c>
       <c r="B428" s="19" t="str">
-        <f aca="false">IF(C428="","",WORKDAY($C$5-1,A428))</f>
+        <f aca="false">IF(C428="","",WORKDAY($C$5-1,A428,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C428" s="20" t="str">
@@ -16597,7 +16709,7 @@
         <v/>
       </c>
       <c r="B429" s="19" t="str">
-        <f aca="false">IF(C429="","",WORKDAY($C$5-1,A429))</f>
+        <f aca="false">IF(C429="","",WORKDAY($C$5-1,A429,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C429" s="20" t="str">
@@ -16634,7 +16746,7 @@
         <v/>
       </c>
       <c r="B430" s="19" t="str">
-        <f aca="false">IF(C430="","",WORKDAY($C$5-1,A430))</f>
+        <f aca="false">IF(C430="","",WORKDAY($C$5-1,A430,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C430" s="20" t="str">
@@ -16671,7 +16783,7 @@
         <v/>
       </c>
       <c r="B431" s="19" t="str">
-        <f aca="false">IF(C431="","",WORKDAY($C$5-1,A431))</f>
+        <f aca="false">IF(C431="","",WORKDAY($C$5-1,A431,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C431" s="20" t="str">
@@ -16708,7 +16820,7 @@
         <v/>
       </c>
       <c r="B432" s="19" t="str">
-        <f aca="false">IF(C432="","",WORKDAY($C$5-1,A432))</f>
+        <f aca="false">IF(C432="","",WORKDAY($C$5-1,A432,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C432" s="20" t="str">
@@ -16745,7 +16857,7 @@
         <v/>
       </c>
       <c r="B433" s="19" t="str">
-        <f aca="false">IF(C433="","",WORKDAY($C$5-1,A433))</f>
+        <f aca="false">IF(C433="","",WORKDAY($C$5-1,A433,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C433" s="20" t="str">
@@ -16782,7 +16894,7 @@
         <v/>
       </c>
       <c r="B434" s="19" t="str">
-        <f aca="false">IF(C434="","",WORKDAY($C$5-1,A434))</f>
+        <f aca="false">IF(C434="","",WORKDAY($C$5-1,A434,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C434" s="20" t="str">
@@ -16819,7 +16931,7 @@
         <v/>
       </c>
       <c r="B435" s="19" t="str">
-        <f aca="false">IF(C435="","",WORKDAY($C$5-1,A435))</f>
+        <f aca="false">IF(C435="","",WORKDAY($C$5-1,A435,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C435" s="20" t="str">
@@ -16856,7 +16968,7 @@
         <v/>
       </c>
       <c r="B436" s="19" t="str">
-        <f aca="false">IF(C436="","",WORKDAY($C$5-1,A436))</f>
+        <f aca="false">IF(C436="","",WORKDAY($C$5-1,A436,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C436" s="20" t="str">
@@ -16893,7 +17005,7 @@
         <v/>
       </c>
       <c r="B437" s="19" t="str">
-        <f aca="false">IF(C437="","",WORKDAY($C$5-1,A437))</f>
+        <f aca="false">IF(C437="","",WORKDAY($C$5-1,A437,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C437" s="20" t="str">
@@ -16930,7 +17042,7 @@
         <v/>
       </c>
       <c r="B438" s="19" t="str">
-        <f aca="false">IF(C438="","",WORKDAY($C$5-1,A438))</f>
+        <f aca="false">IF(C438="","",WORKDAY($C$5-1,A438,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C438" s="20" t="str">
@@ -16967,7 +17079,7 @@
         <v/>
       </c>
       <c r="B439" s="19" t="str">
-        <f aca="false">IF(C439="","",WORKDAY($C$5-1,A439))</f>
+        <f aca="false">IF(C439="","",WORKDAY($C$5-1,A439,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C439" s="20" t="str">
@@ -17004,7 +17116,7 @@
         <v/>
       </c>
       <c r="B440" s="19" t="str">
-        <f aca="false">IF(C440="","",WORKDAY($C$5-1,A440))</f>
+        <f aca="false">IF(C440="","",WORKDAY($C$5-1,A440,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C440" s="20" t="str">
@@ -17041,7 +17153,7 @@
         <v/>
       </c>
       <c r="B441" s="19" t="str">
-        <f aca="false">IF(C441="","",WORKDAY($C$5-1,A441))</f>
+        <f aca="false">IF(C441="","",WORKDAY($C$5-1,A441,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C441" s="20" t="str">
@@ -17078,7 +17190,7 @@
         <v/>
       </c>
       <c r="B442" s="19" t="str">
-        <f aca="false">IF(C442="","",WORKDAY($C$5-1,A442))</f>
+        <f aca="false">IF(C442="","",WORKDAY($C$5-1,A442,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C442" s="20" t="str">
@@ -17115,7 +17227,7 @@
         <v/>
       </c>
       <c r="B443" s="19" t="str">
-        <f aca="false">IF(C443="","",WORKDAY($C$5-1,A443))</f>
+        <f aca="false">IF(C443="","",WORKDAY($C$5-1,A443,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C443" s="20" t="str">
@@ -17152,7 +17264,7 @@
         <v/>
       </c>
       <c r="B444" s="19" t="str">
-        <f aca="false">IF(C444="","",WORKDAY($C$5-1,A444))</f>
+        <f aca="false">IF(C444="","",WORKDAY($C$5-1,A444,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C444" s="20" t="str">
@@ -17189,7 +17301,7 @@
         <v/>
       </c>
       <c r="B445" s="19" t="str">
-        <f aca="false">IF(C445="","",WORKDAY($C$5-1,A445))</f>
+        <f aca="false">IF(C445="","",WORKDAY($C$5-1,A445,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C445" s="20" t="str">
@@ -17226,7 +17338,7 @@
         <v/>
       </c>
       <c r="B446" s="19" t="str">
-        <f aca="false">IF(C446="","",WORKDAY($C$5-1,A446))</f>
+        <f aca="false">IF(C446="","",WORKDAY($C$5-1,A446,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C446" s="20" t="str">
@@ -17263,7 +17375,7 @@
         <v/>
       </c>
       <c r="B447" s="19" t="str">
-        <f aca="false">IF(C447="","",WORKDAY($C$5-1,A447))</f>
+        <f aca="false">IF(C447="","",WORKDAY($C$5-1,A447,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C447" s="20" t="str">
@@ -17300,7 +17412,7 @@
         <v/>
       </c>
       <c r="B448" s="19" t="str">
-        <f aca="false">IF(C448="","",WORKDAY($C$5-1,A448))</f>
+        <f aca="false">IF(C448="","",WORKDAY($C$5-1,A448,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C448" s="20" t="str">
@@ -17337,7 +17449,7 @@
         <v/>
       </c>
       <c r="B449" s="19" t="str">
-        <f aca="false">IF(C449="","",WORKDAY($C$5-1,A449))</f>
+        <f aca="false">IF(C449="","",WORKDAY($C$5-1,A449,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C449" s="20" t="str">
@@ -17374,7 +17486,7 @@
         <v/>
       </c>
       <c r="B450" s="19" t="str">
-        <f aca="false">IF(C450="","",WORKDAY($C$5-1,A450))</f>
+        <f aca="false">IF(C450="","",WORKDAY($C$5-1,A450,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C450" s="20" t="str">
@@ -17411,7 +17523,7 @@
         <v/>
       </c>
       <c r="B451" s="19" t="str">
-        <f aca="false">IF(C451="","",WORKDAY($C$5-1,A451))</f>
+        <f aca="false">IF(C451="","",WORKDAY($C$5-1,A451,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C451" s="20" t="str">
@@ -17448,7 +17560,7 @@
         <v/>
       </c>
       <c r="B452" s="19" t="str">
-        <f aca="false">IF(C452="","",WORKDAY($C$5-1,A452))</f>
+        <f aca="false">IF(C452="","",WORKDAY($C$5-1,A452,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C452" s="20" t="str">
@@ -17485,7 +17597,7 @@
         <v/>
       </c>
       <c r="B453" s="19" t="str">
-        <f aca="false">IF(C453="","",WORKDAY($C$5-1,A453))</f>
+        <f aca="false">IF(C453="","",WORKDAY($C$5-1,A453,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C453" s="20" t="str">
@@ -17522,7 +17634,7 @@
         <v/>
       </c>
       <c r="B454" s="19" t="str">
-        <f aca="false">IF(C454="","",WORKDAY($C$5-1,A454))</f>
+        <f aca="false">IF(C454="","",WORKDAY($C$5-1,A454,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C454" s="20" t="str">
@@ -17559,7 +17671,7 @@
         <v/>
       </c>
       <c r="B455" s="19" t="str">
-        <f aca="false">IF(C455="","",WORKDAY($C$5-1,A455))</f>
+        <f aca="false">IF(C455="","",WORKDAY($C$5-1,A455,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C455" s="20" t="str">
@@ -17596,7 +17708,7 @@
         <v/>
       </c>
       <c r="B456" s="19" t="str">
-        <f aca="false">IF(C456="","",WORKDAY($C$5-1,A456))</f>
+        <f aca="false">IF(C456="","",WORKDAY($C$5-1,A456,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C456" s="20" t="str">
@@ -17633,7 +17745,7 @@
         <v/>
       </c>
       <c r="B457" s="19" t="str">
-        <f aca="false">IF(C457="","",WORKDAY($C$5-1,A457))</f>
+        <f aca="false">IF(C457="","",WORKDAY($C$5-1,A457,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C457" s="20" t="str">
@@ -17670,7 +17782,7 @@
         <v/>
       </c>
       <c r="B458" s="19" t="str">
-        <f aca="false">IF(C458="","",WORKDAY($C$5-1,A458))</f>
+        <f aca="false">IF(C458="","",WORKDAY($C$5-1,A458,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C458" s="20" t="str">
@@ -17707,7 +17819,7 @@
         <v/>
       </c>
       <c r="B459" s="19" t="str">
-        <f aca="false">IF(C459="","",WORKDAY($C$5-1,A459))</f>
+        <f aca="false">IF(C459="","",WORKDAY($C$5-1,A459,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C459" s="20" t="str">
@@ -17744,7 +17856,7 @@
         <v/>
       </c>
       <c r="B460" s="19" t="str">
-        <f aca="false">IF(C460="","",WORKDAY($C$5-1,A460))</f>
+        <f aca="false">IF(C460="","",WORKDAY($C$5-1,A460,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C460" s="20" t="str">
@@ -17781,7 +17893,7 @@
         <v/>
       </c>
       <c r="B461" s="19" t="str">
-        <f aca="false">IF(C461="","",WORKDAY($C$5-1,A461))</f>
+        <f aca="false">IF(C461="","",WORKDAY($C$5-1,A461,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C461" s="20" t="str">
@@ -17818,7 +17930,7 @@
         <v/>
       </c>
       <c r="B462" s="19" t="str">
-        <f aca="false">IF(C462="","",WORKDAY($C$5-1,A462))</f>
+        <f aca="false">IF(C462="","",WORKDAY($C$5-1,A462,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C462" s="20" t="str">
@@ -17855,7 +17967,7 @@
         <v/>
       </c>
       <c r="B463" s="19" t="str">
-        <f aca="false">IF(C463="","",WORKDAY($C$5-1,A463))</f>
+        <f aca="false">IF(C463="","",WORKDAY($C$5-1,A463,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C463" s="20" t="str">
@@ -17892,7 +18004,7 @@
         <v/>
       </c>
       <c r="B464" s="19" t="str">
-        <f aca="false">IF(C464="","",WORKDAY($C$5-1,A464))</f>
+        <f aca="false">IF(C464="","",WORKDAY($C$5-1,A464,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C464" s="20" t="str">
@@ -17929,7 +18041,7 @@
         <v/>
       </c>
       <c r="B465" s="19" t="str">
-        <f aca="false">IF(C465="","",WORKDAY($C$5-1,A465))</f>
+        <f aca="false">IF(C465="","",WORKDAY($C$5-1,A465,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C465" s="20" t="str">
@@ -17966,7 +18078,7 @@
         <v/>
       </c>
       <c r="B466" s="19" t="str">
-        <f aca="false">IF(C466="","",WORKDAY($C$5-1,A466))</f>
+        <f aca="false">IF(C466="","",WORKDAY($C$5-1,A466,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C466" s="20" t="str">
@@ -18003,7 +18115,7 @@
         <v/>
       </c>
       <c r="B467" s="19" t="str">
-        <f aca="false">IF(C467="","",WORKDAY($C$5-1,A467))</f>
+        <f aca="false">IF(C467="","",WORKDAY($C$5-1,A467,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C467" s="20" t="str">
@@ -18040,7 +18152,7 @@
         <v/>
       </c>
       <c r="B468" s="19" t="str">
-        <f aca="false">IF(C468="","",WORKDAY($C$5-1,A468))</f>
+        <f aca="false">IF(C468="","",WORKDAY($C$5-1,A468,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C468" s="20" t="str">
@@ -18077,7 +18189,7 @@
         <v/>
       </c>
       <c r="B469" s="19" t="str">
-        <f aca="false">IF(C469="","",WORKDAY($C$5-1,A469))</f>
+        <f aca="false">IF(C469="","",WORKDAY($C$5-1,A469,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C469" s="20" t="str">
@@ -18114,7 +18226,7 @@
         <v/>
       </c>
       <c r="B470" s="19" t="str">
-        <f aca="false">IF(C470="","",WORKDAY($C$5-1,A470))</f>
+        <f aca="false">IF(C470="","",WORKDAY($C$5-1,A470,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C470" s="20" t="str">
@@ -18151,7 +18263,7 @@
         <v/>
       </c>
       <c r="B471" s="19" t="str">
-        <f aca="false">IF(C471="","",WORKDAY($C$5-1,A471))</f>
+        <f aca="false">IF(C471="","",WORKDAY($C$5-1,A471,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C471" s="20" t="str">
@@ -18188,7 +18300,7 @@
         <v/>
       </c>
       <c r="B472" s="19" t="str">
-        <f aca="false">IF(C472="","",WORKDAY($C$5-1,A472))</f>
+        <f aca="false">IF(C472="","",WORKDAY($C$5-1,A472,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C472" s="20" t="str">
@@ -18225,7 +18337,7 @@
         <v/>
       </c>
       <c r="B473" s="19" t="str">
-        <f aca="false">IF(C473="","",WORKDAY($C$5-1,A473))</f>
+        <f aca="false">IF(C473="","",WORKDAY($C$5-1,A473,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C473" s="20" t="str">
@@ -18262,7 +18374,7 @@
         <v/>
       </c>
       <c r="B474" s="19" t="str">
-        <f aca="false">IF(C474="","",WORKDAY($C$5-1,A474))</f>
+        <f aca="false">IF(C474="","",WORKDAY($C$5-1,A474,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C474" s="20" t="str">
@@ -18299,7 +18411,7 @@
         <v/>
       </c>
       <c r="B475" s="19" t="str">
-        <f aca="false">IF(C475="","",WORKDAY($C$5-1,A475))</f>
+        <f aca="false">IF(C475="","",WORKDAY($C$5-1,A475,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C475" s="20" t="str">
@@ -18336,7 +18448,7 @@
         <v/>
       </c>
       <c r="B476" s="19" t="str">
-        <f aca="false">IF(C476="","",WORKDAY($C$5-1,A476))</f>
+        <f aca="false">IF(C476="","",WORKDAY($C$5-1,A476,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C476" s="20" t="str">
@@ -18373,7 +18485,7 @@
         <v/>
       </c>
       <c r="B477" s="19" t="str">
-        <f aca="false">IF(C477="","",WORKDAY($C$5-1,A477))</f>
+        <f aca="false">IF(C477="","",WORKDAY($C$5-1,A477,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C477" s="20" t="str">
@@ -18410,7 +18522,7 @@
         <v/>
       </c>
       <c r="B478" s="19" t="str">
-        <f aca="false">IF(C478="","",WORKDAY($C$5-1,A478))</f>
+        <f aca="false">IF(C478="","",WORKDAY($C$5-1,A478,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C478" s="20" t="str">
@@ -18447,7 +18559,7 @@
         <v/>
       </c>
       <c r="B479" s="19" t="str">
-        <f aca="false">IF(C479="","",WORKDAY($C$5-1,A479))</f>
+        <f aca="false">IF(C479="","",WORKDAY($C$5-1,A479,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C479" s="20" t="str">
@@ -18484,7 +18596,7 @@
         <v/>
       </c>
       <c r="B480" s="19" t="str">
-        <f aca="false">IF(C480="","",WORKDAY($C$5-1,A480))</f>
+        <f aca="false">IF(C480="","",WORKDAY($C$5-1,A480,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C480" s="20" t="str">
@@ -18521,7 +18633,7 @@
         <v/>
       </c>
       <c r="B481" s="19" t="str">
-        <f aca="false">IF(C481="","",WORKDAY($C$5-1,A481))</f>
+        <f aca="false">IF(C481="","",WORKDAY($C$5-1,A481,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C481" s="20" t="str">
@@ -18558,7 +18670,7 @@
         <v/>
       </c>
       <c r="B482" s="19" t="str">
-        <f aca="false">IF(C482="","",WORKDAY($C$5-1,A482))</f>
+        <f aca="false">IF(C482="","",WORKDAY($C$5-1,A482,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C482" s="20" t="str">
@@ -18595,7 +18707,7 @@
         <v/>
       </c>
       <c r="B483" s="19" t="str">
-        <f aca="false">IF(C483="","",WORKDAY($C$5-1,A483))</f>
+        <f aca="false">IF(C483="","",WORKDAY($C$5-1,A483,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C483" s="20" t="str">
@@ -18632,7 +18744,7 @@
         <v/>
       </c>
       <c r="B484" s="19" t="str">
-        <f aca="false">IF(C484="","",WORKDAY($C$5-1,A484))</f>
+        <f aca="false">IF(C484="","",WORKDAY($C$5-1,A484,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C484" s="20" t="str">
@@ -18669,7 +18781,7 @@
         <v/>
       </c>
       <c r="B485" s="19" t="str">
-        <f aca="false">IF(C485="","",WORKDAY($C$5-1,A485))</f>
+        <f aca="false">IF(C485="","",WORKDAY($C$5-1,A485,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C485" s="20" t="str">
@@ -18706,7 +18818,7 @@
         <v/>
       </c>
       <c r="B486" s="19" t="str">
-        <f aca="false">IF(C486="","",WORKDAY($C$5-1,A486))</f>
+        <f aca="false">IF(C486="","",WORKDAY($C$5-1,A486,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C486" s="20" t="str">
@@ -18743,7 +18855,7 @@
         <v/>
       </c>
       <c r="B487" s="19" t="str">
-        <f aca="false">IF(C487="","",WORKDAY($C$5-1,A487))</f>
+        <f aca="false">IF(C487="","",WORKDAY($C$5-1,A487,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C487" s="20" t="str">
@@ -18780,7 +18892,7 @@
         <v/>
       </c>
       <c r="B488" s="19" t="str">
-        <f aca="false">IF(C488="","",WORKDAY($C$5-1,A488))</f>
+        <f aca="false">IF(C488="","",WORKDAY($C$5-1,A488,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C488" s="20" t="str">
@@ -18817,7 +18929,7 @@
         <v/>
       </c>
       <c r="B489" s="19" t="str">
-        <f aca="false">IF(C489="","",WORKDAY($C$5-1,A489))</f>
+        <f aca="false">IF(C489="","",WORKDAY($C$5-1,A489,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C489" s="20" t="str">
@@ -18854,7 +18966,7 @@
         <v/>
       </c>
       <c r="B490" s="19" t="str">
-        <f aca="false">IF(C490="","",WORKDAY($C$5-1,A490))</f>
+        <f aca="false">IF(C490="","",WORKDAY($C$5-1,A490,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C490" s="20" t="str">
@@ -18891,7 +19003,7 @@
         <v/>
       </c>
       <c r="B491" s="19" t="str">
-        <f aca="false">IF(C491="","",WORKDAY($C$5-1,A491))</f>
+        <f aca="false">IF(C491="","",WORKDAY($C$5-1,A491,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C491" s="20" t="str">
@@ -18928,7 +19040,7 @@
         <v/>
       </c>
       <c r="B492" s="19" t="str">
-        <f aca="false">IF(C492="","",WORKDAY($C$5-1,A492))</f>
+        <f aca="false">IF(C492="","",WORKDAY($C$5-1,A492,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C492" s="20" t="str">
@@ -18965,7 +19077,7 @@
         <v/>
       </c>
       <c r="B493" s="19" t="str">
-        <f aca="false">IF(C493="","",WORKDAY($C$5-1,A493))</f>
+        <f aca="false">IF(C493="","",WORKDAY($C$5-1,A493,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C493" s="20" t="str">
@@ -19002,7 +19114,7 @@
         <v/>
       </c>
       <c r="B494" s="19" t="str">
-        <f aca="false">IF(C494="","",WORKDAY($C$5-1,A494))</f>
+        <f aca="false">IF(C494="","",WORKDAY($C$5-1,A494,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C494" s="20" t="str">
@@ -19039,7 +19151,7 @@
         <v/>
       </c>
       <c r="B495" s="19" t="str">
-        <f aca="false">IF(C495="","",WORKDAY($C$5-1,A495))</f>
+        <f aca="false">IF(C495="","",WORKDAY($C$5-1,A495,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C495" s="20" t="str">
@@ -19076,7 +19188,7 @@
         <v/>
       </c>
       <c r="B496" s="19" t="str">
-        <f aca="false">IF(C496="","",WORKDAY($C$5-1,A496))</f>
+        <f aca="false">IF(C496="","",WORKDAY($C$5-1,A496,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C496" s="20" t="str">
@@ -19113,7 +19225,7 @@
         <v/>
       </c>
       <c r="B497" s="19" t="str">
-        <f aca="false">IF(C497="","",WORKDAY($C$5-1,A497))</f>
+        <f aca="false">IF(C497="","",WORKDAY($C$5-1,A497,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C497" s="20" t="str">
@@ -19150,7 +19262,7 @@
         <v/>
       </c>
       <c r="B498" s="19" t="str">
-        <f aca="false">IF(C498="","",WORKDAY($C$5-1,A498))</f>
+        <f aca="false">IF(C498="","",WORKDAY($C$5-1,A498,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C498" s="20" t="str">
@@ -19187,7 +19299,7 @@
         <v/>
       </c>
       <c r="B499" s="19" t="str">
-        <f aca="false">IF(C499="","",WORKDAY($C$5-1,A499))</f>
+        <f aca="false">IF(C499="","",WORKDAY($C$5-1,A499,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C499" s="20" t="str">
@@ -19224,7 +19336,7 @@
         <v/>
       </c>
       <c r="B500" s="19" t="str">
-        <f aca="false">IF(C500="","",WORKDAY($C$5-1,A500))</f>
+        <f aca="false">IF(C500="","",WORKDAY($C$5-1,A500,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C500" s="20" t="str">
@@ -19261,7 +19373,7 @@
         <v/>
       </c>
       <c r="B501" s="19" t="str">
-        <f aca="false">IF(C501="","",WORKDAY($C$5-1,A501))</f>
+        <f aca="false">IF(C501="","",WORKDAY($C$5-1,A501,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C501" s="20" t="str">
@@ -19298,7 +19410,7 @@
         <v/>
       </c>
       <c r="B502" s="19" t="str">
-        <f aca="false">IF(C502="","",WORKDAY($C$5-1,A502))</f>
+        <f aca="false">IF(C502="","",WORKDAY($C$5-1,A502,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C502" s="20" t="str">
@@ -19335,7 +19447,7 @@
         <v/>
       </c>
       <c r="B503" s="19" t="str">
-        <f aca="false">IF(C503="","",WORKDAY($C$5-1,A503))</f>
+        <f aca="false">IF(C503="","",WORKDAY($C$5-1,A503,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C503" s="20" t="str">
@@ -19372,7 +19484,7 @@
         <v/>
       </c>
       <c r="B504" s="19" t="str">
-        <f aca="false">IF(C504="","",WORKDAY($C$5-1,A504))</f>
+        <f aca="false">IF(C504="","",WORKDAY($C$5-1,A504,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C504" s="20" t="str">
@@ -19409,7 +19521,7 @@
         <v/>
       </c>
       <c r="B505" s="19" t="str">
-        <f aca="false">IF(C505="","",WORKDAY($C$5-1,A505))</f>
+        <f aca="false">IF(C505="","",WORKDAY($C$5-1,A505,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C505" s="20" t="str">
@@ -19446,7 +19558,7 @@
         <v/>
       </c>
       <c r="B506" s="19" t="str">
-        <f aca="false">IF(C506="","",WORKDAY($C$5-1,A506))</f>
+        <f aca="false">IF(C506="","",WORKDAY($C$5-1,A506,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C506" s="20" t="str">
@@ -19483,7 +19595,7 @@
         <v/>
       </c>
       <c r="B507" s="19" t="str">
-        <f aca="false">IF(C507="","",WORKDAY($C$5-1,A507))</f>
+        <f aca="false">IF(C507="","",WORKDAY($C$5-1,A507,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C507" s="20" t="str">
@@ -19520,7 +19632,7 @@
         <v/>
       </c>
       <c r="B508" s="19" t="str">
-        <f aca="false">IF(C508="","",WORKDAY($C$5-1,A508))</f>
+        <f aca="false">IF(C508="","",WORKDAY($C$5-1,A508,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C508" s="20" t="str">
@@ -19557,7 +19669,7 @@
         <v/>
       </c>
       <c r="B509" s="19" t="str">
-        <f aca="false">IF(C509="","",WORKDAY($C$5-1,A509))</f>
+        <f aca="false">IF(C509="","",WORKDAY($C$5-1,A509,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C509" s="20" t="str">
@@ -19594,7 +19706,7 @@
         <v/>
       </c>
       <c r="B510" s="19" t="str">
-        <f aca="false">IF(C510="","",WORKDAY($C$5-1,A510))</f>
+        <f aca="false">IF(C510="","",WORKDAY($C$5-1,A510,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C510" s="20" t="str">
@@ -19631,7 +19743,7 @@
         <v/>
       </c>
       <c r="B511" s="19" t="str">
-        <f aca="false">IF(C511="","",WORKDAY($C$5-1,A511))</f>
+        <f aca="false">IF(C511="","",WORKDAY($C$5-1,A511,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C511" s="20" t="str">
@@ -19668,7 +19780,7 @@
         <v/>
       </c>
       <c r="B512" s="19" t="str">
-        <f aca="false">IF(C512="","",WORKDAY($C$5-1,A512))</f>
+        <f aca="false">IF(C512="","",WORKDAY($C$5-1,A512,'NSE Holidays'!$A$5:$A$64))</f>
         <v/>
       </c>
       <c r="C512" s="20" t="str">
@@ -19766,7 +19878,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{596ABDFB-8924-4732-8F3B-D97075E9C277}</x14:id>
+          <x14:id>{CC907AFD-203E-4E2A-BC8D-63FB6120F290}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -19797,7 +19909,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{596ABDFB-8924-4732-8F3B-D97075E9C277}">
+          <x14:cfRule type="dataBar" id="{CC907AFD-203E-4E2A-BC8D-63FB6120F290}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -19822,6 +19934,675 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <f aca="false">IF(A5="","",A5)</f>
+        <v>46048</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="31"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B6" s="29" t="n">
+        <f aca="false">IF(A6="","",A6)</f>
+        <v>46084</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="31"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B7" s="29" t="n">
+        <f aca="false">IF(A7="","",A7)</f>
+        <v>46107</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="31"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <f aca="false">IF(A8="","",A8)</f>
+        <v>46112</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="31"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B9" s="29" t="n">
+        <f aca="false">IF(A9="","",A9)</f>
+        <v>46115</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B10" s="29" t="n">
+        <f aca="false">IF(A10="","",A10)</f>
+        <v>46126</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="31"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B11" s="29" t="n">
+        <f aca="false">IF(A11="","",A11)</f>
+        <v>46143</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="31"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B12" s="29" t="n">
+        <f aca="false">IF(A12="","",A12)</f>
+        <v>46170</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B13" s="29" t="n">
+        <f aca="false">IF(A13="","",A13)</f>
+        <v>46199</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B14" s="29" t="n">
+        <f aca="false">IF(A14="","",A14)</f>
+        <v>46279</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="31"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B15" s="29" t="n">
+        <f aca="false">IF(A15="","",A15)</f>
+        <v>46297</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B16" s="29" t="n">
+        <f aca="false">IF(A16="","",A16)</f>
+        <v>46315</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="31"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B17" s="29" t="n">
+        <f aca="false">IF(A17="","",A17)</f>
+        <v>46336</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="n">
+        <v>46350</v>
+      </c>
+      <c r="B18" s="29" t="n">
+        <f aca="false">IF(A18="","",A18)</f>
+        <v>46350</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="31"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="n">
+        <v>46381</v>
+      </c>
+      <c r="B19" s="29" t="n">
+        <f aca="false">IF(A19="","",A19)</f>
+        <v>46381</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="31"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="n">
+        <v>46413</v>
+      </c>
+      <c r="B20" s="29" t="n">
+        <f aca="false">IF(A20="","",A20)</f>
+        <v>46413</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="str">
+        <f aca="false">IF(A21="","",A21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29" t="str">
+        <f aca="false">IF(A22="","",A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29" t="str">
+        <f aca="false">IF(A23="","",A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="str">
+        <f aca="false">IF(A24="","",A24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29" t="str">
+        <f aca="false">IF(A25="","",A25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29" t="str">
+        <f aca="false">IF(A26="","",A26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29" t="str">
+        <f aca="false">IF(A27="","",A27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29" t="str">
+        <f aca="false">IF(A28="","",A28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29" t="str">
+        <f aca="false">IF(A29="","",A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29" t="str">
+        <f aca="false">IF(A30="","",A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="30"/>
+      <c r="D30" s="31"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29" t="str">
+        <f aca="false">IF(A31="","",A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29" t="str">
+        <f aca="false">IF(A32="","",A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29" t="str">
+        <f aca="false">IF(A33="","",A33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29" t="str">
+        <f aca="false">IF(A34="","",A34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29" t="str">
+        <f aca="false">IF(A35="","",A35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29" t="str">
+        <f aca="false">IF(A36="","",A36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29" t="str">
+        <f aca="false">IF(A37="","",A37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29" t="str">
+        <f aca="false">IF(A38="","",A38)</f>
+        <v/>
+      </c>
+      <c r="C38" s="30"/>
+      <c r="D38" s="31"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29" t="str">
+        <f aca="false">IF(A39="","",A39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="30"/>
+      <c r="D39" s="31"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29" t="str">
+        <f aca="false">IF(A40="","",A40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="30"/>
+      <c r="D40" s="31"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28"/>
+      <c r="B41" s="29" t="str">
+        <f aca="false">IF(A41="","",A41)</f>
+        <v/>
+      </c>
+      <c r="C41" s="30"/>
+      <c r="D41" s="31"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29" t="str">
+        <f aca="false">IF(A42="","",A42)</f>
+        <v/>
+      </c>
+      <c r="C42" s="30"/>
+      <c r="D42" s="31"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29" t="str">
+        <f aca="false">IF(A43="","",A43)</f>
+        <v/>
+      </c>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29" t="str">
+        <f aca="false">IF(A44="","",A44)</f>
+        <v/>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="31"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28"/>
+      <c r="B45" s="29" t="str">
+        <f aca="false">IF(A45="","",A45)</f>
+        <v/>
+      </c>
+      <c r="C45" s="30"/>
+      <c r="D45" s="31"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29" t="str">
+        <f aca="false">IF(A46="","",A46)</f>
+        <v/>
+      </c>
+      <c r="C46" s="30"/>
+      <c r="D46" s="31"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29" t="str">
+        <f aca="false">IF(A47="","",A47)</f>
+        <v/>
+      </c>
+      <c r="C47" s="30"/>
+      <c r="D47" s="31"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29" t="str">
+        <f aca="false">IF(A48="","",A48)</f>
+        <v/>
+      </c>
+      <c r="C48" s="30"/>
+      <c r="D48" s="31"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29" t="str">
+        <f aca="false">IF(A49="","",A49)</f>
+        <v/>
+      </c>
+      <c r="C49" s="30"/>
+      <c r="D49" s="31"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29" t="str">
+        <f aca="false">IF(A50="","",A50)</f>
+        <v/>
+      </c>
+      <c r="C50" s="30"/>
+      <c r="D50" s="31"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29" t="str">
+        <f aca="false">IF(A51="","",A51)</f>
+        <v/>
+      </c>
+      <c r="C51" s="30"/>
+      <c r="D51" s="31"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29" t="str">
+        <f aca="false">IF(A52="","",A52)</f>
+        <v/>
+      </c>
+      <c r="C52" s="30"/>
+      <c r="D52" s="31"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29" t="str">
+        <f aca="false">IF(A53="","",A53)</f>
+        <v/>
+      </c>
+      <c r="C53" s="30"/>
+      <c r="D53" s="31"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29" t="str">
+        <f aca="false">IF(A54="","",A54)</f>
+        <v/>
+      </c>
+      <c r="C54" s="30"/>
+      <c r="D54" s="31"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="28"/>
+      <c r="B55" s="29" t="str">
+        <f aca="false">IF(A55="","",A55)</f>
+        <v/>
+      </c>
+      <c r="C55" s="30"/>
+      <c r="D55" s="31"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="28"/>
+      <c r="B56" s="29" t="str">
+        <f aca="false">IF(A56="","",A56)</f>
+        <v/>
+      </c>
+      <c r="C56" s="30"/>
+      <c r="D56" s="31"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29" t="str">
+        <f aca="false">IF(A57="","",A57)</f>
+        <v/>
+      </c>
+      <c r="C57" s="30"/>
+      <c r="D57" s="31"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="28"/>
+      <c r="B58" s="29" t="str">
+        <f aca="false">IF(A58="","",A58)</f>
+        <v/>
+      </c>
+      <c r="C58" s="30"/>
+      <c r="D58" s="31"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28"/>
+      <c r="B59" s="29" t="str">
+        <f aca="false">IF(A59="","",A59)</f>
+        <v/>
+      </c>
+      <c r="C59" s="30"/>
+      <c r="D59" s="31"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29" t="str">
+        <f aca="false">IF(A60="","",A60)</f>
+        <v/>
+      </c>
+      <c r="C60" s="30"/>
+      <c r="D60" s="31"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="28"/>
+      <c r="B61" s="29" t="str">
+        <f aca="false">IF(A61="","",A61)</f>
+        <v/>
+      </c>
+      <c r="C61" s="30"/>
+      <c r="D61" s="31"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29" t="str">
+        <f aca="false">IF(A62="","",A62)</f>
+        <v/>
+      </c>
+      <c r="C62" s="30"/>
+      <c r="D62" s="31"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="28"/>
+      <c r="B63" s="29" t="str">
+        <f aca="false">IF(A63="","",A63)</f>
+        <v/>
+      </c>
+      <c r="C63" s="30"/>
+      <c r="D63" s="31"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28"/>
+      <c r="B64" s="29" t="str">
+        <f aca="false">IF(A64="","",A64)</f>
+        <v/>
+      </c>
+      <c r="C64" s="30"/>
+      <c r="D64" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Enter a date, e.g. 26-01-2027." errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A64" type="date">
+      <formula1>1</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -19829,130 +20610,130 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>30</v>
+      <c r="A1" s="32" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26"/>
+      <c r="A2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>31</v>
+      <c r="A3" s="34" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>32</v>
+      <c r="A4" s="35" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>33</v>
+      <c r="A5" s="35" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>34</v>
+      <c r="A6" s="35" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>35</v>
+      <c r="A7" s="35" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>36</v>
+      <c r="A8" s="35" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26"/>
+      <c r="A9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="s">
-        <v>37</v>
+      <c r="A10" s="36" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>38</v>
+      <c r="A11" s="35" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>39</v>
+      <c r="A12" s="35" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>40</v>
+      <c r="A13" s="35" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26"/>
+      <c r="A14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29" t="s">
-        <v>41</v>
+      <c r="A15" s="36" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>42</v>
+      <c r="A16" s="35" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
-        <v>43</v>
+      <c r="A17" s="35" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
-        <v>44</v>
+      <c r="A18" s="35" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26"/>
+      <c r="A19" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="s">
-        <v>45</v>
+      <c r="A20" s="36" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
-        <v>46</v>
+      <c r="A21" s="35" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="s">
-        <v>47</v>
+      <c r="A22" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
-        <v>48</v>
+      <c r="A23" s="35" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>49</v>
+      <c r="A24" s="35" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>50</v>
+      <c r="A25" s="35" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>51</v>
+      <c r="A26" s="35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="s">
-        <v>52</v>
+      <c r="A27" s="35" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Trading_PnL_Tracker.xlsx
+++ b/Trading_PnL_Tracker.xlsx
@@ -53,7 +53,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Provided by you: ₹4,230.</t>
+          <t xml:space="preserve">Provided by you: ₹10,000.</t>
         </r>
       </text>
     </comment>
@@ -101,7 +101,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Enter profit as positive (e.g. 150), loss as negative (e.g. -126.90), 0 if you did not trade. Leave blank for future days.</t>
+          <t xml:space="preserve">Enter profit as positive (e.g. 150), loss as negative (e.g. -300), 0 if you did not trade. Leave blank for future days.</t>
         </r>
       </text>
     </comment>
@@ -110,10 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="93">
-  <si>
-    <t xml:space="preserve">Trading Dashboard — ₹4,230 → ₹1,00,000</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
   <si>
     <t xml:space="preserve">Live summary of the Tracker sheet — enter results there, not here. Figures marked * are projections that assume every daily profit target is met; they are illustrations, not guarantees.</t>
   </si>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t xml:space="preserve">Charts show the first 150 trading days. Blue = actual closing balance; grey dashed = projected balance if every target is met*; green dotted = ₹1,00,000 goal. Full day-by-day detail is on the Tracker sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Trading P/L Tracker — ₹4,230 → ₹1,00,000 Goal</t>
   </si>
   <si>
     <t xml:space="preserve">Important: rows marked "Projection" assume every daily profit target is met. They are illustrations only — not a forecast or a guarantee. Real trading can and does produce losses.</t>
@@ -319,7 +313,7 @@
     <t xml:space="preserve">1. Each evening, go to that day's row on the Tracker sheet and type your result in the yellow "Actual P/L" cell:</t>
   </si>
   <si>
-    <t xml:space="preserve">      • Profit → positive number (e.g. 150)     • Loss → negative number (e.g. -126.90)     • Did not trade → 0</t>
+    <t xml:space="preserve">      • Profit → positive number (e.g. 150)     • Loss → negative number (e.g. -300)     • Did not trade → 0</t>
   </si>
   <si>
     <t xml:space="preserve">2. The Actual Closing Balance fills in automatically and becomes the next day's Opening Capital.</t>
@@ -337,13 +331,13 @@
     <t xml:space="preserve">Worked example (matches the sheet's formulas)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Day 1 opens at ₹4,230.00 → Profit Target ₹126.90, Loss Limit ₹126.90.</t>
+    <t xml:space="preserve">   Day 1 opens at ₹10,000.00 → Profit Target ₹300.00, Loss Limit ₹300.00.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Enter -126.90 in Day 1's Actual P/L → Day 1 closes at ₹4,103.10.</t>
+    <t xml:space="preserve">   Enter -300 in Day 1's Actual P/L → Day 1 closes at ₹9,700.00.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Day 2 then opens at ₹4,103.10 → Profit Target ₹123.09, Loss Limit ₹123.09.</t>
+    <t xml:space="preserve">   Day 2 then opens at ₹9,700.00 → Profit Target ₹291.00, Loss Limit ₹291.00.</t>
   </si>
   <si>
     <t xml:space="preserve">About the projection</t>
@@ -352,7 +346,7 @@
     <t xml:space="preserve">   • Rows marked "Projection" (grey italic) assume every daily profit target is hit. This is an illustration, not a prediction or guarantee.</t>
   </si>
   <si>
-    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹4,230 at 3%/day takes about 108 trading days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
+    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹10,000 at 3%/day takes about 78 trading days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
   </si>
   <si>
     <t xml:space="preserve">   • The table stops at the first day whose projected (or actual) close reaches the goal, and extends automatically after losses (up to 500 days).</t>
@@ -2171,328 +2165,238 @@
                 <c:formatCode>[&gt;=100000]\₹#\,##\,##0.00;\₹#,##0.00</c:formatCode>
                 <c:ptCount val="150"/>
                 <c:pt idx="0">
-                  <c:v>4356.9</c:v>
+                  <c:v>10300</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4487.61</c:v>
+                  <c:v>10609</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4622.24</c:v>
+                  <c:v>10927.27</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4760.91</c:v>
+                  <c:v>11255.09</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4903.74</c:v>
+                  <c:v>11592.74</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5050.85</c:v>
+                  <c:v>11940.52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5202.38</c:v>
+                  <c:v>12298.74</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5358.45</c:v>
+                  <c:v>12667.7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5519.2</c:v>
+                  <c:v>13047.73</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5684.78</c:v>
+                  <c:v>13439.16</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5855.32</c:v>
+                  <c:v>13842.33</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6030.98</c:v>
+                  <c:v>14257.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6211.91</c:v>
+                  <c:v>14685.33</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6398.27</c:v>
+                  <c:v>15125.89</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6590.22</c:v>
+                  <c:v>15579.67</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6787.93</c:v>
+                  <c:v>16047.06</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6991.57</c:v>
+                  <c:v>16528.47</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7201.32</c:v>
+                  <c:v>17024.32</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7417.36</c:v>
+                  <c:v>17535.05</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7639.88</c:v>
+                  <c:v>18061.1</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7869.08</c:v>
+                  <c:v>18602.93</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8105.15</c:v>
+                  <c:v>19161.02</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8348.3</c:v>
+                  <c:v>19735.85</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8598.75</c:v>
+                  <c:v>20327.93</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8856.71</c:v>
+                  <c:v>20937.77</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9122.41</c:v>
+                  <c:v>21565.9</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9396.08</c:v>
+                  <c:v>22212.88</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9677.96</c:v>
+                  <c:v>22879.27</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9968.3</c:v>
+                  <c:v>23565.65</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>10267.35</c:v>
+                  <c:v>24272.62</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>10575.37</c:v>
+                  <c:v>25000.8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>10892.63</c:v>
+                  <c:v>25750.82</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>11219.41</c:v>
+                  <c:v>26523.34</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>11555.99</c:v>
+                  <c:v>27319.04</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>11902.67</c:v>
+                  <c:v>28138.61</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>12259.75</c:v>
+                  <c:v>28982.77</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>12627.54</c:v>
+                  <c:v>29852.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>13006.37</c:v>
+                  <c:v>30747.82</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>13396.56</c:v>
+                  <c:v>31670.25</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>13798.46</c:v>
+                  <c:v>32620.36</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>14212.41</c:v>
+                  <c:v>33598.97</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>14638.78</c:v>
+                  <c:v>34606.94</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>15077.94</c:v>
+                  <c:v>35645.15</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>15530.28</c:v>
+                  <c:v>36714.5</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>15996.19</c:v>
+                  <c:v>37815.94</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>16476.08</c:v>
+                  <c:v>38950.42</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>16970.36</c:v>
+                  <c:v>40118.93</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>17479.47</c:v>
+                  <c:v>41322.5</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>18003.85</c:v>
+                  <c:v>42562.18</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>18543.97</c:v>
+                  <c:v>43839.05</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>19100.29</c:v>
+                  <c:v>45154.22</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>19673.3</c:v>
+                  <c:v>46508.85</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>20263.5</c:v>
+                  <c:v>47904.12</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>20871.41</c:v>
+                  <c:v>49341.24</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>21497.55</c:v>
+                  <c:v>50821.48</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>22142.48</c:v>
+                  <c:v>52346.12</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>22806.75</c:v>
+                  <c:v>53916.5</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>23490.95</c:v>
+                  <c:v>55534</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>24195.68</c:v>
+                  <c:v>57200.02</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>24921.55</c:v>
+                  <c:v>58916.02</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>25669.2</c:v>
+                  <c:v>60683.5</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>26439.28</c:v>
+                  <c:v>62504.01</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>27232.46</c:v>
+                  <c:v>64379.13</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>28049.43</c:v>
+                  <c:v>66310.5</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>28890.91</c:v>
+                  <c:v>68299.82</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>29757.64</c:v>
+                  <c:v>70348.81</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>30650.37</c:v>
+                  <c:v>72459.27</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>31569.88</c:v>
+                  <c:v>74633.05</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>32516.98</c:v>
+                  <c:v>76872.04</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>33492.49</c:v>
+                  <c:v>79178.2</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>34497.26</c:v>
+                  <c:v>81553.5500000001</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>35532.18</c:v>
+                  <c:v>84000.1600000001</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>36598.15</c:v>
+                  <c:v>86520.1600000001</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>37696.09</c:v>
+                  <c:v>89115.7600000001</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>38826.97</c:v>
+                  <c:v>91789.2300000001</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>39991.78</c:v>
+                  <c:v>94542.9100000001</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>41191.53</c:v>
+                  <c:v>97379.2</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>42427.28</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>43700.1</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>45011.1</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>46361.43</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>47752.27</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>49184.84</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>50660.39</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>52180.2</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>53745.61</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>55357.98</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>57018.72</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>58729.28</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>60491.16</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>62305.89</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>64175.07</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>66100.32</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>68083.33</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>70125.83</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>72229.6</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>74396.49</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>76628.38</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>78927.23</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>81295.05</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>83733.9</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>86245.92</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>88833.3</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>91498.3</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>94243.25</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>97070.55</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>99982.67</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>102982.15</c:v>
+                  <c:v>100300.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3251,96 +3155,6 @@
                 <c:pt idx="77">
                   <c:v>100000</c:v>
                 </c:pt>
-                <c:pt idx="78">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>100000</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3354,11 +3168,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21179525"/>
-        <c:axId val="86243756"/>
+        <c:axId val="37480180"/>
+        <c:axId val="15419459"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21179525"/>
+        <c:axId val="37480180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3424,7 +3238,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86243756"/>
+        <c:crossAx val="15419459"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3432,7 +3246,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86243756"/>
+        <c:axId val="15419459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3508,7 +3322,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21179525"/>
+        <c:crossAx val="37480180"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4639,11 +4453,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="100"/>
-        <c:axId val="34704011"/>
-        <c:axId val="56519312"/>
+        <c:axId val="9681223"/>
+        <c:axId val="49602821"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34704011"/>
+        <c:axId val="9681223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4709,7 +4523,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56519312"/>
+        <c:crossAx val="49602821"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4717,7 +4531,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56519312"/>
+        <c:axId val="49602821"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4793,7 +4607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34704011"/>
+        <c:crossAx val="9681223"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5105,13 +4919,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="1" t="str">
+        <f aca="false">"Trading Dashboard — "&amp;TEXT(Tracker!$C$6,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" → "&amp;TEXT(Tracker!$C$7,"[&gt;=100000]₹#\,##\,##0;₹#,##0")</f>
+        <v>Trading Dashboard — ₹10,000 → ₹1,00,000</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -5126,36 +4941,36 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3"/>
       <c r="K4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="n">
         <f aca="false">Tracker!$G$5</f>
-        <v>4230</v>
+        <v>10000</v>
       </c>
       <c r="C5" s="4"/>
       <c r="E5" s="4" t="n">
         <f aca="false">Tracker!$G$6</f>
-        <v>95770</v>
+        <v>90000</v>
       </c>
       <c r="F5" s="4"/>
       <c r="H5" s="5" t="n">
         <f aca="false">Tracker!$J$5</f>
-        <v>0.0423</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="5"/>
       <c r="K5" s="6" t="n">
@@ -5167,7 +4982,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="str">
         <f aca="false">"Started at "&amp;TEXT(Tracker!$C$6,"₹#,##0.00")</f>
-        <v>Started at ₹4,230.00</v>
+        <v>Started at ₹10,000.00</v>
       </c>
       <c r="C6" s="7"/>
       <c r="E6" s="7" t="str">
@@ -5188,19 +5003,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3"/>
     </row>
@@ -5212,12 +5027,12 @@
       <c r="C9" s="8"/>
       <c r="E9" s="4" t="n">
         <f aca="false">Tracker!$G$7</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="F9" s="4"/>
       <c r="H9" s="4" t="n">
         <f aca="false">Tracker!$G$8</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="I9" s="4"/>
       <c r="K9" s="8" t="n">
@@ -5250,19 +5065,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -5312,19 +5127,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3"/>
     </row>
@@ -5341,12 +5156,12 @@
       <c r="F17" s="6"/>
       <c r="H17" s="9" t="n">
         <f aca="false">Tracker!$J$8</f>
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="n">
         <f aca="false">Tracker!$J$9</f>
-        <v>46450</v>
+        <v>46407</v>
       </c>
       <c r="L17" s="8"/>
     </row>
@@ -5374,7 +5189,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5253,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20944C79-1230-4C86-90FB-EF2F5D586326}</x14:id>
+          <x14:id>{237BE720-693F-47F4-9CA4-67FB6EEB7FD7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5465,7 +5280,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20944C79-1230-4C86-90FB-EF2F5D586326}">
+          <x14:cfRule type="dataBar" id="{237BE720-693F-47F4-9CA4-67FB6EEB7FD7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5506,13 +5321,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>19</v>
+      <c r="A1" s="12" t="str">
+        <f aca="false">"Daily Trading P/L Tracker — "&amp;TEXT($C$6,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" → "&amp;TEXT($C$7,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" Goal"</f>
+        <v>Daily Trading P/L Tracker — ₹10,000 → ₹1,00,000 Goal</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5527,12 +5343,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="E4" s="14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
@@ -5542,47 +5358,47 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="16" t="n">
         <v>46291</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="18" t="n">
         <f aca="false">IF($J$6=0,$C$6,INDEX($H$13:$H$512,$J$6))</f>
-        <v>4230</v>
+        <v>10000</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="19" t="n">
         <f aca="false">MIN(1,MAX(0,$G$5/$C$7))</f>
-        <v>0.0423</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="20" t="n">
-        <v>4230</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="21" t="n">
         <f aca="false">MAX(0,$C$7-$G$5)</f>
-        <v>95770</v>
+        <v>90000</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="22" t="n">
@@ -5592,22 +5408,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="20" t="n">
         <v>100000</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="21" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",ROUND($G$5*$C$8,2))</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="23" t="n">
@@ -5617,32 +5433,32 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="24" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="21" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",ROUND($G$5*$C$9,2))</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="23" t="n">
         <f aca="false">COUNTIF($I$13:$I$512,"Projection")</f>
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="24" t="n">
@@ -5658,17 +5474,17 @@
         <v>46293</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="25" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",IF(AND($C$512&lt;&gt;"",N($F$512)&lt;$C$7),"Beyond 500 rows",MAX($B$13:$B$512)))</f>
-        <v>46450</v>
+        <v>46407</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="26"/>
@@ -5683,37 +5499,37 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="D12" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="E12" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="F12" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="G12" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="H12" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="I12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="J12" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="K12" s="28" t="s">
         <v>41</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5727,19 +5543,19 @@
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">$C$6</f>
-        <v>4230</v>
+        <v>10000</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">IF(C13="","",ROUND(C13*$C$8,2))</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">IF(C13="","",ROUND(C13*$C$9,2))</f>
-        <v>126.9</v>
+        <v>300</v>
       </c>
       <c r="F13" s="31" t="n">
         <f aca="false">IF(C13="","",C13+D13)</f>
-        <v>4356.9</v>
+        <v>10300</v>
       </c>
       <c r="G13" s="32"/>
       <c r="H13" s="31" t="str">
@@ -5764,19 +5580,19 @@
       </c>
       <c r="C14" s="31" t="n">
         <f aca="false">IF(C13="","",IF(OR(IF(ISNUMBER(G13),H13,F13)&gt;=$C$7,IF(ISNUMBER(G13),H13,F13)&lt;=0),"",IF(ISNUMBER(G13),H13,F13)))</f>
-        <v>4356.9</v>
+        <v>10300</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">IF(C14="","",ROUND(C14*$C$8,2))</f>
-        <v>130.71</v>
+        <v>309</v>
       </c>
       <c r="E14" s="31" t="n">
         <f aca="false">IF(C14="","",ROUND(C14*$C$9,2))</f>
-        <v>130.71</v>
+        <v>309</v>
       </c>
       <c r="F14" s="31" t="n">
         <f aca="false">IF(C14="","",C14+D14)</f>
-        <v>4487.61</v>
+        <v>10609</v>
       </c>
       <c r="G14" s="32"/>
       <c r="H14" s="31" t="str">
@@ -5801,19 +5617,19 @@
       </c>
       <c r="C15" s="31" t="n">
         <f aca="false">IF(C14="","",IF(OR(IF(ISNUMBER(G14),H14,F14)&gt;=$C$7,IF(ISNUMBER(G14),H14,F14)&lt;=0),"",IF(ISNUMBER(G14),H14,F14)))</f>
-        <v>4487.61</v>
+        <v>10609</v>
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">IF(C15="","",ROUND(C15*$C$8,2))</f>
-        <v>134.63</v>
+        <v>318.27</v>
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">IF(C15="","",ROUND(C15*$C$9,2))</f>
-        <v>134.63</v>
+        <v>318.27</v>
       </c>
       <c r="F15" s="31" t="n">
         <f aca="false">IF(C15="","",C15+D15)</f>
-        <v>4622.24</v>
+        <v>10927.27</v>
       </c>
       <c r="G15" s="32"/>
       <c r="H15" s="31" t="str">
@@ -5838,19 +5654,19 @@
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">IF(C15="","",IF(OR(IF(ISNUMBER(G15),H15,F15)&gt;=$C$7,IF(ISNUMBER(G15),H15,F15)&lt;=0),"",IF(ISNUMBER(G15),H15,F15)))</f>
-        <v>4622.24</v>
+        <v>10927.27</v>
       </c>
       <c r="D16" s="31" t="n">
         <f aca="false">IF(C16="","",ROUND(C16*$C$8,2))</f>
-        <v>138.67</v>
+        <v>327.82</v>
       </c>
       <c r="E16" s="31" t="n">
         <f aca="false">IF(C16="","",ROUND(C16*$C$9,2))</f>
-        <v>138.67</v>
+        <v>327.82</v>
       </c>
       <c r="F16" s="31" t="n">
         <f aca="false">IF(C16="","",C16+D16)</f>
-        <v>4760.91</v>
+        <v>11255.09</v>
       </c>
       <c r="G16" s="32"/>
       <c r="H16" s="31" t="str">
@@ -5875,19 +5691,19 @@
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">IF(C16="","",IF(OR(IF(ISNUMBER(G16),H16,F16)&gt;=$C$7,IF(ISNUMBER(G16),H16,F16)&lt;=0),"",IF(ISNUMBER(G16),H16,F16)))</f>
-        <v>4760.91</v>
+        <v>11255.09</v>
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">IF(C17="","",ROUND(C17*$C$8,2))</f>
-        <v>142.83</v>
+        <v>337.65</v>
       </c>
       <c r="E17" s="31" t="n">
         <f aca="false">IF(C17="","",ROUND(C17*$C$9,2))</f>
-        <v>142.83</v>
+        <v>337.65</v>
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">IF(C17="","",C17+D17)</f>
-        <v>4903.74</v>
+        <v>11592.74</v>
       </c>
       <c r="G17" s="32"/>
       <c r="H17" s="31" t="str">
@@ -5912,19 +5728,19 @@
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IF(C17="","",IF(OR(IF(ISNUMBER(G17),H17,F17)&gt;=$C$7,IF(ISNUMBER(G17),H17,F17)&lt;=0),"",IF(ISNUMBER(G17),H17,F17)))</f>
-        <v>4903.74</v>
+        <v>11592.74</v>
       </c>
       <c r="D18" s="31" t="n">
         <f aca="false">IF(C18="","",ROUND(C18*$C$8,2))</f>
-        <v>147.11</v>
+        <v>347.78</v>
       </c>
       <c r="E18" s="31" t="n">
         <f aca="false">IF(C18="","",ROUND(C18*$C$9,2))</f>
-        <v>147.11</v>
+        <v>347.78</v>
       </c>
       <c r="F18" s="31" t="n">
         <f aca="false">IF(C18="","",C18+D18)</f>
-        <v>5050.85</v>
+        <v>11940.52</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="31" t="str">
@@ -5949,19 +5765,19 @@
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">IF(C18="","",IF(OR(IF(ISNUMBER(G18),H18,F18)&gt;=$C$7,IF(ISNUMBER(G18),H18,F18)&lt;=0),"",IF(ISNUMBER(G18),H18,F18)))</f>
-        <v>5050.85</v>
+        <v>11940.52</v>
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">IF(C19="","",ROUND(C19*$C$8,2))</f>
-        <v>151.53</v>
+        <v>358.22</v>
       </c>
       <c r="E19" s="31" t="n">
         <f aca="false">IF(C19="","",ROUND(C19*$C$9,2))</f>
-        <v>151.53</v>
+        <v>358.22</v>
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">IF(C19="","",C19+D19)</f>
-        <v>5202.38</v>
+        <v>12298.74</v>
       </c>
       <c r="G19" s="32"/>
       <c r="H19" s="31" t="str">
@@ -5986,19 +5802,19 @@
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">IF(C19="","",IF(OR(IF(ISNUMBER(G19),H19,F19)&gt;=$C$7,IF(ISNUMBER(G19),H19,F19)&lt;=0),"",IF(ISNUMBER(G19),H19,F19)))</f>
-        <v>5202.38</v>
+        <v>12298.74</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">IF(C20="","",ROUND(C20*$C$8,2))</f>
-        <v>156.07</v>
+        <v>368.96</v>
       </c>
       <c r="E20" s="31" t="n">
         <f aca="false">IF(C20="","",ROUND(C20*$C$9,2))</f>
-        <v>156.07</v>
+        <v>368.96</v>
       </c>
       <c r="F20" s="31" t="n">
         <f aca="false">IF(C20="","",C20+D20)</f>
-        <v>5358.45</v>
+        <v>12667.7</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="31" t="str">
@@ -6023,19 +5839,19 @@
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">IF(C20="","",IF(OR(IF(ISNUMBER(G20),H20,F20)&gt;=$C$7,IF(ISNUMBER(G20),H20,F20)&lt;=0),"",IF(ISNUMBER(G20),H20,F20)))</f>
-        <v>5358.45</v>
+        <v>12667.7</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">IF(C21="","",ROUND(C21*$C$8,2))</f>
-        <v>160.75</v>
+        <v>380.03</v>
       </c>
       <c r="E21" s="31" t="n">
         <f aca="false">IF(C21="","",ROUND(C21*$C$9,2))</f>
-        <v>160.75</v>
+        <v>380.03</v>
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">IF(C21="","",C21+D21)</f>
-        <v>5519.2</v>
+        <v>13047.73</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="31" t="str">
@@ -6060,19 +5876,19 @@
       </c>
       <c r="C22" s="31" t="n">
         <f aca="false">IF(C21="","",IF(OR(IF(ISNUMBER(G21),H21,F21)&gt;=$C$7,IF(ISNUMBER(G21),H21,F21)&lt;=0),"",IF(ISNUMBER(G21),H21,F21)))</f>
-        <v>5519.2</v>
+        <v>13047.73</v>
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">IF(C22="","",ROUND(C22*$C$8,2))</f>
-        <v>165.58</v>
+        <v>391.43</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">IF(C22="","",ROUND(C22*$C$9,2))</f>
-        <v>165.58</v>
+        <v>391.43</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">IF(C22="","",C22+D22)</f>
-        <v>5684.78</v>
+        <v>13439.16</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="31" t="str">
@@ -6097,19 +5913,19 @@
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">IF(C22="","",IF(OR(IF(ISNUMBER(G22),H22,F22)&gt;=$C$7,IF(ISNUMBER(G22),H22,F22)&lt;=0),"",IF(ISNUMBER(G22),H22,F22)))</f>
-        <v>5684.78</v>
+        <v>13439.16</v>
       </c>
       <c r="D23" s="31" t="n">
         <f aca="false">IF(C23="","",ROUND(C23*$C$8,2))</f>
-        <v>170.54</v>
+        <v>403.17</v>
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">IF(C23="","",ROUND(C23*$C$9,2))</f>
-        <v>170.54</v>
+        <v>403.17</v>
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">IF(C23="","",C23+D23)</f>
-        <v>5855.32</v>
+        <v>13842.33</v>
       </c>
       <c r="G23" s="32"/>
       <c r="H23" s="31" t="str">
@@ -6134,19 +5950,19 @@
       </c>
       <c r="C24" s="31" t="n">
         <f aca="false">IF(C23="","",IF(OR(IF(ISNUMBER(G23),H23,F23)&gt;=$C$7,IF(ISNUMBER(G23),H23,F23)&lt;=0),"",IF(ISNUMBER(G23),H23,F23)))</f>
-        <v>5855.32</v>
+        <v>13842.33</v>
       </c>
       <c r="D24" s="31" t="n">
         <f aca="false">IF(C24="","",ROUND(C24*$C$8,2))</f>
-        <v>175.66</v>
+        <v>415.27</v>
       </c>
       <c r="E24" s="31" t="n">
         <f aca="false">IF(C24="","",ROUND(C24*$C$9,2))</f>
-        <v>175.66</v>
+        <v>415.27</v>
       </c>
       <c r="F24" s="31" t="n">
         <f aca="false">IF(C24="","",C24+D24)</f>
-        <v>6030.98</v>
+        <v>14257.6</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="31" t="str">
@@ -6171,19 +5987,19 @@
       </c>
       <c r="C25" s="31" t="n">
         <f aca="false">IF(C24="","",IF(OR(IF(ISNUMBER(G24),H24,F24)&gt;=$C$7,IF(ISNUMBER(G24),H24,F24)&lt;=0),"",IF(ISNUMBER(G24),H24,F24)))</f>
-        <v>6030.98</v>
+        <v>14257.6</v>
       </c>
       <c r="D25" s="31" t="n">
         <f aca="false">IF(C25="","",ROUND(C25*$C$8,2))</f>
-        <v>180.93</v>
+        <v>427.73</v>
       </c>
       <c r="E25" s="31" t="n">
         <f aca="false">IF(C25="","",ROUND(C25*$C$9,2))</f>
-        <v>180.93</v>
+        <v>427.73</v>
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">IF(C25="","",C25+D25)</f>
-        <v>6211.91</v>
+        <v>14685.33</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="31" t="str">
@@ -6208,19 +6024,19 @@
       </c>
       <c r="C26" s="31" t="n">
         <f aca="false">IF(C25="","",IF(OR(IF(ISNUMBER(G25),H25,F25)&gt;=$C$7,IF(ISNUMBER(G25),H25,F25)&lt;=0),"",IF(ISNUMBER(G25),H25,F25)))</f>
-        <v>6211.91</v>
+        <v>14685.33</v>
       </c>
       <c r="D26" s="31" t="n">
         <f aca="false">IF(C26="","",ROUND(C26*$C$8,2))</f>
-        <v>186.36</v>
+        <v>440.56</v>
       </c>
       <c r="E26" s="31" t="n">
         <f aca="false">IF(C26="","",ROUND(C26*$C$9,2))</f>
-        <v>186.36</v>
+        <v>440.56</v>
       </c>
       <c r="F26" s="31" t="n">
         <f aca="false">IF(C26="","",C26+D26)</f>
-        <v>6398.27</v>
+        <v>15125.89</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="31" t="str">
@@ -6245,19 +6061,19 @@
       </c>
       <c r="C27" s="31" t="n">
         <f aca="false">IF(C26="","",IF(OR(IF(ISNUMBER(G26),H26,F26)&gt;=$C$7,IF(ISNUMBER(G26),H26,F26)&lt;=0),"",IF(ISNUMBER(G26),H26,F26)))</f>
-        <v>6398.27</v>
+        <v>15125.89</v>
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">IF(C27="","",ROUND(C27*$C$8,2))</f>
-        <v>191.95</v>
+        <v>453.78</v>
       </c>
       <c r="E27" s="31" t="n">
         <f aca="false">IF(C27="","",ROUND(C27*$C$9,2))</f>
-        <v>191.95</v>
+        <v>453.78</v>
       </c>
       <c r="F27" s="31" t="n">
         <f aca="false">IF(C27="","",C27+D27)</f>
-        <v>6590.22</v>
+        <v>15579.67</v>
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="31" t="str">
@@ -6282,19 +6098,19 @@
       </c>
       <c r="C28" s="31" t="n">
         <f aca="false">IF(C27="","",IF(OR(IF(ISNUMBER(G27),H27,F27)&gt;=$C$7,IF(ISNUMBER(G27),H27,F27)&lt;=0),"",IF(ISNUMBER(G27),H27,F27)))</f>
-        <v>6590.22</v>
+        <v>15579.67</v>
       </c>
       <c r="D28" s="31" t="n">
         <f aca="false">IF(C28="","",ROUND(C28*$C$8,2))</f>
-        <v>197.71</v>
+        <v>467.39</v>
       </c>
       <c r="E28" s="31" t="n">
         <f aca="false">IF(C28="","",ROUND(C28*$C$9,2))</f>
-        <v>197.71</v>
+        <v>467.39</v>
       </c>
       <c r="F28" s="31" t="n">
         <f aca="false">IF(C28="","",C28+D28)</f>
-        <v>6787.93</v>
+        <v>16047.06</v>
       </c>
       <c r="G28" s="32"/>
       <c r="H28" s="31" t="str">
@@ -6319,19 +6135,19 @@
       </c>
       <c r="C29" s="31" t="n">
         <f aca="false">IF(C28="","",IF(OR(IF(ISNUMBER(G28),H28,F28)&gt;=$C$7,IF(ISNUMBER(G28),H28,F28)&lt;=0),"",IF(ISNUMBER(G28),H28,F28)))</f>
-        <v>6787.93</v>
+        <v>16047.06</v>
       </c>
       <c r="D29" s="31" t="n">
         <f aca="false">IF(C29="","",ROUND(C29*$C$8,2))</f>
-        <v>203.64</v>
+        <v>481.41</v>
       </c>
       <c r="E29" s="31" t="n">
         <f aca="false">IF(C29="","",ROUND(C29*$C$9,2))</f>
-        <v>203.64</v>
+        <v>481.41</v>
       </c>
       <c r="F29" s="31" t="n">
         <f aca="false">IF(C29="","",C29+D29)</f>
-        <v>6991.57</v>
+        <v>16528.47</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="31" t="str">
@@ -6356,19 +6172,19 @@
       </c>
       <c r="C30" s="31" t="n">
         <f aca="false">IF(C29="","",IF(OR(IF(ISNUMBER(G29),H29,F29)&gt;=$C$7,IF(ISNUMBER(G29),H29,F29)&lt;=0),"",IF(ISNUMBER(G29),H29,F29)))</f>
-        <v>6991.57</v>
+        <v>16528.47</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">IF(C30="","",ROUND(C30*$C$8,2))</f>
-        <v>209.75</v>
+        <v>495.85</v>
       </c>
       <c r="E30" s="31" t="n">
         <f aca="false">IF(C30="","",ROUND(C30*$C$9,2))</f>
-        <v>209.75</v>
+        <v>495.85</v>
       </c>
       <c r="F30" s="31" t="n">
         <f aca="false">IF(C30="","",C30+D30)</f>
-        <v>7201.32</v>
+        <v>17024.32</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="31" t="str">
@@ -6393,19 +6209,19 @@
       </c>
       <c r="C31" s="31" t="n">
         <f aca="false">IF(C30="","",IF(OR(IF(ISNUMBER(G30),H30,F30)&gt;=$C$7,IF(ISNUMBER(G30),H30,F30)&lt;=0),"",IF(ISNUMBER(G30),H30,F30)))</f>
-        <v>7201.32</v>
+        <v>17024.32</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">IF(C31="","",ROUND(C31*$C$8,2))</f>
-        <v>216.04</v>
+        <v>510.73</v>
       </c>
       <c r="E31" s="31" t="n">
         <f aca="false">IF(C31="","",ROUND(C31*$C$9,2))</f>
-        <v>216.04</v>
+        <v>510.73</v>
       </c>
       <c r="F31" s="31" t="n">
         <f aca="false">IF(C31="","",C31+D31)</f>
-        <v>7417.36</v>
+        <v>17535.05</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="31" t="str">
@@ -6430,19 +6246,19 @@
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">IF(C31="","",IF(OR(IF(ISNUMBER(G31),H31,F31)&gt;=$C$7,IF(ISNUMBER(G31),H31,F31)&lt;=0),"",IF(ISNUMBER(G31),H31,F31)))</f>
-        <v>7417.36</v>
+        <v>17535.05</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">IF(C32="","",ROUND(C32*$C$8,2))</f>
-        <v>222.52</v>
+        <v>526.05</v>
       </c>
       <c r="E32" s="31" t="n">
         <f aca="false">IF(C32="","",ROUND(C32*$C$9,2))</f>
-        <v>222.52</v>
+        <v>526.05</v>
       </c>
       <c r="F32" s="31" t="n">
         <f aca="false">IF(C32="","",C32+D32)</f>
-        <v>7639.88</v>
+        <v>18061.1</v>
       </c>
       <c r="G32" s="32"/>
       <c r="H32" s="31" t="str">
@@ -6467,19 +6283,19 @@
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IF(C32="","",IF(OR(IF(ISNUMBER(G32),H32,F32)&gt;=$C$7,IF(ISNUMBER(G32),H32,F32)&lt;=0),"",IF(ISNUMBER(G32),H32,F32)))</f>
-        <v>7639.88</v>
+        <v>18061.1</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">IF(C33="","",ROUND(C33*$C$8,2))</f>
-        <v>229.2</v>
+        <v>541.83</v>
       </c>
       <c r="E33" s="31" t="n">
         <f aca="false">IF(C33="","",ROUND(C33*$C$9,2))</f>
-        <v>229.2</v>
+        <v>541.83</v>
       </c>
       <c r="F33" s="31" t="n">
         <f aca="false">IF(C33="","",C33+D33)</f>
-        <v>7869.08</v>
+        <v>18602.93</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="31" t="str">
@@ -6504,19 +6320,19 @@
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IF(C33="","",IF(OR(IF(ISNUMBER(G33),H33,F33)&gt;=$C$7,IF(ISNUMBER(G33),H33,F33)&lt;=0),"",IF(ISNUMBER(G33),H33,F33)))</f>
-        <v>7869.08</v>
+        <v>18602.93</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">IF(C34="","",ROUND(C34*$C$8,2))</f>
-        <v>236.07</v>
+        <v>558.09</v>
       </c>
       <c r="E34" s="31" t="n">
         <f aca="false">IF(C34="","",ROUND(C34*$C$9,2))</f>
-        <v>236.07</v>
+        <v>558.09</v>
       </c>
       <c r="F34" s="31" t="n">
         <f aca="false">IF(C34="","",C34+D34)</f>
-        <v>8105.15</v>
+        <v>19161.02</v>
       </c>
       <c r="G34" s="32"/>
       <c r="H34" s="31" t="str">
@@ -6541,19 +6357,19 @@
       </c>
       <c r="C35" s="31" t="n">
         <f aca="false">IF(C34="","",IF(OR(IF(ISNUMBER(G34),H34,F34)&gt;=$C$7,IF(ISNUMBER(G34),H34,F34)&lt;=0),"",IF(ISNUMBER(G34),H34,F34)))</f>
-        <v>8105.15</v>
+        <v>19161.02</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">IF(C35="","",ROUND(C35*$C$8,2))</f>
-        <v>243.15</v>
+        <v>574.83</v>
       </c>
       <c r="E35" s="31" t="n">
         <f aca="false">IF(C35="","",ROUND(C35*$C$9,2))</f>
-        <v>243.15</v>
+        <v>574.83</v>
       </c>
       <c r="F35" s="31" t="n">
         <f aca="false">IF(C35="","",C35+D35)</f>
-        <v>8348.3</v>
+        <v>19735.85</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="31" t="str">
@@ -6578,19 +6394,19 @@
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">IF(C35="","",IF(OR(IF(ISNUMBER(G35),H35,F35)&gt;=$C$7,IF(ISNUMBER(G35),H35,F35)&lt;=0),"",IF(ISNUMBER(G35),H35,F35)))</f>
-        <v>8348.3</v>
+        <v>19735.85</v>
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">IF(C36="","",ROUND(C36*$C$8,2))</f>
-        <v>250.45</v>
+        <v>592.08</v>
       </c>
       <c r="E36" s="31" t="n">
         <f aca="false">IF(C36="","",ROUND(C36*$C$9,2))</f>
-        <v>250.45</v>
+        <v>592.08</v>
       </c>
       <c r="F36" s="31" t="n">
         <f aca="false">IF(C36="","",C36+D36)</f>
-        <v>8598.75</v>
+        <v>20327.93</v>
       </c>
       <c r="G36" s="32"/>
       <c r="H36" s="31" t="str">
@@ -6615,19 +6431,19 @@
       </c>
       <c r="C37" s="31" t="n">
         <f aca="false">IF(C36="","",IF(OR(IF(ISNUMBER(G36),H36,F36)&gt;=$C$7,IF(ISNUMBER(G36),H36,F36)&lt;=0),"",IF(ISNUMBER(G36),H36,F36)))</f>
-        <v>8598.75</v>
+        <v>20327.93</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">IF(C37="","",ROUND(C37*$C$8,2))</f>
-        <v>257.96</v>
+        <v>609.84</v>
       </c>
       <c r="E37" s="31" t="n">
         <f aca="false">IF(C37="","",ROUND(C37*$C$9,2))</f>
-        <v>257.96</v>
+        <v>609.84</v>
       </c>
       <c r="F37" s="31" t="n">
         <f aca="false">IF(C37="","",C37+D37)</f>
-        <v>8856.71</v>
+        <v>20937.77</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="31" t="str">
@@ -6652,19 +6468,19 @@
       </c>
       <c r="C38" s="31" t="n">
         <f aca="false">IF(C37="","",IF(OR(IF(ISNUMBER(G37),H37,F37)&gt;=$C$7,IF(ISNUMBER(G37),H37,F37)&lt;=0),"",IF(ISNUMBER(G37),H37,F37)))</f>
-        <v>8856.71</v>
+        <v>20937.77</v>
       </c>
       <c r="D38" s="31" t="n">
         <f aca="false">IF(C38="","",ROUND(C38*$C$8,2))</f>
-        <v>265.7</v>
+        <v>628.13</v>
       </c>
       <c r="E38" s="31" t="n">
         <f aca="false">IF(C38="","",ROUND(C38*$C$9,2))</f>
-        <v>265.7</v>
+        <v>628.13</v>
       </c>
       <c r="F38" s="31" t="n">
         <f aca="false">IF(C38="","",C38+D38)</f>
-        <v>9122.41</v>
+        <v>21565.9</v>
       </c>
       <c r="G38" s="32"/>
       <c r="H38" s="31" t="str">
@@ -6689,19 +6505,19 @@
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">IF(C38="","",IF(OR(IF(ISNUMBER(G38),H38,F38)&gt;=$C$7,IF(ISNUMBER(G38),H38,F38)&lt;=0),"",IF(ISNUMBER(G38),H38,F38)))</f>
-        <v>9122.41</v>
+        <v>21565.9</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">IF(C39="","",ROUND(C39*$C$8,2))</f>
-        <v>273.67</v>
+        <v>646.98</v>
       </c>
       <c r="E39" s="31" t="n">
         <f aca="false">IF(C39="","",ROUND(C39*$C$9,2))</f>
-        <v>273.67</v>
+        <v>646.98</v>
       </c>
       <c r="F39" s="31" t="n">
         <f aca="false">IF(C39="","",C39+D39)</f>
-        <v>9396.08</v>
+        <v>22212.88</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="31" t="str">
@@ -6726,19 +6542,19 @@
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">IF(C39="","",IF(OR(IF(ISNUMBER(G39),H39,F39)&gt;=$C$7,IF(ISNUMBER(G39),H39,F39)&lt;=0),"",IF(ISNUMBER(G39),H39,F39)))</f>
-        <v>9396.08</v>
+        <v>22212.88</v>
       </c>
       <c r="D40" s="31" t="n">
         <f aca="false">IF(C40="","",ROUND(C40*$C$8,2))</f>
-        <v>281.88</v>
+        <v>666.39</v>
       </c>
       <c r="E40" s="31" t="n">
         <f aca="false">IF(C40="","",ROUND(C40*$C$9,2))</f>
-        <v>281.88</v>
+        <v>666.39</v>
       </c>
       <c r="F40" s="31" t="n">
         <f aca="false">IF(C40="","",C40+D40)</f>
-        <v>9677.96</v>
+        <v>22879.27</v>
       </c>
       <c r="G40" s="32"/>
       <c r="H40" s="31" t="str">
@@ -6763,19 +6579,19 @@
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">IF(C40="","",IF(OR(IF(ISNUMBER(G40),H40,F40)&gt;=$C$7,IF(ISNUMBER(G40),H40,F40)&lt;=0),"",IF(ISNUMBER(G40),H40,F40)))</f>
-        <v>9677.96</v>
+        <v>22879.27</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">IF(C41="","",ROUND(C41*$C$8,2))</f>
-        <v>290.34</v>
+        <v>686.38</v>
       </c>
       <c r="E41" s="31" t="n">
         <f aca="false">IF(C41="","",ROUND(C41*$C$9,2))</f>
-        <v>290.34</v>
+        <v>686.38</v>
       </c>
       <c r="F41" s="31" t="n">
         <f aca="false">IF(C41="","",C41+D41)</f>
-        <v>9968.3</v>
+        <v>23565.65</v>
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="31" t="str">
@@ -6800,19 +6616,19 @@
       </c>
       <c r="C42" s="31" t="n">
         <f aca="false">IF(C41="","",IF(OR(IF(ISNUMBER(G41),H41,F41)&gt;=$C$7,IF(ISNUMBER(G41),H41,F41)&lt;=0),"",IF(ISNUMBER(G41),H41,F41)))</f>
-        <v>9968.3</v>
+        <v>23565.65</v>
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">IF(C42="","",ROUND(C42*$C$8,2))</f>
-        <v>299.05</v>
+        <v>706.97</v>
       </c>
       <c r="E42" s="31" t="n">
         <f aca="false">IF(C42="","",ROUND(C42*$C$9,2))</f>
-        <v>299.05</v>
+        <v>706.97</v>
       </c>
       <c r="F42" s="31" t="n">
         <f aca="false">IF(C42="","",C42+D42)</f>
-        <v>10267.35</v>
+        <v>24272.62</v>
       </c>
       <c r="G42" s="32"/>
       <c r="H42" s="31" t="str">
@@ -6837,19 +6653,19 @@
       </c>
       <c r="C43" s="31" t="n">
         <f aca="false">IF(C42="","",IF(OR(IF(ISNUMBER(G42),H42,F42)&gt;=$C$7,IF(ISNUMBER(G42),H42,F42)&lt;=0),"",IF(ISNUMBER(G42),H42,F42)))</f>
-        <v>10267.35</v>
+        <v>24272.62</v>
       </c>
       <c r="D43" s="31" t="n">
         <f aca="false">IF(C43="","",ROUND(C43*$C$8,2))</f>
-        <v>308.02</v>
+        <v>728.18</v>
       </c>
       <c r="E43" s="31" t="n">
         <f aca="false">IF(C43="","",ROUND(C43*$C$9,2))</f>
-        <v>308.02</v>
+        <v>728.18</v>
       </c>
       <c r="F43" s="31" t="n">
         <f aca="false">IF(C43="","",C43+D43)</f>
-        <v>10575.37</v>
+        <v>25000.8</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="31" t="str">
@@ -6874,19 +6690,19 @@
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">IF(C43="","",IF(OR(IF(ISNUMBER(G43),H43,F43)&gt;=$C$7,IF(ISNUMBER(G43),H43,F43)&lt;=0),"",IF(ISNUMBER(G43),H43,F43)))</f>
-        <v>10575.37</v>
+        <v>25000.8</v>
       </c>
       <c r="D44" s="31" t="n">
         <f aca="false">IF(C44="","",ROUND(C44*$C$8,2))</f>
-        <v>317.26</v>
+        <v>750.02</v>
       </c>
       <c r="E44" s="31" t="n">
         <f aca="false">IF(C44="","",ROUND(C44*$C$9,2))</f>
-        <v>317.26</v>
+        <v>750.02</v>
       </c>
       <c r="F44" s="31" t="n">
         <f aca="false">IF(C44="","",C44+D44)</f>
-        <v>10892.63</v>
+        <v>25750.82</v>
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="31" t="str">
@@ -6911,19 +6727,19 @@
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">IF(C44="","",IF(OR(IF(ISNUMBER(G44),H44,F44)&gt;=$C$7,IF(ISNUMBER(G44),H44,F44)&lt;=0),"",IF(ISNUMBER(G44),H44,F44)))</f>
-        <v>10892.63</v>
+        <v>25750.82</v>
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">IF(C45="","",ROUND(C45*$C$8,2))</f>
-        <v>326.78</v>
+        <v>772.52</v>
       </c>
       <c r="E45" s="31" t="n">
         <f aca="false">IF(C45="","",ROUND(C45*$C$9,2))</f>
-        <v>326.78</v>
+        <v>772.52</v>
       </c>
       <c r="F45" s="31" t="n">
         <f aca="false">IF(C45="","",C45+D45)</f>
-        <v>11219.41</v>
+        <v>26523.34</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="31" t="str">
@@ -6948,19 +6764,19 @@
       </c>
       <c r="C46" s="31" t="n">
         <f aca="false">IF(C45="","",IF(OR(IF(ISNUMBER(G45),H45,F45)&gt;=$C$7,IF(ISNUMBER(G45),H45,F45)&lt;=0),"",IF(ISNUMBER(G45),H45,F45)))</f>
-        <v>11219.41</v>
+        <v>26523.34</v>
       </c>
       <c r="D46" s="31" t="n">
         <f aca="false">IF(C46="","",ROUND(C46*$C$8,2))</f>
-        <v>336.58</v>
+        <v>795.7</v>
       </c>
       <c r="E46" s="31" t="n">
         <f aca="false">IF(C46="","",ROUND(C46*$C$9,2))</f>
-        <v>336.58</v>
+        <v>795.7</v>
       </c>
       <c r="F46" s="31" t="n">
         <f aca="false">IF(C46="","",C46+D46)</f>
-        <v>11555.99</v>
+        <v>27319.04</v>
       </c>
       <c r="G46" s="32"/>
       <c r="H46" s="31" t="str">
@@ -6985,19 +6801,19 @@
       </c>
       <c r="C47" s="31" t="n">
         <f aca="false">IF(C46="","",IF(OR(IF(ISNUMBER(G46),H46,F46)&gt;=$C$7,IF(ISNUMBER(G46),H46,F46)&lt;=0),"",IF(ISNUMBER(G46),H46,F46)))</f>
-        <v>11555.99</v>
+        <v>27319.04</v>
       </c>
       <c r="D47" s="31" t="n">
         <f aca="false">IF(C47="","",ROUND(C47*$C$8,2))</f>
-        <v>346.68</v>
+        <v>819.57</v>
       </c>
       <c r="E47" s="31" t="n">
         <f aca="false">IF(C47="","",ROUND(C47*$C$9,2))</f>
-        <v>346.68</v>
+        <v>819.57</v>
       </c>
       <c r="F47" s="31" t="n">
         <f aca="false">IF(C47="","",C47+D47)</f>
-        <v>11902.67</v>
+        <v>28138.61</v>
       </c>
       <c r="G47" s="32"/>
       <c r="H47" s="31" t="str">
@@ -7022,19 +6838,19 @@
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">IF(C47="","",IF(OR(IF(ISNUMBER(G47),H47,F47)&gt;=$C$7,IF(ISNUMBER(G47),H47,F47)&lt;=0),"",IF(ISNUMBER(G47),H47,F47)))</f>
-        <v>11902.67</v>
+        <v>28138.61</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">IF(C48="","",ROUND(C48*$C$8,2))</f>
-        <v>357.08</v>
+        <v>844.16</v>
       </c>
       <c r="E48" s="31" t="n">
         <f aca="false">IF(C48="","",ROUND(C48*$C$9,2))</f>
-        <v>357.08</v>
+        <v>844.16</v>
       </c>
       <c r="F48" s="31" t="n">
         <f aca="false">IF(C48="","",C48+D48)</f>
-        <v>12259.75</v>
+        <v>28982.77</v>
       </c>
       <c r="G48" s="32"/>
       <c r="H48" s="31" t="str">
@@ -7059,19 +6875,19 @@
       </c>
       <c r="C49" s="31" t="n">
         <f aca="false">IF(C48="","",IF(OR(IF(ISNUMBER(G48),H48,F48)&gt;=$C$7,IF(ISNUMBER(G48),H48,F48)&lt;=0),"",IF(ISNUMBER(G48),H48,F48)))</f>
-        <v>12259.75</v>
+        <v>28982.77</v>
       </c>
       <c r="D49" s="31" t="n">
         <f aca="false">IF(C49="","",ROUND(C49*$C$8,2))</f>
-        <v>367.79</v>
+        <v>869.48</v>
       </c>
       <c r="E49" s="31" t="n">
         <f aca="false">IF(C49="","",ROUND(C49*$C$9,2))</f>
-        <v>367.79</v>
+        <v>869.48</v>
       </c>
       <c r="F49" s="31" t="n">
         <f aca="false">IF(C49="","",C49+D49)</f>
-        <v>12627.54</v>
+        <v>29852.25</v>
       </c>
       <c r="G49" s="32"/>
       <c r="H49" s="31" t="str">
@@ -7096,19 +6912,19 @@
       </c>
       <c r="C50" s="31" t="n">
         <f aca="false">IF(C49="","",IF(OR(IF(ISNUMBER(G49),H49,F49)&gt;=$C$7,IF(ISNUMBER(G49),H49,F49)&lt;=0),"",IF(ISNUMBER(G49),H49,F49)))</f>
-        <v>12627.54</v>
+        <v>29852.25</v>
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">IF(C50="","",ROUND(C50*$C$8,2))</f>
-        <v>378.83</v>
+        <v>895.57</v>
       </c>
       <c r="E50" s="31" t="n">
         <f aca="false">IF(C50="","",ROUND(C50*$C$9,2))</f>
-        <v>378.83</v>
+        <v>895.57</v>
       </c>
       <c r="F50" s="31" t="n">
         <f aca="false">IF(C50="","",C50+D50)</f>
-        <v>13006.37</v>
+        <v>30747.82</v>
       </c>
       <c r="G50" s="32"/>
       <c r="H50" s="31" t="str">
@@ -7133,19 +6949,19 @@
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">IF(C50="","",IF(OR(IF(ISNUMBER(G50),H50,F50)&gt;=$C$7,IF(ISNUMBER(G50),H50,F50)&lt;=0),"",IF(ISNUMBER(G50),H50,F50)))</f>
-        <v>13006.37</v>
+        <v>30747.82</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">IF(C51="","",ROUND(C51*$C$8,2))</f>
-        <v>390.19</v>
+        <v>922.43</v>
       </c>
       <c r="E51" s="31" t="n">
         <f aca="false">IF(C51="","",ROUND(C51*$C$9,2))</f>
-        <v>390.19</v>
+        <v>922.43</v>
       </c>
       <c r="F51" s="31" t="n">
         <f aca="false">IF(C51="","",C51+D51)</f>
-        <v>13396.56</v>
+        <v>31670.25</v>
       </c>
       <c r="G51" s="32"/>
       <c r="H51" s="31" t="str">
@@ -7170,19 +6986,19 @@
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">IF(C51="","",IF(OR(IF(ISNUMBER(G51),H51,F51)&gt;=$C$7,IF(ISNUMBER(G51),H51,F51)&lt;=0),"",IF(ISNUMBER(G51),H51,F51)))</f>
-        <v>13396.56</v>
+        <v>31670.25</v>
       </c>
       <c r="D52" s="31" t="n">
         <f aca="false">IF(C52="","",ROUND(C52*$C$8,2))</f>
-        <v>401.9</v>
+        <v>950.11</v>
       </c>
       <c r="E52" s="31" t="n">
         <f aca="false">IF(C52="","",ROUND(C52*$C$9,2))</f>
-        <v>401.9</v>
+        <v>950.11</v>
       </c>
       <c r="F52" s="31" t="n">
         <f aca="false">IF(C52="","",C52+D52)</f>
-        <v>13798.46</v>
+        <v>32620.36</v>
       </c>
       <c r="G52" s="32"/>
       <c r="H52" s="31" t="str">
@@ -7207,19 +7023,19 @@
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">IF(C52="","",IF(OR(IF(ISNUMBER(G52),H52,F52)&gt;=$C$7,IF(ISNUMBER(G52),H52,F52)&lt;=0),"",IF(ISNUMBER(G52),H52,F52)))</f>
-        <v>13798.46</v>
+        <v>32620.36</v>
       </c>
       <c r="D53" s="31" t="n">
         <f aca="false">IF(C53="","",ROUND(C53*$C$8,2))</f>
-        <v>413.95</v>
+        <v>978.61</v>
       </c>
       <c r="E53" s="31" t="n">
         <f aca="false">IF(C53="","",ROUND(C53*$C$9,2))</f>
-        <v>413.95</v>
+        <v>978.61</v>
       </c>
       <c r="F53" s="31" t="n">
         <f aca="false">IF(C53="","",C53+D53)</f>
-        <v>14212.41</v>
+        <v>33598.97</v>
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="31" t="str">
@@ -7244,19 +7060,19 @@
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">IF(C53="","",IF(OR(IF(ISNUMBER(G53),H53,F53)&gt;=$C$7,IF(ISNUMBER(G53),H53,F53)&lt;=0),"",IF(ISNUMBER(G53),H53,F53)))</f>
-        <v>14212.41</v>
+        <v>33598.97</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(C54="","",ROUND(C54*$C$8,2))</f>
-        <v>426.37</v>
+        <v>1007.97</v>
       </c>
       <c r="E54" s="31" t="n">
         <f aca="false">IF(C54="","",ROUND(C54*$C$9,2))</f>
-        <v>426.37</v>
+        <v>1007.97</v>
       </c>
       <c r="F54" s="31" t="n">
         <f aca="false">IF(C54="","",C54+D54)</f>
-        <v>14638.78</v>
+        <v>34606.94</v>
       </c>
       <c r="G54" s="32"/>
       <c r="H54" s="31" t="str">
@@ -7281,19 +7097,19 @@
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">IF(C54="","",IF(OR(IF(ISNUMBER(G54),H54,F54)&gt;=$C$7,IF(ISNUMBER(G54),H54,F54)&lt;=0),"",IF(ISNUMBER(G54),H54,F54)))</f>
-        <v>14638.78</v>
+        <v>34606.94</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">IF(C55="","",ROUND(C55*$C$8,2))</f>
-        <v>439.16</v>
+        <v>1038.21</v>
       </c>
       <c r="E55" s="31" t="n">
         <f aca="false">IF(C55="","",ROUND(C55*$C$9,2))</f>
-        <v>439.16</v>
+        <v>1038.21</v>
       </c>
       <c r="F55" s="31" t="n">
         <f aca="false">IF(C55="","",C55+D55)</f>
-        <v>15077.94</v>
+        <v>35645.15</v>
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="31" t="str">
@@ -7318,19 +7134,19 @@
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">IF(C55="","",IF(OR(IF(ISNUMBER(G55),H55,F55)&gt;=$C$7,IF(ISNUMBER(G55),H55,F55)&lt;=0),"",IF(ISNUMBER(G55),H55,F55)))</f>
-        <v>15077.94</v>
+        <v>35645.15</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">IF(C56="","",ROUND(C56*$C$8,2))</f>
-        <v>452.34</v>
+        <v>1069.35</v>
       </c>
       <c r="E56" s="31" t="n">
         <f aca="false">IF(C56="","",ROUND(C56*$C$9,2))</f>
-        <v>452.34</v>
+        <v>1069.35</v>
       </c>
       <c r="F56" s="31" t="n">
         <f aca="false">IF(C56="","",C56+D56)</f>
-        <v>15530.28</v>
+        <v>36714.5</v>
       </c>
       <c r="G56" s="32"/>
       <c r="H56" s="31" t="str">
@@ -7355,19 +7171,19 @@
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">IF(C56="","",IF(OR(IF(ISNUMBER(G56),H56,F56)&gt;=$C$7,IF(ISNUMBER(G56),H56,F56)&lt;=0),"",IF(ISNUMBER(G56),H56,F56)))</f>
-        <v>15530.28</v>
+        <v>36714.5</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(C57="","",ROUND(C57*$C$8,2))</f>
-        <v>465.91</v>
+        <v>1101.44</v>
       </c>
       <c r="E57" s="31" t="n">
         <f aca="false">IF(C57="","",ROUND(C57*$C$9,2))</f>
-        <v>465.91</v>
+        <v>1101.44</v>
       </c>
       <c r="F57" s="31" t="n">
         <f aca="false">IF(C57="","",C57+D57)</f>
-        <v>15996.19</v>
+        <v>37815.94</v>
       </c>
       <c r="G57" s="32"/>
       <c r="H57" s="31" t="str">
@@ -7392,19 +7208,19 @@
       </c>
       <c r="C58" s="31" t="n">
         <f aca="false">IF(C57="","",IF(OR(IF(ISNUMBER(G57),H57,F57)&gt;=$C$7,IF(ISNUMBER(G57),H57,F57)&lt;=0),"",IF(ISNUMBER(G57),H57,F57)))</f>
-        <v>15996.19</v>
+        <v>37815.94</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">IF(C58="","",ROUND(C58*$C$8,2))</f>
-        <v>479.89</v>
+        <v>1134.48</v>
       </c>
       <c r="E58" s="31" t="n">
         <f aca="false">IF(C58="","",ROUND(C58*$C$9,2))</f>
-        <v>479.89</v>
+        <v>1134.48</v>
       </c>
       <c r="F58" s="31" t="n">
         <f aca="false">IF(C58="","",C58+D58)</f>
-        <v>16476.08</v>
+        <v>38950.42</v>
       </c>
       <c r="G58" s="32"/>
       <c r="H58" s="31" t="str">
@@ -7429,19 +7245,19 @@
       </c>
       <c r="C59" s="31" t="n">
         <f aca="false">IF(C58="","",IF(OR(IF(ISNUMBER(G58),H58,F58)&gt;=$C$7,IF(ISNUMBER(G58),H58,F58)&lt;=0),"",IF(ISNUMBER(G58),H58,F58)))</f>
-        <v>16476.08</v>
+        <v>38950.42</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">IF(C59="","",ROUND(C59*$C$8,2))</f>
-        <v>494.28</v>
+        <v>1168.51</v>
       </c>
       <c r="E59" s="31" t="n">
         <f aca="false">IF(C59="","",ROUND(C59*$C$9,2))</f>
-        <v>494.28</v>
+        <v>1168.51</v>
       </c>
       <c r="F59" s="31" t="n">
         <f aca="false">IF(C59="","",C59+D59)</f>
-        <v>16970.36</v>
+        <v>40118.93</v>
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="31" t="str">
@@ -7466,19 +7282,19 @@
       </c>
       <c r="C60" s="31" t="n">
         <f aca="false">IF(C59="","",IF(OR(IF(ISNUMBER(G59),H59,F59)&gt;=$C$7,IF(ISNUMBER(G59),H59,F59)&lt;=0),"",IF(ISNUMBER(G59),H59,F59)))</f>
-        <v>16970.36</v>
+        <v>40118.93</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">IF(C60="","",ROUND(C60*$C$8,2))</f>
-        <v>509.11</v>
+        <v>1203.57</v>
       </c>
       <c r="E60" s="31" t="n">
         <f aca="false">IF(C60="","",ROUND(C60*$C$9,2))</f>
-        <v>509.11</v>
+        <v>1203.57</v>
       </c>
       <c r="F60" s="31" t="n">
         <f aca="false">IF(C60="","",C60+D60)</f>
-        <v>17479.47</v>
+        <v>41322.5</v>
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="31" t="str">
@@ -7503,19 +7319,19 @@
       </c>
       <c r="C61" s="31" t="n">
         <f aca="false">IF(C60="","",IF(OR(IF(ISNUMBER(G60),H60,F60)&gt;=$C$7,IF(ISNUMBER(G60),H60,F60)&lt;=0),"",IF(ISNUMBER(G60),H60,F60)))</f>
-        <v>17479.47</v>
+        <v>41322.5</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">IF(C61="","",ROUND(C61*$C$8,2))</f>
-        <v>524.38</v>
+        <v>1239.68</v>
       </c>
       <c r="E61" s="31" t="n">
         <f aca="false">IF(C61="","",ROUND(C61*$C$9,2))</f>
-        <v>524.38</v>
+        <v>1239.68</v>
       </c>
       <c r="F61" s="31" t="n">
         <f aca="false">IF(C61="","",C61+D61)</f>
-        <v>18003.85</v>
+        <v>42562.18</v>
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="31" t="str">
@@ -7540,19 +7356,19 @@
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">IF(C61="","",IF(OR(IF(ISNUMBER(G61),H61,F61)&gt;=$C$7,IF(ISNUMBER(G61),H61,F61)&lt;=0),"",IF(ISNUMBER(G61),H61,F61)))</f>
-        <v>18003.85</v>
+        <v>42562.18</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">IF(C62="","",ROUND(C62*$C$8,2))</f>
-        <v>540.12</v>
+        <v>1276.87</v>
       </c>
       <c r="E62" s="31" t="n">
         <f aca="false">IF(C62="","",ROUND(C62*$C$9,2))</f>
-        <v>540.12</v>
+        <v>1276.87</v>
       </c>
       <c r="F62" s="31" t="n">
         <f aca="false">IF(C62="","",C62+D62)</f>
-        <v>18543.97</v>
+        <v>43839.05</v>
       </c>
       <c r="G62" s="32"/>
       <c r="H62" s="31" t="str">
@@ -7577,19 +7393,19 @@
       </c>
       <c r="C63" s="31" t="n">
         <f aca="false">IF(C62="","",IF(OR(IF(ISNUMBER(G62),H62,F62)&gt;=$C$7,IF(ISNUMBER(G62),H62,F62)&lt;=0),"",IF(ISNUMBER(G62),H62,F62)))</f>
-        <v>18543.97</v>
+        <v>43839.05</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(C63="","",ROUND(C63*$C$8,2))</f>
-        <v>556.32</v>
+        <v>1315.17</v>
       </c>
       <c r="E63" s="31" t="n">
         <f aca="false">IF(C63="","",ROUND(C63*$C$9,2))</f>
-        <v>556.32</v>
+        <v>1315.17</v>
       </c>
       <c r="F63" s="31" t="n">
         <f aca="false">IF(C63="","",C63+D63)</f>
-        <v>19100.29</v>
+        <v>45154.22</v>
       </c>
       <c r="G63" s="32"/>
       <c r="H63" s="31" t="str">
@@ -7614,19 +7430,19 @@
       </c>
       <c r="C64" s="31" t="n">
         <f aca="false">IF(C63="","",IF(OR(IF(ISNUMBER(G63),H63,F63)&gt;=$C$7,IF(ISNUMBER(G63),H63,F63)&lt;=0),"",IF(ISNUMBER(G63),H63,F63)))</f>
-        <v>19100.29</v>
+        <v>45154.22</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(C64="","",ROUND(C64*$C$8,2))</f>
-        <v>573.01</v>
+        <v>1354.63</v>
       </c>
       <c r="E64" s="31" t="n">
         <f aca="false">IF(C64="","",ROUND(C64*$C$9,2))</f>
-        <v>573.01</v>
+        <v>1354.63</v>
       </c>
       <c r="F64" s="31" t="n">
         <f aca="false">IF(C64="","",C64+D64)</f>
-        <v>19673.3</v>
+        <v>46508.85</v>
       </c>
       <c r="G64" s="32"/>
       <c r="H64" s="31" t="str">
@@ -7651,19 +7467,19 @@
       </c>
       <c r="C65" s="31" t="n">
         <f aca="false">IF(C64="","",IF(OR(IF(ISNUMBER(G64),H64,F64)&gt;=$C$7,IF(ISNUMBER(G64),H64,F64)&lt;=0),"",IF(ISNUMBER(G64),H64,F64)))</f>
-        <v>19673.3</v>
+        <v>46508.85</v>
       </c>
       <c r="D65" s="31" t="n">
         <f aca="false">IF(C65="","",ROUND(C65*$C$8,2))</f>
-        <v>590.2</v>
+        <v>1395.27</v>
       </c>
       <c r="E65" s="31" t="n">
         <f aca="false">IF(C65="","",ROUND(C65*$C$9,2))</f>
-        <v>590.2</v>
+        <v>1395.27</v>
       </c>
       <c r="F65" s="31" t="n">
         <f aca="false">IF(C65="","",C65+D65)</f>
-        <v>20263.5</v>
+        <v>47904.12</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="31" t="str">
@@ -7688,19 +7504,19 @@
       </c>
       <c r="C66" s="31" t="n">
         <f aca="false">IF(C65="","",IF(OR(IF(ISNUMBER(G65),H65,F65)&gt;=$C$7,IF(ISNUMBER(G65),H65,F65)&lt;=0),"",IF(ISNUMBER(G65),H65,F65)))</f>
-        <v>20263.5</v>
+        <v>47904.12</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">IF(C66="","",ROUND(C66*$C$8,2))</f>
-        <v>607.91</v>
+        <v>1437.12</v>
       </c>
       <c r="E66" s="31" t="n">
         <f aca="false">IF(C66="","",ROUND(C66*$C$9,2))</f>
-        <v>607.91</v>
+        <v>1437.12</v>
       </c>
       <c r="F66" s="31" t="n">
         <f aca="false">IF(C66="","",C66+D66)</f>
-        <v>20871.41</v>
+        <v>49341.24</v>
       </c>
       <c r="G66" s="32"/>
       <c r="H66" s="31" t="str">
@@ -7725,19 +7541,19 @@
       </c>
       <c r="C67" s="31" t="n">
         <f aca="false">IF(C66="","",IF(OR(IF(ISNUMBER(G66),H66,F66)&gt;=$C$7,IF(ISNUMBER(G66),H66,F66)&lt;=0),"",IF(ISNUMBER(G66),H66,F66)))</f>
-        <v>20871.41</v>
+        <v>49341.24</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">IF(C67="","",ROUND(C67*$C$8,2))</f>
-        <v>626.14</v>
+        <v>1480.24</v>
       </c>
       <c r="E67" s="31" t="n">
         <f aca="false">IF(C67="","",ROUND(C67*$C$9,2))</f>
-        <v>626.14</v>
+        <v>1480.24</v>
       </c>
       <c r="F67" s="31" t="n">
         <f aca="false">IF(C67="","",C67+D67)</f>
-        <v>21497.55</v>
+        <v>50821.48</v>
       </c>
       <c r="G67" s="32"/>
       <c r="H67" s="31" t="str">
@@ -7762,19 +7578,19 @@
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">IF(C67="","",IF(OR(IF(ISNUMBER(G67),H67,F67)&gt;=$C$7,IF(ISNUMBER(G67),H67,F67)&lt;=0),"",IF(ISNUMBER(G67),H67,F67)))</f>
-        <v>21497.55</v>
+        <v>50821.48</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">IF(C68="","",ROUND(C68*$C$8,2))</f>
-        <v>644.93</v>
+        <v>1524.64</v>
       </c>
       <c r="E68" s="31" t="n">
         <f aca="false">IF(C68="","",ROUND(C68*$C$9,2))</f>
-        <v>644.93</v>
+        <v>1524.64</v>
       </c>
       <c r="F68" s="31" t="n">
         <f aca="false">IF(C68="","",C68+D68)</f>
-        <v>22142.48</v>
+        <v>52346.12</v>
       </c>
       <c r="G68" s="32"/>
       <c r="H68" s="31" t="str">
@@ -7799,19 +7615,19 @@
       </c>
       <c r="C69" s="31" t="n">
         <f aca="false">IF(C68="","",IF(OR(IF(ISNUMBER(G68),H68,F68)&gt;=$C$7,IF(ISNUMBER(G68),H68,F68)&lt;=0),"",IF(ISNUMBER(G68),H68,F68)))</f>
-        <v>22142.48</v>
+        <v>52346.12</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">IF(C69="","",ROUND(C69*$C$8,2))</f>
-        <v>664.27</v>
+        <v>1570.38</v>
       </c>
       <c r="E69" s="31" t="n">
         <f aca="false">IF(C69="","",ROUND(C69*$C$9,2))</f>
-        <v>664.27</v>
+        <v>1570.38</v>
       </c>
       <c r="F69" s="31" t="n">
         <f aca="false">IF(C69="","",C69+D69)</f>
-        <v>22806.75</v>
+        <v>53916.5</v>
       </c>
       <c r="G69" s="32"/>
       <c r="H69" s="31" t="str">
@@ -7836,19 +7652,19 @@
       </c>
       <c r="C70" s="31" t="n">
         <f aca="false">IF(C69="","",IF(OR(IF(ISNUMBER(G69),H69,F69)&gt;=$C$7,IF(ISNUMBER(G69),H69,F69)&lt;=0),"",IF(ISNUMBER(G69),H69,F69)))</f>
-        <v>22806.75</v>
+        <v>53916.5</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">IF(C70="","",ROUND(C70*$C$8,2))</f>
-        <v>684.2</v>
+        <v>1617.5</v>
       </c>
       <c r="E70" s="31" t="n">
         <f aca="false">IF(C70="","",ROUND(C70*$C$9,2))</f>
-        <v>684.2</v>
+        <v>1617.5</v>
       </c>
       <c r="F70" s="31" t="n">
         <f aca="false">IF(C70="","",C70+D70)</f>
-        <v>23490.95</v>
+        <v>55534</v>
       </c>
       <c r="G70" s="32"/>
       <c r="H70" s="31" t="str">
@@ -7873,19 +7689,19 @@
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">IF(C70="","",IF(OR(IF(ISNUMBER(G70),H70,F70)&gt;=$C$7,IF(ISNUMBER(G70),H70,F70)&lt;=0),"",IF(ISNUMBER(G70),H70,F70)))</f>
-        <v>23490.95</v>
+        <v>55534</v>
       </c>
       <c r="D71" s="31" t="n">
         <f aca="false">IF(C71="","",ROUND(C71*$C$8,2))</f>
-        <v>704.73</v>
+        <v>1666.02</v>
       </c>
       <c r="E71" s="31" t="n">
         <f aca="false">IF(C71="","",ROUND(C71*$C$9,2))</f>
-        <v>704.73</v>
+        <v>1666.02</v>
       </c>
       <c r="F71" s="31" t="n">
         <f aca="false">IF(C71="","",C71+D71)</f>
-        <v>24195.68</v>
+        <v>57200.02</v>
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="31" t="str">
@@ -7910,19 +7726,19 @@
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">IF(C71="","",IF(OR(IF(ISNUMBER(G71),H71,F71)&gt;=$C$7,IF(ISNUMBER(G71),H71,F71)&lt;=0),"",IF(ISNUMBER(G71),H71,F71)))</f>
-        <v>24195.68</v>
+        <v>57200.02</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">IF(C72="","",ROUND(C72*$C$8,2))</f>
-        <v>725.87</v>
+        <v>1716</v>
       </c>
       <c r="E72" s="31" t="n">
         <f aca="false">IF(C72="","",ROUND(C72*$C$9,2))</f>
-        <v>725.87</v>
+        <v>1716</v>
       </c>
       <c r="F72" s="31" t="n">
         <f aca="false">IF(C72="","",C72+D72)</f>
-        <v>24921.55</v>
+        <v>58916.02</v>
       </c>
       <c r="G72" s="32"/>
       <c r="H72" s="31" t="str">
@@ -7947,19 +7763,19 @@
       </c>
       <c r="C73" s="31" t="n">
         <f aca="false">IF(C72="","",IF(OR(IF(ISNUMBER(G72),H72,F72)&gt;=$C$7,IF(ISNUMBER(G72),H72,F72)&lt;=0),"",IF(ISNUMBER(G72),H72,F72)))</f>
-        <v>24921.55</v>
+        <v>58916.02</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(C73="","",ROUND(C73*$C$8,2))</f>
-        <v>747.65</v>
+        <v>1767.48</v>
       </c>
       <c r="E73" s="31" t="n">
         <f aca="false">IF(C73="","",ROUND(C73*$C$9,2))</f>
-        <v>747.65</v>
+        <v>1767.48</v>
       </c>
       <c r="F73" s="31" t="n">
         <f aca="false">IF(C73="","",C73+D73)</f>
-        <v>25669.2</v>
+        <v>60683.5</v>
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="31" t="str">
@@ -7984,19 +7800,19 @@
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">IF(C73="","",IF(OR(IF(ISNUMBER(G73),H73,F73)&gt;=$C$7,IF(ISNUMBER(G73),H73,F73)&lt;=0),"",IF(ISNUMBER(G73),H73,F73)))</f>
-        <v>25669.2</v>
+        <v>60683.5</v>
       </c>
       <c r="D74" s="31" t="n">
         <f aca="false">IF(C74="","",ROUND(C74*$C$8,2))</f>
-        <v>770.08</v>
+        <v>1820.51</v>
       </c>
       <c r="E74" s="31" t="n">
         <f aca="false">IF(C74="","",ROUND(C74*$C$9,2))</f>
-        <v>770.08</v>
+        <v>1820.51</v>
       </c>
       <c r="F74" s="31" t="n">
         <f aca="false">IF(C74="","",C74+D74)</f>
-        <v>26439.28</v>
+        <v>62504.01</v>
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="31" t="str">
@@ -8021,19 +7837,19 @@
       </c>
       <c r="C75" s="31" t="n">
         <f aca="false">IF(C74="","",IF(OR(IF(ISNUMBER(G74),H74,F74)&gt;=$C$7,IF(ISNUMBER(G74),H74,F74)&lt;=0),"",IF(ISNUMBER(G74),H74,F74)))</f>
-        <v>26439.28</v>
+        <v>62504.01</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">IF(C75="","",ROUND(C75*$C$8,2))</f>
-        <v>793.18</v>
+        <v>1875.12</v>
       </c>
       <c r="E75" s="31" t="n">
         <f aca="false">IF(C75="","",ROUND(C75*$C$9,2))</f>
-        <v>793.18</v>
+        <v>1875.12</v>
       </c>
       <c r="F75" s="31" t="n">
         <f aca="false">IF(C75="","",C75+D75)</f>
-        <v>27232.46</v>
+        <v>64379.13</v>
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="31" t="str">
@@ -8058,19 +7874,19 @@
       </c>
       <c r="C76" s="31" t="n">
         <f aca="false">IF(C75="","",IF(OR(IF(ISNUMBER(G75),H75,F75)&gt;=$C$7,IF(ISNUMBER(G75),H75,F75)&lt;=0),"",IF(ISNUMBER(G75),H75,F75)))</f>
-        <v>27232.46</v>
+        <v>64379.13</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">IF(C76="","",ROUND(C76*$C$8,2))</f>
-        <v>816.97</v>
+        <v>1931.37</v>
       </c>
       <c r="E76" s="31" t="n">
         <f aca="false">IF(C76="","",ROUND(C76*$C$9,2))</f>
-        <v>816.97</v>
+        <v>1931.37</v>
       </c>
       <c r="F76" s="31" t="n">
         <f aca="false">IF(C76="","",C76+D76)</f>
-        <v>28049.43</v>
+        <v>66310.5</v>
       </c>
       <c r="G76" s="32"/>
       <c r="H76" s="31" t="str">
@@ -8095,19 +7911,19 @@
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">IF(C76="","",IF(OR(IF(ISNUMBER(G76),H76,F76)&gt;=$C$7,IF(ISNUMBER(G76),H76,F76)&lt;=0),"",IF(ISNUMBER(G76),H76,F76)))</f>
-        <v>28049.43</v>
+        <v>66310.5</v>
       </c>
       <c r="D77" s="31" t="n">
         <f aca="false">IF(C77="","",ROUND(C77*$C$8,2))</f>
-        <v>841.48</v>
+        <v>1989.32</v>
       </c>
       <c r="E77" s="31" t="n">
         <f aca="false">IF(C77="","",ROUND(C77*$C$9,2))</f>
-        <v>841.48</v>
+        <v>1989.32</v>
       </c>
       <c r="F77" s="31" t="n">
         <f aca="false">IF(C77="","",C77+D77)</f>
-        <v>28890.91</v>
+        <v>68299.82</v>
       </c>
       <c r="G77" s="32"/>
       <c r="H77" s="31" t="str">
@@ -8132,19 +7948,19 @@
       </c>
       <c r="C78" s="31" t="n">
         <f aca="false">IF(C77="","",IF(OR(IF(ISNUMBER(G77),H77,F77)&gt;=$C$7,IF(ISNUMBER(G77),H77,F77)&lt;=0),"",IF(ISNUMBER(G77),H77,F77)))</f>
-        <v>28890.91</v>
+        <v>68299.82</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(C78="","",ROUND(C78*$C$8,2))</f>
-        <v>866.73</v>
+        <v>2048.99</v>
       </c>
       <c r="E78" s="31" t="n">
         <f aca="false">IF(C78="","",ROUND(C78*$C$9,2))</f>
-        <v>866.73</v>
+        <v>2048.99</v>
       </c>
       <c r="F78" s="31" t="n">
         <f aca="false">IF(C78="","",C78+D78)</f>
-        <v>29757.64</v>
+        <v>70348.81</v>
       </c>
       <c r="G78" s="32"/>
       <c r="H78" s="31" t="str">
@@ -8169,19 +7985,19 @@
       </c>
       <c r="C79" s="31" t="n">
         <f aca="false">IF(C78="","",IF(OR(IF(ISNUMBER(G78),H78,F78)&gt;=$C$7,IF(ISNUMBER(G78),H78,F78)&lt;=0),"",IF(ISNUMBER(G78),H78,F78)))</f>
-        <v>29757.64</v>
+        <v>70348.81</v>
       </c>
       <c r="D79" s="31" t="n">
         <f aca="false">IF(C79="","",ROUND(C79*$C$8,2))</f>
-        <v>892.73</v>
+        <v>2110.46</v>
       </c>
       <c r="E79" s="31" t="n">
         <f aca="false">IF(C79="","",ROUND(C79*$C$9,2))</f>
-        <v>892.73</v>
+        <v>2110.46</v>
       </c>
       <c r="F79" s="31" t="n">
         <f aca="false">IF(C79="","",C79+D79)</f>
-        <v>30650.37</v>
+        <v>72459.27</v>
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="31" t="str">
@@ -8206,19 +8022,19 @@
       </c>
       <c r="C80" s="31" t="n">
         <f aca="false">IF(C79="","",IF(OR(IF(ISNUMBER(G79),H79,F79)&gt;=$C$7,IF(ISNUMBER(G79),H79,F79)&lt;=0),"",IF(ISNUMBER(G79),H79,F79)))</f>
-        <v>30650.37</v>
+        <v>72459.27</v>
       </c>
       <c r="D80" s="31" t="n">
         <f aca="false">IF(C80="","",ROUND(C80*$C$8,2))</f>
-        <v>919.51</v>
+        <v>2173.78</v>
       </c>
       <c r="E80" s="31" t="n">
         <f aca="false">IF(C80="","",ROUND(C80*$C$9,2))</f>
-        <v>919.51</v>
+        <v>2173.78</v>
       </c>
       <c r="F80" s="31" t="n">
         <f aca="false">IF(C80="","",C80+D80)</f>
-        <v>31569.88</v>
+        <v>74633.05</v>
       </c>
       <c r="G80" s="32"/>
       <c r="H80" s="31" t="str">
@@ -8243,19 +8059,19 @@
       </c>
       <c r="C81" s="31" t="n">
         <f aca="false">IF(C80="","",IF(OR(IF(ISNUMBER(G80),H80,F80)&gt;=$C$7,IF(ISNUMBER(G80),H80,F80)&lt;=0),"",IF(ISNUMBER(G80),H80,F80)))</f>
-        <v>31569.88</v>
+        <v>74633.05</v>
       </c>
       <c r="D81" s="31" t="n">
         <f aca="false">IF(C81="","",ROUND(C81*$C$8,2))</f>
-        <v>947.1</v>
+        <v>2238.99</v>
       </c>
       <c r="E81" s="31" t="n">
         <f aca="false">IF(C81="","",ROUND(C81*$C$9,2))</f>
-        <v>947.1</v>
+        <v>2238.99</v>
       </c>
       <c r="F81" s="31" t="n">
         <f aca="false">IF(C81="","",C81+D81)</f>
-        <v>32516.98</v>
+        <v>76872.04</v>
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="31" t="str">
@@ -8280,19 +8096,19 @@
       </c>
       <c r="C82" s="31" t="n">
         <f aca="false">IF(C81="","",IF(OR(IF(ISNUMBER(G81),H81,F81)&gt;=$C$7,IF(ISNUMBER(G81),H81,F81)&lt;=0),"",IF(ISNUMBER(G81),H81,F81)))</f>
-        <v>32516.98</v>
+        <v>76872.04</v>
       </c>
       <c r="D82" s="31" t="n">
         <f aca="false">IF(C82="","",ROUND(C82*$C$8,2))</f>
-        <v>975.51</v>
+        <v>2306.16</v>
       </c>
       <c r="E82" s="31" t="n">
         <f aca="false">IF(C82="","",ROUND(C82*$C$9,2))</f>
-        <v>975.51</v>
+        <v>2306.16</v>
       </c>
       <c r="F82" s="31" t="n">
         <f aca="false">IF(C82="","",C82+D82)</f>
-        <v>33492.49</v>
+        <v>79178.2</v>
       </c>
       <c r="G82" s="32"/>
       <c r="H82" s="31" t="str">
@@ -8317,19 +8133,19 @@
       </c>
       <c r="C83" s="31" t="n">
         <f aca="false">IF(C82="","",IF(OR(IF(ISNUMBER(G82),H82,F82)&gt;=$C$7,IF(ISNUMBER(G82),H82,F82)&lt;=0),"",IF(ISNUMBER(G82),H82,F82)))</f>
-        <v>33492.49</v>
+        <v>79178.2</v>
       </c>
       <c r="D83" s="31" t="n">
         <f aca="false">IF(C83="","",ROUND(C83*$C$8,2))</f>
-        <v>1004.77</v>
+        <v>2375.35</v>
       </c>
       <c r="E83" s="31" t="n">
         <f aca="false">IF(C83="","",ROUND(C83*$C$9,2))</f>
-        <v>1004.77</v>
+        <v>2375.35</v>
       </c>
       <c r="F83" s="31" t="n">
         <f aca="false">IF(C83="","",C83+D83)</f>
-        <v>34497.26</v>
+        <v>81553.5500000001</v>
       </c>
       <c r="G83" s="32"/>
       <c r="H83" s="31" t="str">
@@ -8354,19 +8170,19 @@
       </c>
       <c r="C84" s="31" t="n">
         <f aca="false">IF(C83="","",IF(OR(IF(ISNUMBER(G83),H83,F83)&gt;=$C$7,IF(ISNUMBER(G83),H83,F83)&lt;=0),"",IF(ISNUMBER(G83),H83,F83)))</f>
-        <v>34497.26</v>
+        <v>81553.5500000001</v>
       </c>
       <c r="D84" s="31" t="n">
         <f aca="false">IF(C84="","",ROUND(C84*$C$8,2))</f>
-        <v>1034.92</v>
+        <v>2446.61</v>
       </c>
       <c r="E84" s="31" t="n">
         <f aca="false">IF(C84="","",ROUND(C84*$C$9,2))</f>
-        <v>1034.92</v>
+        <v>2446.61</v>
       </c>
       <c r="F84" s="31" t="n">
         <f aca="false">IF(C84="","",C84+D84)</f>
-        <v>35532.18</v>
+        <v>84000.1600000001</v>
       </c>
       <c r="G84" s="32"/>
       <c r="H84" s="31" t="str">
@@ -8391,19 +8207,19 @@
       </c>
       <c r="C85" s="31" t="n">
         <f aca="false">IF(C84="","",IF(OR(IF(ISNUMBER(G84),H84,F84)&gt;=$C$7,IF(ISNUMBER(G84),H84,F84)&lt;=0),"",IF(ISNUMBER(G84),H84,F84)))</f>
-        <v>35532.18</v>
+        <v>84000.1600000001</v>
       </c>
       <c r="D85" s="31" t="n">
         <f aca="false">IF(C85="","",ROUND(C85*$C$8,2))</f>
-        <v>1065.97</v>
+        <v>2520</v>
       </c>
       <c r="E85" s="31" t="n">
         <f aca="false">IF(C85="","",ROUND(C85*$C$9,2))</f>
-        <v>1065.97</v>
+        <v>2520</v>
       </c>
       <c r="F85" s="31" t="n">
         <f aca="false">IF(C85="","",C85+D85)</f>
-        <v>36598.15</v>
+        <v>86520.1600000001</v>
       </c>
       <c r="G85" s="32"/>
       <c r="H85" s="31" t="str">
@@ -8428,19 +8244,19 @@
       </c>
       <c r="C86" s="31" t="n">
         <f aca="false">IF(C85="","",IF(OR(IF(ISNUMBER(G85),H85,F85)&gt;=$C$7,IF(ISNUMBER(G85),H85,F85)&lt;=0),"",IF(ISNUMBER(G85),H85,F85)))</f>
-        <v>36598.15</v>
+        <v>86520.1600000001</v>
       </c>
       <c r="D86" s="31" t="n">
         <f aca="false">IF(C86="","",ROUND(C86*$C$8,2))</f>
-        <v>1097.94</v>
+        <v>2595.6</v>
       </c>
       <c r="E86" s="31" t="n">
         <f aca="false">IF(C86="","",ROUND(C86*$C$9,2))</f>
-        <v>1097.94</v>
+        <v>2595.6</v>
       </c>
       <c r="F86" s="31" t="n">
         <f aca="false">IF(C86="","",C86+D86)</f>
-        <v>37696.09</v>
+        <v>89115.7600000001</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="31" t="str">
@@ -8465,19 +8281,19 @@
       </c>
       <c r="C87" s="31" t="n">
         <f aca="false">IF(C86="","",IF(OR(IF(ISNUMBER(G86),H86,F86)&gt;=$C$7,IF(ISNUMBER(G86),H86,F86)&lt;=0),"",IF(ISNUMBER(G86),H86,F86)))</f>
-        <v>37696.09</v>
+        <v>89115.7600000001</v>
       </c>
       <c r="D87" s="31" t="n">
         <f aca="false">IF(C87="","",ROUND(C87*$C$8,2))</f>
-        <v>1130.88</v>
+        <v>2673.47</v>
       </c>
       <c r="E87" s="31" t="n">
         <f aca="false">IF(C87="","",ROUND(C87*$C$9,2))</f>
-        <v>1130.88</v>
+        <v>2673.47</v>
       </c>
       <c r="F87" s="31" t="n">
         <f aca="false">IF(C87="","",C87+D87)</f>
-        <v>38826.97</v>
+        <v>91789.2300000001</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="31" t="str">
@@ -8502,19 +8318,19 @@
       </c>
       <c r="C88" s="31" t="n">
         <f aca="false">IF(C87="","",IF(OR(IF(ISNUMBER(G87),H87,F87)&gt;=$C$7,IF(ISNUMBER(G87),H87,F87)&lt;=0),"",IF(ISNUMBER(G87),H87,F87)))</f>
-        <v>38826.97</v>
+        <v>91789.2300000001</v>
       </c>
       <c r="D88" s="31" t="n">
         <f aca="false">IF(C88="","",ROUND(C88*$C$8,2))</f>
-        <v>1164.81</v>
+        <v>2753.68</v>
       </c>
       <c r="E88" s="31" t="n">
         <f aca="false">IF(C88="","",ROUND(C88*$C$9,2))</f>
-        <v>1164.81</v>
+        <v>2753.68</v>
       </c>
       <c r="F88" s="31" t="n">
         <f aca="false">IF(C88="","",C88+D88)</f>
-        <v>39991.78</v>
+        <v>94542.9100000001</v>
       </c>
       <c r="G88" s="32"/>
       <c r="H88" s="31" t="str">
@@ -8539,19 +8355,19 @@
       </c>
       <c r="C89" s="31" t="n">
         <f aca="false">IF(C88="","",IF(OR(IF(ISNUMBER(G88),H88,F88)&gt;=$C$7,IF(ISNUMBER(G88),H88,F88)&lt;=0),"",IF(ISNUMBER(G88),H88,F88)))</f>
-        <v>39991.78</v>
+        <v>94542.9100000001</v>
       </c>
       <c r="D89" s="31" t="n">
         <f aca="false">IF(C89="","",ROUND(C89*$C$8,2))</f>
-        <v>1199.75</v>
+        <v>2836.29</v>
       </c>
       <c r="E89" s="31" t="n">
         <f aca="false">IF(C89="","",ROUND(C89*$C$9,2))</f>
-        <v>1199.75</v>
+        <v>2836.29</v>
       </c>
       <c r="F89" s="31" t="n">
         <f aca="false">IF(C89="","",C89+D89)</f>
-        <v>41191.53</v>
+        <v>97379.2</v>
       </c>
       <c r="G89" s="32"/>
       <c r="H89" s="31" t="str">
@@ -8576,19 +8392,19 @@
       </c>
       <c r="C90" s="31" t="n">
         <f aca="false">IF(C89="","",IF(OR(IF(ISNUMBER(G89),H89,F89)&gt;=$C$7,IF(ISNUMBER(G89),H89,F89)&lt;=0),"",IF(ISNUMBER(G89),H89,F89)))</f>
-        <v>41191.53</v>
+        <v>97379.2</v>
       </c>
       <c r="D90" s="31" t="n">
         <f aca="false">IF(C90="","",ROUND(C90*$C$8,2))</f>
-        <v>1235.75</v>
+        <v>2921.38</v>
       </c>
       <c r="E90" s="31" t="n">
         <f aca="false">IF(C90="","",ROUND(C90*$C$9,2))</f>
-        <v>1235.75</v>
+        <v>2921.38</v>
       </c>
       <c r="F90" s="31" t="n">
         <f aca="false">IF(C90="","",C90+D90)</f>
-        <v>42427.28</v>
+        <v>100300.58</v>
       </c>
       <c r="G90" s="32"/>
       <c r="H90" s="31" t="str">
@@ -8603,29 +8419,29 @@
       <c r="K90" s="35"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="29" t="n">
+      <c r="A91" s="29" t="str">
         <f aca="false">IF(C91="","",ROW()-12)</f>
-        <v>79</v>
-      </c>
-      <c r="B91" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B91" s="30" t="str">
         <f aca="false">IF(C91="","",WORKDAY($C$5-1,A91,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46408</v>
-      </c>
-      <c r="C91" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C91" s="31" t="str">
         <f aca="false">IF(C90="","",IF(OR(IF(ISNUMBER(G90),H90,F90)&gt;=$C$7,IF(ISNUMBER(G90),H90,F90)&lt;=0),"",IF(ISNUMBER(G90),H90,F90)))</f>
-        <v>42427.28</v>
-      </c>
-      <c r="D91" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="31" t="str">
         <f aca="false">IF(C91="","",ROUND(C91*$C$8,2))</f>
-        <v>1272.82</v>
-      </c>
-      <c r="E91" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E91" s="31" t="str">
         <f aca="false">IF(C91="","",ROUND(C91*$C$9,2))</f>
-        <v>1272.82</v>
-      </c>
-      <c r="F91" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F91" s="31" t="str">
         <f aca="false">IF(C91="","",C91+D91)</f>
-        <v>43700.1</v>
+        <v/>
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="31" t="str">
@@ -8634,35 +8450,35 @@
       </c>
       <c r="I91" s="33" t="str">
         <f aca="false">IF(C91="","",IF(ISNUMBER(G91),IF(G91&lt;-E91,"Actual – Loss (limit breached)",IF(G91&lt;0,"Actual – Loss",IF(G91&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J91" s="34"/>
       <c r="K91" s="35"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="29" t="n">
+      <c r="A92" s="29" t="str">
         <f aca="false">IF(C92="","",ROW()-12)</f>
-        <v>80</v>
-      </c>
-      <c r="B92" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B92" s="30" t="str">
         <f aca="false">IF(C92="","",WORKDAY($C$5-1,A92,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46409</v>
-      </c>
-      <c r="C92" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C92" s="31" t="str">
         <f aca="false">IF(C91="","",IF(OR(IF(ISNUMBER(G91),H91,F91)&gt;=$C$7,IF(ISNUMBER(G91),H91,F91)&lt;=0),"",IF(ISNUMBER(G91),H91,F91)))</f>
-        <v>43700.1</v>
-      </c>
-      <c r="D92" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="31" t="str">
         <f aca="false">IF(C92="","",ROUND(C92*$C$8,2))</f>
-        <v>1311</v>
-      </c>
-      <c r="E92" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E92" s="31" t="str">
         <f aca="false">IF(C92="","",ROUND(C92*$C$9,2))</f>
-        <v>1311</v>
-      </c>
-      <c r="F92" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F92" s="31" t="str">
         <f aca="false">IF(C92="","",C92+D92)</f>
-        <v>45011.1</v>
+        <v/>
       </c>
       <c r="G92" s="32"/>
       <c r="H92" s="31" t="str">
@@ -8671,35 +8487,35 @@
       </c>
       <c r="I92" s="33" t="str">
         <f aca="false">IF(C92="","",IF(ISNUMBER(G92),IF(G92&lt;-E92,"Actual – Loss (limit breached)",IF(G92&lt;0,"Actual – Loss",IF(G92&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J92" s="34"/>
       <c r="K92" s="35"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="29" t="n">
+      <c r="A93" s="29" t="str">
         <f aca="false">IF(C93="","",ROW()-12)</f>
-        <v>81</v>
-      </c>
-      <c r="B93" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B93" s="30" t="str">
         <f aca="false">IF(C93="","",WORKDAY($C$5-1,A93,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46412</v>
-      </c>
-      <c r="C93" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C93" s="31" t="str">
         <f aca="false">IF(C92="","",IF(OR(IF(ISNUMBER(G92),H92,F92)&gt;=$C$7,IF(ISNUMBER(G92),H92,F92)&lt;=0),"",IF(ISNUMBER(G92),H92,F92)))</f>
-        <v>45011.1</v>
-      </c>
-      <c r="D93" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="31" t="str">
         <f aca="false">IF(C93="","",ROUND(C93*$C$8,2))</f>
-        <v>1350.33</v>
-      </c>
-      <c r="E93" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E93" s="31" t="str">
         <f aca="false">IF(C93="","",ROUND(C93*$C$9,2))</f>
-        <v>1350.33</v>
-      </c>
-      <c r="F93" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F93" s="31" t="str">
         <f aca="false">IF(C93="","",C93+D93)</f>
-        <v>46361.43</v>
+        <v/>
       </c>
       <c r="G93" s="32"/>
       <c r="H93" s="31" t="str">
@@ -8708,35 +8524,35 @@
       </c>
       <c r="I93" s="33" t="str">
         <f aca="false">IF(C93="","",IF(ISNUMBER(G93),IF(G93&lt;-E93,"Actual – Loss (limit breached)",IF(G93&lt;0,"Actual – Loss",IF(G93&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J93" s="34"/>
       <c r="K93" s="35"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="29" t="n">
+      <c r="A94" s="29" t="str">
         <f aca="false">IF(C94="","",ROW()-12)</f>
-        <v>82</v>
-      </c>
-      <c r="B94" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B94" s="30" t="str">
         <f aca="false">IF(C94="","",WORKDAY($C$5-1,A94,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46414</v>
-      </c>
-      <c r="C94" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C94" s="31" t="str">
         <f aca="false">IF(C93="","",IF(OR(IF(ISNUMBER(G93),H93,F93)&gt;=$C$7,IF(ISNUMBER(G93),H93,F93)&lt;=0),"",IF(ISNUMBER(G93),H93,F93)))</f>
-        <v>46361.43</v>
-      </c>
-      <c r="D94" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="31" t="str">
         <f aca="false">IF(C94="","",ROUND(C94*$C$8,2))</f>
-        <v>1390.84</v>
-      </c>
-      <c r="E94" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E94" s="31" t="str">
         <f aca="false">IF(C94="","",ROUND(C94*$C$9,2))</f>
-        <v>1390.84</v>
-      </c>
-      <c r="F94" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F94" s="31" t="str">
         <f aca="false">IF(C94="","",C94+D94)</f>
-        <v>47752.27</v>
+        <v/>
       </c>
       <c r="G94" s="32"/>
       <c r="H94" s="31" t="str">
@@ -8745,35 +8561,35 @@
       </c>
       <c r="I94" s="33" t="str">
         <f aca="false">IF(C94="","",IF(ISNUMBER(G94),IF(G94&lt;-E94,"Actual – Loss (limit breached)",IF(G94&lt;0,"Actual – Loss",IF(G94&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J94" s="34"/>
       <c r="K94" s="35"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="29" t="n">
+      <c r="A95" s="29" t="str">
         <f aca="false">IF(C95="","",ROW()-12)</f>
-        <v>83</v>
-      </c>
-      <c r="B95" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B95" s="30" t="str">
         <f aca="false">IF(C95="","",WORKDAY($C$5-1,A95,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46415</v>
-      </c>
-      <c r="C95" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C95" s="31" t="str">
         <f aca="false">IF(C94="","",IF(OR(IF(ISNUMBER(G94),H94,F94)&gt;=$C$7,IF(ISNUMBER(G94),H94,F94)&lt;=0),"",IF(ISNUMBER(G94),H94,F94)))</f>
-        <v>47752.27</v>
-      </c>
-      <c r="D95" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="31" t="str">
         <f aca="false">IF(C95="","",ROUND(C95*$C$8,2))</f>
-        <v>1432.57</v>
-      </c>
-      <c r="E95" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E95" s="31" t="str">
         <f aca="false">IF(C95="","",ROUND(C95*$C$9,2))</f>
-        <v>1432.57</v>
-      </c>
-      <c r="F95" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F95" s="31" t="str">
         <f aca="false">IF(C95="","",C95+D95)</f>
-        <v>49184.84</v>
+        <v/>
       </c>
       <c r="G95" s="32"/>
       <c r="H95" s="31" t="str">
@@ -8782,35 +8598,35 @@
       </c>
       <c r="I95" s="33" t="str">
         <f aca="false">IF(C95="","",IF(ISNUMBER(G95),IF(G95&lt;-E95,"Actual – Loss (limit breached)",IF(G95&lt;0,"Actual – Loss",IF(G95&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J95" s="34"/>
       <c r="K95" s="35"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="29" t="n">
+      <c r="A96" s="29" t="str">
         <f aca="false">IF(C96="","",ROW()-12)</f>
-        <v>84</v>
-      </c>
-      <c r="B96" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B96" s="30" t="str">
         <f aca="false">IF(C96="","",WORKDAY($C$5-1,A96,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46416</v>
-      </c>
-      <c r="C96" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C96" s="31" t="str">
         <f aca="false">IF(C95="","",IF(OR(IF(ISNUMBER(G95),H95,F95)&gt;=$C$7,IF(ISNUMBER(G95),H95,F95)&lt;=0),"",IF(ISNUMBER(G95),H95,F95)))</f>
-        <v>49184.84</v>
-      </c>
-      <c r="D96" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="31" t="str">
         <f aca="false">IF(C96="","",ROUND(C96*$C$8,2))</f>
-        <v>1475.55</v>
-      </c>
-      <c r="E96" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E96" s="31" t="str">
         <f aca="false">IF(C96="","",ROUND(C96*$C$9,2))</f>
-        <v>1475.55</v>
-      </c>
-      <c r="F96" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F96" s="31" t="str">
         <f aca="false">IF(C96="","",C96+D96)</f>
-        <v>50660.39</v>
+        <v/>
       </c>
       <c r="G96" s="32"/>
       <c r="H96" s="31" t="str">
@@ -8819,35 +8635,35 @@
       </c>
       <c r="I96" s="33" t="str">
         <f aca="false">IF(C96="","",IF(ISNUMBER(G96),IF(G96&lt;-E96,"Actual – Loss (limit breached)",IF(G96&lt;0,"Actual – Loss",IF(G96&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J96" s="34"/>
       <c r="K96" s="35"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="29" t="n">
+      <c r="A97" s="29" t="str">
         <f aca="false">IF(C97="","",ROW()-12)</f>
-        <v>85</v>
-      </c>
-      <c r="B97" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B97" s="30" t="str">
         <f aca="false">IF(C97="","",WORKDAY($C$5-1,A97,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46419</v>
-      </c>
-      <c r="C97" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C97" s="31" t="str">
         <f aca="false">IF(C96="","",IF(OR(IF(ISNUMBER(G96),H96,F96)&gt;=$C$7,IF(ISNUMBER(G96),H96,F96)&lt;=0),"",IF(ISNUMBER(G96),H96,F96)))</f>
-        <v>50660.39</v>
-      </c>
-      <c r="D97" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="31" t="str">
         <f aca="false">IF(C97="","",ROUND(C97*$C$8,2))</f>
-        <v>1519.81</v>
-      </c>
-      <c r="E97" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E97" s="31" t="str">
         <f aca="false">IF(C97="","",ROUND(C97*$C$9,2))</f>
-        <v>1519.81</v>
-      </c>
-      <c r="F97" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F97" s="31" t="str">
         <f aca="false">IF(C97="","",C97+D97)</f>
-        <v>52180.2</v>
+        <v/>
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="31" t="str">
@@ -8856,35 +8672,35 @@
       </c>
       <c r="I97" s="33" t="str">
         <f aca="false">IF(C97="","",IF(ISNUMBER(G97),IF(G97&lt;-E97,"Actual – Loss (limit breached)",IF(G97&lt;0,"Actual – Loss",IF(G97&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J97" s="34"/>
       <c r="K97" s="35"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="29" t="n">
+      <c r="A98" s="29" t="str">
         <f aca="false">IF(C98="","",ROW()-12)</f>
-        <v>86</v>
-      </c>
-      <c r="B98" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B98" s="30" t="str">
         <f aca="false">IF(C98="","",WORKDAY($C$5-1,A98,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46420</v>
-      </c>
-      <c r="C98" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C98" s="31" t="str">
         <f aca="false">IF(C97="","",IF(OR(IF(ISNUMBER(G97),H97,F97)&gt;=$C$7,IF(ISNUMBER(G97),H97,F97)&lt;=0),"",IF(ISNUMBER(G97),H97,F97)))</f>
-        <v>52180.2</v>
-      </c>
-      <c r="D98" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="31" t="str">
         <f aca="false">IF(C98="","",ROUND(C98*$C$8,2))</f>
-        <v>1565.41</v>
-      </c>
-      <c r="E98" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E98" s="31" t="str">
         <f aca="false">IF(C98="","",ROUND(C98*$C$9,2))</f>
-        <v>1565.41</v>
-      </c>
-      <c r="F98" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F98" s="31" t="str">
         <f aca="false">IF(C98="","",C98+D98)</f>
-        <v>53745.61</v>
+        <v/>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="31" t="str">
@@ -8893,35 +8709,35 @@
       </c>
       <c r="I98" s="33" t="str">
         <f aca="false">IF(C98="","",IF(ISNUMBER(G98),IF(G98&lt;-E98,"Actual – Loss (limit breached)",IF(G98&lt;0,"Actual – Loss",IF(G98&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J98" s="34"/>
       <c r="K98" s="35"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="29" t="n">
+      <c r="A99" s="29" t="str">
         <f aca="false">IF(C99="","",ROW()-12)</f>
-        <v>87</v>
-      </c>
-      <c r="B99" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B99" s="30" t="str">
         <f aca="false">IF(C99="","",WORKDAY($C$5-1,A99,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46421</v>
-      </c>
-      <c r="C99" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C99" s="31" t="str">
         <f aca="false">IF(C98="","",IF(OR(IF(ISNUMBER(G98),H98,F98)&gt;=$C$7,IF(ISNUMBER(G98),H98,F98)&lt;=0),"",IF(ISNUMBER(G98),H98,F98)))</f>
-        <v>53745.61</v>
-      </c>
-      <c r="D99" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="31" t="str">
         <f aca="false">IF(C99="","",ROUND(C99*$C$8,2))</f>
-        <v>1612.37</v>
-      </c>
-      <c r="E99" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E99" s="31" t="str">
         <f aca="false">IF(C99="","",ROUND(C99*$C$9,2))</f>
-        <v>1612.37</v>
-      </c>
-      <c r="F99" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F99" s="31" t="str">
         <f aca="false">IF(C99="","",C99+D99)</f>
-        <v>55357.98</v>
+        <v/>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="31" t="str">
@@ -8930,35 +8746,35 @@
       </c>
       <c r="I99" s="33" t="str">
         <f aca="false">IF(C99="","",IF(ISNUMBER(G99),IF(G99&lt;-E99,"Actual – Loss (limit breached)",IF(G99&lt;0,"Actual – Loss",IF(G99&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J99" s="34"/>
       <c r="K99" s="35"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="29" t="n">
+      <c r="A100" s="29" t="str">
         <f aca="false">IF(C100="","",ROW()-12)</f>
-        <v>88</v>
-      </c>
-      <c r="B100" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B100" s="30" t="str">
         <f aca="false">IF(C100="","",WORKDAY($C$5-1,A100,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46422</v>
-      </c>
-      <c r="C100" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C100" s="31" t="str">
         <f aca="false">IF(C99="","",IF(OR(IF(ISNUMBER(G99),H99,F99)&gt;=$C$7,IF(ISNUMBER(G99),H99,F99)&lt;=0),"",IF(ISNUMBER(G99),H99,F99)))</f>
-        <v>55357.98</v>
-      </c>
-      <c r="D100" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="31" t="str">
         <f aca="false">IF(C100="","",ROUND(C100*$C$8,2))</f>
-        <v>1660.74</v>
-      </c>
-      <c r="E100" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E100" s="31" t="str">
         <f aca="false">IF(C100="","",ROUND(C100*$C$9,2))</f>
-        <v>1660.74</v>
-      </c>
-      <c r="F100" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F100" s="31" t="str">
         <f aca="false">IF(C100="","",C100+D100)</f>
-        <v>57018.72</v>
+        <v/>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="31" t="str">
@@ -8967,35 +8783,35 @@
       </c>
       <c r="I100" s="33" t="str">
         <f aca="false">IF(C100="","",IF(ISNUMBER(G100),IF(G100&lt;-E100,"Actual – Loss (limit breached)",IF(G100&lt;0,"Actual – Loss",IF(G100&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J100" s="34"/>
       <c r="K100" s="35"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="29" t="n">
+      <c r="A101" s="29" t="str">
         <f aca="false">IF(C101="","",ROW()-12)</f>
-        <v>89</v>
-      </c>
-      <c r="B101" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B101" s="30" t="str">
         <f aca="false">IF(C101="","",WORKDAY($C$5-1,A101,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46423</v>
-      </c>
-      <c r="C101" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C101" s="31" t="str">
         <f aca="false">IF(C100="","",IF(OR(IF(ISNUMBER(G100),H100,F100)&gt;=$C$7,IF(ISNUMBER(G100),H100,F100)&lt;=0),"",IF(ISNUMBER(G100),H100,F100)))</f>
-        <v>57018.72</v>
-      </c>
-      <c r="D101" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="31" t="str">
         <f aca="false">IF(C101="","",ROUND(C101*$C$8,2))</f>
-        <v>1710.56</v>
-      </c>
-      <c r="E101" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E101" s="31" t="str">
         <f aca="false">IF(C101="","",ROUND(C101*$C$9,2))</f>
-        <v>1710.56</v>
-      </c>
-      <c r="F101" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F101" s="31" t="str">
         <f aca="false">IF(C101="","",C101+D101)</f>
-        <v>58729.28</v>
+        <v/>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="31" t="str">
@@ -9004,35 +8820,35 @@
       </c>
       <c r="I101" s="33" t="str">
         <f aca="false">IF(C101="","",IF(ISNUMBER(G101),IF(G101&lt;-E101,"Actual – Loss (limit breached)",IF(G101&lt;0,"Actual – Loss",IF(G101&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J101" s="34"/>
       <c r="K101" s="35"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="29" t="n">
+      <c r="A102" s="29" t="str">
         <f aca="false">IF(C102="","",ROW()-12)</f>
-        <v>90</v>
-      </c>
-      <c r="B102" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B102" s="30" t="str">
         <f aca="false">IF(C102="","",WORKDAY($C$5-1,A102,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46426</v>
-      </c>
-      <c r="C102" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C102" s="31" t="str">
         <f aca="false">IF(C101="","",IF(OR(IF(ISNUMBER(G101),H101,F101)&gt;=$C$7,IF(ISNUMBER(G101),H101,F101)&lt;=0),"",IF(ISNUMBER(G101),H101,F101)))</f>
-        <v>58729.28</v>
-      </c>
-      <c r="D102" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="31" t="str">
         <f aca="false">IF(C102="","",ROUND(C102*$C$8,2))</f>
-        <v>1761.88</v>
-      </c>
-      <c r="E102" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E102" s="31" t="str">
         <f aca="false">IF(C102="","",ROUND(C102*$C$9,2))</f>
-        <v>1761.88</v>
-      </c>
-      <c r="F102" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F102" s="31" t="str">
         <f aca="false">IF(C102="","",C102+D102)</f>
-        <v>60491.16</v>
+        <v/>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="31" t="str">
@@ -9041,35 +8857,35 @@
       </c>
       <c r="I102" s="33" t="str">
         <f aca="false">IF(C102="","",IF(ISNUMBER(G102),IF(G102&lt;-E102,"Actual – Loss (limit breached)",IF(G102&lt;0,"Actual – Loss",IF(G102&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J102" s="34"/>
       <c r="K102" s="35"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="29" t="n">
+      <c r="A103" s="29" t="str">
         <f aca="false">IF(C103="","",ROW()-12)</f>
-        <v>91</v>
-      </c>
-      <c r="B103" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B103" s="30" t="str">
         <f aca="false">IF(C103="","",WORKDAY($C$5-1,A103,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46427</v>
-      </c>
-      <c r="C103" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C103" s="31" t="str">
         <f aca="false">IF(C102="","",IF(OR(IF(ISNUMBER(G102),H102,F102)&gt;=$C$7,IF(ISNUMBER(G102),H102,F102)&lt;=0),"",IF(ISNUMBER(G102),H102,F102)))</f>
-        <v>60491.16</v>
-      </c>
-      <c r="D103" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="31" t="str">
         <f aca="false">IF(C103="","",ROUND(C103*$C$8,2))</f>
-        <v>1814.73</v>
-      </c>
-      <c r="E103" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E103" s="31" t="str">
         <f aca="false">IF(C103="","",ROUND(C103*$C$9,2))</f>
-        <v>1814.73</v>
-      </c>
-      <c r="F103" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F103" s="31" t="str">
         <f aca="false">IF(C103="","",C103+D103)</f>
-        <v>62305.89</v>
+        <v/>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="31" t="str">
@@ -9078,35 +8894,35 @@
       </c>
       <c r="I103" s="33" t="str">
         <f aca="false">IF(C103="","",IF(ISNUMBER(G103),IF(G103&lt;-E103,"Actual – Loss (limit breached)",IF(G103&lt;0,"Actual – Loss",IF(G103&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J103" s="34"/>
       <c r="K103" s="35"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="29" t="n">
+      <c r="A104" s="29" t="str">
         <f aca="false">IF(C104="","",ROW()-12)</f>
-        <v>92</v>
-      </c>
-      <c r="B104" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B104" s="30" t="str">
         <f aca="false">IF(C104="","",WORKDAY($C$5-1,A104,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46428</v>
-      </c>
-      <c r="C104" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C104" s="31" t="str">
         <f aca="false">IF(C103="","",IF(OR(IF(ISNUMBER(G103),H103,F103)&gt;=$C$7,IF(ISNUMBER(G103),H103,F103)&lt;=0),"",IF(ISNUMBER(G103),H103,F103)))</f>
-        <v>62305.89</v>
-      </c>
-      <c r="D104" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="31" t="str">
         <f aca="false">IF(C104="","",ROUND(C104*$C$8,2))</f>
-        <v>1869.18</v>
-      </c>
-      <c r="E104" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E104" s="31" t="str">
         <f aca="false">IF(C104="","",ROUND(C104*$C$9,2))</f>
-        <v>1869.18</v>
-      </c>
-      <c r="F104" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F104" s="31" t="str">
         <f aca="false">IF(C104="","",C104+D104)</f>
-        <v>64175.07</v>
+        <v/>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="31" t="str">
@@ -9115,35 +8931,35 @@
       </c>
       <c r="I104" s="33" t="str">
         <f aca="false">IF(C104="","",IF(ISNUMBER(G104),IF(G104&lt;-E104,"Actual – Loss (limit breached)",IF(G104&lt;0,"Actual – Loss",IF(G104&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J104" s="34"/>
       <c r="K104" s="35"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="29" t="n">
+      <c r="A105" s="29" t="str">
         <f aca="false">IF(C105="","",ROW()-12)</f>
-        <v>93</v>
-      </c>
-      <c r="B105" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B105" s="30" t="str">
         <f aca="false">IF(C105="","",WORKDAY($C$5-1,A105,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46429</v>
-      </c>
-      <c r="C105" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C105" s="31" t="str">
         <f aca="false">IF(C104="","",IF(OR(IF(ISNUMBER(G104),H104,F104)&gt;=$C$7,IF(ISNUMBER(G104),H104,F104)&lt;=0),"",IF(ISNUMBER(G104),H104,F104)))</f>
-        <v>64175.07</v>
-      </c>
-      <c r="D105" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="31" t="str">
         <f aca="false">IF(C105="","",ROUND(C105*$C$8,2))</f>
-        <v>1925.25</v>
-      </c>
-      <c r="E105" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E105" s="31" t="str">
         <f aca="false">IF(C105="","",ROUND(C105*$C$9,2))</f>
-        <v>1925.25</v>
-      </c>
-      <c r="F105" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F105" s="31" t="str">
         <f aca="false">IF(C105="","",C105+D105)</f>
-        <v>66100.32</v>
+        <v/>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="31" t="str">
@@ -9152,35 +8968,35 @@
       </c>
       <c r="I105" s="33" t="str">
         <f aca="false">IF(C105="","",IF(ISNUMBER(G105),IF(G105&lt;-E105,"Actual – Loss (limit breached)",IF(G105&lt;0,"Actual – Loss",IF(G105&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J105" s="34"/>
       <c r="K105" s="35"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="29" t="n">
+      <c r="A106" s="29" t="str">
         <f aca="false">IF(C106="","",ROW()-12)</f>
-        <v>94</v>
-      </c>
-      <c r="B106" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B106" s="30" t="str">
         <f aca="false">IF(C106="","",WORKDAY($C$5-1,A106,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46430</v>
-      </c>
-      <c r="C106" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C106" s="31" t="str">
         <f aca="false">IF(C105="","",IF(OR(IF(ISNUMBER(G105),H105,F105)&gt;=$C$7,IF(ISNUMBER(G105),H105,F105)&lt;=0),"",IF(ISNUMBER(G105),H105,F105)))</f>
-        <v>66100.32</v>
-      </c>
-      <c r="D106" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="31" t="str">
         <f aca="false">IF(C106="","",ROUND(C106*$C$8,2))</f>
-        <v>1983.01</v>
-      </c>
-      <c r="E106" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E106" s="31" t="str">
         <f aca="false">IF(C106="","",ROUND(C106*$C$9,2))</f>
-        <v>1983.01</v>
-      </c>
-      <c r="F106" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F106" s="31" t="str">
         <f aca="false">IF(C106="","",C106+D106)</f>
-        <v>68083.33</v>
+        <v/>
       </c>
       <c r="G106" s="32"/>
       <c r="H106" s="31" t="str">
@@ -9189,35 +9005,35 @@
       </c>
       <c r="I106" s="33" t="str">
         <f aca="false">IF(C106="","",IF(ISNUMBER(G106),IF(G106&lt;-E106,"Actual – Loss (limit breached)",IF(G106&lt;0,"Actual – Loss",IF(G106&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J106" s="34"/>
       <c r="K106" s="35"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="29" t="n">
+      <c r="A107" s="29" t="str">
         <f aca="false">IF(C107="","",ROW()-12)</f>
-        <v>95</v>
-      </c>
-      <c r="B107" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B107" s="30" t="str">
         <f aca="false">IF(C107="","",WORKDAY($C$5-1,A107,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46433</v>
-      </c>
-      <c r="C107" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C107" s="31" t="str">
         <f aca="false">IF(C106="","",IF(OR(IF(ISNUMBER(G106),H106,F106)&gt;=$C$7,IF(ISNUMBER(G106),H106,F106)&lt;=0),"",IF(ISNUMBER(G106),H106,F106)))</f>
-        <v>68083.33</v>
-      </c>
-      <c r="D107" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="31" t="str">
         <f aca="false">IF(C107="","",ROUND(C107*$C$8,2))</f>
-        <v>2042.5</v>
-      </c>
-      <c r="E107" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E107" s="31" t="str">
         <f aca="false">IF(C107="","",ROUND(C107*$C$9,2))</f>
-        <v>2042.5</v>
-      </c>
-      <c r="F107" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F107" s="31" t="str">
         <f aca="false">IF(C107="","",C107+D107)</f>
-        <v>70125.83</v>
+        <v/>
       </c>
       <c r="G107" s="32"/>
       <c r="H107" s="31" t="str">
@@ -9226,35 +9042,35 @@
       </c>
       <c r="I107" s="33" t="str">
         <f aca="false">IF(C107="","",IF(ISNUMBER(G107),IF(G107&lt;-E107,"Actual – Loss (limit breached)",IF(G107&lt;0,"Actual – Loss",IF(G107&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J107" s="34"/>
       <c r="K107" s="35"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="29" t="n">
+      <c r="A108" s="29" t="str">
         <f aca="false">IF(C108="","",ROW()-12)</f>
-        <v>96</v>
-      </c>
-      <c r="B108" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B108" s="30" t="str">
         <f aca="false">IF(C108="","",WORKDAY($C$5-1,A108,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46434</v>
-      </c>
-      <c r="C108" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C108" s="31" t="str">
         <f aca="false">IF(C107="","",IF(OR(IF(ISNUMBER(G107),H107,F107)&gt;=$C$7,IF(ISNUMBER(G107),H107,F107)&lt;=0),"",IF(ISNUMBER(G107),H107,F107)))</f>
-        <v>70125.83</v>
-      </c>
-      <c r="D108" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="31" t="str">
         <f aca="false">IF(C108="","",ROUND(C108*$C$8,2))</f>
-        <v>2103.77</v>
-      </c>
-      <c r="E108" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E108" s="31" t="str">
         <f aca="false">IF(C108="","",ROUND(C108*$C$9,2))</f>
-        <v>2103.77</v>
-      </c>
-      <c r="F108" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F108" s="31" t="str">
         <f aca="false">IF(C108="","",C108+D108)</f>
-        <v>72229.6</v>
+        <v/>
       </c>
       <c r="G108" s="32"/>
       <c r="H108" s="31" t="str">
@@ -9263,35 +9079,35 @@
       </c>
       <c r="I108" s="33" t="str">
         <f aca="false">IF(C108="","",IF(ISNUMBER(G108),IF(G108&lt;-E108,"Actual – Loss (limit breached)",IF(G108&lt;0,"Actual – Loss",IF(G108&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J108" s="34"/>
       <c r="K108" s="35"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="29" t="n">
+      <c r="A109" s="29" t="str">
         <f aca="false">IF(C109="","",ROW()-12)</f>
-        <v>97</v>
-      </c>
-      <c r="B109" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B109" s="30" t="str">
         <f aca="false">IF(C109="","",WORKDAY($C$5-1,A109,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46435</v>
-      </c>
-      <c r="C109" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C109" s="31" t="str">
         <f aca="false">IF(C108="","",IF(OR(IF(ISNUMBER(G108),H108,F108)&gt;=$C$7,IF(ISNUMBER(G108),H108,F108)&lt;=0),"",IF(ISNUMBER(G108),H108,F108)))</f>
-        <v>72229.6</v>
-      </c>
-      <c r="D109" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="31" t="str">
         <f aca="false">IF(C109="","",ROUND(C109*$C$8,2))</f>
-        <v>2166.89</v>
-      </c>
-      <c r="E109" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E109" s="31" t="str">
         <f aca="false">IF(C109="","",ROUND(C109*$C$9,2))</f>
-        <v>2166.89</v>
-      </c>
-      <c r="F109" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="31" t="str">
         <f aca="false">IF(C109="","",C109+D109)</f>
-        <v>74396.49</v>
+        <v/>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="31" t="str">
@@ -9300,35 +9116,35 @@
       </c>
       <c r="I109" s="33" t="str">
         <f aca="false">IF(C109="","",IF(ISNUMBER(G109),IF(G109&lt;-E109,"Actual – Loss (limit breached)",IF(G109&lt;0,"Actual – Loss",IF(G109&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J109" s="34"/>
       <c r="K109" s="35"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="29" t="n">
+      <c r="A110" s="29" t="str">
         <f aca="false">IF(C110="","",ROW()-12)</f>
-        <v>98</v>
-      </c>
-      <c r="B110" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B110" s="30" t="str">
         <f aca="false">IF(C110="","",WORKDAY($C$5-1,A110,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46436</v>
-      </c>
-      <c r="C110" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C110" s="31" t="str">
         <f aca="false">IF(C109="","",IF(OR(IF(ISNUMBER(G109),H109,F109)&gt;=$C$7,IF(ISNUMBER(G109),H109,F109)&lt;=0),"",IF(ISNUMBER(G109),H109,F109)))</f>
-        <v>74396.49</v>
-      </c>
-      <c r="D110" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="31" t="str">
         <f aca="false">IF(C110="","",ROUND(C110*$C$8,2))</f>
-        <v>2231.89</v>
-      </c>
-      <c r="E110" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E110" s="31" t="str">
         <f aca="false">IF(C110="","",ROUND(C110*$C$9,2))</f>
-        <v>2231.89</v>
-      </c>
-      <c r="F110" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="31" t="str">
         <f aca="false">IF(C110="","",C110+D110)</f>
-        <v>76628.38</v>
+        <v/>
       </c>
       <c r="G110" s="32"/>
       <c r="H110" s="31" t="str">
@@ -9337,35 +9153,35 @@
       </c>
       <c r="I110" s="33" t="str">
         <f aca="false">IF(C110="","",IF(ISNUMBER(G110),IF(G110&lt;-E110,"Actual – Loss (limit breached)",IF(G110&lt;0,"Actual – Loss",IF(G110&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J110" s="34"/>
       <c r="K110" s="35"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="29" t="n">
+      <c r="A111" s="29" t="str">
         <f aca="false">IF(C111="","",ROW()-12)</f>
-        <v>99</v>
-      </c>
-      <c r="B111" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B111" s="30" t="str">
         <f aca="false">IF(C111="","",WORKDAY($C$5-1,A111,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46437</v>
-      </c>
-      <c r="C111" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C111" s="31" t="str">
         <f aca="false">IF(C110="","",IF(OR(IF(ISNUMBER(G110),H110,F110)&gt;=$C$7,IF(ISNUMBER(G110),H110,F110)&lt;=0),"",IF(ISNUMBER(G110),H110,F110)))</f>
-        <v>76628.38</v>
-      </c>
-      <c r="D111" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="31" t="str">
         <f aca="false">IF(C111="","",ROUND(C111*$C$8,2))</f>
-        <v>2298.85</v>
-      </c>
-      <c r="E111" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E111" s="31" t="str">
         <f aca="false">IF(C111="","",ROUND(C111*$C$9,2))</f>
-        <v>2298.85</v>
-      </c>
-      <c r="F111" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F111" s="31" t="str">
         <f aca="false">IF(C111="","",C111+D111)</f>
-        <v>78927.23</v>
+        <v/>
       </c>
       <c r="G111" s="32"/>
       <c r="H111" s="31" t="str">
@@ -9374,35 +9190,35 @@
       </c>
       <c r="I111" s="33" t="str">
         <f aca="false">IF(C111="","",IF(ISNUMBER(G111),IF(G111&lt;-E111,"Actual – Loss (limit breached)",IF(G111&lt;0,"Actual – Loss",IF(G111&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J111" s="34"/>
       <c r="K111" s="35"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="29" t="n">
+      <c r="A112" s="29" t="str">
         <f aca="false">IF(C112="","",ROW()-12)</f>
-        <v>100</v>
-      </c>
-      <c r="B112" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B112" s="30" t="str">
         <f aca="false">IF(C112="","",WORKDAY($C$5-1,A112,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46440</v>
-      </c>
-      <c r="C112" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C112" s="31" t="str">
         <f aca="false">IF(C111="","",IF(OR(IF(ISNUMBER(G111),H111,F111)&gt;=$C$7,IF(ISNUMBER(G111),H111,F111)&lt;=0),"",IF(ISNUMBER(G111),H111,F111)))</f>
-        <v>78927.23</v>
-      </c>
-      <c r="D112" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="31" t="str">
         <f aca="false">IF(C112="","",ROUND(C112*$C$8,2))</f>
-        <v>2367.82</v>
-      </c>
-      <c r="E112" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E112" s="31" t="str">
         <f aca="false">IF(C112="","",ROUND(C112*$C$9,2))</f>
-        <v>2367.82</v>
-      </c>
-      <c r="F112" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F112" s="31" t="str">
         <f aca="false">IF(C112="","",C112+D112)</f>
-        <v>81295.05</v>
+        <v/>
       </c>
       <c r="G112" s="32"/>
       <c r="H112" s="31" t="str">
@@ -9411,35 +9227,35 @@
       </c>
       <c r="I112" s="33" t="str">
         <f aca="false">IF(C112="","",IF(ISNUMBER(G112),IF(G112&lt;-E112,"Actual – Loss (limit breached)",IF(G112&lt;0,"Actual – Loss",IF(G112&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J112" s="34"/>
       <c r="K112" s="35"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="29" t="n">
+      <c r="A113" s="29" t="str">
         <f aca="false">IF(C113="","",ROW()-12)</f>
-        <v>101</v>
-      </c>
-      <c r="B113" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B113" s="30" t="str">
         <f aca="false">IF(C113="","",WORKDAY($C$5-1,A113,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46441</v>
-      </c>
-      <c r="C113" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C113" s="31" t="str">
         <f aca="false">IF(C112="","",IF(OR(IF(ISNUMBER(G112),H112,F112)&gt;=$C$7,IF(ISNUMBER(G112),H112,F112)&lt;=0),"",IF(ISNUMBER(G112),H112,F112)))</f>
-        <v>81295.05</v>
-      </c>
-      <c r="D113" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="31" t="str">
         <f aca="false">IF(C113="","",ROUND(C113*$C$8,2))</f>
-        <v>2438.85</v>
-      </c>
-      <c r="E113" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E113" s="31" t="str">
         <f aca="false">IF(C113="","",ROUND(C113*$C$9,2))</f>
-        <v>2438.85</v>
-      </c>
-      <c r="F113" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F113" s="31" t="str">
         <f aca="false">IF(C113="","",C113+D113)</f>
-        <v>83733.9</v>
+        <v/>
       </c>
       <c r="G113" s="32"/>
       <c r="H113" s="31" t="str">
@@ -9448,35 +9264,35 @@
       </c>
       <c r="I113" s="33" t="str">
         <f aca="false">IF(C113="","",IF(ISNUMBER(G113),IF(G113&lt;-E113,"Actual – Loss (limit breached)",IF(G113&lt;0,"Actual – Loss",IF(G113&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J113" s="34"/>
       <c r="K113" s="35"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="29" t="n">
+      <c r="A114" s="29" t="str">
         <f aca="false">IF(C114="","",ROW()-12)</f>
-        <v>102</v>
-      </c>
-      <c r="B114" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B114" s="30" t="str">
         <f aca="false">IF(C114="","",WORKDAY($C$5-1,A114,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46442</v>
-      </c>
-      <c r="C114" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C114" s="31" t="str">
         <f aca="false">IF(C113="","",IF(OR(IF(ISNUMBER(G113),H113,F113)&gt;=$C$7,IF(ISNUMBER(G113),H113,F113)&lt;=0),"",IF(ISNUMBER(G113),H113,F113)))</f>
-        <v>83733.9</v>
-      </c>
-      <c r="D114" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="31" t="str">
         <f aca="false">IF(C114="","",ROUND(C114*$C$8,2))</f>
-        <v>2512.02</v>
-      </c>
-      <c r="E114" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E114" s="31" t="str">
         <f aca="false">IF(C114="","",ROUND(C114*$C$9,2))</f>
-        <v>2512.02</v>
-      </c>
-      <c r="F114" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F114" s="31" t="str">
         <f aca="false">IF(C114="","",C114+D114)</f>
-        <v>86245.92</v>
+        <v/>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="31" t="str">
@@ -9485,35 +9301,35 @@
       </c>
       <c r="I114" s="33" t="str">
         <f aca="false">IF(C114="","",IF(ISNUMBER(G114),IF(G114&lt;-E114,"Actual – Loss (limit breached)",IF(G114&lt;0,"Actual – Loss",IF(G114&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J114" s="34"/>
       <c r="K114" s="35"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="29" t="n">
+      <c r="A115" s="29" t="str">
         <f aca="false">IF(C115="","",ROW()-12)</f>
-        <v>103</v>
-      </c>
-      <c r="B115" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B115" s="30" t="str">
         <f aca="false">IF(C115="","",WORKDAY($C$5-1,A115,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46443</v>
-      </c>
-      <c r="C115" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C115" s="31" t="str">
         <f aca="false">IF(C114="","",IF(OR(IF(ISNUMBER(G114),H114,F114)&gt;=$C$7,IF(ISNUMBER(G114),H114,F114)&lt;=0),"",IF(ISNUMBER(G114),H114,F114)))</f>
-        <v>86245.92</v>
-      </c>
-      <c r="D115" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="31" t="str">
         <f aca="false">IF(C115="","",ROUND(C115*$C$8,2))</f>
-        <v>2587.38</v>
-      </c>
-      <c r="E115" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E115" s="31" t="str">
         <f aca="false">IF(C115="","",ROUND(C115*$C$9,2))</f>
-        <v>2587.38</v>
-      </c>
-      <c r="F115" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F115" s="31" t="str">
         <f aca="false">IF(C115="","",C115+D115)</f>
-        <v>88833.3</v>
+        <v/>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="31" t="str">
@@ -9522,35 +9338,35 @@
       </c>
       <c r="I115" s="33" t="str">
         <f aca="false">IF(C115="","",IF(ISNUMBER(G115),IF(G115&lt;-E115,"Actual – Loss (limit breached)",IF(G115&lt;0,"Actual – Loss",IF(G115&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J115" s="34"/>
       <c r="K115" s="35"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="29" t="n">
+      <c r="A116" s="29" t="str">
         <f aca="false">IF(C116="","",ROW()-12)</f>
-        <v>104</v>
-      </c>
-      <c r="B116" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B116" s="30" t="str">
         <f aca="false">IF(C116="","",WORKDAY($C$5-1,A116,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46444</v>
-      </c>
-      <c r="C116" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C116" s="31" t="str">
         <f aca="false">IF(C115="","",IF(OR(IF(ISNUMBER(G115),H115,F115)&gt;=$C$7,IF(ISNUMBER(G115),H115,F115)&lt;=0),"",IF(ISNUMBER(G115),H115,F115)))</f>
-        <v>88833.3</v>
-      </c>
-      <c r="D116" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="31" t="str">
         <f aca="false">IF(C116="","",ROUND(C116*$C$8,2))</f>
-        <v>2665</v>
-      </c>
-      <c r="E116" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E116" s="31" t="str">
         <f aca="false">IF(C116="","",ROUND(C116*$C$9,2))</f>
-        <v>2665</v>
-      </c>
-      <c r="F116" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F116" s="31" t="str">
         <f aca="false">IF(C116="","",C116+D116)</f>
-        <v>91498.3</v>
+        <v/>
       </c>
       <c r="G116" s="32"/>
       <c r="H116" s="31" t="str">
@@ -9559,35 +9375,35 @@
       </c>
       <c r="I116" s="33" t="str">
         <f aca="false">IF(C116="","",IF(ISNUMBER(G116),IF(G116&lt;-E116,"Actual – Loss (limit breached)",IF(G116&lt;0,"Actual – Loss",IF(G116&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J116" s="34"/>
       <c r="K116" s="35"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="29" t="n">
+      <c r="A117" s="29" t="str">
         <f aca="false">IF(C117="","",ROW()-12)</f>
-        <v>105</v>
-      </c>
-      <c r="B117" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B117" s="30" t="str">
         <f aca="false">IF(C117="","",WORKDAY($C$5-1,A117,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46447</v>
-      </c>
-      <c r="C117" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C117" s="31" t="str">
         <f aca="false">IF(C116="","",IF(OR(IF(ISNUMBER(G116),H116,F116)&gt;=$C$7,IF(ISNUMBER(G116),H116,F116)&lt;=0),"",IF(ISNUMBER(G116),H116,F116)))</f>
-        <v>91498.3</v>
-      </c>
-      <c r="D117" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="31" t="str">
         <f aca="false">IF(C117="","",ROUND(C117*$C$8,2))</f>
-        <v>2744.95</v>
-      </c>
-      <c r="E117" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E117" s="31" t="str">
         <f aca="false">IF(C117="","",ROUND(C117*$C$9,2))</f>
-        <v>2744.95</v>
-      </c>
-      <c r="F117" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F117" s="31" t="str">
         <f aca="false">IF(C117="","",C117+D117)</f>
-        <v>94243.25</v>
+        <v/>
       </c>
       <c r="G117" s="32"/>
       <c r="H117" s="31" t="str">
@@ -9596,35 +9412,35 @@
       </c>
       <c r="I117" s="33" t="str">
         <f aca="false">IF(C117="","",IF(ISNUMBER(G117),IF(G117&lt;-E117,"Actual – Loss (limit breached)",IF(G117&lt;0,"Actual – Loss",IF(G117&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J117" s="34"/>
       <c r="K117" s="35"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="29" t="n">
+      <c r="A118" s="29" t="str">
         <f aca="false">IF(C118="","",ROW()-12)</f>
-        <v>106</v>
-      </c>
-      <c r="B118" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B118" s="30" t="str">
         <f aca="false">IF(C118="","",WORKDAY($C$5-1,A118,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46448</v>
-      </c>
-      <c r="C118" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C118" s="31" t="str">
         <f aca="false">IF(C117="","",IF(OR(IF(ISNUMBER(G117),H117,F117)&gt;=$C$7,IF(ISNUMBER(G117),H117,F117)&lt;=0),"",IF(ISNUMBER(G117),H117,F117)))</f>
-        <v>94243.25</v>
-      </c>
-      <c r="D118" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="31" t="str">
         <f aca="false">IF(C118="","",ROUND(C118*$C$8,2))</f>
-        <v>2827.3</v>
-      </c>
-      <c r="E118" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E118" s="31" t="str">
         <f aca="false">IF(C118="","",ROUND(C118*$C$9,2))</f>
-        <v>2827.3</v>
-      </c>
-      <c r="F118" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F118" s="31" t="str">
         <f aca="false">IF(C118="","",C118+D118)</f>
-        <v>97070.55</v>
+        <v/>
       </c>
       <c r="G118" s="32"/>
       <c r="H118" s="31" t="str">
@@ -9633,35 +9449,35 @@
       </c>
       <c r="I118" s="33" t="str">
         <f aca="false">IF(C118="","",IF(ISNUMBER(G118),IF(G118&lt;-E118,"Actual – Loss (limit breached)",IF(G118&lt;0,"Actual – Loss",IF(G118&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J118" s="34"/>
       <c r="K118" s="35"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="29" t="n">
+      <c r="A119" s="29" t="str">
         <f aca="false">IF(C119="","",ROW()-12)</f>
-        <v>107</v>
-      </c>
-      <c r="B119" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B119" s="30" t="str">
         <f aca="false">IF(C119="","",WORKDAY($C$5-1,A119,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46449</v>
-      </c>
-      <c r="C119" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C119" s="31" t="str">
         <f aca="false">IF(C118="","",IF(OR(IF(ISNUMBER(G118),H118,F118)&gt;=$C$7,IF(ISNUMBER(G118),H118,F118)&lt;=0),"",IF(ISNUMBER(G118),H118,F118)))</f>
-        <v>97070.55</v>
-      </c>
-      <c r="D119" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="31" t="str">
         <f aca="false">IF(C119="","",ROUND(C119*$C$8,2))</f>
-        <v>2912.12</v>
-      </c>
-      <c r="E119" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E119" s="31" t="str">
         <f aca="false">IF(C119="","",ROUND(C119*$C$9,2))</f>
-        <v>2912.12</v>
-      </c>
-      <c r="F119" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F119" s="31" t="str">
         <f aca="false">IF(C119="","",C119+D119)</f>
-        <v>99982.67</v>
+        <v/>
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="31" t="str">
@@ -9670,35 +9486,35 @@
       </c>
       <c r="I119" s="33" t="str">
         <f aca="false">IF(C119="","",IF(ISNUMBER(G119),IF(G119&lt;-E119,"Actual – Loss (limit breached)",IF(G119&lt;0,"Actual – Loss",IF(G119&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J119" s="34"/>
       <c r="K119" s="35"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="29" t="n">
+      <c r="A120" s="29" t="str">
         <f aca="false">IF(C120="","",ROW()-12)</f>
-        <v>108</v>
-      </c>
-      <c r="B120" s="30" t="n">
+        <v/>
+      </c>
+      <c r="B120" s="30" t="str">
         <f aca="false">IF(C120="","",WORKDAY($C$5-1,A120,'NSE Holidays'!$A$5:$A$64))</f>
-        <v>46450</v>
-      </c>
-      <c r="C120" s="31" t="n">
+        <v/>
+      </c>
+      <c r="C120" s="31" t="str">
         <f aca="false">IF(C119="","",IF(OR(IF(ISNUMBER(G119),H119,F119)&gt;=$C$7,IF(ISNUMBER(G119),H119,F119)&lt;=0),"",IF(ISNUMBER(G119),H119,F119)))</f>
-        <v>99982.67</v>
-      </c>
-      <c r="D120" s="31" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="31" t="str">
         <f aca="false">IF(C120="","",ROUND(C120*$C$8,2))</f>
-        <v>2999.48</v>
-      </c>
-      <c r="E120" s="31" t="n">
+        <v/>
+      </c>
+      <c r="E120" s="31" t="str">
         <f aca="false">IF(C120="","",ROUND(C120*$C$9,2))</f>
-        <v>2999.48</v>
-      </c>
-      <c r="F120" s="31" t="n">
+        <v/>
+      </c>
+      <c r="F120" s="31" t="str">
         <f aca="false">IF(C120="","",C120+D120)</f>
-        <v>102982.15</v>
+        <v/>
       </c>
       <c r="G120" s="32"/>
       <c r="H120" s="31" t="str">
@@ -9707,7 +9523,7 @@
       </c>
       <c r="I120" s="33" t="str">
         <f aca="false">IF(C120="","",IF(ISNUMBER(G120),IF(G120&lt;-E120,"Actual – Loss (limit breached)",IF(G120&lt;0,"Actual – Loss",IF(G120&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v>Projection</v>
+        <v/>
       </c>
       <c r="J120" s="34"/>
       <c r="K120" s="35"/>
@@ -24283,7 +24099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B0253C8C-E067-49B8-8765-D72A4CF7BC92}</x14:id>
+          <x14:id>{30708037-DD56-4CBC-A46E-B63AFD9017C0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24314,7 +24130,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B0253C8C-E067-49B8-8765-D72A4CF7BC92}">
+          <x14:cfRule type="dataBar" id="{30708037-DD56-4CBC-A46E-B63AFD9017C0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -24350,12 +24166,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -24363,16 +24179,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24384,7 +24200,7 @@
         <v>46048</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="42"/>
     </row>
@@ -24397,7 +24213,7 @@
         <v>46084</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="42"/>
     </row>
@@ -24410,7 +24226,7 @@
         <v>46107</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="42"/>
     </row>
@@ -24423,7 +24239,7 @@
         <v>46112</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" s="42"/>
     </row>
@@ -24436,7 +24252,7 @@
         <v>46115</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" s="42"/>
     </row>
@@ -24449,7 +24265,7 @@
         <v>46126</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="42"/>
     </row>
@@ -24462,7 +24278,7 @@
         <v>46143</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" s="42"/>
     </row>
@@ -24475,7 +24291,7 @@
         <v>46170</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="42"/>
     </row>
@@ -24488,7 +24304,7 @@
         <v>46199</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" s="42"/>
     </row>
@@ -24501,7 +24317,7 @@
         <v>46279</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="42"/>
     </row>
@@ -24514,7 +24330,7 @@
         <v>46297</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="42"/>
     </row>
@@ -24527,7 +24343,7 @@
         <v>46315</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" s="42"/>
     </row>
@@ -24540,10 +24356,10 @@
         <v>46336</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24555,7 +24371,7 @@
         <v>46350</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" s="42"/>
     </row>
@@ -24568,7 +24384,7 @@
         <v>46381</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="42"/>
     </row>
@@ -24581,10 +24397,10 @@
         <v>46413</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25016,7 +24832,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25024,32 +24840,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25057,22 +24873,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25080,22 +24896,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="47" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="46" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25103,42 +24919,42 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="47" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="46" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -25162,22 +24978,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="F1" s="48" t="s">
         <v>90</v>
-      </c>
-      <c r="D1" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="48" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25190,7 +25006,7 @@
       </c>
       <c r="C2" s="31" t="n">
         <f aca="false">IF(Tracker!$C13="",NA(),IF(A2&lt;Tracker!$J$6,NA(),IF(A2=Tracker!$J$6,Tracker!$H13,Tracker!$F13)))</f>
-        <v>4356.9</v>
+        <v>10300</v>
       </c>
       <c r="D2" s="31" t="n">
         <f aca="false">IF(Tracker!$C13="",NA(),Tracker!$C$7)</f>
@@ -25215,7 +25031,7 @@
       </c>
       <c r="C3" s="31" t="n">
         <f aca="false">IF(Tracker!$C14="",NA(),IF(A3&lt;Tracker!$J$6,NA(),IF(A3=Tracker!$J$6,Tracker!$H14,Tracker!$F14)))</f>
-        <v>4487.61</v>
+        <v>10609</v>
       </c>
       <c r="D3" s="31" t="n">
         <f aca="false">IF(Tracker!$C14="",NA(),Tracker!$C$7)</f>
@@ -25240,7 +25056,7 @@
       </c>
       <c r="C4" s="31" t="n">
         <f aca="false">IF(Tracker!$C15="",NA(),IF(A4&lt;Tracker!$J$6,NA(),IF(A4=Tracker!$J$6,Tracker!$H15,Tracker!$F15)))</f>
-        <v>4622.24</v>
+        <v>10927.27</v>
       </c>
       <c r="D4" s="31" t="n">
         <f aca="false">IF(Tracker!$C15="",NA(),Tracker!$C$7)</f>
@@ -25265,7 +25081,7 @@
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">IF(Tracker!$C16="",NA(),IF(A5&lt;Tracker!$J$6,NA(),IF(A5=Tracker!$J$6,Tracker!$H16,Tracker!$F16)))</f>
-        <v>4760.91</v>
+        <v>11255.09</v>
       </c>
       <c r="D5" s="31" t="n">
         <f aca="false">IF(Tracker!$C16="",NA(),Tracker!$C$7)</f>
@@ -25290,7 +25106,7 @@
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">IF(Tracker!$C17="",NA(),IF(A6&lt;Tracker!$J$6,NA(),IF(A6=Tracker!$J$6,Tracker!$H17,Tracker!$F17)))</f>
-        <v>4903.74</v>
+        <v>11592.74</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">IF(Tracker!$C17="",NA(),Tracker!$C$7)</f>
@@ -25315,7 +25131,7 @@
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">IF(Tracker!$C18="",NA(),IF(A7&lt;Tracker!$J$6,NA(),IF(A7=Tracker!$J$6,Tracker!$H18,Tracker!$F18)))</f>
-        <v>5050.85</v>
+        <v>11940.52</v>
       </c>
       <c r="D7" s="31" t="n">
         <f aca="false">IF(Tracker!$C18="",NA(),Tracker!$C$7)</f>
@@ -25340,7 +25156,7 @@
       </c>
       <c r="C8" s="31" t="n">
         <f aca="false">IF(Tracker!$C19="",NA(),IF(A8&lt;Tracker!$J$6,NA(),IF(A8=Tracker!$J$6,Tracker!$H19,Tracker!$F19)))</f>
-        <v>5202.38</v>
+        <v>12298.74</v>
       </c>
       <c r="D8" s="31" t="n">
         <f aca="false">IF(Tracker!$C19="",NA(),Tracker!$C$7)</f>
@@ -25365,7 +25181,7 @@
       </c>
       <c r="C9" s="31" t="n">
         <f aca="false">IF(Tracker!$C20="",NA(),IF(A9&lt;Tracker!$J$6,NA(),IF(A9=Tracker!$J$6,Tracker!$H20,Tracker!$F20)))</f>
-        <v>5358.45</v>
+        <v>12667.7</v>
       </c>
       <c r="D9" s="31" t="n">
         <f aca="false">IF(Tracker!$C20="",NA(),Tracker!$C$7)</f>
@@ -25390,7 +25206,7 @@
       </c>
       <c r="C10" s="31" t="n">
         <f aca="false">IF(Tracker!$C21="",NA(),IF(A10&lt;Tracker!$J$6,NA(),IF(A10=Tracker!$J$6,Tracker!$H21,Tracker!$F21)))</f>
-        <v>5519.2</v>
+        <v>13047.73</v>
       </c>
       <c r="D10" s="31" t="n">
         <f aca="false">IF(Tracker!$C21="",NA(),Tracker!$C$7)</f>
@@ -25415,7 +25231,7 @@
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">IF(Tracker!$C22="",NA(),IF(A11&lt;Tracker!$J$6,NA(),IF(A11=Tracker!$J$6,Tracker!$H22,Tracker!$F22)))</f>
-        <v>5684.78</v>
+        <v>13439.16</v>
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">IF(Tracker!$C22="",NA(),Tracker!$C$7)</f>
@@ -25440,7 +25256,7 @@
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">IF(Tracker!$C23="",NA(),IF(A12&lt;Tracker!$J$6,NA(),IF(A12=Tracker!$J$6,Tracker!$H23,Tracker!$F23)))</f>
-        <v>5855.32</v>
+        <v>13842.33</v>
       </c>
       <c r="D12" s="31" t="n">
         <f aca="false">IF(Tracker!$C23="",NA(),Tracker!$C$7)</f>
@@ -25465,7 +25281,7 @@
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">IF(Tracker!$C24="",NA(),IF(A13&lt;Tracker!$J$6,NA(),IF(A13=Tracker!$J$6,Tracker!$H24,Tracker!$F24)))</f>
-        <v>6030.98</v>
+        <v>14257.6</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">IF(Tracker!$C24="",NA(),Tracker!$C$7)</f>
@@ -25490,7 +25306,7 @@
       </c>
       <c r="C14" s="31" t="n">
         <f aca="false">IF(Tracker!$C25="",NA(),IF(A14&lt;Tracker!$J$6,NA(),IF(A14=Tracker!$J$6,Tracker!$H25,Tracker!$F25)))</f>
-        <v>6211.91</v>
+        <v>14685.33</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">IF(Tracker!$C25="",NA(),Tracker!$C$7)</f>
@@ -25515,7 +25331,7 @@
       </c>
       <c r="C15" s="31" t="n">
         <f aca="false">IF(Tracker!$C26="",NA(),IF(A15&lt;Tracker!$J$6,NA(),IF(A15=Tracker!$J$6,Tracker!$H26,Tracker!$F26)))</f>
-        <v>6398.27</v>
+        <v>15125.89</v>
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">IF(Tracker!$C26="",NA(),Tracker!$C$7)</f>
@@ -25540,7 +25356,7 @@
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">IF(Tracker!$C27="",NA(),IF(A16&lt;Tracker!$J$6,NA(),IF(A16=Tracker!$J$6,Tracker!$H27,Tracker!$F27)))</f>
-        <v>6590.22</v>
+        <v>15579.67</v>
       </c>
       <c r="D16" s="31" t="n">
         <f aca="false">IF(Tracker!$C27="",NA(),Tracker!$C$7)</f>
@@ -25565,7 +25381,7 @@
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">IF(Tracker!$C28="",NA(),IF(A17&lt;Tracker!$J$6,NA(),IF(A17=Tracker!$J$6,Tracker!$H28,Tracker!$F28)))</f>
-        <v>6787.93</v>
+        <v>16047.06</v>
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">IF(Tracker!$C28="",NA(),Tracker!$C$7)</f>
@@ -25590,7 +25406,7 @@
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IF(Tracker!$C29="",NA(),IF(A18&lt;Tracker!$J$6,NA(),IF(A18=Tracker!$J$6,Tracker!$H29,Tracker!$F29)))</f>
-        <v>6991.57</v>
+        <v>16528.47</v>
       </c>
       <c r="D18" s="31" t="n">
         <f aca="false">IF(Tracker!$C29="",NA(),Tracker!$C$7)</f>
@@ -25615,7 +25431,7 @@
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">IF(Tracker!$C30="",NA(),IF(A19&lt;Tracker!$J$6,NA(),IF(A19=Tracker!$J$6,Tracker!$H30,Tracker!$F30)))</f>
-        <v>7201.32</v>
+        <v>17024.32</v>
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">IF(Tracker!$C30="",NA(),Tracker!$C$7)</f>
@@ -25640,7 +25456,7 @@
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">IF(Tracker!$C31="",NA(),IF(A20&lt;Tracker!$J$6,NA(),IF(A20=Tracker!$J$6,Tracker!$H31,Tracker!$F31)))</f>
-        <v>7417.36</v>
+        <v>17535.05</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">IF(Tracker!$C31="",NA(),Tracker!$C$7)</f>
@@ -25665,7 +25481,7 @@
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">IF(Tracker!$C32="",NA(),IF(A21&lt;Tracker!$J$6,NA(),IF(A21=Tracker!$J$6,Tracker!$H32,Tracker!$F32)))</f>
-        <v>7639.88</v>
+        <v>18061.1</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">IF(Tracker!$C32="",NA(),Tracker!$C$7)</f>
@@ -25690,7 +25506,7 @@
       </c>
       <c r="C22" s="31" t="n">
         <f aca="false">IF(Tracker!$C33="",NA(),IF(A22&lt;Tracker!$J$6,NA(),IF(A22=Tracker!$J$6,Tracker!$H33,Tracker!$F33)))</f>
-        <v>7869.08</v>
+        <v>18602.93</v>
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">IF(Tracker!$C33="",NA(),Tracker!$C$7)</f>
@@ -25715,7 +25531,7 @@
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">IF(Tracker!$C34="",NA(),IF(A23&lt;Tracker!$J$6,NA(),IF(A23=Tracker!$J$6,Tracker!$H34,Tracker!$F34)))</f>
-        <v>8105.15</v>
+        <v>19161.02</v>
       </c>
       <c r="D23" s="31" t="n">
         <f aca="false">IF(Tracker!$C34="",NA(),Tracker!$C$7)</f>
@@ -25740,7 +25556,7 @@
       </c>
       <c r="C24" s="31" t="n">
         <f aca="false">IF(Tracker!$C35="",NA(),IF(A24&lt;Tracker!$J$6,NA(),IF(A24=Tracker!$J$6,Tracker!$H35,Tracker!$F35)))</f>
-        <v>8348.3</v>
+        <v>19735.85</v>
       </c>
       <c r="D24" s="31" t="n">
         <f aca="false">IF(Tracker!$C35="",NA(),Tracker!$C$7)</f>
@@ -25765,7 +25581,7 @@
       </c>
       <c r="C25" s="31" t="n">
         <f aca="false">IF(Tracker!$C36="",NA(),IF(A25&lt;Tracker!$J$6,NA(),IF(A25=Tracker!$J$6,Tracker!$H36,Tracker!$F36)))</f>
-        <v>8598.75</v>
+        <v>20327.93</v>
       </c>
       <c r="D25" s="31" t="n">
         <f aca="false">IF(Tracker!$C36="",NA(),Tracker!$C$7)</f>
@@ -25790,7 +25606,7 @@
       </c>
       <c r="C26" s="31" t="n">
         <f aca="false">IF(Tracker!$C37="",NA(),IF(A26&lt;Tracker!$J$6,NA(),IF(A26=Tracker!$J$6,Tracker!$H37,Tracker!$F37)))</f>
-        <v>8856.71</v>
+        <v>20937.77</v>
       </c>
       <c r="D26" s="31" t="n">
         <f aca="false">IF(Tracker!$C37="",NA(),Tracker!$C$7)</f>
@@ -25815,7 +25631,7 @@
       </c>
       <c r="C27" s="31" t="n">
         <f aca="false">IF(Tracker!$C38="",NA(),IF(A27&lt;Tracker!$J$6,NA(),IF(A27=Tracker!$J$6,Tracker!$H38,Tracker!$F38)))</f>
-        <v>9122.41</v>
+        <v>21565.9</v>
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">IF(Tracker!$C38="",NA(),Tracker!$C$7)</f>
@@ -25840,7 +25656,7 @@
       </c>
       <c r="C28" s="31" t="n">
         <f aca="false">IF(Tracker!$C39="",NA(),IF(A28&lt;Tracker!$J$6,NA(),IF(A28=Tracker!$J$6,Tracker!$H39,Tracker!$F39)))</f>
-        <v>9396.08</v>
+        <v>22212.88</v>
       </c>
       <c r="D28" s="31" t="n">
         <f aca="false">IF(Tracker!$C39="",NA(),Tracker!$C$7)</f>
@@ -25865,7 +25681,7 @@
       </c>
       <c r="C29" s="31" t="n">
         <f aca="false">IF(Tracker!$C40="",NA(),IF(A29&lt;Tracker!$J$6,NA(),IF(A29=Tracker!$J$6,Tracker!$H40,Tracker!$F40)))</f>
-        <v>9677.96</v>
+        <v>22879.27</v>
       </c>
       <c r="D29" s="31" t="n">
         <f aca="false">IF(Tracker!$C40="",NA(),Tracker!$C$7)</f>
@@ -25890,7 +25706,7 @@
       </c>
       <c r="C30" s="31" t="n">
         <f aca="false">IF(Tracker!$C41="",NA(),IF(A30&lt;Tracker!$J$6,NA(),IF(A30=Tracker!$J$6,Tracker!$H41,Tracker!$F41)))</f>
-        <v>9968.3</v>
+        <v>23565.65</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">IF(Tracker!$C41="",NA(),Tracker!$C$7)</f>
@@ -25915,7 +25731,7 @@
       </c>
       <c r="C31" s="31" t="n">
         <f aca="false">IF(Tracker!$C42="",NA(),IF(A31&lt;Tracker!$J$6,NA(),IF(A31=Tracker!$J$6,Tracker!$H42,Tracker!$F42)))</f>
-        <v>10267.35</v>
+        <v>24272.62</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">IF(Tracker!$C42="",NA(),Tracker!$C$7)</f>
@@ -25940,7 +25756,7 @@
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">IF(Tracker!$C43="",NA(),IF(A32&lt;Tracker!$J$6,NA(),IF(A32=Tracker!$J$6,Tracker!$H43,Tracker!$F43)))</f>
-        <v>10575.37</v>
+        <v>25000.8</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">IF(Tracker!$C43="",NA(),Tracker!$C$7)</f>
@@ -25965,7 +25781,7 @@
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IF(Tracker!$C44="",NA(),IF(A33&lt;Tracker!$J$6,NA(),IF(A33=Tracker!$J$6,Tracker!$H44,Tracker!$F44)))</f>
-        <v>10892.63</v>
+        <v>25750.82</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">IF(Tracker!$C44="",NA(),Tracker!$C$7)</f>
@@ -25990,7 +25806,7 @@
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IF(Tracker!$C45="",NA(),IF(A34&lt;Tracker!$J$6,NA(),IF(A34=Tracker!$J$6,Tracker!$H45,Tracker!$F45)))</f>
-        <v>11219.41</v>
+        <v>26523.34</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">IF(Tracker!$C45="",NA(),Tracker!$C$7)</f>
@@ -26015,7 +25831,7 @@
       </c>
       <c r="C35" s="31" t="n">
         <f aca="false">IF(Tracker!$C46="",NA(),IF(A35&lt;Tracker!$J$6,NA(),IF(A35=Tracker!$J$6,Tracker!$H46,Tracker!$F46)))</f>
-        <v>11555.99</v>
+        <v>27319.04</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">IF(Tracker!$C46="",NA(),Tracker!$C$7)</f>
@@ -26040,7 +25856,7 @@
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">IF(Tracker!$C47="",NA(),IF(A36&lt;Tracker!$J$6,NA(),IF(A36=Tracker!$J$6,Tracker!$H47,Tracker!$F47)))</f>
-        <v>11902.67</v>
+        <v>28138.61</v>
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">IF(Tracker!$C47="",NA(),Tracker!$C$7)</f>
@@ -26065,7 +25881,7 @@
       </c>
       <c r="C37" s="31" t="n">
         <f aca="false">IF(Tracker!$C48="",NA(),IF(A37&lt;Tracker!$J$6,NA(),IF(A37=Tracker!$J$6,Tracker!$H48,Tracker!$F48)))</f>
-        <v>12259.75</v>
+        <v>28982.77</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">IF(Tracker!$C48="",NA(),Tracker!$C$7)</f>
@@ -26090,7 +25906,7 @@
       </c>
       <c r="C38" s="31" t="n">
         <f aca="false">IF(Tracker!$C49="",NA(),IF(A38&lt;Tracker!$J$6,NA(),IF(A38=Tracker!$J$6,Tracker!$H49,Tracker!$F49)))</f>
-        <v>12627.54</v>
+        <v>29852.25</v>
       </c>
       <c r="D38" s="31" t="n">
         <f aca="false">IF(Tracker!$C49="",NA(),Tracker!$C$7)</f>
@@ -26115,7 +25931,7 @@
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">IF(Tracker!$C50="",NA(),IF(A39&lt;Tracker!$J$6,NA(),IF(A39=Tracker!$J$6,Tracker!$H50,Tracker!$F50)))</f>
-        <v>13006.37</v>
+        <v>30747.82</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">IF(Tracker!$C50="",NA(),Tracker!$C$7)</f>
@@ -26140,7 +25956,7 @@
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">IF(Tracker!$C51="",NA(),IF(A40&lt;Tracker!$J$6,NA(),IF(A40=Tracker!$J$6,Tracker!$H51,Tracker!$F51)))</f>
-        <v>13396.56</v>
+        <v>31670.25</v>
       </c>
       <c r="D40" s="31" t="n">
         <f aca="false">IF(Tracker!$C51="",NA(),Tracker!$C$7)</f>
@@ -26165,7 +25981,7 @@
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">IF(Tracker!$C52="",NA(),IF(A41&lt;Tracker!$J$6,NA(),IF(A41=Tracker!$J$6,Tracker!$H52,Tracker!$F52)))</f>
-        <v>13798.46</v>
+        <v>32620.36</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">IF(Tracker!$C52="",NA(),Tracker!$C$7)</f>
@@ -26190,7 +26006,7 @@
       </c>
       <c r="C42" s="31" t="n">
         <f aca="false">IF(Tracker!$C53="",NA(),IF(A42&lt;Tracker!$J$6,NA(),IF(A42=Tracker!$J$6,Tracker!$H53,Tracker!$F53)))</f>
-        <v>14212.41</v>
+        <v>33598.97</v>
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">IF(Tracker!$C53="",NA(),Tracker!$C$7)</f>
@@ -26215,7 +26031,7 @@
       </c>
       <c r="C43" s="31" t="n">
         <f aca="false">IF(Tracker!$C54="",NA(),IF(A43&lt;Tracker!$J$6,NA(),IF(A43=Tracker!$J$6,Tracker!$H54,Tracker!$F54)))</f>
-        <v>14638.78</v>
+        <v>34606.94</v>
       </c>
       <c r="D43" s="31" t="n">
         <f aca="false">IF(Tracker!$C54="",NA(),Tracker!$C$7)</f>
@@ -26240,7 +26056,7 @@
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">IF(Tracker!$C55="",NA(),IF(A44&lt;Tracker!$J$6,NA(),IF(A44=Tracker!$J$6,Tracker!$H55,Tracker!$F55)))</f>
-        <v>15077.94</v>
+        <v>35645.15</v>
       </c>
       <c r="D44" s="31" t="n">
         <f aca="false">IF(Tracker!$C55="",NA(),Tracker!$C$7)</f>
@@ -26265,7 +26081,7 @@
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">IF(Tracker!$C56="",NA(),IF(A45&lt;Tracker!$J$6,NA(),IF(A45=Tracker!$J$6,Tracker!$H56,Tracker!$F56)))</f>
-        <v>15530.28</v>
+        <v>36714.5</v>
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">IF(Tracker!$C56="",NA(),Tracker!$C$7)</f>
@@ -26290,7 +26106,7 @@
       </c>
       <c r="C46" s="31" t="n">
         <f aca="false">IF(Tracker!$C57="",NA(),IF(A46&lt;Tracker!$J$6,NA(),IF(A46=Tracker!$J$6,Tracker!$H57,Tracker!$F57)))</f>
-        <v>15996.19</v>
+        <v>37815.94</v>
       </c>
       <c r="D46" s="31" t="n">
         <f aca="false">IF(Tracker!$C57="",NA(),Tracker!$C$7)</f>
@@ -26315,7 +26131,7 @@
       </c>
       <c r="C47" s="31" t="n">
         <f aca="false">IF(Tracker!$C58="",NA(),IF(A47&lt;Tracker!$J$6,NA(),IF(A47=Tracker!$J$6,Tracker!$H58,Tracker!$F58)))</f>
-        <v>16476.08</v>
+        <v>38950.42</v>
       </c>
       <c r="D47" s="31" t="n">
         <f aca="false">IF(Tracker!$C58="",NA(),Tracker!$C$7)</f>
@@ -26340,7 +26156,7 @@
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">IF(Tracker!$C59="",NA(),IF(A48&lt;Tracker!$J$6,NA(),IF(A48=Tracker!$J$6,Tracker!$H59,Tracker!$F59)))</f>
-        <v>16970.36</v>
+        <v>40118.93</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">IF(Tracker!$C59="",NA(),Tracker!$C$7)</f>
@@ -26365,7 +26181,7 @@
       </c>
       <c r="C49" s="31" t="n">
         <f aca="false">IF(Tracker!$C60="",NA(),IF(A49&lt;Tracker!$J$6,NA(),IF(A49=Tracker!$J$6,Tracker!$H60,Tracker!$F60)))</f>
-        <v>17479.47</v>
+        <v>41322.5</v>
       </c>
       <c r="D49" s="31" t="n">
         <f aca="false">IF(Tracker!$C60="",NA(),Tracker!$C$7)</f>
@@ -26390,7 +26206,7 @@
       </c>
       <c r="C50" s="31" t="n">
         <f aca="false">IF(Tracker!$C61="",NA(),IF(A50&lt;Tracker!$J$6,NA(),IF(A50=Tracker!$J$6,Tracker!$H61,Tracker!$F61)))</f>
-        <v>18003.85</v>
+        <v>42562.18</v>
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">IF(Tracker!$C61="",NA(),Tracker!$C$7)</f>
@@ -26415,7 +26231,7 @@
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">IF(Tracker!$C62="",NA(),IF(A51&lt;Tracker!$J$6,NA(),IF(A51=Tracker!$J$6,Tracker!$H62,Tracker!$F62)))</f>
-        <v>18543.97</v>
+        <v>43839.05</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">IF(Tracker!$C62="",NA(),Tracker!$C$7)</f>
@@ -26440,7 +26256,7 @@
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">IF(Tracker!$C63="",NA(),IF(A52&lt;Tracker!$J$6,NA(),IF(A52=Tracker!$J$6,Tracker!$H63,Tracker!$F63)))</f>
-        <v>19100.29</v>
+        <v>45154.22</v>
       </c>
       <c r="D52" s="31" t="n">
         <f aca="false">IF(Tracker!$C63="",NA(),Tracker!$C$7)</f>
@@ -26465,7 +26281,7 @@
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">IF(Tracker!$C64="",NA(),IF(A53&lt;Tracker!$J$6,NA(),IF(A53=Tracker!$J$6,Tracker!$H64,Tracker!$F64)))</f>
-        <v>19673.3</v>
+        <v>46508.85</v>
       </c>
       <c r="D53" s="31" t="n">
         <f aca="false">IF(Tracker!$C64="",NA(),Tracker!$C$7)</f>
@@ -26490,7 +26306,7 @@
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">IF(Tracker!$C65="",NA(),IF(A54&lt;Tracker!$J$6,NA(),IF(A54=Tracker!$J$6,Tracker!$H65,Tracker!$F65)))</f>
-        <v>20263.5</v>
+        <v>47904.12</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(Tracker!$C65="",NA(),Tracker!$C$7)</f>
@@ -26515,7 +26331,7 @@
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">IF(Tracker!$C66="",NA(),IF(A55&lt;Tracker!$J$6,NA(),IF(A55=Tracker!$J$6,Tracker!$H66,Tracker!$F66)))</f>
-        <v>20871.41</v>
+        <v>49341.24</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">IF(Tracker!$C66="",NA(),Tracker!$C$7)</f>
@@ -26540,7 +26356,7 @@
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">IF(Tracker!$C67="",NA(),IF(A56&lt;Tracker!$J$6,NA(),IF(A56=Tracker!$J$6,Tracker!$H67,Tracker!$F67)))</f>
-        <v>21497.55</v>
+        <v>50821.48</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">IF(Tracker!$C67="",NA(),Tracker!$C$7)</f>
@@ -26565,7 +26381,7 @@
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">IF(Tracker!$C68="",NA(),IF(A57&lt;Tracker!$J$6,NA(),IF(A57=Tracker!$J$6,Tracker!$H68,Tracker!$F68)))</f>
-        <v>22142.48</v>
+        <v>52346.12</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(Tracker!$C68="",NA(),Tracker!$C$7)</f>
@@ -26590,7 +26406,7 @@
       </c>
       <c r="C58" s="31" t="n">
         <f aca="false">IF(Tracker!$C69="",NA(),IF(A58&lt;Tracker!$J$6,NA(),IF(A58=Tracker!$J$6,Tracker!$H69,Tracker!$F69)))</f>
-        <v>22806.75</v>
+        <v>53916.5</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">IF(Tracker!$C69="",NA(),Tracker!$C$7)</f>
@@ -26615,7 +26431,7 @@
       </c>
       <c r="C59" s="31" t="n">
         <f aca="false">IF(Tracker!$C70="",NA(),IF(A59&lt;Tracker!$J$6,NA(),IF(A59=Tracker!$J$6,Tracker!$H70,Tracker!$F70)))</f>
-        <v>23490.95</v>
+        <v>55534</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">IF(Tracker!$C70="",NA(),Tracker!$C$7)</f>
@@ -26640,7 +26456,7 @@
       </c>
       <c r="C60" s="31" t="n">
         <f aca="false">IF(Tracker!$C71="",NA(),IF(A60&lt;Tracker!$J$6,NA(),IF(A60=Tracker!$J$6,Tracker!$H71,Tracker!$F71)))</f>
-        <v>24195.68</v>
+        <v>57200.02</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">IF(Tracker!$C71="",NA(),Tracker!$C$7)</f>
@@ -26665,7 +26481,7 @@
       </c>
       <c r="C61" s="31" t="n">
         <f aca="false">IF(Tracker!$C72="",NA(),IF(A61&lt;Tracker!$J$6,NA(),IF(A61=Tracker!$J$6,Tracker!$H72,Tracker!$F72)))</f>
-        <v>24921.55</v>
+        <v>58916.02</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">IF(Tracker!$C72="",NA(),Tracker!$C$7)</f>
@@ -26690,7 +26506,7 @@
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">IF(Tracker!$C73="",NA(),IF(A62&lt;Tracker!$J$6,NA(),IF(A62=Tracker!$J$6,Tracker!$H73,Tracker!$F73)))</f>
-        <v>25669.2</v>
+        <v>60683.5</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">IF(Tracker!$C73="",NA(),Tracker!$C$7)</f>
@@ -26715,7 +26531,7 @@
       </c>
       <c r="C63" s="31" t="n">
         <f aca="false">IF(Tracker!$C74="",NA(),IF(A63&lt;Tracker!$J$6,NA(),IF(A63=Tracker!$J$6,Tracker!$H74,Tracker!$F74)))</f>
-        <v>26439.28</v>
+        <v>62504.01</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(Tracker!$C74="",NA(),Tracker!$C$7)</f>
@@ -26740,7 +26556,7 @@
       </c>
       <c r="C64" s="31" t="n">
         <f aca="false">IF(Tracker!$C75="",NA(),IF(A64&lt;Tracker!$J$6,NA(),IF(A64=Tracker!$J$6,Tracker!$H75,Tracker!$F75)))</f>
-        <v>27232.46</v>
+        <v>64379.13</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(Tracker!$C75="",NA(),Tracker!$C$7)</f>
@@ -26765,7 +26581,7 @@
       </c>
       <c r="C65" s="31" t="n">
         <f aca="false">IF(Tracker!$C76="",NA(),IF(A65&lt;Tracker!$J$6,NA(),IF(A65=Tracker!$J$6,Tracker!$H76,Tracker!$F76)))</f>
-        <v>28049.43</v>
+        <v>66310.5</v>
       </c>
       <c r="D65" s="31" t="n">
         <f aca="false">IF(Tracker!$C76="",NA(),Tracker!$C$7)</f>
@@ -26790,7 +26606,7 @@
       </c>
       <c r="C66" s="31" t="n">
         <f aca="false">IF(Tracker!$C77="",NA(),IF(A66&lt;Tracker!$J$6,NA(),IF(A66=Tracker!$J$6,Tracker!$H77,Tracker!$F77)))</f>
-        <v>28890.91</v>
+        <v>68299.82</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">IF(Tracker!$C77="",NA(),Tracker!$C$7)</f>
@@ -26815,7 +26631,7 @@
       </c>
       <c r="C67" s="31" t="n">
         <f aca="false">IF(Tracker!$C78="",NA(),IF(A67&lt;Tracker!$J$6,NA(),IF(A67=Tracker!$J$6,Tracker!$H78,Tracker!$F78)))</f>
-        <v>29757.64</v>
+        <v>70348.81</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">IF(Tracker!$C78="",NA(),Tracker!$C$7)</f>
@@ -26840,7 +26656,7 @@
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">IF(Tracker!$C79="",NA(),IF(A68&lt;Tracker!$J$6,NA(),IF(A68=Tracker!$J$6,Tracker!$H79,Tracker!$F79)))</f>
-        <v>30650.37</v>
+        <v>72459.27</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">IF(Tracker!$C79="",NA(),Tracker!$C$7)</f>
@@ -26865,7 +26681,7 @@
       </c>
       <c r="C69" s="31" t="n">
         <f aca="false">IF(Tracker!$C80="",NA(),IF(A69&lt;Tracker!$J$6,NA(),IF(A69=Tracker!$J$6,Tracker!$H80,Tracker!$F80)))</f>
-        <v>31569.88</v>
+        <v>74633.05</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">IF(Tracker!$C80="",NA(),Tracker!$C$7)</f>
@@ -26890,7 +26706,7 @@
       </c>
       <c r="C70" s="31" t="n">
         <f aca="false">IF(Tracker!$C81="",NA(),IF(A70&lt;Tracker!$J$6,NA(),IF(A70=Tracker!$J$6,Tracker!$H81,Tracker!$F81)))</f>
-        <v>32516.98</v>
+        <v>76872.04</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">IF(Tracker!$C81="",NA(),Tracker!$C$7)</f>
@@ -26915,7 +26731,7 @@
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">IF(Tracker!$C82="",NA(),IF(A71&lt;Tracker!$J$6,NA(),IF(A71=Tracker!$J$6,Tracker!$H82,Tracker!$F82)))</f>
-        <v>33492.49</v>
+        <v>79178.2</v>
       </c>
       <c r="D71" s="31" t="n">
         <f aca="false">IF(Tracker!$C82="",NA(),Tracker!$C$7)</f>
@@ -26940,7 +26756,7 @@
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">IF(Tracker!$C83="",NA(),IF(A72&lt;Tracker!$J$6,NA(),IF(A72=Tracker!$J$6,Tracker!$H83,Tracker!$F83)))</f>
-        <v>34497.26</v>
+        <v>81553.5500000001</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">IF(Tracker!$C83="",NA(),Tracker!$C$7)</f>
@@ -26965,7 +26781,7 @@
       </c>
       <c r="C73" s="31" t="n">
         <f aca="false">IF(Tracker!$C84="",NA(),IF(A73&lt;Tracker!$J$6,NA(),IF(A73=Tracker!$J$6,Tracker!$H84,Tracker!$F84)))</f>
-        <v>35532.18</v>
+        <v>84000.1600000001</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(Tracker!$C84="",NA(),Tracker!$C$7)</f>
@@ -26990,7 +26806,7 @@
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">IF(Tracker!$C85="",NA(),IF(A74&lt;Tracker!$J$6,NA(),IF(A74=Tracker!$J$6,Tracker!$H85,Tracker!$F85)))</f>
-        <v>36598.15</v>
+        <v>86520.1600000001</v>
       </c>
       <c r="D74" s="31" t="n">
         <f aca="false">IF(Tracker!$C85="",NA(),Tracker!$C$7)</f>
@@ -27015,7 +26831,7 @@
       </c>
       <c r="C75" s="31" t="n">
         <f aca="false">IF(Tracker!$C86="",NA(),IF(A75&lt;Tracker!$J$6,NA(),IF(A75=Tracker!$J$6,Tracker!$H86,Tracker!$F86)))</f>
-        <v>37696.09</v>
+        <v>89115.7600000001</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">IF(Tracker!$C86="",NA(),Tracker!$C$7)</f>
@@ -27040,7 +26856,7 @@
       </c>
       <c r="C76" s="31" t="n">
         <f aca="false">IF(Tracker!$C87="",NA(),IF(A76&lt;Tracker!$J$6,NA(),IF(A76=Tracker!$J$6,Tracker!$H87,Tracker!$F87)))</f>
-        <v>38826.97</v>
+        <v>91789.2300000001</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">IF(Tracker!$C87="",NA(),Tracker!$C$7)</f>
@@ -27065,7 +26881,7 @@
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">IF(Tracker!$C88="",NA(),IF(A77&lt;Tracker!$J$6,NA(),IF(A77=Tracker!$J$6,Tracker!$H88,Tracker!$F88)))</f>
-        <v>39991.78</v>
+        <v>94542.9100000001</v>
       </c>
       <c r="D77" s="31" t="n">
         <f aca="false">IF(Tracker!$C88="",NA(),Tracker!$C$7)</f>
@@ -27090,7 +26906,7 @@
       </c>
       <c r="C78" s="31" t="n">
         <f aca="false">IF(Tracker!$C89="",NA(),IF(A78&lt;Tracker!$J$6,NA(),IF(A78=Tracker!$J$6,Tracker!$H89,Tracker!$F89)))</f>
-        <v>41191.53</v>
+        <v>97379.2</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(Tracker!$C89="",NA(),Tracker!$C$7)</f>
@@ -27115,7 +26931,7 @@
       </c>
       <c r="C79" s="31" t="n">
         <f aca="false">IF(Tracker!$C90="",NA(),IF(A79&lt;Tracker!$J$6,NA(),IF(A79=Tracker!$J$6,Tracker!$H90,Tracker!$F90)))</f>
-        <v>42427.28</v>
+        <v>100300.58</v>
       </c>
       <c r="D79" s="31" t="n">
         <f aca="false">IF(Tracker!$C90="",NA(),Tracker!$C$7)</f>
@@ -27138,13 +26954,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G91),Tracker!$H91,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C80" s="31" t="n">
+      <c r="C80" s="33" t="e">
         <f aca="false">IF(Tracker!$C91="",NA(),IF(A80&lt;Tracker!$J$6,NA(),IF(A80=Tracker!$J$6,Tracker!$H91,Tracker!$F91)))</f>
-        <v>43700.1</v>
-      </c>
-      <c r="D80" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D80" s="33" t="e">
         <f aca="false">IF(Tracker!$C91="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E80" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G91),N(Tracker!$G91)&gt;0),Tracker!$G91,NA())</f>
@@ -27163,13 +26979,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G92),Tracker!$H92,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C81" s="31" t="n">
+      <c r="C81" s="33" t="e">
         <f aca="false">IF(Tracker!$C92="",NA(),IF(A81&lt;Tracker!$J$6,NA(),IF(A81=Tracker!$J$6,Tracker!$H92,Tracker!$F92)))</f>
-        <v>45011.1</v>
-      </c>
-      <c r="D81" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D81" s="33" t="e">
         <f aca="false">IF(Tracker!$C92="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E81" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G92),N(Tracker!$G92)&gt;0),Tracker!$G92,NA())</f>
@@ -27188,13 +27004,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G93),Tracker!$H93,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C82" s="33" t="e">
         <f aca="false">IF(Tracker!$C93="",NA(),IF(A82&lt;Tracker!$J$6,NA(),IF(A82=Tracker!$J$6,Tracker!$H93,Tracker!$F93)))</f>
-        <v>46361.43</v>
-      </c>
-      <c r="D82" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D82" s="33" t="e">
         <f aca="false">IF(Tracker!$C93="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E82" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G93),N(Tracker!$G93)&gt;0),Tracker!$G93,NA())</f>
@@ -27213,13 +27029,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G94),Tracker!$H94,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C83" s="31" t="n">
+      <c r="C83" s="33" t="e">
         <f aca="false">IF(Tracker!$C94="",NA(),IF(A83&lt;Tracker!$J$6,NA(),IF(A83=Tracker!$J$6,Tracker!$H94,Tracker!$F94)))</f>
-        <v>47752.27</v>
-      </c>
-      <c r="D83" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D83" s="33" t="e">
         <f aca="false">IF(Tracker!$C94="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E83" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G94),N(Tracker!$G94)&gt;0),Tracker!$G94,NA())</f>
@@ -27238,13 +27054,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G95),Tracker!$H95,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C84" s="31" t="n">
+      <c r="C84" s="33" t="e">
         <f aca="false">IF(Tracker!$C95="",NA(),IF(A84&lt;Tracker!$J$6,NA(),IF(A84=Tracker!$J$6,Tracker!$H95,Tracker!$F95)))</f>
-        <v>49184.84</v>
-      </c>
-      <c r="D84" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D84" s="33" t="e">
         <f aca="false">IF(Tracker!$C95="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E84" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G95),N(Tracker!$G95)&gt;0),Tracker!$G95,NA())</f>
@@ -27263,13 +27079,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G96),Tracker!$H96,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C85" s="31" t="n">
+      <c r="C85" s="33" t="e">
         <f aca="false">IF(Tracker!$C96="",NA(),IF(A85&lt;Tracker!$J$6,NA(),IF(A85=Tracker!$J$6,Tracker!$H96,Tracker!$F96)))</f>
-        <v>50660.39</v>
-      </c>
-      <c r="D85" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D85" s="33" t="e">
         <f aca="false">IF(Tracker!$C96="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E85" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G96),N(Tracker!$G96)&gt;0),Tracker!$G96,NA())</f>
@@ -27288,13 +27104,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G97),Tracker!$H97,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C86" s="31" t="n">
+      <c r="C86" s="33" t="e">
         <f aca="false">IF(Tracker!$C97="",NA(),IF(A86&lt;Tracker!$J$6,NA(),IF(A86=Tracker!$J$6,Tracker!$H97,Tracker!$F97)))</f>
-        <v>52180.2</v>
-      </c>
-      <c r="D86" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D86" s="33" t="e">
         <f aca="false">IF(Tracker!$C97="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E86" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G97),N(Tracker!$G97)&gt;0),Tracker!$G97,NA())</f>
@@ -27313,13 +27129,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G98),Tracker!$H98,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C87" s="31" t="n">
+      <c r="C87" s="33" t="e">
         <f aca="false">IF(Tracker!$C98="",NA(),IF(A87&lt;Tracker!$J$6,NA(),IF(A87=Tracker!$J$6,Tracker!$H98,Tracker!$F98)))</f>
-        <v>53745.61</v>
-      </c>
-      <c r="D87" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D87" s="33" t="e">
         <f aca="false">IF(Tracker!$C98="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E87" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G98),N(Tracker!$G98)&gt;0),Tracker!$G98,NA())</f>
@@ -27338,13 +27154,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G99),Tracker!$H99,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C88" s="31" t="n">
+      <c r="C88" s="33" t="e">
         <f aca="false">IF(Tracker!$C99="",NA(),IF(A88&lt;Tracker!$J$6,NA(),IF(A88=Tracker!$J$6,Tracker!$H99,Tracker!$F99)))</f>
-        <v>55357.98</v>
-      </c>
-      <c r="D88" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D88" s="33" t="e">
         <f aca="false">IF(Tracker!$C99="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E88" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G99),N(Tracker!$G99)&gt;0),Tracker!$G99,NA())</f>
@@ -27363,13 +27179,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G100),Tracker!$H100,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C89" s="31" t="n">
+      <c r="C89" s="33" t="e">
         <f aca="false">IF(Tracker!$C100="",NA(),IF(A89&lt;Tracker!$J$6,NA(),IF(A89=Tracker!$J$6,Tracker!$H100,Tracker!$F100)))</f>
-        <v>57018.72</v>
-      </c>
-      <c r="D89" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D89" s="33" t="e">
         <f aca="false">IF(Tracker!$C100="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E89" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G100),N(Tracker!$G100)&gt;0),Tracker!$G100,NA())</f>
@@ -27388,13 +27204,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G101),Tracker!$H101,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C90" s="31" t="n">
+      <c r="C90" s="33" t="e">
         <f aca="false">IF(Tracker!$C101="",NA(),IF(A90&lt;Tracker!$J$6,NA(),IF(A90=Tracker!$J$6,Tracker!$H101,Tracker!$F101)))</f>
-        <v>58729.28</v>
-      </c>
-      <c r="D90" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D90" s="33" t="e">
         <f aca="false">IF(Tracker!$C101="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E90" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G101),N(Tracker!$G101)&gt;0),Tracker!$G101,NA())</f>
@@ -27413,13 +27229,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G102),Tracker!$H102,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C91" s="31" t="n">
+      <c r="C91" s="33" t="e">
         <f aca="false">IF(Tracker!$C102="",NA(),IF(A91&lt;Tracker!$J$6,NA(),IF(A91=Tracker!$J$6,Tracker!$H102,Tracker!$F102)))</f>
-        <v>60491.16</v>
-      </c>
-      <c r="D91" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D91" s="33" t="e">
         <f aca="false">IF(Tracker!$C102="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E91" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G102),N(Tracker!$G102)&gt;0),Tracker!$G102,NA())</f>
@@ -27438,13 +27254,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G103),Tracker!$H103,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C92" s="31" t="n">
+      <c r="C92" s="33" t="e">
         <f aca="false">IF(Tracker!$C103="",NA(),IF(A92&lt;Tracker!$J$6,NA(),IF(A92=Tracker!$J$6,Tracker!$H103,Tracker!$F103)))</f>
-        <v>62305.89</v>
-      </c>
-      <c r="D92" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D92" s="33" t="e">
         <f aca="false">IF(Tracker!$C103="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E92" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G103),N(Tracker!$G103)&gt;0),Tracker!$G103,NA())</f>
@@ -27463,13 +27279,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G104),Tracker!$H104,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C93" s="31" t="n">
+      <c r="C93" s="33" t="e">
         <f aca="false">IF(Tracker!$C104="",NA(),IF(A93&lt;Tracker!$J$6,NA(),IF(A93=Tracker!$J$6,Tracker!$H104,Tracker!$F104)))</f>
-        <v>64175.07</v>
-      </c>
-      <c r="D93" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D93" s="33" t="e">
         <f aca="false">IF(Tracker!$C104="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E93" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G104),N(Tracker!$G104)&gt;0),Tracker!$G104,NA())</f>
@@ -27488,13 +27304,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G105),Tracker!$H105,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C94" s="31" t="n">
+      <c r="C94" s="33" t="e">
         <f aca="false">IF(Tracker!$C105="",NA(),IF(A94&lt;Tracker!$J$6,NA(),IF(A94=Tracker!$J$6,Tracker!$H105,Tracker!$F105)))</f>
-        <v>66100.32</v>
-      </c>
-      <c r="D94" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D94" s="33" t="e">
         <f aca="false">IF(Tracker!$C105="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E94" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G105),N(Tracker!$G105)&gt;0),Tracker!$G105,NA())</f>
@@ -27513,13 +27329,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G106),Tracker!$H106,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C95" s="31" t="n">
+      <c r="C95" s="33" t="e">
         <f aca="false">IF(Tracker!$C106="",NA(),IF(A95&lt;Tracker!$J$6,NA(),IF(A95=Tracker!$J$6,Tracker!$H106,Tracker!$F106)))</f>
-        <v>68083.33</v>
-      </c>
-      <c r="D95" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D95" s="33" t="e">
         <f aca="false">IF(Tracker!$C106="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E95" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G106),N(Tracker!$G106)&gt;0),Tracker!$G106,NA())</f>
@@ -27538,13 +27354,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G107),Tracker!$H107,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C96" s="31" t="n">
+      <c r="C96" s="33" t="e">
         <f aca="false">IF(Tracker!$C107="",NA(),IF(A96&lt;Tracker!$J$6,NA(),IF(A96=Tracker!$J$6,Tracker!$H107,Tracker!$F107)))</f>
-        <v>70125.83</v>
-      </c>
-      <c r="D96" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D96" s="33" t="e">
         <f aca="false">IF(Tracker!$C107="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E96" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G107),N(Tracker!$G107)&gt;0),Tracker!$G107,NA())</f>
@@ -27563,13 +27379,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G108),Tracker!$H108,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C97" s="31" t="n">
+      <c r="C97" s="33" t="e">
         <f aca="false">IF(Tracker!$C108="",NA(),IF(A97&lt;Tracker!$J$6,NA(),IF(A97=Tracker!$J$6,Tracker!$H108,Tracker!$F108)))</f>
-        <v>72229.6</v>
-      </c>
-      <c r="D97" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D97" s="33" t="e">
         <f aca="false">IF(Tracker!$C108="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E97" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G108),N(Tracker!$G108)&gt;0),Tracker!$G108,NA())</f>
@@ -27588,13 +27404,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G109),Tracker!$H109,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C98" s="31" t="n">
+      <c r="C98" s="33" t="e">
         <f aca="false">IF(Tracker!$C109="",NA(),IF(A98&lt;Tracker!$J$6,NA(),IF(A98=Tracker!$J$6,Tracker!$H109,Tracker!$F109)))</f>
-        <v>74396.49</v>
-      </c>
-      <c r="D98" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D98" s="33" t="e">
         <f aca="false">IF(Tracker!$C109="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E98" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G109),N(Tracker!$G109)&gt;0),Tracker!$G109,NA())</f>
@@ -27613,13 +27429,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G110),Tracker!$H110,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C99" s="31" t="n">
+      <c r="C99" s="33" t="e">
         <f aca="false">IF(Tracker!$C110="",NA(),IF(A99&lt;Tracker!$J$6,NA(),IF(A99=Tracker!$J$6,Tracker!$H110,Tracker!$F110)))</f>
-        <v>76628.38</v>
-      </c>
-      <c r="D99" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D99" s="33" t="e">
         <f aca="false">IF(Tracker!$C110="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E99" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G110),N(Tracker!$G110)&gt;0),Tracker!$G110,NA())</f>
@@ -27638,13 +27454,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G111),Tracker!$H111,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C100" s="31" t="n">
+      <c r="C100" s="33" t="e">
         <f aca="false">IF(Tracker!$C111="",NA(),IF(A100&lt;Tracker!$J$6,NA(),IF(A100=Tracker!$J$6,Tracker!$H111,Tracker!$F111)))</f>
-        <v>78927.23</v>
-      </c>
-      <c r="D100" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D100" s="33" t="e">
         <f aca="false">IF(Tracker!$C111="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E100" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G111),N(Tracker!$G111)&gt;0),Tracker!$G111,NA())</f>
@@ -27663,13 +27479,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G112),Tracker!$H112,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C101" s="31" t="n">
+      <c r="C101" s="33" t="e">
         <f aca="false">IF(Tracker!$C112="",NA(),IF(A101&lt;Tracker!$J$6,NA(),IF(A101=Tracker!$J$6,Tracker!$H112,Tracker!$F112)))</f>
-        <v>81295.05</v>
-      </c>
-      <c r="D101" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D101" s="33" t="e">
         <f aca="false">IF(Tracker!$C112="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E101" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G112),N(Tracker!$G112)&gt;0),Tracker!$G112,NA())</f>
@@ -27688,13 +27504,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G113),Tracker!$H113,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C102" s="31" t="n">
+      <c r="C102" s="33" t="e">
         <f aca="false">IF(Tracker!$C113="",NA(),IF(A102&lt;Tracker!$J$6,NA(),IF(A102=Tracker!$J$6,Tracker!$H113,Tracker!$F113)))</f>
-        <v>83733.9</v>
-      </c>
-      <c r="D102" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D102" s="33" t="e">
         <f aca="false">IF(Tracker!$C113="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E102" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G113),N(Tracker!$G113)&gt;0),Tracker!$G113,NA())</f>
@@ -27713,13 +27529,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G114),Tracker!$H114,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C103" s="31" t="n">
+      <c r="C103" s="33" t="e">
         <f aca="false">IF(Tracker!$C114="",NA(),IF(A103&lt;Tracker!$J$6,NA(),IF(A103=Tracker!$J$6,Tracker!$H114,Tracker!$F114)))</f>
-        <v>86245.92</v>
-      </c>
-      <c r="D103" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D103" s="33" t="e">
         <f aca="false">IF(Tracker!$C114="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E103" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G114),N(Tracker!$G114)&gt;0),Tracker!$G114,NA())</f>
@@ -27738,13 +27554,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G115),Tracker!$H115,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C104" s="31" t="n">
+      <c r="C104" s="33" t="e">
         <f aca="false">IF(Tracker!$C115="",NA(),IF(A104&lt;Tracker!$J$6,NA(),IF(A104=Tracker!$J$6,Tracker!$H115,Tracker!$F115)))</f>
-        <v>88833.3</v>
-      </c>
-      <c r="D104" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D104" s="33" t="e">
         <f aca="false">IF(Tracker!$C115="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E104" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G115),N(Tracker!$G115)&gt;0),Tracker!$G115,NA())</f>
@@ -27763,13 +27579,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G116),Tracker!$H116,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C105" s="31" t="n">
+      <c r="C105" s="33" t="e">
         <f aca="false">IF(Tracker!$C116="",NA(),IF(A105&lt;Tracker!$J$6,NA(),IF(A105=Tracker!$J$6,Tracker!$H116,Tracker!$F116)))</f>
-        <v>91498.3</v>
-      </c>
-      <c r="D105" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D105" s="33" t="e">
         <f aca="false">IF(Tracker!$C116="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E105" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G116),N(Tracker!$G116)&gt;0),Tracker!$G116,NA())</f>
@@ -27788,13 +27604,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G117),Tracker!$H117,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C106" s="31" t="n">
+      <c r="C106" s="33" t="e">
         <f aca="false">IF(Tracker!$C117="",NA(),IF(A106&lt;Tracker!$J$6,NA(),IF(A106=Tracker!$J$6,Tracker!$H117,Tracker!$F117)))</f>
-        <v>94243.25</v>
-      </c>
-      <c r="D106" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D106" s="33" t="e">
         <f aca="false">IF(Tracker!$C117="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E106" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G117),N(Tracker!$G117)&gt;0),Tracker!$G117,NA())</f>
@@ -27813,13 +27629,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G118),Tracker!$H118,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C107" s="31" t="n">
+      <c r="C107" s="33" t="e">
         <f aca="false">IF(Tracker!$C118="",NA(),IF(A107&lt;Tracker!$J$6,NA(),IF(A107=Tracker!$J$6,Tracker!$H118,Tracker!$F118)))</f>
-        <v>97070.55</v>
-      </c>
-      <c r="D107" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D107" s="33" t="e">
         <f aca="false">IF(Tracker!$C118="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E107" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G118),N(Tracker!$G118)&gt;0),Tracker!$G118,NA())</f>
@@ -27838,13 +27654,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G119),Tracker!$H119,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C108" s="31" t="n">
+      <c r="C108" s="33" t="e">
         <f aca="false">IF(Tracker!$C119="",NA(),IF(A108&lt;Tracker!$J$6,NA(),IF(A108=Tracker!$J$6,Tracker!$H119,Tracker!$F119)))</f>
-        <v>99982.67</v>
-      </c>
-      <c r="D108" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D108" s="33" t="e">
         <f aca="false">IF(Tracker!$C119="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E108" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G119),N(Tracker!$G119)&gt;0),Tracker!$G119,NA())</f>
@@ -27863,13 +27679,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G120),Tracker!$H120,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C109" s="31" t="n">
+      <c r="C109" s="33" t="e">
         <f aca="false">IF(Tracker!$C120="",NA(),IF(A109&lt;Tracker!$J$6,NA(),IF(A109=Tracker!$J$6,Tracker!$H120,Tracker!$F120)))</f>
-        <v>102982.15</v>
-      </c>
-      <c r="D109" s="31" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="D109" s="33" t="e">
         <f aca="false">IF(Tracker!$C120="",NA(),Tracker!$C$7)</f>
-        <v>100000</v>
+        <v>#N/A</v>
       </c>
       <c r="E109" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G120),N(Tracker!$G120)&gt;0),Tracker!$G120,NA())</f>

--- a/Trading_PnL_Tracker.xlsx
+++ b/Trading_PnL_Tracker.xlsx
@@ -53,7 +53,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Provided by you: ₹10,000.</t>
+          <t xml:space="preserve">Provided by you: ₹4,220 (4.22k).</t>
         </r>
       </text>
     </comment>
@@ -101,7 +101,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Enter profit as positive (e.g. 150), loss as negative (e.g. -300), 0 if you did not trade. Leave blank for future days.</t>
+          <t xml:space="preserve">Enter profit as positive (e.g. 150), loss as negative (e.g. -126.60), 0 if you did not trade. Leave blank for future days.</t>
         </r>
       </text>
     </comment>
@@ -313,7 +313,7 @@
     <t xml:space="preserve">1. Each evening, go to that day's row on the Tracker sheet and type your result in the yellow "Actual P/L" cell:</t>
   </si>
   <si>
-    <t xml:space="preserve">      • Profit → positive number (e.g. 150)     • Loss → negative number (e.g. -300)     • Did not trade → 0</t>
+    <t xml:space="preserve">      • Profit → positive number (e.g. 150)     • Loss → negative number (e.g. -126.60)     • Did not trade → 0</t>
   </si>
   <si>
     <t xml:space="preserve">2. The Actual Closing Balance fills in automatically and becomes the next day's Opening Capital.</t>
@@ -331,13 +331,13 @@
     <t xml:space="preserve">Worked example (matches the sheet's formulas)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Day 1 opens at ₹10,000.00 → Profit Target ₹300.00, Loss Limit ₹300.00.</t>
+    <t xml:space="preserve">   Day 1 opens at ₹4,220.00 → Profit Target ₹126.60, Loss Limit ₹126.60.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Enter -300 in Day 1's Actual P/L → Day 1 closes at ₹9,700.00.</t>
+    <t xml:space="preserve">   Enter -126.60 in Day 1's Actual P/L → Day 1 closes at ₹4,093.40.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Day 2 then opens at ₹9,700.00 → Profit Target ₹291.00, Loss Limit ₹291.00.</t>
+    <t xml:space="preserve">   Day 2 then opens at ₹4,093.40 → Profit Target ₹122.80, Loss Limit ₹122.80.</t>
   </si>
   <si>
     <t xml:space="preserve">About the projection</t>
@@ -346,7 +346,7 @@
     <t xml:space="preserve">   • Rows marked "Projection" (grey italic) assume every daily profit target is hit. This is an illustration, not a prediction or guarantee.</t>
   </si>
   <si>
-    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹10,000 at 3%/day takes about 78 trading days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
+    <t xml:space="preserve">   • With no losses at all, reaching ₹1,00,000 from ₹4,220 at 3%/day takes about 108 trading days (with paisa rounding). Any loss or no-trade day extends the timeline.</t>
   </si>
   <si>
     <t xml:space="preserve">   • The table stops at the first day whose projected (or actual) close reaches the goal, and extends automatically after losses (up to 500 days).</t>
@@ -2165,238 +2165,328 @@
                 <c:formatCode>[&gt;=100000]\₹#\,##\,##0.00;\₹#,##0.00</c:formatCode>
                 <c:ptCount val="150"/>
                 <c:pt idx="0">
-                  <c:v>10300</c:v>
+                  <c:v>4346.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10609</c:v>
+                  <c:v>4477</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10927.27</c:v>
+                  <c:v>4611.31</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11255.09</c:v>
+                  <c:v>4749.65</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11592.74</c:v>
+                  <c:v>4892.14</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11940.52</c:v>
+                  <c:v>5038.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12298.74</c:v>
+                  <c:v>5190.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12667.7</c:v>
+                  <c:v>5345.77</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13047.73</c:v>
+                  <c:v>5506.14</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13439.16</c:v>
+                  <c:v>5671.32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13842.33</c:v>
+                  <c:v>5841.46</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14257.6</c:v>
+                  <c:v>6016.7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14685.33</c:v>
+                  <c:v>6197.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15125.89</c:v>
+                  <c:v>6383.12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15579.67</c:v>
+                  <c:v>6574.61</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16047.06</c:v>
+                  <c:v>6771.85</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16528.47</c:v>
+                  <c:v>6975.01</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17024.32</c:v>
+                  <c:v>7184.26</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>17535.05</c:v>
+                  <c:v>7399.79</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>18061.1</c:v>
+                  <c:v>7621.78</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>18602.93</c:v>
+                  <c:v>7850.43</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19161.02</c:v>
+                  <c:v>8085.94</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>19735.85</c:v>
+                  <c:v>8328.52</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>20327.93</c:v>
+                  <c:v>8578.38</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>20937.77</c:v>
+                  <c:v>8835.73</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>21565.9</c:v>
+                  <c:v>9100.8</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>22212.88</c:v>
+                  <c:v>9373.82</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>22879.27</c:v>
+                  <c:v>9655.03</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>23565.65</c:v>
+                  <c:v>9944.68</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>24272.62</c:v>
+                  <c:v>10243.02</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>25000.8</c:v>
+                  <c:v>10550.31</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>25750.82</c:v>
+                  <c:v>10866.82</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>26523.34</c:v>
+                  <c:v>11192.82</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>27319.04</c:v>
+                  <c:v>11528.6</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>28138.61</c:v>
+                  <c:v>11874.46</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>28982.77</c:v>
+                  <c:v>12230.69</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>29852.25</c:v>
+                  <c:v>12597.61</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>30747.82</c:v>
+                  <c:v>12975.54</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>31670.25</c:v>
+                  <c:v>13364.81</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>32620.36</c:v>
+                  <c:v>13765.75</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>33598.97</c:v>
+                  <c:v>14178.72</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>34606.94</c:v>
+                  <c:v>14604.08</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>35645.15</c:v>
+                  <c:v>15042.2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>36714.5</c:v>
+                  <c:v>15493.47</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>37815.94</c:v>
+                  <c:v>15958.27</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>38950.42</c:v>
+                  <c:v>16437.02</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>40118.93</c:v>
+                  <c:v>16930.13</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>41322.5</c:v>
+                  <c:v>17438.03</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>42562.18</c:v>
+                  <c:v>17961.17</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>43839.05</c:v>
+                  <c:v>18500.01</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>45154.22</c:v>
+                  <c:v>19055.01</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>46508.85</c:v>
+                  <c:v>19626.66</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>47904.12</c:v>
+                  <c:v>20215.46</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>49341.24</c:v>
+                  <c:v>20821.92</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>50821.48</c:v>
+                  <c:v>21446.58</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>52346.12</c:v>
+                  <c:v>22089.98</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>53916.5</c:v>
+                  <c:v>22752.68</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>55534</c:v>
+                  <c:v>23435.26</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>57200.02</c:v>
+                  <c:v>24138.32</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>58916.02</c:v>
+                  <c:v>24862.47</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>60683.5</c:v>
+                  <c:v>25608.34</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62504.01</c:v>
+                  <c:v>26376.59</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>64379.13</c:v>
+                  <c:v>27167.89</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>66310.5</c:v>
+                  <c:v>27982.93</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>68299.82</c:v>
+                  <c:v>28822.42</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>70348.81</c:v>
+                  <c:v>29687.09</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>72459.27</c:v>
+                  <c:v>30577.7</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>74633.05</c:v>
+                  <c:v>31495.03</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>76872.04</c:v>
+                  <c:v>32439.88</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>79178.2</c:v>
+                  <c:v>33413.08</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>81553.5500000001</c:v>
+                  <c:v>34415.47</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>84000.1600000001</c:v>
+                  <c:v>35447.93</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>86520.1600000001</c:v>
+                  <c:v>36511.37</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>89115.7600000001</c:v>
+                  <c:v>37606.71</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>91789.2300000001</c:v>
+                  <c:v>38734.91</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>94542.9100000001</c:v>
+                  <c:v>39896.96</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>97379.2</c:v>
+                  <c:v>41093.87</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>100300.58</c:v>
+                  <c:v>42326.69</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>43596.49</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>44904.38</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46251.51</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>47639.06</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>49068.23</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>50540.28</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>52056.49</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>53618.18</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>55226.73</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>56883.53</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>58590.04</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>60347.74</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>62158.17</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>64022.92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>65943.61</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>67921.92</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>69959.58</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>72058.37</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>74220.12</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>76446.72</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>78740.12</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>81102.32</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>83535.39</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>86041.45</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>88622.69</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>91281.37</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>94019.81</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>96840.4</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>99745.61</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>102737.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3155,6 +3245,96 @@
                 <c:pt idx="77">
                   <c:v>100000</c:v>
                 </c:pt>
+                <c:pt idx="78">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>100000</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3168,11 +3348,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37480180"/>
-        <c:axId val="15419459"/>
+        <c:axId val="93378786"/>
+        <c:axId val="9909550"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37480180"/>
+        <c:axId val="93378786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3238,7 +3418,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15419459"/>
+        <c:crossAx val="9909550"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3246,7 +3426,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15419459"/>
+        <c:axId val="9909550"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3322,7 +3502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37480180"/>
+        <c:crossAx val="93378786"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4453,11 +4633,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="100"/>
-        <c:axId val="9681223"/>
-        <c:axId val="49602821"/>
+        <c:axId val="57354433"/>
+        <c:axId val="36989024"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9681223"/>
+        <c:axId val="57354433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4523,7 +4703,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49602821"/>
+        <c:crossAx val="36989024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4531,7 +4711,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49602821"/>
+        <c:axId val="36989024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4607,7 +4787,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9681223"/>
+        <c:crossAx val="57354433"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4921,7 +5101,7 @@
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="str">
         <f aca="false">"Trading Dashboard — "&amp;TEXT(Tracker!$C$6,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" → "&amp;TEXT(Tracker!$C$7,"[&gt;=100000]₹#\,##\,##0;₹#,##0")</f>
-        <v>Trading Dashboard — ₹10,000 → ₹1,00,000</v>
+        <v>Trading Dashboard — ₹4,220 → ₹1,00,000</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4960,17 +5140,17 @@
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="n">
         <f aca="false">Tracker!$G$5</f>
-        <v>10000</v>
+        <v>4220</v>
       </c>
       <c r="C5" s="4"/>
       <c r="E5" s="4" t="n">
         <f aca="false">Tracker!$G$6</f>
-        <v>90000</v>
+        <v>95780</v>
       </c>
       <c r="F5" s="4"/>
       <c r="H5" s="5" t="n">
         <f aca="false">Tracker!$J$5</f>
-        <v>0.1</v>
+        <v>0.0422</v>
       </c>
       <c r="I5" s="5"/>
       <c r="K5" s="6" t="n">
@@ -4982,7 +5162,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="str">
         <f aca="false">"Started at "&amp;TEXT(Tracker!$C$6,"₹#,##0.00")</f>
-        <v>Started at ₹10,000.00</v>
+        <v>Started at ₹4,220.00</v>
       </c>
       <c r="C6" s="7"/>
       <c r="E6" s="7" t="str">
@@ -5027,12 +5207,12 @@
       <c r="C9" s="8"/>
       <c r="E9" s="4" t="n">
         <f aca="false">Tracker!$G$7</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="F9" s="4"/>
       <c r="H9" s="4" t="n">
         <f aca="false">Tracker!$G$8</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="I9" s="4"/>
       <c r="K9" s="8" t="n">
@@ -5156,12 +5336,12 @@
       <c r="F17" s="6"/>
       <c r="H17" s="9" t="n">
         <f aca="false">Tracker!$J$8</f>
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="n">
         <f aca="false">Tracker!$J$9</f>
-        <v>46407</v>
+        <v>46450</v>
       </c>
       <c r="L17" s="8"/>
     </row>
@@ -5253,7 +5433,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{237BE720-693F-47F4-9CA4-67FB6EEB7FD7}</x14:id>
+          <x14:id>{69C7FA00-FA1C-4398-B8E1-83328C2B89BB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5280,7 +5460,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{237BE720-693F-47F4-9CA4-67FB6EEB7FD7}">
+          <x14:cfRule type="dataBar" id="{69C7FA00-FA1C-4398-B8E1-83328C2B89BB}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5323,7 +5503,7 @@
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="str">
         <f aca="false">"Daily Trading P/L Tracker — "&amp;TEXT($C$6,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" → "&amp;TEXT($C$7,"[&gt;=100000]₹#\,##\,##0;₹#,##0")&amp;" Goal"</f>
-        <v>Daily Trading P/L Tracker — ₹10,000 → ₹1,00,000 Goal</v>
+        <v>Daily Trading P/L Tracker — ₹4,220 → ₹1,00,000 Goal</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5370,7 +5550,7 @@
       <c r="F5" s="17"/>
       <c r="G5" s="18" t="n">
         <f aca="false">IF($J$6=0,$C$6,INDEX($H$13:$H$512,$J$6))</f>
-        <v>10000</v>
+        <v>4220</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>3</v>
@@ -5378,7 +5558,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="19" t="n">
         <f aca="false">MIN(1,MAX(0,$G$5/$C$7))</f>
-        <v>0.1</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5387,7 +5567,7 @@
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="20" t="n">
-        <v>10000</v>
+        <v>4220</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>23</v>
@@ -5395,7 +5575,7 @@
       <c r="F6" s="17"/>
       <c r="G6" s="21" t="n">
         <f aca="false">MAX(0,$C$7-$G$5)</f>
-        <v>90000</v>
+        <v>95780</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>24</v>
@@ -5420,7 +5600,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="21" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",ROUND($G$5*$C$8,2))</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>26</v>
@@ -5445,7 +5625,7 @@
       <c r="F8" s="17"/>
       <c r="G8" s="21" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",ROUND($G$5*$C$9,2))</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>28</v>
@@ -5453,7 +5633,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="23" t="n">
         <f aca="false">COUNTIF($I$13:$I$512,"Projection")</f>
-        <v>78</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5479,7 +5659,7 @@
       <c r="I9" s="17"/>
       <c r="J9" s="25" t="n">
         <f aca="false">IF($G$5&gt;=$C$7,"Goal reached",IF(AND($C$512&lt;&gt;"",N($F$512)&lt;$C$7),"Beyond 500 rows",MAX($B$13:$B$512)))</f>
-        <v>46407</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5543,19 +5723,19 @@
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">$C$6</f>
-        <v>10000</v>
+        <v>4220</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">IF(C13="","",ROUND(C13*$C$8,2))</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="E13" s="31" t="n">
         <f aca="false">IF(C13="","",ROUND(C13*$C$9,2))</f>
-        <v>300</v>
+        <v>126.6</v>
       </c>
       <c r="F13" s="31" t="n">
         <f aca="false">IF(C13="","",C13+D13)</f>
-        <v>10300</v>
+        <v>4346.6</v>
       </c>
       <c r="G13" s="32"/>
       <c r="H13" s="31" t="str">
@@ -5580,19 +5760,19 @@
       </c>
       <c r="C14" s="31" t="n">
         <f aca="false">IF(C13="","",IF(OR(IF(ISNUMBER(G13),H13,F13)&gt;=$C$7,IF(ISNUMBER(G13),H13,F13)&lt;=0),"",IF(ISNUMBER(G13),H13,F13)))</f>
-        <v>10300</v>
+        <v>4346.6</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">IF(C14="","",ROUND(C14*$C$8,2))</f>
-        <v>309</v>
+        <v>130.4</v>
       </c>
       <c r="E14" s="31" t="n">
         <f aca="false">IF(C14="","",ROUND(C14*$C$9,2))</f>
-        <v>309</v>
+        <v>130.4</v>
       </c>
       <c r="F14" s="31" t="n">
         <f aca="false">IF(C14="","",C14+D14)</f>
-        <v>10609</v>
+        <v>4477</v>
       </c>
       <c r="G14" s="32"/>
       <c r="H14" s="31" t="str">
@@ -5617,19 +5797,19 @@
       </c>
       <c r="C15" s="31" t="n">
         <f aca="false">IF(C14="","",IF(OR(IF(ISNUMBER(G14),H14,F14)&gt;=$C$7,IF(ISNUMBER(G14),H14,F14)&lt;=0),"",IF(ISNUMBER(G14),H14,F14)))</f>
-        <v>10609</v>
+        <v>4477</v>
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">IF(C15="","",ROUND(C15*$C$8,2))</f>
-        <v>318.27</v>
+        <v>134.31</v>
       </c>
       <c r="E15" s="31" t="n">
         <f aca="false">IF(C15="","",ROUND(C15*$C$9,2))</f>
-        <v>318.27</v>
+        <v>134.31</v>
       </c>
       <c r="F15" s="31" t="n">
         <f aca="false">IF(C15="","",C15+D15)</f>
-        <v>10927.27</v>
+        <v>4611.31</v>
       </c>
       <c r="G15" s="32"/>
       <c r="H15" s="31" t="str">
@@ -5654,19 +5834,19 @@
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">IF(C15="","",IF(OR(IF(ISNUMBER(G15),H15,F15)&gt;=$C$7,IF(ISNUMBER(G15),H15,F15)&lt;=0),"",IF(ISNUMBER(G15),H15,F15)))</f>
-        <v>10927.27</v>
+        <v>4611.31</v>
       </c>
       <c r="D16" s="31" t="n">
         <f aca="false">IF(C16="","",ROUND(C16*$C$8,2))</f>
-        <v>327.82</v>
+        <v>138.34</v>
       </c>
       <c r="E16" s="31" t="n">
         <f aca="false">IF(C16="","",ROUND(C16*$C$9,2))</f>
-        <v>327.82</v>
+        <v>138.34</v>
       </c>
       <c r="F16" s="31" t="n">
         <f aca="false">IF(C16="","",C16+D16)</f>
-        <v>11255.09</v>
+        <v>4749.65</v>
       </c>
       <c r="G16" s="32"/>
       <c r="H16" s="31" t="str">
@@ -5691,19 +5871,19 @@
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">IF(C16="","",IF(OR(IF(ISNUMBER(G16),H16,F16)&gt;=$C$7,IF(ISNUMBER(G16),H16,F16)&lt;=0),"",IF(ISNUMBER(G16),H16,F16)))</f>
-        <v>11255.09</v>
+        <v>4749.65</v>
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">IF(C17="","",ROUND(C17*$C$8,2))</f>
-        <v>337.65</v>
+        <v>142.49</v>
       </c>
       <c r="E17" s="31" t="n">
         <f aca="false">IF(C17="","",ROUND(C17*$C$9,2))</f>
-        <v>337.65</v>
+        <v>142.49</v>
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">IF(C17="","",C17+D17)</f>
-        <v>11592.74</v>
+        <v>4892.14</v>
       </c>
       <c r="G17" s="32"/>
       <c r="H17" s="31" t="str">
@@ -5728,19 +5908,19 @@
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IF(C17="","",IF(OR(IF(ISNUMBER(G17),H17,F17)&gt;=$C$7,IF(ISNUMBER(G17),H17,F17)&lt;=0),"",IF(ISNUMBER(G17),H17,F17)))</f>
-        <v>11592.74</v>
+        <v>4892.14</v>
       </c>
       <c r="D18" s="31" t="n">
         <f aca="false">IF(C18="","",ROUND(C18*$C$8,2))</f>
-        <v>347.78</v>
+        <v>146.76</v>
       </c>
       <c r="E18" s="31" t="n">
         <f aca="false">IF(C18="","",ROUND(C18*$C$9,2))</f>
-        <v>347.78</v>
+        <v>146.76</v>
       </c>
       <c r="F18" s="31" t="n">
         <f aca="false">IF(C18="","",C18+D18)</f>
-        <v>11940.52</v>
+        <v>5038.9</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="31" t="str">
@@ -5765,19 +5945,19 @@
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">IF(C18="","",IF(OR(IF(ISNUMBER(G18),H18,F18)&gt;=$C$7,IF(ISNUMBER(G18),H18,F18)&lt;=0),"",IF(ISNUMBER(G18),H18,F18)))</f>
-        <v>11940.52</v>
+        <v>5038.9</v>
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">IF(C19="","",ROUND(C19*$C$8,2))</f>
-        <v>358.22</v>
+        <v>151.17</v>
       </c>
       <c r="E19" s="31" t="n">
         <f aca="false">IF(C19="","",ROUND(C19*$C$9,2))</f>
-        <v>358.22</v>
+        <v>151.17</v>
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">IF(C19="","",C19+D19)</f>
-        <v>12298.74</v>
+        <v>5190.07</v>
       </c>
       <c r="G19" s="32"/>
       <c r="H19" s="31" t="str">
@@ -5802,19 +5982,19 @@
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">IF(C19="","",IF(OR(IF(ISNUMBER(G19),H19,F19)&gt;=$C$7,IF(ISNUMBER(G19),H19,F19)&lt;=0),"",IF(ISNUMBER(G19),H19,F19)))</f>
-        <v>12298.74</v>
+        <v>5190.07</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">IF(C20="","",ROUND(C20*$C$8,2))</f>
-        <v>368.96</v>
+        <v>155.7</v>
       </c>
       <c r="E20" s="31" t="n">
         <f aca="false">IF(C20="","",ROUND(C20*$C$9,2))</f>
-        <v>368.96</v>
+        <v>155.7</v>
       </c>
       <c r="F20" s="31" t="n">
         <f aca="false">IF(C20="","",C20+D20)</f>
-        <v>12667.7</v>
+        <v>5345.77</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="31" t="str">
@@ -5839,19 +6019,19 @@
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">IF(C20="","",IF(OR(IF(ISNUMBER(G20),H20,F20)&gt;=$C$7,IF(ISNUMBER(G20),H20,F20)&lt;=0),"",IF(ISNUMBER(G20),H20,F20)))</f>
-        <v>12667.7</v>
+        <v>5345.77</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">IF(C21="","",ROUND(C21*$C$8,2))</f>
-        <v>380.03</v>
+        <v>160.37</v>
       </c>
       <c r="E21" s="31" t="n">
         <f aca="false">IF(C21="","",ROUND(C21*$C$9,2))</f>
-        <v>380.03</v>
+        <v>160.37</v>
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">IF(C21="","",C21+D21)</f>
-        <v>13047.73</v>
+        <v>5506.14</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="31" t="str">
@@ -5876,19 +6056,19 @@
       </c>
       <c r="C22" s="31" t="n">
         <f aca="false">IF(C21="","",IF(OR(IF(ISNUMBER(G21),H21,F21)&gt;=$C$7,IF(ISNUMBER(G21),H21,F21)&lt;=0),"",IF(ISNUMBER(G21),H21,F21)))</f>
-        <v>13047.73</v>
+        <v>5506.14</v>
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">IF(C22="","",ROUND(C22*$C$8,2))</f>
-        <v>391.43</v>
+        <v>165.18</v>
       </c>
       <c r="E22" s="31" t="n">
         <f aca="false">IF(C22="","",ROUND(C22*$C$9,2))</f>
-        <v>391.43</v>
+        <v>165.18</v>
       </c>
       <c r="F22" s="31" t="n">
         <f aca="false">IF(C22="","",C22+D22)</f>
-        <v>13439.16</v>
+        <v>5671.32</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="31" t="str">
@@ -5913,19 +6093,19 @@
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">IF(C22="","",IF(OR(IF(ISNUMBER(G22),H22,F22)&gt;=$C$7,IF(ISNUMBER(G22),H22,F22)&lt;=0),"",IF(ISNUMBER(G22),H22,F22)))</f>
-        <v>13439.16</v>
+        <v>5671.32</v>
       </c>
       <c r="D23" s="31" t="n">
         <f aca="false">IF(C23="","",ROUND(C23*$C$8,2))</f>
-        <v>403.17</v>
+        <v>170.14</v>
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">IF(C23="","",ROUND(C23*$C$9,2))</f>
-        <v>403.17</v>
+        <v>170.14</v>
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">IF(C23="","",C23+D23)</f>
-        <v>13842.33</v>
+        <v>5841.46</v>
       </c>
       <c r="G23" s="32"/>
       <c r="H23" s="31" t="str">
@@ -5950,19 +6130,19 @@
       </c>
       <c r="C24" s="31" t="n">
         <f aca="false">IF(C23="","",IF(OR(IF(ISNUMBER(G23),H23,F23)&gt;=$C$7,IF(ISNUMBER(G23),H23,F23)&lt;=0),"",IF(ISNUMBER(G23),H23,F23)))</f>
-        <v>13842.33</v>
+        <v>5841.46</v>
       </c>
       <c r="D24" s="31" t="n">
         <f aca="false">IF(C24="","",ROUND(C24*$C$8,2))</f>
-        <v>415.27</v>
+        <v>175.24</v>
       </c>
       <c r="E24" s="31" t="n">
         <f aca="false">IF(C24="","",ROUND(C24*$C$9,2))</f>
-        <v>415.27</v>
+        <v>175.24</v>
       </c>
       <c r="F24" s="31" t="n">
         <f aca="false">IF(C24="","",C24+D24)</f>
-        <v>14257.6</v>
+        <v>6016.7</v>
       </c>
       <c r="G24" s="32"/>
       <c r="H24" s="31" t="str">
@@ -5987,19 +6167,19 @@
       </c>
       <c r="C25" s="31" t="n">
         <f aca="false">IF(C24="","",IF(OR(IF(ISNUMBER(G24),H24,F24)&gt;=$C$7,IF(ISNUMBER(G24),H24,F24)&lt;=0),"",IF(ISNUMBER(G24),H24,F24)))</f>
-        <v>14257.6</v>
+        <v>6016.7</v>
       </c>
       <c r="D25" s="31" t="n">
         <f aca="false">IF(C25="","",ROUND(C25*$C$8,2))</f>
-        <v>427.73</v>
+        <v>180.5</v>
       </c>
       <c r="E25" s="31" t="n">
         <f aca="false">IF(C25="","",ROUND(C25*$C$9,2))</f>
-        <v>427.73</v>
+        <v>180.5</v>
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">IF(C25="","",C25+D25)</f>
-        <v>14685.33</v>
+        <v>6197.2</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="31" t="str">
@@ -6024,19 +6204,19 @@
       </c>
       <c r="C26" s="31" t="n">
         <f aca="false">IF(C25="","",IF(OR(IF(ISNUMBER(G25),H25,F25)&gt;=$C$7,IF(ISNUMBER(G25),H25,F25)&lt;=0),"",IF(ISNUMBER(G25),H25,F25)))</f>
-        <v>14685.33</v>
+        <v>6197.2</v>
       </c>
       <c r="D26" s="31" t="n">
         <f aca="false">IF(C26="","",ROUND(C26*$C$8,2))</f>
-        <v>440.56</v>
+        <v>185.92</v>
       </c>
       <c r="E26" s="31" t="n">
         <f aca="false">IF(C26="","",ROUND(C26*$C$9,2))</f>
-        <v>440.56</v>
+        <v>185.92</v>
       </c>
       <c r="F26" s="31" t="n">
         <f aca="false">IF(C26="","",C26+D26)</f>
-        <v>15125.89</v>
+        <v>6383.12</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="31" t="str">
@@ -6061,19 +6241,19 @@
       </c>
       <c r="C27" s="31" t="n">
         <f aca="false">IF(C26="","",IF(OR(IF(ISNUMBER(G26),H26,F26)&gt;=$C$7,IF(ISNUMBER(G26),H26,F26)&lt;=0),"",IF(ISNUMBER(G26),H26,F26)))</f>
-        <v>15125.89</v>
+        <v>6383.12</v>
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">IF(C27="","",ROUND(C27*$C$8,2))</f>
-        <v>453.78</v>
+        <v>191.49</v>
       </c>
       <c r="E27" s="31" t="n">
         <f aca="false">IF(C27="","",ROUND(C27*$C$9,2))</f>
-        <v>453.78</v>
+        <v>191.49</v>
       </c>
       <c r="F27" s="31" t="n">
         <f aca="false">IF(C27="","",C27+D27)</f>
-        <v>15579.67</v>
+        <v>6574.61</v>
       </c>
       <c r="G27" s="32"/>
       <c r="H27" s="31" t="str">
@@ -6098,19 +6278,19 @@
       </c>
       <c r="C28" s="31" t="n">
         <f aca="false">IF(C27="","",IF(OR(IF(ISNUMBER(G27),H27,F27)&gt;=$C$7,IF(ISNUMBER(G27),H27,F27)&lt;=0),"",IF(ISNUMBER(G27),H27,F27)))</f>
-        <v>15579.67</v>
+        <v>6574.61</v>
       </c>
       <c r="D28" s="31" t="n">
         <f aca="false">IF(C28="","",ROUND(C28*$C$8,2))</f>
-        <v>467.39</v>
+        <v>197.24</v>
       </c>
       <c r="E28" s="31" t="n">
         <f aca="false">IF(C28="","",ROUND(C28*$C$9,2))</f>
-        <v>467.39</v>
+        <v>197.24</v>
       </c>
       <c r="F28" s="31" t="n">
         <f aca="false">IF(C28="","",C28+D28)</f>
-        <v>16047.06</v>
+        <v>6771.85</v>
       </c>
       <c r="G28" s="32"/>
       <c r="H28" s="31" t="str">
@@ -6135,19 +6315,19 @@
       </c>
       <c r="C29" s="31" t="n">
         <f aca="false">IF(C28="","",IF(OR(IF(ISNUMBER(G28),H28,F28)&gt;=$C$7,IF(ISNUMBER(G28),H28,F28)&lt;=0),"",IF(ISNUMBER(G28),H28,F28)))</f>
-        <v>16047.06</v>
+        <v>6771.85</v>
       </c>
       <c r="D29" s="31" t="n">
         <f aca="false">IF(C29="","",ROUND(C29*$C$8,2))</f>
-        <v>481.41</v>
+        <v>203.16</v>
       </c>
       <c r="E29" s="31" t="n">
         <f aca="false">IF(C29="","",ROUND(C29*$C$9,2))</f>
-        <v>481.41</v>
+        <v>203.16</v>
       </c>
       <c r="F29" s="31" t="n">
         <f aca="false">IF(C29="","",C29+D29)</f>
-        <v>16528.47</v>
+        <v>6975.01</v>
       </c>
       <c r="G29" s="32"/>
       <c r="H29" s="31" t="str">
@@ -6172,19 +6352,19 @@
       </c>
       <c r="C30" s="31" t="n">
         <f aca="false">IF(C29="","",IF(OR(IF(ISNUMBER(G29),H29,F29)&gt;=$C$7,IF(ISNUMBER(G29),H29,F29)&lt;=0),"",IF(ISNUMBER(G29),H29,F29)))</f>
-        <v>16528.47</v>
+        <v>6975.01</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">IF(C30="","",ROUND(C30*$C$8,2))</f>
-        <v>495.85</v>
+        <v>209.25</v>
       </c>
       <c r="E30" s="31" t="n">
         <f aca="false">IF(C30="","",ROUND(C30*$C$9,2))</f>
-        <v>495.85</v>
+        <v>209.25</v>
       </c>
       <c r="F30" s="31" t="n">
         <f aca="false">IF(C30="","",C30+D30)</f>
-        <v>17024.32</v>
+        <v>7184.26</v>
       </c>
       <c r="G30" s="32"/>
       <c r="H30" s="31" t="str">
@@ -6209,19 +6389,19 @@
       </c>
       <c r="C31" s="31" t="n">
         <f aca="false">IF(C30="","",IF(OR(IF(ISNUMBER(G30),H30,F30)&gt;=$C$7,IF(ISNUMBER(G30),H30,F30)&lt;=0),"",IF(ISNUMBER(G30),H30,F30)))</f>
-        <v>17024.32</v>
+        <v>7184.26</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">IF(C31="","",ROUND(C31*$C$8,2))</f>
-        <v>510.73</v>
+        <v>215.53</v>
       </c>
       <c r="E31" s="31" t="n">
         <f aca="false">IF(C31="","",ROUND(C31*$C$9,2))</f>
-        <v>510.73</v>
+        <v>215.53</v>
       </c>
       <c r="F31" s="31" t="n">
         <f aca="false">IF(C31="","",C31+D31)</f>
-        <v>17535.05</v>
+        <v>7399.79</v>
       </c>
       <c r="G31" s="32"/>
       <c r="H31" s="31" t="str">
@@ -6246,19 +6426,19 @@
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">IF(C31="","",IF(OR(IF(ISNUMBER(G31),H31,F31)&gt;=$C$7,IF(ISNUMBER(G31),H31,F31)&lt;=0),"",IF(ISNUMBER(G31),H31,F31)))</f>
-        <v>17535.05</v>
+        <v>7399.79</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">IF(C32="","",ROUND(C32*$C$8,2))</f>
-        <v>526.05</v>
+        <v>221.99</v>
       </c>
       <c r="E32" s="31" t="n">
         <f aca="false">IF(C32="","",ROUND(C32*$C$9,2))</f>
-        <v>526.05</v>
+        <v>221.99</v>
       </c>
       <c r="F32" s="31" t="n">
         <f aca="false">IF(C32="","",C32+D32)</f>
-        <v>18061.1</v>
+        <v>7621.78</v>
       </c>
       <c r="G32" s="32"/>
       <c r="H32" s="31" t="str">
@@ -6283,19 +6463,19 @@
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IF(C32="","",IF(OR(IF(ISNUMBER(G32),H32,F32)&gt;=$C$7,IF(ISNUMBER(G32),H32,F32)&lt;=0),"",IF(ISNUMBER(G32),H32,F32)))</f>
-        <v>18061.1</v>
+        <v>7621.78</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">IF(C33="","",ROUND(C33*$C$8,2))</f>
-        <v>541.83</v>
+        <v>228.65</v>
       </c>
       <c r="E33" s="31" t="n">
         <f aca="false">IF(C33="","",ROUND(C33*$C$9,2))</f>
-        <v>541.83</v>
+        <v>228.65</v>
       </c>
       <c r="F33" s="31" t="n">
         <f aca="false">IF(C33="","",C33+D33)</f>
-        <v>18602.93</v>
+        <v>7850.43</v>
       </c>
       <c r="G33" s="32"/>
       <c r="H33" s="31" t="str">
@@ -6320,19 +6500,19 @@
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IF(C33="","",IF(OR(IF(ISNUMBER(G33),H33,F33)&gt;=$C$7,IF(ISNUMBER(G33),H33,F33)&lt;=0),"",IF(ISNUMBER(G33),H33,F33)))</f>
-        <v>18602.93</v>
+        <v>7850.43</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">IF(C34="","",ROUND(C34*$C$8,2))</f>
-        <v>558.09</v>
+        <v>235.51</v>
       </c>
       <c r="E34" s="31" t="n">
         <f aca="false">IF(C34="","",ROUND(C34*$C$9,2))</f>
-        <v>558.09</v>
+        <v>235.51</v>
       </c>
       <c r="F34" s="31" t="n">
         <f aca="false">IF(C34="","",C34+D34)</f>
-        <v>19161.02</v>
+        <v>8085.94</v>
       </c>
       <c r="G34" s="32"/>
       <c r="H34" s="31" t="str">
@@ -6357,19 +6537,19 @@
       </c>
       <c r="C35" s="31" t="n">
         <f aca="false">IF(C34="","",IF(OR(IF(ISNUMBER(G34),H34,F34)&gt;=$C$7,IF(ISNUMBER(G34),H34,F34)&lt;=0),"",IF(ISNUMBER(G34),H34,F34)))</f>
-        <v>19161.02</v>
+        <v>8085.94</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">IF(C35="","",ROUND(C35*$C$8,2))</f>
-        <v>574.83</v>
+        <v>242.58</v>
       </c>
       <c r="E35" s="31" t="n">
         <f aca="false">IF(C35="","",ROUND(C35*$C$9,2))</f>
-        <v>574.83</v>
+        <v>242.58</v>
       </c>
       <c r="F35" s="31" t="n">
         <f aca="false">IF(C35="","",C35+D35)</f>
-        <v>19735.85</v>
+        <v>8328.52</v>
       </c>
       <c r="G35" s="32"/>
       <c r="H35" s="31" t="str">
@@ -6394,19 +6574,19 @@
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">IF(C35="","",IF(OR(IF(ISNUMBER(G35),H35,F35)&gt;=$C$7,IF(ISNUMBER(G35),H35,F35)&lt;=0),"",IF(ISNUMBER(G35),H35,F35)))</f>
-        <v>19735.85</v>
+        <v>8328.52</v>
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">IF(C36="","",ROUND(C36*$C$8,2))</f>
-        <v>592.08</v>
+        <v>249.86</v>
       </c>
       <c r="E36" s="31" t="n">
         <f aca="false">IF(C36="","",ROUND(C36*$C$9,2))</f>
-        <v>592.08</v>
+        <v>249.86</v>
       </c>
       <c r="F36" s="31" t="n">
         <f aca="false">IF(C36="","",C36+D36)</f>
-        <v>20327.93</v>
+        <v>8578.38</v>
       </c>
       <c r="G36" s="32"/>
       <c r="H36" s="31" t="str">
@@ -6431,19 +6611,19 @@
       </c>
       <c r="C37" s="31" t="n">
         <f aca="false">IF(C36="","",IF(OR(IF(ISNUMBER(G36),H36,F36)&gt;=$C$7,IF(ISNUMBER(G36),H36,F36)&lt;=0),"",IF(ISNUMBER(G36),H36,F36)))</f>
-        <v>20327.93</v>
+        <v>8578.38</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">IF(C37="","",ROUND(C37*$C$8,2))</f>
-        <v>609.84</v>
+        <v>257.35</v>
       </c>
       <c r="E37" s="31" t="n">
         <f aca="false">IF(C37="","",ROUND(C37*$C$9,2))</f>
-        <v>609.84</v>
+        <v>257.35</v>
       </c>
       <c r="F37" s="31" t="n">
         <f aca="false">IF(C37="","",C37+D37)</f>
-        <v>20937.77</v>
+        <v>8835.73</v>
       </c>
       <c r="G37" s="32"/>
       <c r="H37" s="31" t="str">
@@ -6468,19 +6648,19 @@
       </c>
       <c r="C38" s="31" t="n">
         <f aca="false">IF(C37="","",IF(OR(IF(ISNUMBER(G37),H37,F37)&gt;=$C$7,IF(ISNUMBER(G37),H37,F37)&lt;=0),"",IF(ISNUMBER(G37),H37,F37)))</f>
-        <v>20937.77</v>
+        <v>8835.73</v>
       </c>
       <c r="D38" s="31" t="n">
         <f aca="false">IF(C38="","",ROUND(C38*$C$8,2))</f>
-        <v>628.13</v>
+        <v>265.07</v>
       </c>
       <c r="E38" s="31" t="n">
         <f aca="false">IF(C38="","",ROUND(C38*$C$9,2))</f>
-        <v>628.13</v>
+        <v>265.07</v>
       </c>
       <c r="F38" s="31" t="n">
         <f aca="false">IF(C38="","",C38+D38)</f>
-        <v>21565.9</v>
+        <v>9100.8</v>
       </c>
       <c r="G38" s="32"/>
       <c r="H38" s="31" t="str">
@@ -6505,19 +6685,19 @@
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">IF(C38="","",IF(OR(IF(ISNUMBER(G38),H38,F38)&gt;=$C$7,IF(ISNUMBER(G38),H38,F38)&lt;=0),"",IF(ISNUMBER(G38),H38,F38)))</f>
-        <v>21565.9</v>
+        <v>9100.8</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">IF(C39="","",ROUND(C39*$C$8,2))</f>
-        <v>646.98</v>
+        <v>273.02</v>
       </c>
       <c r="E39" s="31" t="n">
         <f aca="false">IF(C39="","",ROUND(C39*$C$9,2))</f>
-        <v>646.98</v>
+        <v>273.02</v>
       </c>
       <c r="F39" s="31" t="n">
         <f aca="false">IF(C39="","",C39+D39)</f>
-        <v>22212.88</v>
+        <v>9373.82</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="31" t="str">
@@ -6542,19 +6722,19 @@
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">IF(C39="","",IF(OR(IF(ISNUMBER(G39),H39,F39)&gt;=$C$7,IF(ISNUMBER(G39),H39,F39)&lt;=0),"",IF(ISNUMBER(G39),H39,F39)))</f>
-        <v>22212.88</v>
+        <v>9373.82</v>
       </c>
       <c r="D40" s="31" t="n">
         <f aca="false">IF(C40="","",ROUND(C40*$C$8,2))</f>
-        <v>666.39</v>
+        <v>281.21</v>
       </c>
       <c r="E40" s="31" t="n">
         <f aca="false">IF(C40="","",ROUND(C40*$C$9,2))</f>
-        <v>666.39</v>
+        <v>281.21</v>
       </c>
       <c r="F40" s="31" t="n">
         <f aca="false">IF(C40="","",C40+D40)</f>
-        <v>22879.27</v>
+        <v>9655.03</v>
       </c>
       <c r="G40" s="32"/>
       <c r="H40" s="31" t="str">
@@ -6579,19 +6759,19 @@
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">IF(C40="","",IF(OR(IF(ISNUMBER(G40),H40,F40)&gt;=$C$7,IF(ISNUMBER(G40),H40,F40)&lt;=0),"",IF(ISNUMBER(G40),H40,F40)))</f>
-        <v>22879.27</v>
+        <v>9655.03</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">IF(C41="","",ROUND(C41*$C$8,2))</f>
-        <v>686.38</v>
+        <v>289.65</v>
       </c>
       <c r="E41" s="31" t="n">
         <f aca="false">IF(C41="","",ROUND(C41*$C$9,2))</f>
-        <v>686.38</v>
+        <v>289.65</v>
       </c>
       <c r="F41" s="31" t="n">
         <f aca="false">IF(C41="","",C41+D41)</f>
-        <v>23565.65</v>
+        <v>9944.68</v>
       </c>
       <c r="G41" s="32"/>
       <c r="H41" s="31" t="str">
@@ -6616,19 +6796,19 @@
       </c>
       <c r="C42" s="31" t="n">
         <f aca="false">IF(C41="","",IF(OR(IF(ISNUMBER(G41),H41,F41)&gt;=$C$7,IF(ISNUMBER(G41),H41,F41)&lt;=0),"",IF(ISNUMBER(G41),H41,F41)))</f>
-        <v>23565.65</v>
+        <v>9944.68</v>
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">IF(C42="","",ROUND(C42*$C$8,2))</f>
-        <v>706.97</v>
+        <v>298.34</v>
       </c>
       <c r="E42" s="31" t="n">
         <f aca="false">IF(C42="","",ROUND(C42*$C$9,2))</f>
-        <v>706.97</v>
+        <v>298.34</v>
       </c>
       <c r="F42" s="31" t="n">
         <f aca="false">IF(C42="","",C42+D42)</f>
-        <v>24272.62</v>
+        <v>10243.02</v>
       </c>
       <c r="G42" s="32"/>
       <c r="H42" s="31" t="str">
@@ -6653,19 +6833,19 @@
       </c>
       <c r="C43" s="31" t="n">
         <f aca="false">IF(C42="","",IF(OR(IF(ISNUMBER(G42),H42,F42)&gt;=$C$7,IF(ISNUMBER(G42),H42,F42)&lt;=0),"",IF(ISNUMBER(G42),H42,F42)))</f>
-        <v>24272.62</v>
+        <v>10243.02</v>
       </c>
       <c r="D43" s="31" t="n">
         <f aca="false">IF(C43="","",ROUND(C43*$C$8,2))</f>
-        <v>728.18</v>
+        <v>307.29</v>
       </c>
       <c r="E43" s="31" t="n">
         <f aca="false">IF(C43="","",ROUND(C43*$C$9,2))</f>
-        <v>728.18</v>
+        <v>307.29</v>
       </c>
       <c r="F43" s="31" t="n">
         <f aca="false">IF(C43="","",C43+D43)</f>
-        <v>25000.8</v>
+        <v>10550.31</v>
       </c>
       <c r="G43" s="32"/>
       <c r="H43" s="31" t="str">
@@ -6690,19 +6870,19 @@
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">IF(C43="","",IF(OR(IF(ISNUMBER(G43),H43,F43)&gt;=$C$7,IF(ISNUMBER(G43),H43,F43)&lt;=0),"",IF(ISNUMBER(G43),H43,F43)))</f>
-        <v>25000.8</v>
+        <v>10550.31</v>
       </c>
       <c r="D44" s="31" t="n">
         <f aca="false">IF(C44="","",ROUND(C44*$C$8,2))</f>
-        <v>750.02</v>
+        <v>316.51</v>
       </c>
       <c r="E44" s="31" t="n">
         <f aca="false">IF(C44="","",ROUND(C44*$C$9,2))</f>
-        <v>750.02</v>
+        <v>316.51</v>
       </c>
       <c r="F44" s="31" t="n">
         <f aca="false">IF(C44="","",C44+D44)</f>
-        <v>25750.82</v>
+        <v>10866.82</v>
       </c>
       <c r="G44" s="32"/>
       <c r="H44" s="31" t="str">
@@ -6727,19 +6907,19 @@
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">IF(C44="","",IF(OR(IF(ISNUMBER(G44),H44,F44)&gt;=$C$7,IF(ISNUMBER(G44),H44,F44)&lt;=0),"",IF(ISNUMBER(G44),H44,F44)))</f>
-        <v>25750.82</v>
+        <v>10866.82</v>
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">IF(C45="","",ROUND(C45*$C$8,2))</f>
-        <v>772.52</v>
+        <v>326</v>
       </c>
       <c r="E45" s="31" t="n">
         <f aca="false">IF(C45="","",ROUND(C45*$C$9,2))</f>
-        <v>772.52</v>
+        <v>326</v>
       </c>
       <c r="F45" s="31" t="n">
         <f aca="false">IF(C45="","",C45+D45)</f>
-        <v>26523.34</v>
+        <v>11192.82</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="31" t="str">
@@ -6764,19 +6944,19 @@
       </c>
       <c r="C46" s="31" t="n">
         <f aca="false">IF(C45="","",IF(OR(IF(ISNUMBER(G45),H45,F45)&gt;=$C$7,IF(ISNUMBER(G45),H45,F45)&lt;=0),"",IF(ISNUMBER(G45),H45,F45)))</f>
-        <v>26523.34</v>
+        <v>11192.82</v>
       </c>
       <c r="D46" s="31" t="n">
         <f aca="false">IF(C46="","",ROUND(C46*$C$8,2))</f>
-        <v>795.7</v>
+        <v>335.78</v>
       </c>
       <c r="E46" s="31" t="n">
         <f aca="false">IF(C46="","",ROUND(C46*$C$9,2))</f>
-        <v>795.7</v>
+        <v>335.78</v>
       </c>
       <c r="F46" s="31" t="n">
         <f aca="false">IF(C46="","",C46+D46)</f>
-        <v>27319.04</v>
+        <v>11528.6</v>
       </c>
       <c r="G46" s="32"/>
       <c r="H46" s="31" t="str">
@@ -6801,19 +6981,19 @@
       </c>
       <c r="C47" s="31" t="n">
         <f aca="false">IF(C46="","",IF(OR(IF(ISNUMBER(G46),H46,F46)&gt;=$C$7,IF(ISNUMBER(G46),H46,F46)&lt;=0),"",IF(ISNUMBER(G46),H46,F46)))</f>
-        <v>27319.04</v>
+        <v>11528.6</v>
       </c>
       <c r="D47" s="31" t="n">
         <f aca="false">IF(C47="","",ROUND(C47*$C$8,2))</f>
-        <v>819.57</v>
+        <v>345.86</v>
       </c>
       <c r="E47" s="31" t="n">
         <f aca="false">IF(C47="","",ROUND(C47*$C$9,2))</f>
-        <v>819.57</v>
+        <v>345.86</v>
       </c>
       <c r="F47" s="31" t="n">
         <f aca="false">IF(C47="","",C47+D47)</f>
-        <v>28138.61</v>
+        <v>11874.46</v>
       </c>
       <c r="G47" s="32"/>
       <c r="H47" s="31" t="str">
@@ -6838,19 +7018,19 @@
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">IF(C47="","",IF(OR(IF(ISNUMBER(G47),H47,F47)&gt;=$C$7,IF(ISNUMBER(G47),H47,F47)&lt;=0),"",IF(ISNUMBER(G47),H47,F47)))</f>
-        <v>28138.61</v>
+        <v>11874.46</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">IF(C48="","",ROUND(C48*$C$8,2))</f>
-        <v>844.16</v>
+        <v>356.23</v>
       </c>
       <c r="E48" s="31" t="n">
         <f aca="false">IF(C48="","",ROUND(C48*$C$9,2))</f>
-        <v>844.16</v>
+        <v>356.23</v>
       </c>
       <c r="F48" s="31" t="n">
         <f aca="false">IF(C48="","",C48+D48)</f>
-        <v>28982.77</v>
+        <v>12230.69</v>
       </c>
       <c r="G48" s="32"/>
       <c r="H48" s="31" t="str">
@@ -6875,19 +7055,19 @@
       </c>
       <c r="C49" s="31" t="n">
         <f aca="false">IF(C48="","",IF(OR(IF(ISNUMBER(G48),H48,F48)&gt;=$C$7,IF(ISNUMBER(G48),H48,F48)&lt;=0),"",IF(ISNUMBER(G48),H48,F48)))</f>
-        <v>28982.77</v>
+        <v>12230.69</v>
       </c>
       <c r="D49" s="31" t="n">
         <f aca="false">IF(C49="","",ROUND(C49*$C$8,2))</f>
-        <v>869.48</v>
+        <v>366.92</v>
       </c>
       <c r="E49" s="31" t="n">
         <f aca="false">IF(C49="","",ROUND(C49*$C$9,2))</f>
-        <v>869.48</v>
+        <v>366.92</v>
       </c>
       <c r="F49" s="31" t="n">
         <f aca="false">IF(C49="","",C49+D49)</f>
-        <v>29852.25</v>
+        <v>12597.61</v>
       </c>
       <c r="G49" s="32"/>
       <c r="H49" s="31" t="str">
@@ -6912,19 +7092,19 @@
       </c>
       <c r="C50" s="31" t="n">
         <f aca="false">IF(C49="","",IF(OR(IF(ISNUMBER(G49),H49,F49)&gt;=$C$7,IF(ISNUMBER(G49),H49,F49)&lt;=0),"",IF(ISNUMBER(G49),H49,F49)))</f>
-        <v>29852.25</v>
+        <v>12597.61</v>
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">IF(C50="","",ROUND(C50*$C$8,2))</f>
-        <v>895.57</v>
+        <v>377.93</v>
       </c>
       <c r="E50" s="31" t="n">
         <f aca="false">IF(C50="","",ROUND(C50*$C$9,2))</f>
-        <v>895.57</v>
+        <v>377.93</v>
       </c>
       <c r="F50" s="31" t="n">
         <f aca="false">IF(C50="","",C50+D50)</f>
-        <v>30747.82</v>
+        <v>12975.54</v>
       </c>
       <c r="G50" s="32"/>
       <c r="H50" s="31" t="str">
@@ -6949,19 +7129,19 @@
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">IF(C50="","",IF(OR(IF(ISNUMBER(G50),H50,F50)&gt;=$C$7,IF(ISNUMBER(G50),H50,F50)&lt;=0),"",IF(ISNUMBER(G50),H50,F50)))</f>
-        <v>30747.82</v>
+        <v>12975.54</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">IF(C51="","",ROUND(C51*$C$8,2))</f>
-        <v>922.43</v>
+        <v>389.27</v>
       </c>
       <c r="E51" s="31" t="n">
         <f aca="false">IF(C51="","",ROUND(C51*$C$9,2))</f>
-        <v>922.43</v>
+        <v>389.27</v>
       </c>
       <c r="F51" s="31" t="n">
         <f aca="false">IF(C51="","",C51+D51)</f>
-        <v>31670.25</v>
+        <v>13364.81</v>
       </c>
       <c r="G51" s="32"/>
       <c r="H51" s="31" t="str">
@@ -6986,19 +7166,19 @@
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">IF(C51="","",IF(OR(IF(ISNUMBER(G51),H51,F51)&gt;=$C$7,IF(ISNUMBER(G51),H51,F51)&lt;=0),"",IF(ISNUMBER(G51),H51,F51)))</f>
-        <v>31670.25</v>
+        <v>13364.81</v>
       </c>
       <c r="D52" s="31" t="n">
         <f aca="false">IF(C52="","",ROUND(C52*$C$8,2))</f>
-        <v>950.11</v>
+        <v>400.94</v>
       </c>
       <c r="E52" s="31" t="n">
         <f aca="false">IF(C52="","",ROUND(C52*$C$9,2))</f>
-        <v>950.11</v>
+        <v>400.94</v>
       </c>
       <c r="F52" s="31" t="n">
         <f aca="false">IF(C52="","",C52+D52)</f>
-        <v>32620.36</v>
+        <v>13765.75</v>
       </c>
       <c r="G52" s="32"/>
       <c r="H52" s="31" t="str">
@@ -7023,19 +7203,19 @@
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">IF(C52="","",IF(OR(IF(ISNUMBER(G52),H52,F52)&gt;=$C$7,IF(ISNUMBER(G52),H52,F52)&lt;=0),"",IF(ISNUMBER(G52),H52,F52)))</f>
-        <v>32620.36</v>
+        <v>13765.75</v>
       </c>
       <c r="D53" s="31" t="n">
         <f aca="false">IF(C53="","",ROUND(C53*$C$8,2))</f>
-        <v>978.61</v>
+        <v>412.97</v>
       </c>
       <c r="E53" s="31" t="n">
         <f aca="false">IF(C53="","",ROUND(C53*$C$9,2))</f>
-        <v>978.61</v>
+        <v>412.97</v>
       </c>
       <c r="F53" s="31" t="n">
         <f aca="false">IF(C53="","",C53+D53)</f>
-        <v>33598.97</v>
+        <v>14178.72</v>
       </c>
       <c r="G53" s="32"/>
       <c r="H53" s="31" t="str">
@@ -7060,19 +7240,19 @@
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">IF(C53="","",IF(OR(IF(ISNUMBER(G53),H53,F53)&gt;=$C$7,IF(ISNUMBER(G53),H53,F53)&lt;=0),"",IF(ISNUMBER(G53),H53,F53)))</f>
-        <v>33598.97</v>
+        <v>14178.72</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(C54="","",ROUND(C54*$C$8,2))</f>
-        <v>1007.97</v>
+        <v>425.36</v>
       </c>
       <c r="E54" s="31" t="n">
         <f aca="false">IF(C54="","",ROUND(C54*$C$9,2))</f>
-        <v>1007.97</v>
+        <v>425.36</v>
       </c>
       <c r="F54" s="31" t="n">
         <f aca="false">IF(C54="","",C54+D54)</f>
-        <v>34606.94</v>
+        <v>14604.08</v>
       </c>
       <c r="G54" s="32"/>
       <c r="H54" s="31" t="str">
@@ -7097,19 +7277,19 @@
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">IF(C54="","",IF(OR(IF(ISNUMBER(G54),H54,F54)&gt;=$C$7,IF(ISNUMBER(G54),H54,F54)&lt;=0),"",IF(ISNUMBER(G54),H54,F54)))</f>
-        <v>34606.94</v>
+        <v>14604.08</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">IF(C55="","",ROUND(C55*$C$8,2))</f>
-        <v>1038.21</v>
+        <v>438.12</v>
       </c>
       <c r="E55" s="31" t="n">
         <f aca="false">IF(C55="","",ROUND(C55*$C$9,2))</f>
-        <v>1038.21</v>
+        <v>438.12</v>
       </c>
       <c r="F55" s="31" t="n">
         <f aca="false">IF(C55="","",C55+D55)</f>
-        <v>35645.15</v>
+        <v>15042.2</v>
       </c>
       <c r="G55" s="32"/>
       <c r="H55" s="31" t="str">
@@ -7134,19 +7314,19 @@
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">IF(C55="","",IF(OR(IF(ISNUMBER(G55),H55,F55)&gt;=$C$7,IF(ISNUMBER(G55),H55,F55)&lt;=0),"",IF(ISNUMBER(G55),H55,F55)))</f>
-        <v>35645.15</v>
+        <v>15042.2</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">IF(C56="","",ROUND(C56*$C$8,2))</f>
-        <v>1069.35</v>
+        <v>451.27</v>
       </c>
       <c r="E56" s="31" t="n">
         <f aca="false">IF(C56="","",ROUND(C56*$C$9,2))</f>
-        <v>1069.35</v>
+        <v>451.27</v>
       </c>
       <c r="F56" s="31" t="n">
         <f aca="false">IF(C56="","",C56+D56)</f>
-        <v>36714.5</v>
+        <v>15493.47</v>
       </c>
       <c r="G56" s="32"/>
       <c r="H56" s="31" t="str">
@@ -7171,19 +7351,19 @@
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">IF(C56="","",IF(OR(IF(ISNUMBER(G56),H56,F56)&gt;=$C$7,IF(ISNUMBER(G56),H56,F56)&lt;=0),"",IF(ISNUMBER(G56),H56,F56)))</f>
-        <v>36714.5</v>
+        <v>15493.47</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(C57="","",ROUND(C57*$C$8,2))</f>
-        <v>1101.44</v>
+        <v>464.8</v>
       </c>
       <c r="E57" s="31" t="n">
         <f aca="false">IF(C57="","",ROUND(C57*$C$9,2))</f>
-        <v>1101.44</v>
+        <v>464.8</v>
       </c>
       <c r="F57" s="31" t="n">
         <f aca="false">IF(C57="","",C57+D57)</f>
-        <v>37815.94</v>
+        <v>15958.27</v>
       </c>
       <c r="G57" s="32"/>
       <c r="H57" s="31" t="str">
@@ -7208,19 +7388,19 @@
       </c>
       <c r="C58" s="31" t="n">
         <f aca="false">IF(C57="","",IF(OR(IF(ISNUMBER(G57),H57,F57)&gt;=$C$7,IF(ISNUMBER(G57),H57,F57)&lt;=0),"",IF(ISNUMBER(G57),H57,F57)))</f>
-        <v>37815.94</v>
+        <v>15958.27</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">IF(C58="","",ROUND(C58*$C$8,2))</f>
-        <v>1134.48</v>
+        <v>478.75</v>
       </c>
       <c r="E58" s="31" t="n">
         <f aca="false">IF(C58="","",ROUND(C58*$C$9,2))</f>
-        <v>1134.48</v>
+        <v>478.75</v>
       </c>
       <c r="F58" s="31" t="n">
         <f aca="false">IF(C58="","",C58+D58)</f>
-        <v>38950.42</v>
+        <v>16437.02</v>
       </c>
       <c r="G58" s="32"/>
       <c r="H58" s="31" t="str">
@@ -7245,19 +7425,19 @@
       </c>
       <c r="C59" s="31" t="n">
         <f aca="false">IF(C58="","",IF(OR(IF(ISNUMBER(G58),H58,F58)&gt;=$C$7,IF(ISNUMBER(G58),H58,F58)&lt;=0),"",IF(ISNUMBER(G58),H58,F58)))</f>
-        <v>38950.42</v>
+        <v>16437.02</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">IF(C59="","",ROUND(C59*$C$8,2))</f>
-        <v>1168.51</v>
+        <v>493.11</v>
       </c>
       <c r="E59" s="31" t="n">
         <f aca="false">IF(C59="","",ROUND(C59*$C$9,2))</f>
-        <v>1168.51</v>
+        <v>493.11</v>
       </c>
       <c r="F59" s="31" t="n">
         <f aca="false">IF(C59="","",C59+D59)</f>
-        <v>40118.93</v>
+        <v>16930.13</v>
       </c>
       <c r="G59" s="32"/>
       <c r="H59" s="31" t="str">
@@ -7282,19 +7462,19 @@
       </c>
       <c r="C60" s="31" t="n">
         <f aca="false">IF(C59="","",IF(OR(IF(ISNUMBER(G59),H59,F59)&gt;=$C$7,IF(ISNUMBER(G59),H59,F59)&lt;=0),"",IF(ISNUMBER(G59),H59,F59)))</f>
-        <v>40118.93</v>
+        <v>16930.13</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">IF(C60="","",ROUND(C60*$C$8,2))</f>
-        <v>1203.57</v>
+        <v>507.9</v>
       </c>
       <c r="E60" s="31" t="n">
         <f aca="false">IF(C60="","",ROUND(C60*$C$9,2))</f>
-        <v>1203.57</v>
+        <v>507.9</v>
       </c>
       <c r="F60" s="31" t="n">
         <f aca="false">IF(C60="","",C60+D60)</f>
-        <v>41322.5</v>
+        <v>17438.03</v>
       </c>
       <c r="G60" s="32"/>
       <c r="H60" s="31" t="str">
@@ -7319,19 +7499,19 @@
       </c>
       <c r="C61" s="31" t="n">
         <f aca="false">IF(C60="","",IF(OR(IF(ISNUMBER(G60),H60,F60)&gt;=$C$7,IF(ISNUMBER(G60),H60,F60)&lt;=0),"",IF(ISNUMBER(G60),H60,F60)))</f>
-        <v>41322.5</v>
+        <v>17438.03</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">IF(C61="","",ROUND(C61*$C$8,2))</f>
-        <v>1239.68</v>
+        <v>523.14</v>
       </c>
       <c r="E61" s="31" t="n">
         <f aca="false">IF(C61="","",ROUND(C61*$C$9,2))</f>
-        <v>1239.68</v>
+        <v>523.14</v>
       </c>
       <c r="F61" s="31" t="n">
         <f aca="false">IF(C61="","",C61+D61)</f>
-        <v>42562.18</v>
+        <v>17961.17</v>
       </c>
       <c r="G61" s="32"/>
       <c r="H61" s="31" t="str">
@@ -7356,19 +7536,19 @@
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">IF(C61="","",IF(OR(IF(ISNUMBER(G61),H61,F61)&gt;=$C$7,IF(ISNUMBER(G61),H61,F61)&lt;=0),"",IF(ISNUMBER(G61),H61,F61)))</f>
-        <v>42562.18</v>
+        <v>17961.17</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">IF(C62="","",ROUND(C62*$C$8,2))</f>
-        <v>1276.87</v>
+        <v>538.84</v>
       </c>
       <c r="E62" s="31" t="n">
         <f aca="false">IF(C62="","",ROUND(C62*$C$9,2))</f>
-        <v>1276.87</v>
+        <v>538.84</v>
       </c>
       <c r="F62" s="31" t="n">
         <f aca="false">IF(C62="","",C62+D62)</f>
-        <v>43839.05</v>
+        <v>18500.01</v>
       </c>
       <c r="G62" s="32"/>
       <c r="H62" s="31" t="str">
@@ -7393,19 +7573,19 @@
       </c>
       <c r="C63" s="31" t="n">
         <f aca="false">IF(C62="","",IF(OR(IF(ISNUMBER(G62),H62,F62)&gt;=$C$7,IF(ISNUMBER(G62),H62,F62)&lt;=0),"",IF(ISNUMBER(G62),H62,F62)))</f>
-        <v>43839.05</v>
+        <v>18500.01</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(C63="","",ROUND(C63*$C$8,2))</f>
-        <v>1315.17</v>
+        <v>555</v>
       </c>
       <c r="E63" s="31" t="n">
         <f aca="false">IF(C63="","",ROUND(C63*$C$9,2))</f>
-        <v>1315.17</v>
+        <v>555</v>
       </c>
       <c r="F63" s="31" t="n">
         <f aca="false">IF(C63="","",C63+D63)</f>
-        <v>45154.22</v>
+        <v>19055.01</v>
       </c>
       <c r="G63" s="32"/>
       <c r="H63" s="31" t="str">
@@ -7430,19 +7610,19 @@
       </c>
       <c r="C64" s="31" t="n">
         <f aca="false">IF(C63="","",IF(OR(IF(ISNUMBER(G63),H63,F63)&gt;=$C$7,IF(ISNUMBER(G63),H63,F63)&lt;=0),"",IF(ISNUMBER(G63),H63,F63)))</f>
-        <v>45154.22</v>
+        <v>19055.01</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(C64="","",ROUND(C64*$C$8,2))</f>
-        <v>1354.63</v>
+        <v>571.65</v>
       </c>
       <c r="E64" s="31" t="n">
         <f aca="false">IF(C64="","",ROUND(C64*$C$9,2))</f>
-        <v>1354.63</v>
+        <v>571.65</v>
       </c>
       <c r="F64" s="31" t="n">
         <f aca="false">IF(C64="","",C64+D64)</f>
-        <v>46508.85</v>
+        <v>19626.66</v>
       </c>
       <c r="G64" s="32"/>
       <c r="H64" s="31" t="str">
@@ -7467,19 +7647,19 @@
       </c>
       <c r="C65" s="31" t="n">
         <f aca="false">IF(C64="","",IF(OR(IF(ISNUMBER(G64),H64,F64)&gt;=$C$7,IF(ISNUMBER(G64),H64,F64)&lt;=0),"",IF(ISNUMBER(G64),H64,F64)))</f>
-        <v>46508.85</v>
+        <v>19626.66</v>
       </c>
       <c r="D65" s="31" t="n">
         <f aca="false">IF(C65="","",ROUND(C65*$C$8,2))</f>
-        <v>1395.27</v>
+        <v>588.8</v>
       </c>
       <c r="E65" s="31" t="n">
         <f aca="false">IF(C65="","",ROUND(C65*$C$9,2))</f>
-        <v>1395.27</v>
+        <v>588.8</v>
       </c>
       <c r="F65" s="31" t="n">
         <f aca="false">IF(C65="","",C65+D65)</f>
-        <v>47904.12</v>
+        <v>20215.46</v>
       </c>
       <c r="G65" s="32"/>
       <c r="H65" s="31" t="str">
@@ -7504,19 +7684,19 @@
       </c>
       <c r="C66" s="31" t="n">
         <f aca="false">IF(C65="","",IF(OR(IF(ISNUMBER(G65),H65,F65)&gt;=$C$7,IF(ISNUMBER(G65),H65,F65)&lt;=0),"",IF(ISNUMBER(G65),H65,F65)))</f>
-        <v>47904.12</v>
+        <v>20215.46</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">IF(C66="","",ROUND(C66*$C$8,2))</f>
-        <v>1437.12</v>
+        <v>606.46</v>
       </c>
       <c r="E66" s="31" t="n">
         <f aca="false">IF(C66="","",ROUND(C66*$C$9,2))</f>
-        <v>1437.12</v>
+        <v>606.46</v>
       </c>
       <c r="F66" s="31" t="n">
         <f aca="false">IF(C66="","",C66+D66)</f>
-        <v>49341.24</v>
+        <v>20821.92</v>
       </c>
       <c r="G66" s="32"/>
       <c r="H66" s="31" t="str">
@@ -7541,19 +7721,19 @@
       </c>
       <c r="C67" s="31" t="n">
         <f aca="false">IF(C66="","",IF(OR(IF(ISNUMBER(G66),H66,F66)&gt;=$C$7,IF(ISNUMBER(G66),H66,F66)&lt;=0),"",IF(ISNUMBER(G66),H66,F66)))</f>
-        <v>49341.24</v>
+        <v>20821.92</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">IF(C67="","",ROUND(C67*$C$8,2))</f>
-        <v>1480.24</v>
+        <v>624.66</v>
       </c>
       <c r="E67" s="31" t="n">
         <f aca="false">IF(C67="","",ROUND(C67*$C$9,2))</f>
-        <v>1480.24</v>
+        <v>624.66</v>
       </c>
       <c r="F67" s="31" t="n">
         <f aca="false">IF(C67="","",C67+D67)</f>
-        <v>50821.48</v>
+        <v>21446.58</v>
       </c>
       <c r="G67" s="32"/>
       <c r="H67" s="31" t="str">
@@ -7578,19 +7758,19 @@
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">IF(C67="","",IF(OR(IF(ISNUMBER(G67),H67,F67)&gt;=$C$7,IF(ISNUMBER(G67),H67,F67)&lt;=0),"",IF(ISNUMBER(G67),H67,F67)))</f>
-        <v>50821.48</v>
+        <v>21446.58</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">IF(C68="","",ROUND(C68*$C$8,2))</f>
-        <v>1524.64</v>
+        <v>643.4</v>
       </c>
       <c r="E68" s="31" t="n">
         <f aca="false">IF(C68="","",ROUND(C68*$C$9,2))</f>
-        <v>1524.64</v>
+        <v>643.4</v>
       </c>
       <c r="F68" s="31" t="n">
         <f aca="false">IF(C68="","",C68+D68)</f>
-        <v>52346.12</v>
+        <v>22089.98</v>
       </c>
       <c r="G68" s="32"/>
       <c r="H68" s="31" t="str">
@@ -7615,19 +7795,19 @@
       </c>
       <c r="C69" s="31" t="n">
         <f aca="false">IF(C68="","",IF(OR(IF(ISNUMBER(G68),H68,F68)&gt;=$C$7,IF(ISNUMBER(G68),H68,F68)&lt;=0),"",IF(ISNUMBER(G68),H68,F68)))</f>
-        <v>52346.12</v>
+        <v>22089.98</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">IF(C69="","",ROUND(C69*$C$8,2))</f>
-        <v>1570.38</v>
+        <v>662.7</v>
       </c>
       <c r="E69" s="31" t="n">
         <f aca="false">IF(C69="","",ROUND(C69*$C$9,2))</f>
-        <v>1570.38</v>
+        <v>662.7</v>
       </c>
       <c r="F69" s="31" t="n">
         <f aca="false">IF(C69="","",C69+D69)</f>
-        <v>53916.5</v>
+        <v>22752.68</v>
       </c>
       <c r="G69" s="32"/>
       <c r="H69" s="31" t="str">
@@ -7652,19 +7832,19 @@
       </c>
       <c r="C70" s="31" t="n">
         <f aca="false">IF(C69="","",IF(OR(IF(ISNUMBER(G69),H69,F69)&gt;=$C$7,IF(ISNUMBER(G69),H69,F69)&lt;=0),"",IF(ISNUMBER(G69),H69,F69)))</f>
-        <v>53916.5</v>
+        <v>22752.68</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">IF(C70="","",ROUND(C70*$C$8,2))</f>
-        <v>1617.5</v>
+        <v>682.58</v>
       </c>
       <c r="E70" s="31" t="n">
         <f aca="false">IF(C70="","",ROUND(C70*$C$9,2))</f>
-        <v>1617.5</v>
+        <v>682.58</v>
       </c>
       <c r="F70" s="31" t="n">
         <f aca="false">IF(C70="","",C70+D70)</f>
-        <v>55534</v>
+        <v>23435.26</v>
       </c>
       <c r="G70" s="32"/>
       <c r="H70" s="31" t="str">
@@ -7689,19 +7869,19 @@
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">IF(C70="","",IF(OR(IF(ISNUMBER(G70),H70,F70)&gt;=$C$7,IF(ISNUMBER(G70),H70,F70)&lt;=0),"",IF(ISNUMBER(G70),H70,F70)))</f>
-        <v>55534</v>
+        <v>23435.26</v>
       </c>
       <c r="D71" s="31" t="n">
         <f aca="false">IF(C71="","",ROUND(C71*$C$8,2))</f>
-        <v>1666.02</v>
+        <v>703.06</v>
       </c>
       <c r="E71" s="31" t="n">
         <f aca="false">IF(C71="","",ROUND(C71*$C$9,2))</f>
-        <v>1666.02</v>
+        <v>703.06</v>
       </c>
       <c r="F71" s="31" t="n">
         <f aca="false">IF(C71="","",C71+D71)</f>
-        <v>57200.02</v>
+        <v>24138.32</v>
       </c>
       <c r="G71" s="32"/>
       <c r="H71" s="31" t="str">
@@ -7726,19 +7906,19 @@
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">IF(C71="","",IF(OR(IF(ISNUMBER(G71),H71,F71)&gt;=$C$7,IF(ISNUMBER(G71),H71,F71)&lt;=0),"",IF(ISNUMBER(G71),H71,F71)))</f>
-        <v>57200.02</v>
+        <v>24138.32</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">IF(C72="","",ROUND(C72*$C$8,2))</f>
-        <v>1716</v>
+        <v>724.15</v>
       </c>
       <c r="E72" s="31" t="n">
         <f aca="false">IF(C72="","",ROUND(C72*$C$9,2))</f>
-        <v>1716</v>
+        <v>724.15</v>
       </c>
       <c r="F72" s="31" t="n">
         <f aca="false">IF(C72="","",C72+D72)</f>
-        <v>58916.02</v>
+        <v>24862.47</v>
       </c>
       <c r="G72" s="32"/>
       <c r="H72" s="31" t="str">
@@ -7763,19 +7943,19 @@
       </c>
       <c r="C73" s="31" t="n">
         <f aca="false">IF(C72="","",IF(OR(IF(ISNUMBER(G72),H72,F72)&gt;=$C$7,IF(ISNUMBER(G72),H72,F72)&lt;=0),"",IF(ISNUMBER(G72),H72,F72)))</f>
-        <v>58916.02</v>
+        <v>24862.47</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(C73="","",ROUND(C73*$C$8,2))</f>
-        <v>1767.48</v>
+        <v>745.87</v>
       </c>
       <c r="E73" s="31" t="n">
         <f aca="false">IF(C73="","",ROUND(C73*$C$9,2))</f>
-        <v>1767.48</v>
+        <v>745.87</v>
       </c>
       <c r="F73" s="31" t="n">
         <f aca="false">IF(C73="","",C73+D73)</f>
-        <v>60683.5</v>
+        <v>25608.34</v>
       </c>
       <c r="G73" s="32"/>
       <c r="H73" s="31" t="str">
@@ -7800,19 +7980,19 @@
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">IF(C73="","",IF(OR(IF(ISNUMBER(G73),H73,F73)&gt;=$C$7,IF(ISNUMBER(G73),H73,F73)&lt;=0),"",IF(ISNUMBER(G73),H73,F73)))</f>
-        <v>60683.5</v>
+        <v>25608.34</v>
       </c>
       <c r="D74" s="31" t="n">
         <f aca="false">IF(C74="","",ROUND(C74*$C$8,2))</f>
-        <v>1820.51</v>
+        <v>768.25</v>
       </c>
       <c r="E74" s="31" t="n">
         <f aca="false">IF(C74="","",ROUND(C74*$C$9,2))</f>
-        <v>1820.51</v>
+        <v>768.25</v>
       </c>
       <c r="F74" s="31" t="n">
         <f aca="false">IF(C74="","",C74+D74)</f>
-        <v>62504.01</v>
+        <v>26376.59</v>
       </c>
       <c r="G74" s="32"/>
       <c r="H74" s="31" t="str">
@@ -7837,19 +8017,19 @@
       </c>
       <c r="C75" s="31" t="n">
         <f aca="false">IF(C74="","",IF(OR(IF(ISNUMBER(G74),H74,F74)&gt;=$C$7,IF(ISNUMBER(G74),H74,F74)&lt;=0),"",IF(ISNUMBER(G74),H74,F74)))</f>
-        <v>62504.01</v>
+        <v>26376.59</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">IF(C75="","",ROUND(C75*$C$8,2))</f>
-        <v>1875.12</v>
+        <v>791.3</v>
       </c>
       <c r="E75" s="31" t="n">
         <f aca="false">IF(C75="","",ROUND(C75*$C$9,2))</f>
-        <v>1875.12</v>
+        <v>791.3</v>
       </c>
       <c r="F75" s="31" t="n">
         <f aca="false">IF(C75="","",C75+D75)</f>
-        <v>64379.13</v>
+        <v>27167.89</v>
       </c>
       <c r="G75" s="32"/>
       <c r="H75" s="31" t="str">
@@ -7874,19 +8054,19 @@
       </c>
       <c r="C76" s="31" t="n">
         <f aca="false">IF(C75="","",IF(OR(IF(ISNUMBER(G75),H75,F75)&gt;=$C$7,IF(ISNUMBER(G75),H75,F75)&lt;=0),"",IF(ISNUMBER(G75),H75,F75)))</f>
-        <v>64379.13</v>
+        <v>27167.89</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">IF(C76="","",ROUND(C76*$C$8,2))</f>
-        <v>1931.37</v>
+        <v>815.04</v>
       </c>
       <c r="E76" s="31" t="n">
         <f aca="false">IF(C76="","",ROUND(C76*$C$9,2))</f>
-        <v>1931.37</v>
+        <v>815.04</v>
       </c>
       <c r="F76" s="31" t="n">
         <f aca="false">IF(C76="","",C76+D76)</f>
-        <v>66310.5</v>
+        <v>27982.93</v>
       </c>
       <c r="G76" s="32"/>
       <c r="H76" s="31" t="str">
@@ -7911,19 +8091,19 @@
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">IF(C76="","",IF(OR(IF(ISNUMBER(G76),H76,F76)&gt;=$C$7,IF(ISNUMBER(G76),H76,F76)&lt;=0),"",IF(ISNUMBER(G76),H76,F76)))</f>
-        <v>66310.5</v>
+        <v>27982.93</v>
       </c>
       <c r="D77" s="31" t="n">
         <f aca="false">IF(C77="","",ROUND(C77*$C$8,2))</f>
-        <v>1989.32</v>
+        <v>839.49</v>
       </c>
       <c r="E77" s="31" t="n">
         <f aca="false">IF(C77="","",ROUND(C77*$C$9,2))</f>
-        <v>1989.32</v>
+        <v>839.49</v>
       </c>
       <c r="F77" s="31" t="n">
         <f aca="false">IF(C77="","",C77+D77)</f>
-        <v>68299.82</v>
+        <v>28822.42</v>
       </c>
       <c r="G77" s="32"/>
       <c r="H77" s="31" t="str">
@@ -7948,19 +8128,19 @@
       </c>
       <c r="C78" s="31" t="n">
         <f aca="false">IF(C77="","",IF(OR(IF(ISNUMBER(G77),H77,F77)&gt;=$C$7,IF(ISNUMBER(G77),H77,F77)&lt;=0),"",IF(ISNUMBER(G77),H77,F77)))</f>
-        <v>68299.82</v>
+        <v>28822.42</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(C78="","",ROUND(C78*$C$8,2))</f>
-        <v>2048.99</v>
+        <v>864.67</v>
       </c>
       <c r="E78" s="31" t="n">
         <f aca="false">IF(C78="","",ROUND(C78*$C$9,2))</f>
-        <v>2048.99</v>
+        <v>864.67</v>
       </c>
       <c r="F78" s="31" t="n">
         <f aca="false">IF(C78="","",C78+D78)</f>
-        <v>70348.81</v>
+        <v>29687.09</v>
       </c>
       <c r="G78" s="32"/>
       <c r="H78" s="31" t="str">
@@ -7985,19 +8165,19 @@
       </c>
       <c r="C79" s="31" t="n">
         <f aca="false">IF(C78="","",IF(OR(IF(ISNUMBER(G78),H78,F78)&gt;=$C$7,IF(ISNUMBER(G78),H78,F78)&lt;=0),"",IF(ISNUMBER(G78),H78,F78)))</f>
-        <v>70348.81</v>
+        <v>29687.09</v>
       </c>
       <c r="D79" s="31" t="n">
         <f aca="false">IF(C79="","",ROUND(C79*$C$8,2))</f>
-        <v>2110.46</v>
+        <v>890.61</v>
       </c>
       <c r="E79" s="31" t="n">
         <f aca="false">IF(C79="","",ROUND(C79*$C$9,2))</f>
-        <v>2110.46</v>
+        <v>890.61</v>
       </c>
       <c r="F79" s="31" t="n">
         <f aca="false">IF(C79="","",C79+D79)</f>
-        <v>72459.27</v>
+        <v>30577.7</v>
       </c>
       <c r="G79" s="32"/>
       <c r="H79" s="31" t="str">
@@ -8022,19 +8202,19 @@
       </c>
       <c r="C80" s="31" t="n">
         <f aca="false">IF(C79="","",IF(OR(IF(ISNUMBER(G79),H79,F79)&gt;=$C$7,IF(ISNUMBER(G79),H79,F79)&lt;=0),"",IF(ISNUMBER(G79),H79,F79)))</f>
-        <v>72459.27</v>
+        <v>30577.7</v>
       </c>
       <c r="D80" s="31" t="n">
         <f aca="false">IF(C80="","",ROUND(C80*$C$8,2))</f>
-        <v>2173.78</v>
+        <v>917.33</v>
       </c>
       <c r="E80" s="31" t="n">
         <f aca="false">IF(C80="","",ROUND(C80*$C$9,2))</f>
-        <v>2173.78</v>
+        <v>917.33</v>
       </c>
       <c r="F80" s="31" t="n">
         <f aca="false">IF(C80="","",C80+D80)</f>
-        <v>74633.05</v>
+        <v>31495.03</v>
       </c>
       <c r="G80" s="32"/>
       <c r="H80" s="31" t="str">
@@ -8059,19 +8239,19 @@
       </c>
       <c r="C81" s="31" t="n">
         <f aca="false">IF(C80="","",IF(OR(IF(ISNUMBER(G80),H80,F80)&gt;=$C$7,IF(ISNUMBER(G80),H80,F80)&lt;=0),"",IF(ISNUMBER(G80),H80,F80)))</f>
-        <v>74633.05</v>
+        <v>31495.03</v>
       </c>
       <c r="D81" s="31" t="n">
         <f aca="false">IF(C81="","",ROUND(C81*$C$8,2))</f>
-        <v>2238.99</v>
+        <v>944.85</v>
       </c>
       <c r="E81" s="31" t="n">
         <f aca="false">IF(C81="","",ROUND(C81*$C$9,2))</f>
-        <v>2238.99</v>
+        <v>944.85</v>
       </c>
       <c r="F81" s="31" t="n">
         <f aca="false">IF(C81="","",C81+D81)</f>
-        <v>76872.04</v>
+        <v>32439.88</v>
       </c>
       <c r="G81" s="32"/>
       <c r="H81" s="31" t="str">
@@ -8096,19 +8276,19 @@
       </c>
       <c r="C82" s="31" t="n">
         <f aca="false">IF(C81="","",IF(OR(IF(ISNUMBER(G81),H81,F81)&gt;=$C$7,IF(ISNUMBER(G81),H81,F81)&lt;=0),"",IF(ISNUMBER(G81),H81,F81)))</f>
-        <v>76872.04</v>
+        <v>32439.88</v>
       </c>
       <c r="D82" s="31" t="n">
         <f aca="false">IF(C82="","",ROUND(C82*$C$8,2))</f>
-        <v>2306.16</v>
+        <v>973.2</v>
       </c>
       <c r="E82" s="31" t="n">
         <f aca="false">IF(C82="","",ROUND(C82*$C$9,2))</f>
-        <v>2306.16</v>
+        <v>973.2</v>
       </c>
       <c r="F82" s="31" t="n">
         <f aca="false">IF(C82="","",C82+D82)</f>
-        <v>79178.2</v>
+        <v>33413.08</v>
       </c>
       <c r="G82" s="32"/>
       <c r="H82" s="31" t="str">
@@ -8133,19 +8313,19 @@
       </c>
       <c r="C83" s="31" t="n">
         <f aca="false">IF(C82="","",IF(OR(IF(ISNUMBER(G82),H82,F82)&gt;=$C$7,IF(ISNUMBER(G82),H82,F82)&lt;=0),"",IF(ISNUMBER(G82),H82,F82)))</f>
-        <v>79178.2</v>
+        <v>33413.08</v>
       </c>
       <c r="D83" s="31" t="n">
         <f aca="false">IF(C83="","",ROUND(C83*$C$8,2))</f>
-        <v>2375.35</v>
+        <v>1002.39</v>
       </c>
       <c r="E83" s="31" t="n">
         <f aca="false">IF(C83="","",ROUND(C83*$C$9,2))</f>
-        <v>2375.35</v>
+        <v>1002.39</v>
       </c>
       <c r="F83" s="31" t="n">
         <f aca="false">IF(C83="","",C83+D83)</f>
-        <v>81553.5500000001</v>
+        <v>34415.47</v>
       </c>
       <c r="G83" s="32"/>
       <c r="H83" s="31" t="str">
@@ -8170,19 +8350,19 @@
       </c>
       <c r="C84" s="31" t="n">
         <f aca="false">IF(C83="","",IF(OR(IF(ISNUMBER(G83),H83,F83)&gt;=$C$7,IF(ISNUMBER(G83),H83,F83)&lt;=0),"",IF(ISNUMBER(G83),H83,F83)))</f>
-        <v>81553.5500000001</v>
+        <v>34415.47</v>
       </c>
       <c r="D84" s="31" t="n">
         <f aca="false">IF(C84="","",ROUND(C84*$C$8,2))</f>
-        <v>2446.61</v>
+        <v>1032.46</v>
       </c>
       <c r="E84" s="31" t="n">
         <f aca="false">IF(C84="","",ROUND(C84*$C$9,2))</f>
-        <v>2446.61</v>
+        <v>1032.46</v>
       </c>
       <c r="F84" s="31" t="n">
         <f aca="false">IF(C84="","",C84+D84)</f>
-        <v>84000.1600000001</v>
+        <v>35447.93</v>
       </c>
       <c r="G84" s="32"/>
       <c r="H84" s="31" t="str">
@@ -8207,19 +8387,19 @@
       </c>
       <c r="C85" s="31" t="n">
         <f aca="false">IF(C84="","",IF(OR(IF(ISNUMBER(G84),H84,F84)&gt;=$C$7,IF(ISNUMBER(G84),H84,F84)&lt;=0),"",IF(ISNUMBER(G84),H84,F84)))</f>
-        <v>84000.1600000001</v>
+        <v>35447.93</v>
       </c>
       <c r="D85" s="31" t="n">
         <f aca="false">IF(C85="","",ROUND(C85*$C$8,2))</f>
-        <v>2520</v>
+        <v>1063.44</v>
       </c>
       <c r="E85" s="31" t="n">
         <f aca="false">IF(C85="","",ROUND(C85*$C$9,2))</f>
-        <v>2520</v>
+        <v>1063.44</v>
       </c>
       <c r="F85" s="31" t="n">
         <f aca="false">IF(C85="","",C85+D85)</f>
-        <v>86520.1600000001</v>
+        <v>36511.37</v>
       </c>
       <c r="G85" s="32"/>
       <c r="H85" s="31" t="str">
@@ -8244,19 +8424,19 @@
       </c>
       <c r="C86" s="31" t="n">
         <f aca="false">IF(C85="","",IF(OR(IF(ISNUMBER(G85),H85,F85)&gt;=$C$7,IF(ISNUMBER(G85),H85,F85)&lt;=0),"",IF(ISNUMBER(G85),H85,F85)))</f>
-        <v>86520.1600000001</v>
+        <v>36511.37</v>
       </c>
       <c r="D86" s="31" t="n">
         <f aca="false">IF(C86="","",ROUND(C86*$C$8,2))</f>
-        <v>2595.6</v>
+        <v>1095.34</v>
       </c>
       <c r="E86" s="31" t="n">
         <f aca="false">IF(C86="","",ROUND(C86*$C$9,2))</f>
-        <v>2595.6</v>
+        <v>1095.34</v>
       </c>
       <c r="F86" s="31" t="n">
         <f aca="false">IF(C86="","",C86+D86)</f>
-        <v>89115.7600000001</v>
+        <v>37606.71</v>
       </c>
       <c r="G86" s="32"/>
       <c r="H86" s="31" t="str">
@@ -8281,19 +8461,19 @@
       </c>
       <c r="C87" s="31" t="n">
         <f aca="false">IF(C86="","",IF(OR(IF(ISNUMBER(G86),H86,F86)&gt;=$C$7,IF(ISNUMBER(G86),H86,F86)&lt;=0),"",IF(ISNUMBER(G86),H86,F86)))</f>
-        <v>89115.7600000001</v>
+        <v>37606.71</v>
       </c>
       <c r="D87" s="31" t="n">
         <f aca="false">IF(C87="","",ROUND(C87*$C$8,2))</f>
-        <v>2673.47</v>
+        <v>1128.2</v>
       </c>
       <c r="E87" s="31" t="n">
         <f aca="false">IF(C87="","",ROUND(C87*$C$9,2))</f>
-        <v>2673.47</v>
+        <v>1128.2</v>
       </c>
       <c r="F87" s="31" t="n">
         <f aca="false">IF(C87="","",C87+D87)</f>
-        <v>91789.2300000001</v>
+        <v>38734.91</v>
       </c>
       <c r="G87" s="32"/>
       <c r="H87" s="31" t="str">
@@ -8318,19 +8498,19 @@
       </c>
       <c r="C88" s="31" t="n">
         <f aca="false">IF(C87="","",IF(OR(IF(ISNUMBER(G87),H87,F87)&gt;=$C$7,IF(ISNUMBER(G87),H87,F87)&lt;=0),"",IF(ISNUMBER(G87),H87,F87)))</f>
-        <v>91789.2300000001</v>
+        <v>38734.91</v>
       </c>
       <c r="D88" s="31" t="n">
         <f aca="false">IF(C88="","",ROUND(C88*$C$8,2))</f>
-        <v>2753.68</v>
+        <v>1162.05</v>
       </c>
       <c r="E88" s="31" t="n">
         <f aca="false">IF(C88="","",ROUND(C88*$C$9,2))</f>
-        <v>2753.68</v>
+        <v>1162.05</v>
       </c>
       <c r="F88" s="31" t="n">
         <f aca="false">IF(C88="","",C88+D88)</f>
-        <v>94542.9100000001</v>
+        <v>39896.96</v>
       </c>
       <c r="G88" s="32"/>
       <c r="H88" s="31" t="str">
@@ -8355,19 +8535,19 @@
       </c>
       <c r="C89" s="31" t="n">
         <f aca="false">IF(C88="","",IF(OR(IF(ISNUMBER(G88),H88,F88)&gt;=$C$7,IF(ISNUMBER(G88),H88,F88)&lt;=0),"",IF(ISNUMBER(G88),H88,F88)))</f>
-        <v>94542.9100000001</v>
+        <v>39896.96</v>
       </c>
       <c r="D89" s="31" t="n">
         <f aca="false">IF(C89="","",ROUND(C89*$C$8,2))</f>
-        <v>2836.29</v>
+        <v>1196.91</v>
       </c>
       <c r="E89" s="31" t="n">
         <f aca="false">IF(C89="","",ROUND(C89*$C$9,2))</f>
-        <v>2836.29</v>
+        <v>1196.91</v>
       </c>
       <c r="F89" s="31" t="n">
         <f aca="false">IF(C89="","",C89+D89)</f>
-        <v>97379.2</v>
+        <v>41093.87</v>
       </c>
       <c r="G89" s="32"/>
       <c r="H89" s="31" t="str">
@@ -8392,19 +8572,19 @@
       </c>
       <c r="C90" s="31" t="n">
         <f aca="false">IF(C89="","",IF(OR(IF(ISNUMBER(G89),H89,F89)&gt;=$C$7,IF(ISNUMBER(G89),H89,F89)&lt;=0),"",IF(ISNUMBER(G89),H89,F89)))</f>
-        <v>97379.2</v>
+        <v>41093.87</v>
       </c>
       <c r="D90" s="31" t="n">
         <f aca="false">IF(C90="","",ROUND(C90*$C$8,2))</f>
-        <v>2921.38</v>
+        <v>1232.82</v>
       </c>
       <c r="E90" s="31" t="n">
         <f aca="false">IF(C90="","",ROUND(C90*$C$9,2))</f>
-        <v>2921.38</v>
+        <v>1232.82</v>
       </c>
       <c r="F90" s="31" t="n">
         <f aca="false">IF(C90="","",C90+D90)</f>
-        <v>100300.58</v>
+        <v>42326.69</v>
       </c>
       <c r="G90" s="32"/>
       <c r="H90" s="31" t="str">
@@ -8419,29 +8599,29 @@
       <c r="K90" s="35"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="29" t="str">
+      <c r="A91" s="29" t="n">
         <f aca="false">IF(C91="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B91" s="30" t="str">
+        <v>79</v>
+      </c>
+      <c r="B91" s="30" t="n">
         <f aca="false">IF(C91="","",WORKDAY($C$5-1,A91,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C91" s="31" t="str">
+        <v>46408</v>
+      </c>
+      <c r="C91" s="31" t="n">
         <f aca="false">IF(C90="","",IF(OR(IF(ISNUMBER(G90),H90,F90)&gt;=$C$7,IF(ISNUMBER(G90),H90,F90)&lt;=0),"",IF(ISNUMBER(G90),H90,F90)))</f>
-        <v/>
-      </c>
-      <c r="D91" s="31" t="str">
+        <v>42326.69</v>
+      </c>
+      <c r="D91" s="31" t="n">
         <f aca="false">IF(C91="","",ROUND(C91*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E91" s="31" t="str">
+        <v>1269.8</v>
+      </c>
+      <c r="E91" s="31" t="n">
         <f aca="false">IF(C91="","",ROUND(C91*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F91" s="31" t="str">
+        <v>1269.8</v>
+      </c>
+      <c r="F91" s="31" t="n">
         <f aca="false">IF(C91="","",C91+D91)</f>
-        <v/>
+        <v>43596.49</v>
       </c>
       <c r="G91" s="32"/>
       <c r="H91" s="31" t="str">
@@ -8450,35 +8630,35 @@
       </c>
       <c r="I91" s="33" t="str">
         <f aca="false">IF(C91="","",IF(ISNUMBER(G91),IF(G91&lt;-E91,"Actual – Loss (limit breached)",IF(G91&lt;0,"Actual – Loss",IF(G91&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J91" s="34"/>
       <c r="K91" s="35"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="29" t="str">
+      <c r="A92" s="29" t="n">
         <f aca="false">IF(C92="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B92" s="30" t="str">
+        <v>80</v>
+      </c>
+      <c r="B92" s="30" t="n">
         <f aca="false">IF(C92="","",WORKDAY($C$5-1,A92,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C92" s="31" t="str">
+        <v>46409</v>
+      </c>
+      <c r="C92" s="31" t="n">
         <f aca="false">IF(C91="","",IF(OR(IF(ISNUMBER(G91),H91,F91)&gt;=$C$7,IF(ISNUMBER(G91),H91,F91)&lt;=0),"",IF(ISNUMBER(G91),H91,F91)))</f>
-        <v/>
-      </c>
-      <c r="D92" s="31" t="str">
+        <v>43596.49</v>
+      </c>
+      <c r="D92" s="31" t="n">
         <f aca="false">IF(C92="","",ROUND(C92*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E92" s="31" t="str">
+        <v>1307.89</v>
+      </c>
+      <c r="E92" s="31" t="n">
         <f aca="false">IF(C92="","",ROUND(C92*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F92" s="31" t="str">
+        <v>1307.89</v>
+      </c>
+      <c r="F92" s="31" t="n">
         <f aca="false">IF(C92="","",C92+D92)</f>
-        <v/>
+        <v>44904.38</v>
       </c>
       <c r="G92" s="32"/>
       <c r="H92" s="31" t="str">
@@ -8487,35 +8667,35 @@
       </c>
       <c r="I92" s="33" t="str">
         <f aca="false">IF(C92="","",IF(ISNUMBER(G92),IF(G92&lt;-E92,"Actual – Loss (limit breached)",IF(G92&lt;0,"Actual – Loss",IF(G92&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J92" s="34"/>
       <c r="K92" s="35"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="29" t="str">
+      <c r="A93" s="29" t="n">
         <f aca="false">IF(C93="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B93" s="30" t="str">
+        <v>81</v>
+      </c>
+      <c r="B93" s="30" t="n">
         <f aca="false">IF(C93="","",WORKDAY($C$5-1,A93,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C93" s="31" t="str">
+        <v>46412</v>
+      </c>
+      <c r="C93" s="31" t="n">
         <f aca="false">IF(C92="","",IF(OR(IF(ISNUMBER(G92),H92,F92)&gt;=$C$7,IF(ISNUMBER(G92),H92,F92)&lt;=0),"",IF(ISNUMBER(G92),H92,F92)))</f>
-        <v/>
-      </c>
-      <c r="D93" s="31" t="str">
+        <v>44904.38</v>
+      </c>
+      <c r="D93" s="31" t="n">
         <f aca="false">IF(C93="","",ROUND(C93*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E93" s="31" t="str">
+        <v>1347.13</v>
+      </c>
+      <c r="E93" s="31" t="n">
         <f aca="false">IF(C93="","",ROUND(C93*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F93" s="31" t="str">
+        <v>1347.13</v>
+      </c>
+      <c r="F93" s="31" t="n">
         <f aca="false">IF(C93="","",C93+D93)</f>
-        <v/>
+        <v>46251.51</v>
       </c>
       <c r="G93" s="32"/>
       <c r="H93" s="31" t="str">
@@ -8524,35 +8704,35 @@
       </c>
       <c r="I93" s="33" t="str">
         <f aca="false">IF(C93="","",IF(ISNUMBER(G93),IF(G93&lt;-E93,"Actual – Loss (limit breached)",IF(G93&lt;0,"Actual – Loss",IF(G93&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J93" s="34"/>
       <c r="K93" s="35"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="29" t="str">
+      <c r="A94" s="29" t="n">
         <f aca="false">IF(C94="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B94" s="30" t="str">
+        <v>82</v>
+      </c>
+      <c r="B94" s="30" t="n">
         <f aca="false">IF(C94="","",WORKDAY($C$5-1,A94,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C94" s="31" t="str">
+        <v>46414</v>
+      </c>
+      <c r="C94" s="31" t="n">
         <f aca="false">IF(C93="","",IF(OR(IF(ISNUMBER(G93),H93,F93)&gt;=$C$7,IF(ISNUMBER(G93),H93,F93)&lt;=0),"",IF(ISNUMBER(G93),H93,F93)))</f>
-        <v/>
-      </c>
-      <c r="D94" s="31" t="str">
+        <v>46251.51</v>
+      </c>
+      <c r="D94" s="31" t="n">
         <f aca="false">IF(C94="","",ROUND(C94*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E94" s="31" t="str">
+        <v>1387.55</v>
+      </c>
+      <c r="E94" s="31" t="n">
         <f aca="false">IF(C94="","",ROUND(C94*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F94" s="31" t="str">
+        <v>1387.55</v>
+      </c>
+      <c r="F94" s="31" t="n">
         <f aca="false">IF(C94="","",C94+D94)</f>
-        <v/>
+        <v>47639.06</v>
       </c>
       <c r="G94" s="32"/>
       <c r="H94" s="31" t="str">
@@ -8561,35 +8741,35 @@
       </c>
       <c r="I94" s="33" t="str">
         <f aca="false">IF(C94="","",IF(ISNUMBER(G94),IF(G94&lt;-E94,"Actual – Loss (limit breached)",IF(G94&lt;0,"Actual – Loss",IF(G94&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J94" s="34"/>
       <c r="K94" s="35"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="29" t="str">
+      <c r="A95" s="29" t="n">
         <f aca="false">IF(C95="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B95" s="30" t="str">
+        <v>83</v>
+      </c>
+      <c r="B95" s="30" t="n">
         <f aca="false">IF(C95="","",WORKDAY($C$5-1,A95,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C95" s="31" t="str">
+        <v>46415</v>
+      </c>
+      <c r="C95" s="31" t="n">
         <f aca="false">IF(C94="","",IF(OR(IF(ISNUMBER(G94),H94,F94)&gt;=$C$7,IF(ISNUMBER(G94),H94,F94)&lt;=0),"",IF(ISNUMBER(G94),H94,F94)))</f>
-        <v/>
-      </c>
-      <c r="D95" s="31" t="str">
+        <v>47639.06</v>
+      </c>
+      <c r="D95" s="31" t="n">
         <f aca="false">IF(C95="","",ROUND(C95*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E95" s="31" t="str">
+        <v>1429.17</v>
+      </c>
+      <c r="E95" s="31" t="n">
         <f aca="false">IF(C95="","",ROUND(C95*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F95" s="31" t="str">
+        <v>1429.17</v>
+      </c>
+      <c r="F95" s="31" t="n">
         <f aca="false">IF(C95="","",C95+D95)</f>
-        <v/>
+        <v>49068.23</v>
       </c>
       <c r="G95" s="32"/>
       <c r="H95" s="31" t="str">
@@ -8598,35 +8778,35 @@
       </c>
       <c r="I95" s="33" t="str">
         <f aca="false">IF(C95="","",IF(ISNUMBER(G95),IF(G95&lt;-E95,"Actual – Loss (limit breached)",IF(G95&lt;0,"Actual – Loss",IF(G95&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J95" s="34"/>
       <c r="K95" s="35"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="29" t="str">
+      <c r="A96" s="29" t="n">
         <f aca="false">IF(C96="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B96" s="30" t="str">
+        <v>84</v>
+      </c>
+      <c r="B96" s="30" t="n">
         <f aca="false">IF(C96="","",WORKDAY($C$5-1,A96,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C96" s="31" t="str">
+        <v>46416</v>
+      </c>
+      <c r="C96" s="31" t="n">
         <f aca="false">IF(C95="","",IF(OR(IF(ISNUMBER(G95),H95,F95)&gt;=$C$7,IF(ISNUMBER(G95),H95,F95)&lt;=0),"",IF(ISNUMBER(G95),H95,F95)))</f>
-        <v/>
-      </c>
-      <c r="D96" s="31" t="str">
+        <v>49068.23</v>
+      </c>
+      <c r="D96" s="31" t="n">
         <f aca="false">IF(C96="","",ROUND(C96*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E96" s="31" t="str">
+        <v>1472.05</v>
+      </c>
+      <c r="E96" s="31" t="n">
         <f aca="false">IF(C96="","",ROUND(C96*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F96" s="31" t="str">
+        <v>1472.05</v>
+      </c>
+      <c r="F96" s="31" t="n">
         <f aca="false">IF(C96="","",C96+D96)</f>
-        <v/>
+        <v>50540.28</v>
       </c>
       <c r="G96" s="32"/>
       <c r="H96" s="31" t="str">
@@ -8635,35 +8815,35 @@
       </c>
       <c r="I96" s="33" t="str">
         <f aca="false">IF(C96="","",IF(ISNUMBER(G96),IF(G96&lt;-E96,"Actual – Loss (limit breached)",IF(G96&lt;0,"Actual – Loss",IF(G96&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J96" s="34"/>
       <c r="K96" s="35"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="29" t="str">
+      <c r="A97" s="29" t="n">
         <f aca="false">IF(C97="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B97" s="30" t="str">
+        <v>85</v>
+      </c>
+      <c r="B97" s="30" t="n">
         <f aca="false">IF(C97="","",WORKDAY($C$5-1,A97,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C97" s="31" t="str">
+        <v>46419</v>
+      </c>
+      <c r="C97" s="31" t="n">
         <f aca="false">IF(C96="","",IF(OR(IF(ISNUMBER(G96),H96,F96)&gt;=$C$7,IF(ISNUMBER(G96),H96,F96)&lt;=0),"",IF(ISNUMBER(G96),H96,F96)))</f>
-        <v/>
-      </c>
-      <c r="D97" s="31" t="str">
+        <v>50540.28</v>
+      </c>
+      <c r="D97" s="31" t="n">
         <f aca="false">IF(C97="","",ROUND(C97*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E97" s="31" t="str">
+        <v>1516.21</v>
+      </c>
+      <c r="E97" s="31" t="n">
         <f aca="false">IF(C97="","",ROUND(C97*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F97" s="31" t="str">
+        <v>1516.21</v>
+      </c>
+      <c r="F97" s="31" t="n">
         <f aca="false">IF(C97="","",C97+D97)</f>
-        <v/>
+        <v>52056.49</v>
       </c>
       <c r="G97" s="32"/>
       <c r="H97" s="31" t="str">
@@ -8672,35 +8852,35 @@
       </c>
       <c r="I97" s="33" t="str">
         <f aca="false">IF(C97="","",IF(ISNUMBER(G97),IF(G97&lt;-E97,"Actual – Loss (limit breached)",IF(G97&lt;0,"Actual – Loss",IF(G97&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J97" s="34"/>
       <c r="K97" s="35"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="29" t="str">
+      <c r="A98" s="29" t="n">
         <f aca="false">IF(C98="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B98" s="30" t="str">
+        <v>86</v>
+      </c>
+      <c r="B98" s="30" t="n">
         <f aca="false">IF(C98="","",WORKDAY($C$5-1,A98,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C98" s="31" t="str">
+        <v>46420</v>
+      </c>
+      <c r="C98" s="31" t="n">
         <f aca="false">IF(C97="","",IF(OR(IF(ISNUMBER(G97),H97,F97)&gt;=$C$7,IF(ISNUMBER(G97),H97,F97)&lt;=0),"",IF(ISNUMBER(G97),H97,F97)))</f>
-        <v/>
-      </c>
-      <c r="D98" s="31" t="str">
+        <v>52056.49</v>
+      </c>
+      <c r="D98" s="31" t="n">
         <f aca="false">IF(C98="","",ROUND(C98*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E98" s="31" t="str">
+        <v>1561.69</v>
+      </c>
+      <c r="E98" s="31" t="n">
         <f aca="false">IF(C98="","",ROUND(C98*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F98" s="31" t="str">
+        <v>1561.69</v>
+      </c>
+      <c r="F98" s="31" t="n">
         <f aca="false">IF(C98="","",C98+D98)</f>
-        <v/>
+        <v>53618.18</v>
       </c>
       <c r="G98" s="32"/>
       <c r="H98" s="31" t="str">
@@ -8709,35 +8889,35 @@
       </c>
       <c r="I98" s="33" t="str">
         <f aca="false">IF(C98="","",IF(ISNUMBER(G98),IF(G98&lt;-E98,"Actual – Loss (limit breached)",IF(G98&lt;0,"Actual – Loss",IF(G98&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J98" s="34"/>
       <c r="K98" s="35"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="29" t="str">
+      <c r="A99" s="29" t="n">
         <f aca="false">IF(C99="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B99" s="30" t="str">
+        <v>87</v>
+      </c>
+      <c r="B99" s="30" t="n">
         <f aca="false">IF(C99="","",WORKDAY($C$5-1,A99,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C99" s="31" t="str">
+        <v>46421</v>
+      </c>
+      <c r="C99" s="31" t="n">
         <f aca="false">IF(C98="","",IF(OR(IF(ISNUMBER(G98),H98,F98)&gt;=$C$7,IF(ISNUMBER(G98),H98,F98)&lt;=0),"",IF(ISNUMBER(G98),H98,F98)))</f>
-        <v/>
-      </c>
-      <c r="D99" s="31" t="str">
+        <v>53618.18</v>
+      </c>
+      <c r="D99" s="31" t="n">
         <f aca="false">IF(C99="","",ROUND(C99*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E99" s="31" t="str">
+        <v>1608.55</v>
+      </c>
+      <c r="E99" s="31" t="n">
         <f aca="false">IF(C99="","",ROUND(C99*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F99" s="31" t="str">
+        <v>1608.55</v>
+      </c>
+      <c r="F99" s="31" t="n">
         <f aca="false">IF(C99="","",C99+D99)</f>
-        <v/>
+        <v>55226.73</v>
       </c>
       <c r="G99" s="32"/>
       <c r="H99" s="31" t="str">
@@ -8746,35 +8926,35 @@
       </c>
       <c r="I99" s="33" t="str">
         <f aca="false">IF(C99="","",IF(ISNUMBER(G99),IF(G99&lt;-E99,"Actual – Loss (limit breached)",IF(G99&lt;0,"Actual – Loss",IF(G99&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J99" s="34"/>
       <c r="K99" s="35"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="29" t="str">
+      <c r="A100" s="29" t="n">
         <f aca="false">IF(C100="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B100" s="30" t="str">
+        <v>88</v>
+      </c>
+      <c r="B100" s="30" t="n">
         <f aca="false">IF(C100="","",WORKDAY($C$5-1,A100,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C100" s="31" t="str">
+        <v>46422</v>
+      </c>
+      <c r="C100" s="31" t="n">
         <f aca="false">IF(C99="","",IF(OR(IF(ISNUMBER(G99),H99,F99)&gt;=$C$7,IF(ISNUMBER(G99),H99,F99)&lt;=0),"",IF(ISNUMBER(G99),H99,F99)))</f>
-        <v/>
-      </c>
-      <c r="D100" s="31" t="str">
+        <v>55226.73</v>
+      </c>
+      <c r="D100" s="31" t="n">
         <f aca="false">IF(C100="","",ROUND(C100*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E100" s="31" t="str">
+        <v>1656.8</v>
+      </c>
+      <c r="E100" s="31" t="n">
         <f aca="false">IF(C100="","",ROUND(C100*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F100" s="31" t="str">
+        <v>1656.8</v>
+      </c>
+      <c r="F100" s="31" t="n">
         <f aca="false">IF(C100="","",C100+D100)</f>
-        <v/>
+        <v>56883.53</v>
       </c>
       <c r="G100" s="32"/>
       <c r="H100" s="31" t="str">
@@ -8783,35 +8963,35 @@
       </c>
       <c r="I100" s="33" t="str">
         <f aca="false">IF(C100="","",IF(ISNUMBER(G100),IF(G100&lt;-E100,"Actual – Loss (limit breached)",IF(G100&lt;0,"Actual – Loss",IF(G100&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J100" s="34"/>
       <c r="K100" s="35"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="29" t="str">
+      <c r="A101" s="29" t="n">
         <f aca="false">IF(C101="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B101" s="30" t="str">
+        <v>89</v>
+      </c>
+      <c r="B101" s="30" t="n">
         <f aca="false">IF(C101="","",WORKDAY($C$5-1,A101,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C101" s="31" t="str">
+        <v>46423</v>
+      </c>
+      <c r="C101" s="31" t="n">
         <f aca="false">IF(C100="","",IF(OR(IF(ISNUMBER(G100),H100,F100)&gt;=$C$7,IF(ISNUMBER(G100),H100,F100)&lt;=0),"",IF(ISNUMBER(G100),H100,F100)))</f>
-        <v/>
-      </c>
-      <c r="D101" s="31" t="str">
+        <v>56883.53</v>
+      </c>
+      <c r="D101" s="31" t="n">
         <f aca="false">IF(C101="","",ROUND(C101*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E101" s="31" t="str">
+        <v>1706.51</v>
+      </c>
+      <c r="E101" s="31" t="n">
         <f aca="false">IF(C101="","",ROUND(C101*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F101" s="31" t="str">
+        <v>1706.51</v>
+      </c>
+      <c r="F101" s="31" t="n">
         <f aca="false">IF(C101="","",C101+D101)</f>
-        <v/>
+        <v>58590.04</v>
       </c>
       <c r="G101" s="32"/>
       <c r="H101" s="31" t="str">
@@ -8820,35 +9000,35 @@
       </c>
       <c r="I101" s="33" t="str">
         <f aca="false">IF(C101="","",IF(ISNUMBER(G101),IF(G101&lt;-E101,"Actual – Loss (limit breached)",IF(G101&lt;0,"Actual – Loss",IF(G101&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J101" s="34"/>
       <c r="K101" s="35"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="29" t="str">
+      <c r="A102" s="29" t="n">
         <f aca="false">IF(C102="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B102" s="30" t="str">
+        <v>90</v>
+      </c>
+      <c r="B102" s="30" t="n">
         <f aca="false">IF(C102="","",WORKDAY($C$5-1,A102,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C102" s="31" t="str">
+        <v>46426</v>
+      </c>
+      <c r="C102" s="31" t="n">
         <f aca="false">IF(C101="","",IF(OR(IF(ISNUMBER(G101),H101,F101)&gt;=$C$7,IF(ISNUMBER(G101),H101,F101)&lt;=0),"",IF(ISNUMBER(G101),H101,F101)))</f>
-        <v/>
-      </c>
-      <c r="D102" s="31" t="str">
+        <v>58590.04</v>
+      </c>
+      <c r="D102" s="31" t="n">
         <f aca="false">IF(C102="","",ROUND(C102*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E102" s="31" t="str">
+        <v>1757.7</v>
+      </c>
+      <c r="E102" s="31" t="n">
         <f aca="false">IF(C102="","",ROUND(C102*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F102" s="31" t="str">
+        <v>1757.7</v>
+      </c>
+      <c r="F102" s="31" t="n">
         <f aca="false">IF(C102="","",C102+D102)</f>
-        <v/>
+        <v>60347.74</v>
       </c>
       <c r="G102" s="32"/>
       <c r="H102" s="31" t="str">
@@ -8857,35 +9037,35 @@
       </c>
       <c r="I102" s="33" t="str">
         <f aca="false">IF(C102="","",IF(ISNUMBER(G102),IF(G102&lt;-E102,"Actual – Loss (limit breached)",IF(G102&lt;0,"Actual – Loss",IF(G102&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J102" s="34"/>
       <c r="K102" s="35"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="29" t="str">
+      <c r="A103" s="29" t="n">
         <f aca="false">IF(C103="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B103" s="30" t="str">
+        <v>91</v>
+      </c>
+      <c r="B103" s="30" t="n">
         <f aca="false">IF(C103="","",WORKDAY($C$5-1,A103,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C103" s="31" t="str">
+        <v>46427</v>
+      </c>
+      <c r="C103" s="31" t="n">
         <f aca="false">IF(C102="","",IF(OR(IF(ISNUMBER(G102),H102,F102)&gt;=$C$7,IF(ISNUMBER(G102),H102,F102)&lt;=0),"",IF(ISNUMBER(G102),H102,F102)))</f>
-        <v/>
-      </c>
-      <c r="D103" s="31" t="str">
+        <v>60347.74</v>
+      </c>
+      <c r="D103" s="31" t="n">
         <f aca="false">IF(C103="","",ROUND(C103*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E103" s="31" t="str">
+        <v>1810.43</v>
+      </c>
+      <c r="E103" s="31" t="n">
         <f aca="false">IF(C103="","",ROUND(C103*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F103" s="31" t="str">
+        <v>1810.43</v>
+      </c>
+      <c r="F103" s="31" t="n">
         <f aca="false">IF(C103="","",C103+D103)</f>
-        <v/>
+        <v>62158.17</v>
       </c>
       <c r="G103" s="32"/>
       <c r="H103" s="31" t="str">
@@ -8894,35 +9074,35 @@
       </c>
       <c r="I103" s="33" t="str">
         <f aca="false">IF(C103="","",IF(ISNUMBER(G103),IF(G103&lt;-E103,"Actual – Loss (limit breached)",IF(G103&lt;0,"Actual – Loss",IF(G103&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J103" s="34"/>
       <c r="K103" s="35"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="29" t="str">
+      <c r="A104" s="29" t="n">
         <f aca="false">IF(C104="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B104" s="30" t="str">
+        <v>92</v>
+      </c>
+      <c r="B104" s="30" t="n">
         <f aca="false">IF(C104="","",WORKDAY($C$5-1,A104,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C104" s="31" t="str">
+        <v>46428</v>
+      </c>
+      <c r="C104" s="31" t="n">
         <f aca="false">IF(C103="","",IF(OR(IF(ISNUMBER(G103),H103,F103)&gt;=$C$7,IF(ISNUMBER(G103),H103,F103)&lt;=0),"",IF(ISNUMBER(G103),H103,F103)))</f>
-        <v/>
-      </c>
-      <c r="D104" s="31" t="str">
+        <v>62158.17</v>
+      </c>
+      <c r="D104" s="31" t="n">
         <f aca="false">IF(C104="","",ROUND(C104*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E104" s="31" t="str">
+        <v>1864.75</v>
+      </c>
+      <c r="E104" s="31" t="n">
         <f aca="false">IF(C104="","",ROUND(C104*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F104" s="31" t="str">
+        <v>1864.75</v>
+      </c>
+      <c r="F104" s="31" t="n">
         <f aca="false">IF(C104="","",C104+D104)</f>
-        <v/>
+        <v>64022.92</v>
       </c>
       <c r="G104" s="32"/>
       <c r="H104" s="31" t="str">
@@ -8931,35 +9111,35 @@
       </c>
       <c r="I104" s="33" t="str">
         <f aca="false">IF(C104="","",IF(ISNUMBER(G104),IF(G104&lt;-E104,"Actual – Loss (limit breached)",IF(G104&lt;0,"Actual – Loss",IF(G104&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J104" s="34"/>
       <c r="K104" s="35"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="29" t="str">
+      <c r="A105" s="29" t="n">
         <f aca="false">IF(C105="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B105" s="30" t="str">
+        <v>93</v>
+      </c>
+      <c r="B105" s="30" t="n">
         <f aca="false">IF(C105="","",WORKDAY($C$5-1,A105,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C105" s="31" t="str">
+        <v>46429</v>
+      </c>
+      <c r="C105" s="31" t="n">
         <f aca="false">IF(C104="","",IF(OR(IF(ISNUMBER(G104),H104,F104)&gt;=$C$7,IF(ISNUMBER(G104),H104,F104)&lt;=0),"",IF(ISNUMBER(G104),H104,F104)))</f>
-        <v/>
-      </c>
-      <c r="D105" s="31" t="str">
+        <v>64022.92</v>
+      </c>
+      <c r="D105" s="31" t="n">
         <f aca="false">IF(C105="","",ROUND(C105*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E105" s="31" t="str">
+        <v>1920.69</v>
+      </c>
+      <c r="E105" s="31" t="n">
         <f aca="false">IF(C105="","",ROUND(C105*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F105" s="31" t="str">
+        <v>1920.69</v>
+      </c>
+      <c r="F105" s="31" t="n">
         <f aca="false">IF(C105="","",C105+D105)</f>
-        <v/>
+        <v>65943.61</v>
       </c>
       <c r="G105" s="32"/>
       <c r="H105" s="31" t="str">
@@ -8968,35 +9148,35 @@
       </c>
       <c r="I105" s="33" t="str">
         <f aca="false">IF(C105="","",IF(ISNUMBER(G105),IF(G105&lt;-E105,"Actual – Loss (limit breached)",IF(G105&lt;0,"Actual – Loss",IF(G105&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J105" s="34"/>
       <c r="K105" s="35"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="29" t="str">
+      <c r="A106" s="29" t="n">
         <f aca="false">IF(C106="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B106" s="30" t="str">
+        <v>94</v>
+      </c>
+      <c r="B106" s="30" t="n">
         <f aca="false">IF(C106="","",WORKDAY($C$5-1,A106,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C106" s="31" t="str">
+        <v>46430</v>
+      </c>
+      <c r="C106" s="31" t="n">
         <f aca="false">IF(C105="","",IF(OR(IF(ISNUMBER(G105),H105,F105)&gt;=$C$7,IF(ISNUMBER(G105),H105,F105)&lt;=0),"",IF(ISNUMBER(G105),H105,F105)))</f>
-        <v/>
-      </c>
-      <c r="D106" s="31" t="str">
+        <v>65943.61</v>
+      </c>
+      <c r="D106" s="31" t="n">
         <f aca="false">IF(C106="","",ROUND(C106*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E106" s="31" t="str">
+        <v>1978.31</v>
+      </c>
+      <c r="E106" s="31" t="n">
         <f aca="false">IF(C106="","",ROUND(C106*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F106" s="31" t="str">
+        <v>1978.31</v>
+      </c>
+      <c r="F106" s="31" t="n">
         <f aca="false">IF(C106="","",C106+D106)</f>
-        <v/>
+        <v>67921.92</v>
       </c>
       <c r="G106" s="32"/>
       <c r="H106" s="31" t="str">
@@ -9005,35 +9185,35 @@
       </c>
       <c r="I106" s="33" t="str">
         <f aca="false">IF(C106="","",IF(ISNUMBER(G106),IF(G106&lt;-E106,"Actual – Loss (limit breached)",IF(G106&lt;0,"Actual – Loss",IF(G106&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J106" s="34"/>
       <c r="K106" s="35"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="29" t="str">
+      <c r="A107" s="29" t="n">
         <f aca="false">IF(C107="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B107" s="30" t="str">
+        <v>95</v>
+      </c>
+      <c r="B107" s="30" t="n">
         <f aca="false">IF(C107="","",WORKDAY($C$5-1,A107,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C107" s="31" t="str">
+        <v>46433</v>
+      </c>
+      <c r="C107" s="31" t="n">
         <f aca="false">IF(C106="","",IF(OR(IF(ISNUMBER(G106),H106,F106)&gt;=$C$7,IF(ISNUMBER(G106),H106,F106)&lt;=0),"",IF(ISNUMBER(G106),H106,F106)))</f>
-        <v/>
-      </c>
-      <c r="D107" s="31" t="str">
+        <v>67921.92</v>
+      </c>
+      <c r="D107" s="31" t="n">
         <f aca="false">IF(C107="","",ROUND(C107*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E107" s="31" t="str">
+        <v>2037.66</v>
+      </c>
+      <c r="E107" s="31" t="n">
         <f aca="false">IF(C107="","",ROUND(C107*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F107" s="31" t="str">
+        <v>2037.66</v>
+      </c>
+      <c r="F107" s="31" t="n">
         <f aca="false">IF(C107="","",C107+D107)</f>
-        <v/>
+        <v>69959.58</v>
       </c>
       <c r="G107" s="32"/>
       <c r="H107" s="31" t="str">
@@ -9042,35 +9222,35 @@
       </c>
       <c r="I107" s="33" t="str">
         <f aca="false">IF(C107="","",IF(ISNUMBER(G107),IF(G107&lt;-E107,"Actual – Loss (limit breached)",IF(G107&lt;0,"Actual – Loss",IF(G107&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J107" s="34"/>
       <c r="K107" s="35"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="29" t="str">
+      <c r="A108" s="29" t="n">
         <f aca="false">IF(C108="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B108" s="30" t="str">
+        <v>96</v>
+      </c>
+      <c r="B108" s="30" t="n">
         <f aca="false">IF(C108="","",WORKDAY($C$5-1,A108,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C108" s="31" t="str">
+        <v>46434</v>
+      </c>
+      <c r="C108" s="31" t="n">
         <f aca="false">IF(C107="","",IF(OR(IF(ISNUMBER(G107),H107,F107)&gt;=$C$7,IF(ISNUMBER(G107),H107,F107)&lt;=0),"",IF(ISNUMBER(G107),H107,F107)))</f>
-        <v/>
-      </c>
-      <c r="D108" s="31" t="str">
+        <v>69959.58</v>
+      </c>
+      <c r="D108" s="31" t="n">
         <f aca="false">IF(C108="","",ROUND(C108*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E108" s="31" t="str">
+        <v>2098.79</v>
+      </c>
+      <c r="E108" s="31" t="n">
         <f aca="false">IF(C108="","",ROUND(C108*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F108" s="31" t="str">
+        <v>2098.79</v>
+      </c>
+      <c r="F108" s="31" t="n">
         <f aca="false">IF(C108="","",C108+D108)</f>
-        <v/>
+        <v>72058.37</v>
       </c>
       <c r="G108" s="32"/>
       <c r="H108" s="31" t="str">
@@ -9079,35 +9259,35 @@
       </c>
       <c r="I108" s="33" t="str">
         <f aca="false">IF(C108="","",IF(ISNUMBER(G108),IF(G108&lt;-E108,"Actual – Loss (limit breached)",IF(G108&lt;0,"Actual – Loss",IF(G108&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J108" s="34"/>
       <c r="K108" s="35"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="29" t="str">
+      <c r="A109" s="29" t="n">
         <f aca="false">IF(C109="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B109" s="30" t="str">
+        <v>97</v>
+      </c>
+      <c r="B109" s="30" t="n">
         <f aca="false">IF(C109="","",WORKDAY($C$5-1,A109,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C109" s="31" t="str">
+        <v>46435</v>
+      </c>
+      <c r="C109" s="31" t="n">
         <f aca="false">IF(C108="","",IF(OR(IF(ISNUMBER(G108),H108,F108)&gt;=$C$7,IF(ISNUMBER(G108),H108,F108)&lt;=0),"",IF(ISNUMBER(G108),H108,F108)))</f>
-        <v/>
-      </c>
-      <c r="D109" s="31" t="str">
+        <v>72058.37</v>
+      </c>
+      <c r="D109" s="31" t="n">
         <f aca="false">IF(C109="","",ROUND(C109*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E109" s="31" t="str">
+        <v>2161.75</v>
+      </c>
+      <c r="E109" s="31" t="n">
         <f aca="false">IF(C109="","",ROUND(C109*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F109" s="31" t="str">
+        <v>2161.75</v>
+      </c>
+      <c r="F109" s="31" t="n">
         <f aca="false">IF(C109="","",C109+D109)</f>
-        <v/>
+        <v>74220.12</v>
       </c>
       <c r="G109" s="32"/>
       <c r="H109" s="31" t="str">
@@ -9116,35 +9296,35 @@
       </c>
       <c r="I109" s="33" t="str">
         <f aca="false">IF(C109="","",IF(ISNUMBER(G109),IF(G109&lt;-E109,"Actual – Loss (limit breached)",IF(G109&lt;0,"Actual – Loss",IF(G109&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J109" s="34"/>
       <c r="K109" s="35"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="29" t="str">
+      <c r="A110" s="29" t="n">
         <f aca="false">IF(C110="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B110" s="30" t="str">
+        <v>98</v>
+      </c>
+      <c r="B110" s="30" t="n">
         <f aca="false">IF(C110="","",WORKDAY($C$5-1,A110,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C110" s="31" t="str">
+        <v>46436</v>
+      </c>
+      <c r="C110" s="31" t="n">
         <f aca="false">IF(C109="","",IF(OR(IF(ISNUMBER(G109),H109,F109)&gt;=$C$7,IF(ISNUMBER(G109),H109,F109)&lt;=0),"",IF(ISNUMBER(G109),H109,F109)))</f>
-        <v/>
-      </c>
-      <c r="D110" s="31" t="str">
+        <v>74220.12</v>
+      </c>
+      <c r="D110" s="31" t="n">
         <f aca="false">IF(C110="","",ROUND(C110*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E110" s="31" t="str">
+        <v>2226.6</v>
+      </c>
+      <c r="E110" s="31" t="n">
         <f aca="false">IF(C110="","",ROUND(C110*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F110" s="31" t="str">
+        <v>2226.6</v>
+      </c>
+      <c r="F110" s="31" t="n">
         <f aca="false">IF(C110="","",C110+D110)</f>
-        <v/>
+        <v>76446.72</v>
       </c>
       <c r="G110" s="32"/>
       <c r="H110" s="31" t="str">
@@ -9153,35 +9333,35 @@
       </c>
       <c r="I110" s="33" t="str">
         <f aca="false">IF(C110="","",IF(ISNUMBER(G110),IF(G110&lt;-E110,"Actual – Loss (limit breached)",IF(G110&lt;0,"Actual – Loss",IF(G110&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J110" s="34"/>
       <c r="K110" s="35"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="29" t="str">
+      <c r="A111" s="29" t="n">
         <f aca="false">IF(C111="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B111" s="30" t="str">
+        <v>99</v>
+      </c>
+      <c r="B111" s="30" t="n">
         <f aca="false">IF(C111="","",WORKDAY($C$5-1,A111,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C111" s="31" t="str">
+        <v>46437</v>
+      </c>
+      <c r="C111" s="31" t="n">
         <f aca="false">IF(C110="","",IF(OR(IF(ISNUMBER(G110),H110,F110)&gt;=$C$7,IF(ISNUMBER(G110),H110,F110)&lt;=0),"",IF(ISNUMBER(G110),H110,F110)))</f>
-        <v/>
-      </c>
-      <c r="D111" s="31" t="str">
+        <v>76446.72</v>
+      </c>
+      <c r="D111" s="31" t="n">
         <f aca="false">IF(C111="","",ROUND(C111*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E111" s="31" t="str">
+        <v>2293.4</v>
+      </c>
+      <c r="E111" s="31" t="n">
         <f aca="false">IF(C111="","",ROUND(C111*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F111" s="31" t="str">
+        <v>2293.4</v>
+      </c>
+      <c r="F111" s="31" t="n">
         <f aca="false">IF(C111="","",C111+D111)</f>
-        <v/>
+        <v>78740.12</v>
       </c>
       <c r="G111" s="32"/>
       <c r="H111" s="31" t="str">
@@ -9190,35 +9370,35 @@
       </c>
       <c r="I111" s="33" t="str">
         <f aca="false">IF(C111="","",IF(ISNUMBER(G111),IF(G111&lt;-E111,"Actual – Loss (limit breached)",IF(G111&lt;0,"Actual – Loss",IF(G111&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J111" s="34"/>
       <c r="K111" s="35"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="29" t="str">
+      <c r="A112" s="29" t="n">
         <f aca="false">IF(C112="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B112" s="30" t="str">
+        <v>100</v>
+      </c>
+      <c r="B112" s="30" t="n">
         <f aca="false">IF(C112="","",WORKDAY($C$5-1,A112,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C112" s="31" t="str">
+        <v>46440</v>
+      </c>
+      <c r="C112" s="31" t="n">
         <f aca="false">IF(C111="","",IF(OR(IF(ISNUMBER(G111),H111,F111)&gt;=$C$7,IF(ISNUMBER(G111),H111,F111)&lt;=0),"",IF(ISNUMBER(G111),H111,F111)))</f>
-        <v/>
-      </c>
-      <c r="D112" s="31" t="str">
+        <v>78740.12</v>
+      </c>
+      <c r="D112" s="31" t="n">
         <f aca="false">IF(C112="","",ROUND(C112*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E112" s="31" t="str">
+        <v>2362.2</v>
+      </c>
+      <c r="E112" s="31" t="n">
         <f aca="false">IF(C112="","",ROUND(C112*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F112" s="31" t="str">
+        <v>2362.2</v>
+      </c>
+      <c r="F112" s="31" t="n">
         <f aca="false">IF(C112="","",C112+D112)</f>
-        <v/>
+        <v>81102.32</v>
       </c>
       <c r="G112" s="32"/>
       <c r="H112" s="31" t="str">
@@ -9227,35 +9407,35 @@
       </c>
       <c r="I112" s="33" t="str">
         <f aca="false">IF(C112="","",IF(ISNUMBER(G112),IF(G112&lt;-E112,"Actual – Loss (limit breached)",IF(G112&lt;0,"Actual – Loss",IF(G112&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J112" s="34"/>
       <c r="K112" s="35"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="29" t="str">
+      <c r="A113" s="29" t="n">
         <f aca="false">IF(C113="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B113" s="30" t="str">
+        <v>101</v>
+      </c>
+      <c r="B113" s="30" t="n">
         <f aca="false">IF(C113="","",WORKDAY($C$5-1,A113,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C113" s="31" t="str">
+        <v>46441</v>
+      </c>
+      <c r="C113" s="31" t="n">
         <f aca="false">IF(C112="","",IF(OR(IF(ISNUMBER(G112),H112,F112)&gt;=$C$7,IF(ISNUMBER(G112),H112,F112)&lt;=0),"",IF(ISNUMBER(G112),H112,F112)))</f>
-        <v/>
-      </c>
-      <c r="D113" s="31" t="str">
+        <v>81102.32</v>
+      </c>
+      <c r="D113" s="31" t="n">
         <f aca="false">IF(C113="","",ROUND(C113*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E113" s="31" t="str">
+        <v>2433.07</v>
+      </c>
+      <c r="E113" s="31" t="n">
         <f aca="false">IF(C113="","",ROUND(C113*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F113" s="31" t="str">
+        <v>2433.07</v>
+      </c>
+      <c r="F113" s="31" t="n">
         <f aca="false">IF(C113="","",C113+D113)</f>
-        <v/>
+        <v>83535.39</v>
       </c>
       <c r="G113" s="32"/>
       <c r="H113" s="31" t="str">
@@ -9264,35 +9444,35 @@
       </c>
       <c r="I113" s="33" t="str">
         <f aca="false">IF(C113="","",IF(ISNUMBER(G113),IF(G113&lt;-E113,"Actual – Loss (limit breached)",IF(G113&lt;0,"Actual – Loss",IF(G113&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J113" s="34"/>
       <c r="K113" s="35"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="29" t="str">
+      <c r="A114" s="29" t="n">
         <f aca="false">IF(C114="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B114" s="30" t="str">
+        <v>102</v>
+      </c>
+      <c r="B114" s="30" t="n">
         <f aca="false">IF(C114="","",WORKDAY($C$5-1,A114,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C114" s="31" t="str">
+        <v>46442</v>
+      </c>
+      <c r="C114" s="31" t="n">
         <f aca="false">IF(C113="","",IF(OR(IF(ISNUMBER(G113),H113,F113)&gt;=$C$7,IF(ISNUMBER(G113),H113,F113)&lt;=0),"",IF(ISNUMBER(G113),H113,F113)))</f>
-        <v/>
-      </c>
-      <c r="D114" s="31" t="str">
+        <v>83535.39</v>
+      </c>
+      <c r="D114" s="31" t="n">
         <f aca="false">IF(C114="","",ROUND(C114*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E114" s="31" t="str">
+        <v>2506.06</v>
+      </c>
+      <c r="E114" s="31" t="n">
         <f aca="false">IF(C114="","",ROUND(C114*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F114" s="31" t="str">
+        <v>2506.06</v>
+      </c>
+      <c r="F114" s="31" t="n">
         <f aca="false">IF(C114="","",C114+D114)</f>
-        <v/>
+        <v>86041.45</v>
       </c>
       <c r="G114" s="32"/>
       <c r="H114" s="31" t="str">
@@ -9301,35 +9481,35 @@
       </c>
       <c r="I114" s="33" t="str">
         <f aca="false">IF(C114="","",IF(ISNUMBER(G114),IF(G114&lt;-E114,"Actual – Loss (limit breached)",IF(G114&lt;0,"Actual – Loss",IF(G114&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J114" s="34"/>
       <c r="K114" s="35"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="29" t="str">
+      <c r="A115" s="29" t="n">
         <f aca="false">IF(C115="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B115" s="30" t="str">
+        <v>103</v>
+      </c>
+      <c r="B115" s="30" t="n">
         <f aca="false">IF(C115="","",WORKDAY($C$5-1,A115,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C115" s="31" t="str">
+        <v>46443</v>
+      </c>
+      <c r="C115" s="31" t="n">
         <f aca="false">IF(C114="","",IF(OR(IF(ISNUMBER(G114),H114,F114)&gt;=$C$7,IF(ISNUMBER(G114),H114,F114)&lt;=0),"",IF(ISNUMBER(G114),H114,F114)))</f>
-        <v/>
-      </c>
-      <c r="D115" s="31" t="str">
+        <v>86041.45</v>
+      </c>
+      <c r="D115" s="31" t="n">
         <f aca="false">IF(C115="","",ROUND(C115*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E115" s="31" t="str">
+        <v>2581.24</v>
+      </c>
+      <c r="E115" s="31" t="n">
         <f aca="false">IF(C115="","",ROUND(C115*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F115" s="31" t="str">
+        <v>2581.24</v>
+      </c>
+      <c r="F115" s="31" t="n">
         <f aca="false">IF(C115="","",C115+D115)</f>
-        <v/>
+        <v>88622.69</v>
       </c>
       <c r="G115" s="32"/>
       <c r="H115" s="31" t="str">
@@ -9338,35 +9518,35 @@
       </c>
       <c r="I115" s="33" t="str">
         <f aca="false">IF(C115="","",IF(ISNUMBER(G115),IF(G115&lt;-E115,"Actual – Loss (limit breached)",IF(G115&lt;0,"Actual – Loss",IF(G115&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J115" s="34"/>
       <c r="K115" s="35"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="29" t="str">
+      <c r="A116" s="29" t="n">
         <f aca="false">IF(C116="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B116" s="30" t="str">
+        <v>104</v>
+      </c>
+      <c r="B116" s="30" t="n">
         <f aca="false">IF(C116="","",WORKDAY($C$5-1,A116,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C116" s="31" t="str">
+        <v>46444</v>
+      </c>
+      <c r="C116" s="31" t="n">
         <f aca="false">IF(C115="","",IF(OR(IF(ISNUMBER(G115),H115,F115)&gt;=$C$7,IF(ISNUMBER(G115),H115,F115)&lt;=0),"",IF(ISNUMBER(G115),H115,F115)))</f>
-        <v/>
-      </c>
-      <c r="D116" s="31" t="str">
+        <v>88622.69</v>
+      </c>
+      <c r="D116" s="31" t="n">
         <f aca="false">IF(C116="","",ROUND(C116*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E116" s="31" t="str">
+        <v>2658.68</v>
+      </c>
+      <c r="E116" s="31" t="n">
         <f aca="false">IF(C116="","",ROUND(C116*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F116" s="31" t="str">
+        <v>2658.68</v>
+      </c>
+      <c r="F116" s="31" t="n">
         <f aca="false">IF(C116="","",C116+D116)</f>
-        <v/>
+        <v>91281.37</v>
       </c>
       <c r="G116" s="32"/>
       <c r="H116" s="31" t="str">
@@ -9375,35 +9555,35 @@
       </c>
       <c r="I116" s="33" t="str">
         <f aca="false">IF(C116="","",IF(ISNUMBER(G116),IF(G116&lt;-E116,"Actual – Loss (limit breached)",IF(G116&lt;0,"Actual – Loss",IF(G116&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J116" s="34"/>
       <c r="K116" s="35"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="29" t="str">
+      <c r="A117" s="29" t="n">
         <f aca="false">IF(C117="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B117" s="30" t="str">
+        <v>105</v>
+      </c>
+      <c r="B117" s="30" t="n">
         <f aca="false">IF(C117="","",WORKDAY($C$5-1,A117,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C117" s="31" t="str">
+        <v>46447</v>
+      </c>
+      <c r="C117" s="31" t="n">
         <f aca="false">IF(C116="","",IF(OR(IF(ISNUMBER(G116),H116,F116)&gt;=$C$7,IF(ISNUMBER(G116),H116,F116)&lt;=0),"",IF(ISNUMBER(G116),H116,F116)))</f>
-        <v/>
-      </c>
-      <c r="D117" s="31" t="str">
+        <v>91281.37</v>
+      </c>
+      <c r="D117" s="31" t="n">
         <f aca="false">IF(C117="","",ROUND(C117*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E117" s="31" t="str">
+        <v>2738.44</v>
+      </c>
+      <c r="E117" s="31" t="n">
         <f aca="false">IF(C117="","",ROUND(C117*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F117" s="31" t="str">
+        <v>2738.44</v>
+      </c>
+      <c r="F117" s="31" t="n">
         <f aca="false">IF(C117="","",C117+D117)</f>
-        <v/>
+        <v>94019.81</v>
       </c>
       <c r="G117" s="32"/>
       <c r="H117" s="31" t="str">
@@ -9412,35 +9592,35 @@
       </c>
       <c r="I117" s="33" t="str">
         <f aca="false">IF(C117="","",IF(ISNUMBER(G117),IF(G117&lt;-E117,"Actual – Loss (limit breached)",IF(G117&lt;0,"Actual – Loss",IF(G117&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J117" s="34"/>
       <c r="K117" s="35"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="29" t="str">
+      <c r="A118" s="29" t="n">
         <f aca="false">IF(C118="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B118" s="30" t="str">
+        <v>106</v>
+      </c>
+      <c r="B118" s="30" t="n">
         <f aca="false">IF(C118="","",WORKDAY($C$5-1,A118,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C118" s="31" t="str">
+        <v>46448</v>
+      </c>
+      <c r="C118" s="31" t="n">
         <f aca="false">IF(C117="","",IF(OR(IF(ISNUMBER(G117),H117,F117)&gt;=$C$7,IF(ISNUMBER(G117),H117,F117)&lt;=0),"",IF(ISNUMBER(G117),H117,F117)))</f>
-        <v/>
-      </c>
-      <c r="D118" s="31" t="str">
+        <v>94019.81</v>
+      </c>
+      <c r="D118" s="31" t="n">
         <f aca="false">IF(C118="","",ROUND(C118*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E118" s="31" t="str">
+        <v>2820.59</v>
+      </c>
+      <c r="E118" s="31" t="n">
         <f aca="false">IF(C118="","",ROUND(C118*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F118" s="31" t="str">
+        <v>2820.59</v>
+      </c>
+      <c r="F118" s="31" t="n">
         <f aca="false">IF(C118="","",C118+D118)</f>
-        <v/>
+        <v>96840.4</v>
       </c>
       <c r="G118" s="32"/>
       <c r="H118" s="31" t="str">
@@ -9449,35 +9629,35 @@
       </c>
       <c r="I118" s="33" t="str">
         <f aca="false">IF(C118="","",IF(ISNUMBER(G118),IF(G118&lt;-E118,"Actual – Loss (limit breached)",IF(G118&lt;0,"Actual – Loss",IF(G118&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J118" s="34"/>
       <c r="K118" s="35"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="29" t="str">
+      <c r="A119" s="29" t="n">
         <f aca="false">IF(C119="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B119" s="30" t="str">
+        <v>107</v>
+      </c>
+      <c r="B119" s="30" t="n">
         <f aca="false">IF(C119="","",WORKDAY($C$5-1,A119,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C119" s="31" t="str">
+        <v>46449</v>
+      </c>
+      <c r="C119" s="31" t="n">
         <f aca="false">IF(C118="","",IF(OR(IF(ISNUMBER(G118),H118,F118)&gt;=$C$7,IF(ISNUMBER(G118),H118,F118)&lt;=0),"",IF(ISNUMBER(G118),H118,F118)))</f>
-        <v/>
-      </c>
-      <c r="D119" s="31" t="str">
+        <v>96840.4</v>
+      </c>
+      <c r="D119" s="31" t="n">
         <f aca="false">IF(C119="","",ROUND(C119*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E119" s="31" t="str">
+        <v>2905.21</v>
+      </c>
+      <c r="E119" s="31" t="n">
         <f aca="false">IF(C119="","",ROUND(C119*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F119" s="31" t="str">
+        <v>2905.21</v>
+      </c>
+      <c r="F119" s="31" t="n">
         <f aca="false">IF(C119="","",C119+D119)</f>
-        <v/>
+        <v>99745.61</v>
       </c>
       <c r="G119" s="32"/>
       <c r="H119" s="31" t="str">
@@ -9486,35 +9666,35 @@
       </c>
       <c r="I119" s="33" t="str">
         <f aca="false">IF(C119="","",IF(ISNUMBER(G119),IF(G119&lt;-E119,"Actual – Loss (limit breached)",IF(G119&lt;0,"Actual – Loss",IF(G119&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J119" s="34"/>
       <c r="K119" s="35"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="29" t="str">
+      <c r="A120" s="29" t="n">
         <f aca="false">IF(C120="","",ROW()-12)</f>
-        <v/>
-      </c>
-      <c r="B120" s="30" t="str">
+        <v>108</v>
+      </c>
+      <c r="B120" s="30" t="n">
         <f aca="false">IF(C120="","",WORKDAY($C$5-1,A120,'NSE Holidays'!$A$5:$A$64))</f>
-        <v/>
-      </c>
-      <c r="C120" s="31" t="str">
+        <v>46450</v>
+      </c>
+      <c r="C120" s="31" t="n">
         <f aca="false">IF(C119="","",IF(OR(IF(ISNUMBER(G119),H119,F119)&gt;=$C$7,IF(ISNUMBER(G119),H119,F119)&lt;=0),"",IF(ISNUMBER(G119),H119,F119)))</f>
-        <v/>
-      </c>
-      <c r="D120" s="31" t="str">
+        <v>99745.61</v>
+      </c>
+      <c r="D120" s="31" t="n">
         <f aca="false">IF(C120="","",ROUND(C120*$C$8,2))</f>
-        <v/>
-      </c>
-      <c r="E120" s="31" t="str">
+        <v>2992.37</v>
+      </c>
+      <c r="E120" s="31" t="n">
         <f aca="false">IF(C120="","",ROUND(C120*$C$9,2))</f>
-        <v/>
-      </c>
-      <c r="F120" s="31" t="str">
+        <v>2992.37</v>
+      </c>
+      <c r="F120" s="31" t="n">
         <f aca="false">IF(C120="","",C120+D120)</f>
-        <v/>
+        <v>102737.98</v>
       </c>
       <c r="G120" s="32"/>
       <c r="H120" s="31" t="str">
@@ -9523,7 +9703,7 @@
       </c>
       <c r="I120" s="33" t="str">
         <f aca="false">IF(C120="","",IF(ISNUMBER(G120),IF(G120&lt;-E120,"Actual – Loss (limit breached)",IF(G120&lt;0,"Actual – Loss",IF(G120&gt;0,"Actual – Profit","Actual – No trade"))),"Projection"))</f>
-        <v/>
+        <v>Projection</v>
       </c>
       <c r="J120" s="34"/>
       <c r="K120" s="35"/>
@@ -24099,7 +24279,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30708037-DD56-4CBC-A46E-B63AFD9017C0}</x14:id>
+          <x14:id>{675722B3-1132-46A9-B034-19BEA030BF91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24130,7 +24310,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{30708037-DD56-4CBC-A46E-B63AFD9017C0}">
+          <x14:cfRule type="dataBar" id="{675722B3-1132-46A9-B034-19BEA030BF91}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -25006,7 +25186,7 @@
       </c>
       <c r="C2" s="31" t="n">
         <f aca="false">IF(Tracker!$C13="",NA(),IF(A2&lt;Tracker!$J$6,NA(),IF(A2=Tracker!$J$6,Tracker!$H13,Tracker!$F13)))</f>
-        <v>10300</v>
+        <v>4346.6</v>
       </c>
       <c r="D2" s="31" t="n">
         <f aca="false">IF(Tracker!$C13="",NA(),Tracker!$C$7)</f>
@@ -25031,7 +25211,7 @@
       </c>
       <c r="C3" s="31" t="n">
         <f aca="false">IF(Tracker!$C14="",NA(),IF(A3&lt;Tracker!$J$6,NA(),IF(A3=Tracker!$J$6,Tracker!$H14,Tracker!$F14)))</f>
-        <v>10609</v>
+        <v>4477</v>
       </c>
       <c r="D3" s="31" t="n">
         <f aca="false">IF(Tracker!$C14="",NA(),Tracker!$C$7)</f>
@@ -25056,7 +25236,7 @@
       </c>
       <c r="C4" s="31" t="n">
         <f aca="false">IF(Tracker!$C15="",NA(),IF(A4&lt;Tracker!$J$6,NA(),IF(A4=Tracker!$J$6,Tracker!$H15,Tracker!$F15)))</f>
-        <v>10927.27</v>
+        <v>4611.31</v>
       </c>
       <c r="D4" s="31" t="n">
         <f aca="false">IF(Tracker!$C15="",NA(),Tracker!$C$7)</f>
@@ -25081,7 +25261,7 @@
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">IF(Tracker!$C16="",NA(),IF(A5&lt;Tracker!$J$6,NA(),IF(A5=Tracker!$J$6,Tracker!$H16,Tracker!$F16)))</f>
-        <v>11255.09</v>
+        <v>4749.65</v>
       </c>
       <c r="D5" s="31" t="n">
         <f aca="false">IF(Tracker!$C16="",NA(),Tracker!$C$7)</f>
@@ -25106,7 +25286,7 @@
       </c>
       <c r="C6" s="31" t="n">
         <f aca="false">IF(Tracker!$C17="",NA(),IF(A6&lt;Tracker!$J$6,NA(),IF(A6=Tracker!$J$6,Tracker!$H17,Tracker!$F17)))</f>
-        <v>11592.74</v>
+        <v>4892.14</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">IF(Tracker!$C17="",NA(),Tracker!$C$7)</f>
@@ -25131,7 +25311,7 @@
       </c>
       <c r="C7" s="31" t="n">
         <f aca="false">IF(Tracker!$C18="",NA(),IF(A7&lt;Tracker!$J$6,NA(),IF(A7=Tracker!$J$6,Tracker!$H18,Tracker!$F18)))</f>
-        <v>11940.52</v>
+        <v>5038.9</v>
       </c>
       <c r="D7" s="31" t="n">
         <f aca="false">IF(Tracker!$C18="",NA(),Tracker!$C$7)</f>
@@ -25156,7 +25336,7 @@
       </c>
       <c r="C8" s="31" t="n">
         <f aca="false">IF(Tracker!$C19="",NA(),IF(A8&lt;Tracker!$J$6,NA(),IF(A8=Tracker!$J$6,Tracker!$H19,Tracker!$F19)))</f>
-        <v>12298.74</v>
+        <v>5190.07</v>
       </c>
       <c r="D8" s="31" t="n">
         <f aca="false">IF(Tracker!$C19="",NA(),Tracker!$C$7)</f>
@@ -25181,7 +25361,7 @@
       </c>
       <c r="C9" s="31" t="n">
         <f aca="false">IF(Tracker!$C20="",NA(),IF(A9&lt;Tracker!$J$6,NA(),IF(A9=Tracker!$J$6,Tracker!$H20,Tracker!$F20)))</f>
-        <v>12667.7</v>
+        <v>5345.77</v>
       </c>
       <c r="D9" s="31" t="n">
         <f aca="false">IF(Tracker!$C20="",NA(),Tracker!$C$7)</f>
@@ -25206,7 +25386,7 @@
       </c>
       <c r="C10" s="31" t="n">
         <f aca="false">IF(Tracker!$C21="",NA(),IF(A10&lt;Tracker!$J$6,NA(),IF(A10=Tracker!$J$6,Tracker!$H21,Tracker!$F21)))</f>
-        <v>13047.73</v>
+        <v>5506.14</v>
       </c>
       <c r="D10" s="31" t="n">
         <f aca="false">IF(Tracker!$C21="",NA(),Tracker!$C$7)</f>
@@ -25231,7 +25411,7 @@
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">IF(Tracker!$C22="",NA(),IF(A11&lt;Tracker!$J$6,NA(),IF(A11=Tracker!$J$6,Tracker!$H22,Tracker!$F22)))</f>
-        <v>13439.16</v>
+        <v>5671.32</v>
       </c>
       <c r="D11" s="31" t="n">
         <f aca="false">IF(Tracker!$C22="",NA(),Tracker!$C$7)</f>
@@ -25256,7 +25436,7 @@
       </c>
       <c r="C12" s="31" t="n">
         <f aca="false">IF(Tracker!$C23="",NA(),IF(A12&lt;Tracker!$J$6,NA(),IF(A12=Tracker!$J$6,Tracker!$H23,Tracker!$F23)))</f>
-        <v>13842.33</v>
+        <v>5841.46</v>
       </c>
       <c r="D12" s="31" t="n">
         <f aca="false">IF(Tracker!$C23="",NA(),Tracker!$C$7)</f>
@@ -25281,7 +25461,7 @@
       </c>
       <c r="C13" s="31" t="n">
         <f aca="false">IF(Tracker!$C24="",NA(),IF(A13&lt;Tracker!$J$6,NA(),IF(A13=Tracker!$J$6,Tracker!$H24,Tracker!$F24)))</f>
-        <v>14257.6</v>
+        <v>6016.7</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">IF(Tracker!$C24="",NA(),Tracker!$C$7)</f>
@@ -25306,7 +25486,7 @@
       </c>
       <c r="C14" s="31" t="n">
         <f aca="false">IF(Tracker!$C25="",NA(),IF(A14&lt;Tracker!$J$6,NA(),IF(A14=Tracker!$J$6,Tracker!$H25,Tracker!$F25)))</f>
-        <v>14685.33</v>
+        <v>6197.2</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">IF(Tracker!$C25="",NA(),Tracker!$C$7)</f>
@@ -25331,7 +25511,7 @@
       </c>
       <c r="C15" s="31" t="n">
         <f aca="false">IF(Tracker!$C26="",NA(),IF(A15&lt;Tracker!$J$6,NA(),IF(A15=Tracker!$J$6,Tracker!$H26,Tracker!$F26)))</f>
-        <v>15125.89</v>
+        <v>6383.12</v>
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">IF(Tracker!$C26="",NA(),Tracker!$C$7)</f>
@@ -25356,7 +25536,7 @@
       </c>
       <c r="C16" s="31" t="n">
         <f aca="false">IF(Tracker!$C27="",NA(),IF(A16&lt;Tracker!$J$6,NA(),IF(A16=Tracker!$J$6,Tracker!$H27,Tracker!$F27)))</f>
-        <v>15579.67</v>
+        <v>6574.61</v>
       </c>
       <c r="D16" s="31" t="n">
         <f aca="false">IF(Tracker!$C27="",NA(),Tracker!$C$7)</f>
@@ -25381,7 +25561,7 @@
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">IF(Tracker!$C28="",NA(),IF(A17&lt;Tracker!$J$6,NA(),IF(A17=Tracker!$J$6,Tracker!$H28,Tracker!$F28)))</f>
-        <v>16047.06</v>
+        <v>6771.85</v>
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">IF(Tracker!$C28="",NA(),Tracker!$C$7)</f>
@@ -25406,7 +25586,7 @@
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IF(Tracker!$C29="",NA(),IF(A18&lt;Tracker!$J$6,NA(),IF(A18=Tracker!$J$6,Tracker!$H29,Tracker!$F29)))</f>
-        <v>16528.47</v>
+        <v>6975.01</v>
       </c>
       <c r="D18" s="31" t="n">
         <f aca="false">IF(Tracker!$C29="",NA(),Tracker!$C$7)</f>
@@ -25431,7 +25611,7 @@
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">IF(Tracker!$C30="",NA(),IF(A19&lt;Tracker!$J$6,NA(),IF(A19=Tracker!$J$6,Tracker!$H30,Tracker!$F30)))</f>
-        <v>17024.32</v>
+        <v>7184.26</v>
       </c>
       <c r="D19" s="31" t="n">
         <f aca="false">IF(Tracker!$C30="",NA(),Tracker!$C$7)</f>
@@ -25456,7 +25636,7 @@
       </c>
       <c r="C20" s="31" t="n">
         <f aca="false">IF(Tracker!$C31="",NA(),IF(A20&lt;Tracker!$J$6,NA(),IF(A20=Tracker!$J$6,Tracker!$H31,Tracker!$F31)))</f>
-        <v>17535.05</v>
+        <v>7399.79</v>
       </c>
       <c r="D20" s="31" t="n">
         <f aca="false">IF(Tracker!$C31="",NA(),Tracker!$C$7)</f>
@@ -25481,7 +25661,7 @@
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">IF(Tracker!$C32="",NA(),IF(A21&lt;Tracker!$J$6,NA(),IF(A21=Tracker!$J$6,Tracker!$H32,Tracker!$F32)))</f>
-        <v>18061.1</v>
+        <v>7621.78</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">IF(Tracker!$C32="",NA(),Tracker!$C$7)</f>
@@ -25506,7 +25686,7 @@
       </c>
       <c r="C22" s="31" t="n">
         <f aca="false">IF(Tracker!$C33="",NA(),IF(A22&lt;Tracker!$J$6,NA(),IF(A22=Tracker!$J$6,Tracker!$H33,Tracker!$F33)))</f>
-        <v>18602.93</v>
+        <v>7850.43</v>
       </c>
       <c r="D22" s="31" t="n">
         <f aca="false">IF(Tracker!$C33="",NA(),Tracker!$C$7)</f>
@@ -25531,7 +25711,7 @@
       </c>
       <c r="C23" s="31" t="n">
         <f aca="false">IF(Tracker!$C34="",NA(),IF(A23&lt;Tracker!$J$6,NA(),IF(A23=Tracker!$J$6,Tracker!$H34,Tracker!$F34)))</f>
-        <v>19161.02</v>
+        <v>8085.94</v>
       </c>
       <c r="D23" s="31" t="n">
         <f aca="false">IF(Tracker!$C34="",NA(),Tracker!$C$7)</f>
@@ -25556,7 +25736,7 @@
       </c>
       <c r="C24" s="31" t="n">
         <f aca="false">IF(Tracker!$C35="",NA(),IF(A24&lt;Tracker!$J$6,NA(),IF(A24=Tracker!$J$6,Tracker!$H35,Tracker!$F35)))</f>
-        <v>19735.85</v>
+        <v>8328.52</v>
       </c>
       <c r="D24" s="31" t="n">
         <f aca="false">IF(Tracker!$C35="",NA(),Tracker!$C$7)</f>
@@ -25581,7 +25761,7 @@
       </c>
       <c r="C25" s="31" t="n">
         <f aca="false">IF(Tracker!$C36="",NA(),IF(A25&lt;Tracker!$J$6,NA(),IF(A25=Tracker!$J$6,Tracker!$H36,Tracker!$F36)))</f>
-        <v>20327.93</v>
+        <v>8578.38</v>
       </c>
       <c r="D25" s="31" t="n">
         <f aca="false">IF(Tracker!$C36="",NA(),Tracker!$C$7)</f>
@@ -25606,7 +25786,7 @@
       </c>
       <c r="C26" s="31" t="n">
         <f aca="false">IF(Tracker!$C37="",NA(),IF(A26&lt;Tracker!$J$6,NA(),IF(A26=Tracker!$J$6,Tracker!$H37,Tracker!$F37)))</f>
-        <v>20937.77</v>
+        <v>8835.73</v>
       </c>
       <c r="D26" s="31" t="n">
         <f aca="false">IF(Tracker!$C37="",NA(),Tracker!$C$7)</f>
@@ -25631,7 +25811,7 @@
       </c>
       <c r="C27" s="31" t="n">
         <f aca="false">IF(Tracker!$C38="",NA(),IF(A27&lt;Tracker!$J$6,NA(),IF(A27=Tracker!$J$6,Tracker!$H38,Tracker!$F38)))</f>
-        <v>21565.9</v>
+        <v>9100.8</v>
       </c>
       <c r="D27" s="31" t="n">
         <f aca="false">IF(Tracker!$C38="",NA(),Tracker!$C$7)</f>
@@ -25656,7 +25836,7 @@
       </c>
       <c r="C28" s="31" t="n">
         <f aca="false">IF(Tracker!$C39="",NA(),IF(A28&lt;Tracker!$J$6,NA(),IF(A28=Tracker!$J$6,Tracker!$H39,Tracker!$F39)))</f>
-        <v>22212.88</v>
+        <v>9373.82</v>
       </c>
       <c r="D28" s="31" t="n">
         <f aca="false">IF(Tracker!$C39="",NA(),Tracker!$C$7)</f>
@@ -25681,7 +25861,7 @@
       </c>
       <c r="C29" s="31" t="n">
         <f aca="false">IF(Tracker!$C40="",NA(),IF(A29&lt;Tracker!$J$6,NA(),IF(A29=Tracker!$J$6,Tracker!$H40,Tracker!$F40)))</f>
-        <v>22879.27</v>
+        <v>9655.03</v>
       </c>
       <c r="D29" s="31" t="n">
         <f aca="false">IF(Tracker!$C40="",NA(),Tracker!$C$7)</f>
@@ -25706,7 +25886,7 @@
       </c>
       <c r="C30" s="31" t="n">
         <f aca="false">IF(Tracker!$C41="",NA(),IF(A30&lt;Tracker!$J$6,NA(),IF(A30=Tracker!$J$6,Tracker!$H41,Tracker!$F41)))</f>
-        <v>23565.65</v>
+        <v>9944.68</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">IF(Tracker!$C41="",NA(),Tracker!$C$7)</f>
@@ -25731,7 +25911,7 @@
       </c>
       <c r="C31" s="31" t="n">
         <f aca="false">IF(Tracker!$C42="",NA(),IF(A31&lt;Tracker!$J$6,NA(),IF(A31=Tracker!$J$6,Tracker!$H42,Tracker!$F42)))</f>
-        <v>24272.62</v>
+        <v>10243.02</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">IF(Tracker!$C42="",NA(),Tracker!$C$7)</f>
@@ -25756,7 +25936,7 @@
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">IF(Tracker!$C43="",NA(),IF(A32&lt;Tracker!$J$6,NA(),IF(A32=Tracker!$J$6,Tracker!$H43,Tracker!$F43)))</f>
-        <v>25000.8</v>
+        <v>10550.31</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">IF(Tracker!$C43="",NA(),Tracker!$C$7)</f>
@@ -25781,7 +25961,7 @@
       </c>
       <c r="C33" s="31" t="n">
         <f aca="false">IF(Tracker!$C44="",NA(),IF(A33&lt;Tracker!$J$6,NA(),IF(A33=Tracker!$J$6,Tracker!$H44,Tracker!$F44)))</f>
-        <v>25750.82</v>
+        <v>10866.82</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">IF(Tracker!$C44="",NA(),Tracker!$C$7)</f>
@@ -25806,7 +25986,7 @@
       </c>
       <c r="C34" s="31" t="n">
         <f aca="false">IF(Tracker!$C45="",NA(),IF(A34&lt;Tracker!$J$6,NA(),IF(A34=Tracker!$J$6,Tracker!$H45,Tracker!$F45)))</f>
-        <v>26523.34</v>
+        <v>11192.82</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">IF(Tracker!$C45="",NA(),Tracker!$C$7)</f>
@@ -25831,7 +26011,7 @@
       </c>
       <c r="C35" s="31" t="n">
         <f aca="false">IF(Tracker!$C46="",NA(),IF(A35&lt;Tracker!$J$6,NA(),IF(A35=Tracker!$J$6,Tracker!$H46,Tracker!$F46)))</f>
-        <v>27319.04</v>
+        <v>11528.6</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">IF(Tracker!$C46="",NA(),Tracker!$C$7)</f>
@@ -25856,7 +26036,7 @@
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">IF(Tracker!$C47="",NA(),IF(A36&lt;Tracker!$J$6,NA(),IF(A36=Tracker!$J$6,Tracker!$H47,Tracker!$F47)))</f>
-        <v>28138.61</v>
+        <v>11874.46</v>
       </c>
       <c r="D36" s="31" t="n">
         <f aca="false">IF(Tracker!$C47="",NA(),Tracker!$C$7)</f>
@@ -25881,7 +26061,7 @@
       </c>
       <c r="C37" s="31" t="n">
         <f aca="false">IF(Tracker!$C48="",NA(),IF(A37&lt;Tracker!$J$6,NA(),IF(A37=Tracker!$J$6,Tracker!$H48,Tracker!$F48)))</f>
-        <v>28982.77</v>
+        <v>12230.69</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">IF(Tracker!$C48="",NA(),Tracker!$C$7)</f>
@@ -25906,7 +26086,7 @@
       </c>
       <c r="C38" s="31" t="n">
         <f aca="false">IF(Tracker!$C49="",NA(),IF(A38&lt;Tracker!$J$6,NA(),IF(A38=Tracker!$J$6,Tracker!$H49,Tracker!$F49)))</f>
-        <v>29852.25</v>
+        <v>12597.61</v>
       </c>
       <c r="D38" s="31" t="n">
         <f aca="false">IF(Tracker!$C49="",NA(),Tracker!$C$7)</f>
@@ -25931,7 +26111,7 @@
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">IF(Tracker!$C50="",NA(),IF(A39&lt;Tracker!$J$6,NA(),IF(A39=Tracker!$J$6,Tracker!$H50,Tracker!$F50)))</f>
-        <v>30747.82</v>
+        <v>12975.54</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">IF(Tracker!$C50="",NA(),Tracker!$C$7)</f>
@@ -25956,7 +26136,7 @@
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">IF(Tracker!$C51="",NA(),IF(A40&lt;Tracker!$J$6,NA(),IF(A40=Tracker!$J$6,Tracker!$H51,Tracker!$F51)))</f>
-        <v>31670.25</v>
+        <v>13364.81</v>
       </c>
       <c r="D40" s="31" t="n">
         <f aca="false">IF(Tracker!$C51="",NA(),Tracker!$C$7)</f>
@@ -25981,7 +26161,7 @@
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">IF(Tracker!$C52="",NA(),IF(A41&lt;Tracker!$J$6,NA(),IF(A41=Tracker!$J$6,Tracker!$H52,Tracker!$F52)))</f>
-        <v>32620.36</v>
+        <v>13765.75</v>
       </c>
       <c r="D41" s="31" t="n">
         <f aca="false">IF(Tracker!$C52="",NA(),Tracker!$C$7)</f>
@@ -26006,7 +26186,7 @@
       </c>
       <c r="C42" s="31" t="n">
         <f aca="false">IF(Tracker!$C53="",NA(),IF(A42&lt;Tracker!$J$6,NA(),IF(A42=Tracker!$J$6,Tracker!$H53,Tracker!$F53)))</f>
-        <v>33598.97</v>
+        <v>14178.72</v>
       </c>
       <c r="D42" s="31" t="n">
         <f aca="false">IF(Tracker!$C53="",NA(),Tracker!$C$7)</f>
@@ -26031,7 +26211,7 @@
       </c>
       <c r="C43" s="31" t="n">
         <f aca="false">IF(Tracker!$C54="",NA(),IF(A43&lt;Tracker!$J$6,NA(),IF(A43=Tracker!$J$6,Tracker!$H54,Tracker!$F54)))</f>
-        <v>34606.94</v>
+        <v>14604.08</v>
       </c>
       <c r="D43" s="31" t="n">
         <f aca="false">IF(Tracker!$C54="",NA(),Tracker!$C$7)</f>
@@ -26056,7 +26236,7 @@
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">IF(Tracker!$C55="",NA(),IF(A44&lt;Tracker!$J$6,NA(),IF(A44=Tracker!$J$6,Tracker!$H55,Tracker!$F55)))</f>
-        <v>35645.15</v>
+        <v>15042.2</v>
       </c>
       <c r="D44" s="31" t="n">
         <f aca="false">IF(Tracker!$C55="",NA(),Tracker!$C$7)</f>
@@ -26081,7 +26261,7 @@
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">IF(Tracker!$C56="",NA(),IF(A45&lt;Tracker!$J$6,NA(),IF(A45=Tracker!$J$6,Tracker!$H56,Tracker!$F56)))</f>
-        <v>36714.5</v>
+        <v>15493.47</v>
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">IF(Tracker!$C56="",NA(),Tracker!$C$7)</f>
@@ -26106,7 +26286,7 @@
       </c>
       <c r="C46" s="31" t="n">
         <f aca="false">IF(Tracker!$C57="",NA(),IF(A46&lt;Tracker!$J$6,NA(),IF(A46=Tracker!$J$6,Tracker!$H57,Tracker!$F57)))</f>
-        <v>37815.94</v>
+        <v>15958.27</v>
       </c>
       <c r="D46" s="31" t="n">
         <f aca="false">IF(Tracker!$C57="",NA(),Tracker!$C$7)</f>
@@ -26131,7 +26311,7 @@
       </c>
       <c r="C47" s="31" t="n">
         <f aca="false">IF(Tracker!$C58="",NA(),IF(A47&lt;Tracker!$J$6,NA(),IF(A47=Tracker!$J$6,Tracker!$H58,Tracker!$F58)))</f>
-        <v>38950.42</v>
+        <v>16437.02</v>
       </c>
       <c r="D47" s="31" t="n">
         <f aca="false">IF(Tracker!$C58="",NA(),Tracker!$C$7)</f>
@@ -26156,7 +26336,7 @@
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">IF(Tracker!$C59="",NA(),IF(A48&lt;Tracker!$J$6,NA(),IF(A48=Tracker!$J$6,Tracker!$H59,Tracker!$F59)))</f>
-        <v>40118.93</v>
+        <v>16930.13</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">IF(Tracker!$C59="",NA(),Tracker!$C$7)</f>
@@ -26181,7 +26361,7 @@
       </c>
       <c r="C49" s="31" t="n">
         <f aca="false">IF(Tracker!$C60="",NA(),IF(A49&lt;Tracker!$J$6,NA(),IF(A49=Tracker!$J$6,Tracker!$H60,Tracker!$F60)))</f>
-        <v>41322.5</v>
+        <v>17438.03</v>
       </c>
       <c r="D49" s="31" t="n">
         <f aca="false">IF(Tracker!$C60="",NA(),Tracker!$C$7)</f>
@@ -26206,7 +26386,7 @@
       </c>
       <c r="C50" s="31" t="n">
         <f aca="false">IF(Tracker!$C61="",NA(),IF(A50&lt;Tracker!$J$6,NA(),IF(A50=Tracker!$J$6,Tracker!$H61,Tracker!$F61)))</f>
-        <v>42562.18</v>
+        <v>17961.17</v>
       </c>
       <c r="D50" s="31" t="n">
         <f aca="false">IF(Tracker!$C61="",NA(),Tracker!$C$7)</f>
@@ -26231,7 +26411,7 @@
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">IF(Tracker!$C62="",NA(),IF(A51&lt;Tracker!$J$6,NA(),IF(A51=Tracker!$J$6,Tracker!$H62,Tracker!$F62)))</f>
-        <v>43839.05</v>
+        <v>18500.01</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">IF(Tracker!$C62="",NA(),Tracker!$C$7)</f>
@@ -26256,7 +26436,7 @@
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">IF(Tracker!$C63="",NA(),IF(A52&lt;Tracker!$J$6,NA(),IF(A52=Tracker!$J$6,Tracker!$H63,Tracker!$F63)))</f>
-        <v>45154.22</v>
+        <v>19055.01</v>
       </c>
       <c r="D52" s="31" t="n">
         <f aca="false">IF(Tracker!$C63="",NA(),Tracker!$C$7)</f>
@@ -26281,7 +26461,7 @@
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">IF(Tracker!$C64="",NA(),IF(A53&lt;Tracker!$J$6,NA(),IF(A53=Tracker!$J$6,Tracker!$H64,Tracker!$F64)))</f>
-        <v>46508.85</v>
+        <v>19626.66</v>
       </c>
       <c r="D53" s="31" t="n">
         <f aca="false">IF(Tracker!$C64="",NA(),Tracker!$C$7)</f>
@@ -26306,7 +26486,7 @@
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">IF(Tracker!$C65="",NA(),IF(A54&lt;Tracker!$J$6,NA(),IF(A54=Tracker!$J$6,Tracker!$H65,Tracker!$F65)))</f>
-        <v>47904.12</v>
+        <v>20215.46</v>
       </c>
       <c r="D54" s="31" t="n">
         <f aca="false">IF(Tracker!$C65="",NA(),Tracker!$C$7)</f>
@@ -26331,7 +26511,7 @@
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">IF(Tracker!$C66="",NA(),IF(A55&lt;Tracker!$J$6,NA(),IF(A55=Tracker!$J$6,Tracker!$H66,Tracker!$F66)))</f>
-        <v>49341.24</v>
+        <v>20821.92</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">IF(Tracker!$C66="",NA(),Tracker!$C$7)</f>
@@ -26356,7 +26536,7 @@
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">IF(Tracker!$C67="",NA(),IF(A56&lt;Tracker!$J$6,NA(),IF(A56=Tracker!$J$6,Tracker!$H67,Tracker!$F67)))</f>
-        <v>50821.48</v>
+        <v>21446.58</v>
       </c>
       <c r="D56" s="31" t="n">
         <f aca="false">IF(Tracker!$C67="",NA(),Tracker!$C$7)</f>
@@ -26381,7 +26561,7 @@
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">IF(Tracker!$C68="",NA(),IF(A57&lt;Tracker!$J$6,NA(),IF(A57=Tracker!$J$6,Tracker!$H68,Tracker!$F68)))</f>
-        <v>52346.12</v>
+        <v>22089.98</v>
       </c>
       <c r="D57" s="31" t="n">
         <f aca="false">IF(Tracker!$C68="",NA(),Tracker!$C$7)</f>
@@ -26406,7 +26586,7 @@
       </c>
       <c r="C58" s="31" t="n">
         <f aca="false">IF(Tracker!$C69="",NA(),IF(A58&lt;Tracker!$J$6,NA(),IF(A58=Tracker!$J$6,Tracker!$H69,Tracker!$F69)))</f>
-        <v>53916.5</v>
+        <v>22752.68</v>
       </c>
       <c r="D58" s="31" t="n">
         <f aca="false">IF(Tracker!$C69="",NA(),Tracker!$C$7)</f>
@@ -26431,7 +26611,7 @@
       </c>
       <c r="C59" s="31" t="n">
         <f aca="false">IF(Tracker!$C70="",NA(),IF(A59&lt;Tracker!$J$6,NA(),IF(A59=Tracker!$J$6,Tracker!$H70,Tracker!$F70)))</f>
-        <v>55534</v>
+        <v>23435.26</v>
       </c>
       <c r="D59" s="31" t="n">
         <f aca="false">IF(Tracker!$C70="",NA(),Tracker!$C$7)</f>
@@ -26456,7 +26636,7 @@
       </c>
       <c r="C60" s="31" t="n">
         <f aca="false">IF(Tracker!$C71="",NA(),IF(A60&lt;Tracker!$J$6,NA(),IF(A60=Tracker!$J$6,Tracker!$H71,Tracker!$F71)))</f>
-        <v>57200.02</v>
+        <v>24138.32</v>
       </c>
       <c r="D60" s="31" t="n">
         <f aca="false">IF(Tracker!$C71="",NA(),Tracker!$C$7)</f>
@@ -26481,7 +26661,7 @@
       </c>
       <c r="C61" s="31" t="n">
         <f aca="false">IF(Tracker!$C72="",NA(),IF(A61&lt;Tracker!$J$6,NA(),IF(A61=Tracker!$J$6,Tracker!$H72,Tracker!$F72)))</f>
-        <v>58916.02</v>
+        <v>24862.47</v>
       </c>
       <c r="D61" s="31" t="n">
         <f aca="false">IF(Tracker!$C72="",NA(),Tracker!$C$7)</f>
@@ -26506,7 +26686,7 @@
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">IF(Tracker!$C73="",NA(),IF(A62&lt;Tracker!$J$6,NA(),IF(A62=Tracker!$J$6,Tracker!$H73,Tracker!$F73)))</f>
-        <v>60683.5</v>
+        <v>25608.34</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">IF(Tracker!$C73="",NA(),Tracker!$C$7)</f>
@@ -26531,7 +26711,7 @@
       </c>
       <c r="C63" s="31" t="n">
         <f aca="false">IF(Tracker!$C74="",NA(),IF(A63&lt;Tracker!$J$6,NA(),IF(A63=Tracker!$J$6,Tracker!$H74,Tracker!$F74)))</f>
-        <v>62504.01</v>
+        <v>26376.59</v>
       </c>
       <c r="D63" s="31" t="n">
         <f aca="false">IF(Tracker!$C74="",NA(),Tracker!$C$7)</f>
@@ -26556,7 +26736,7 @@
       </c>
       <c r="C64" s="31" t="n">
         <f aca="false">IF(Tracker!$C75="",NA(),IF(A64&lt;Tracker!$J$6,NA(),IF(A64=Tracker!$J$6,Tracker!$H75,Tracker!$F75)))</f>
-        <v>64379.13</v>
+        <v>27167.89</v>
       </c>
       <c r="D64" s="31" t="n">
         <f aca="false">IF(Tracker!$C75="",NA(),Tracker!$C$7)</f>
@@ -26581,7 +26761,7 @@
       </c>
       <c r="C65" s="31" t="n">
         <f aca="false">IF(Tracker!$C76="",NA(),IF(A65&lt;Tracker!$J$6,NA(),IF(A65=Tracker!$J$6,Tracker!$H76,Tracker!$F76)))</f>
-        <v>66310.5</v>
+        <v>27982.93</v>
       </c>
       <c r="D65" s="31" t="n">
         <f aca="false">IF(Tracker!$C76="",NA(),Tracker!$C$7)</f>
@@ -26606,7 +26786,7 @@
       </c>
       <c r="C66" s="31" t="n">
         <f aca="false">IF(Tracker!$C77="",NA(),IF(A66&lt;Tracker!$J$6,NA(),IF(A66=Tracker!$J$6,Tracker!$H77,Tracker!$F77)))</f>
-        <v>68299.82</v>
+        <v>28822.42</v>
       </c>
       <c r="D66" s="31" t="n">
         <f aca="false">IF(Tracker!$C77="",NA(),Tracker!$C$7)</f>
@@ -26631,7 +26811,7 @@
       </c>
       <c r="C67" s="31" t="n">
         <f aca="false">IF(Tracker!$C78="",NA(),IF(A67&lt;Tracker!$J$6,NA(),IF(A67=Tracker!$J$6,Tracker!$H78,Tracker!$F78)))</f>
-        <v>70348.81</v>
+        <v>29687.09</v>
       </c>
       <c r="D67" s="31" t="n">
         <f aca="false">IF(Tracker!$C78="",NA(),Tracker!$C$7)</f>
@@ -26656,7 +26836,7 @@
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">IF(Tracker!$C79="",NA(),IF(A68&lt;Tracker!$J$6,NA(),IF(A68=Tracker!$J$6,Tracker!$H79,Tracker!$F79)))</f>
-        <v>72459.27</v>
+        <v>30577.7</v>
       </c>
       <c r="D68" s="31" t="n">
         <f aca="false">IF(Tracker!$C79="",NA(),Tracker!$C$7)</f>
@@ -26681,7 +26861,7 @@
       </c>
       <c r="C69" s="31" t="n">
         <f aca="false">IF(Tracker!$C80="",NA(),IF(A69&lt;Tracker!$J$6,NA(),IF(A69=Tracker!$J$6,Tracker!$H80,Tracker!$F80)))</f>
-        <v>74633.05</v>
+        <v>31495.03</v>
       </c>
       <c r="D69" s="31" t="n">
         <f aca="false">IF(Tracker!$C80="",NA(),Tracker!$C$7)</f>
@@ -26706,7 +26886,7 @@
       </c>
       <c r="C70" s="31" t="n">
         <f aca="false">IF(Tracker!$C81="",NA(),IF(A70&lt;Tracker!$J$6,NA(),IF(A70=Tracker!$J$6,Tracker!$H81,Tracker!$F81)))</f>
-        <v>76872.04</v>
+        <v>32439.88</v>
       </c>
       <c r="D70" s="31" t="n">
         <f aca="false">IF(Tracker!$C81="",NA(),Tracker!$C$7)</f>
@@ -26731,7 +26911,7 @@
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">IF(Tracker!$C82="",NA(),IF(A71&lt;Tracker!$J$6,NA(),IF(A71=Tracker!$J$6,Tracker!$H82,Tracker!$F82)))</f>
-        <v>79178.2</v>
+        <v>33413.08</v>
       </c>
       <c r="D71" s="31" t="n">
         <f aca="false">IF(Tracker!$C82="",NA(),Tracker!$C$7)</f>
@@ -26756,7 +26936,7 @@
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">IF(Tracker!$C83="",NA(),IF(A72&lt;Tracker!$J$6,NA(),IF(A72=Tracker!$J$6,Tracker!$H83,Tracker!$F83)))</f>
-        <v>81553.5500000001</v>
+        <v>34415.47</v>
       </c>
       <c r="D72" s="31" t="n">
         <f aca="false">IF(Tracker!$C83="",NA(),Tracker!$C$7)</f>
@@ -26781,7 +26961,7 @@
       </c>
       <c r="C73" s="31" t="n">
         <f aca="false">IF(Tracker!$C84="",NA(),IF(A73&lt;Tracker!$J$6,NA(),IF(A73=Tracker!$J$6,Tracker!$H84,Tracker!$F84)))</f>
-        <v>84000.1600000001</v>
+        <v>35447.93</v>
       </c>
       <c r="D73" s="31" t="n">
         <f aca="false">IF(Tracker!$C84="",NA(),Tracker!$C$7)</f>
@@ -26806,7 +26986,7 @@
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">IF(Tracker!$C85="",NA(),IF(A74&lt;Tracker!$J$6,NA(),IF(A74=Tracker!$J$6,Tracker!$H85,Tracker!$F85)))</f>
-        <v>86520.1600000001</v>
+        <v>36511.37</v>
       </c>
       <c r="D74" s="31" t="n">
         <f aca="false">IF(Tracker!$C85="",NA(),Tracker!$C$7)</f>
@@ -26831,7 +27011,7 @@
       </c>
       <c r="C75" s="31" t="n">
         <f aca="false">IF(Tracker!$C86="",NA(),IF(A75&lt;Tracker!$J$6,NA(),IF(A75=Tracker!$J$6,Tracker!$H86,Tracker!$F86)))</f>
-        <v>89115.7600000001</v>
+        <v>37606.71</v>
       </c>
       <c r="D75" s="31" t="n">
         <f aca="false">IF(Tracker!$C86="",NA(),Tracker!$C$7)</f>
@@ -26856,7 +27036,7 @@
       </c>
       <c r="C76" s="31" t="n">
         <f aca="false">IF(Tracker!$C87="",NA(),IF(A76&lt;Tracker!$J$6,NA(),IF(A76=Tracker!$J$6,Tracker!$H87,Tracker!$F87)))</f>
-        <v>91789.2300000001</v>
+        <v>38734.91</v>
       </c>
       <c r="D76" s="31" t="n">
         <f aca="false">IF(Tracker!$C87="",NA(),Tracker!$C$7)</f>
@@ -26881,7 +27061,7 @@
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">IF(Tracker!$C88="",NA(),IF(A77&lt;Tracker!$J$6,NA(),IF(A77=Tracker!$J$6,Tracker!$H88,Tracker!$F88)))</f>
-        <v>94542.9100000001</v>
+        <v>39896.96</v>
       </c>
       <c r="D77" s="31" t="n">
         <f aca="false">IF(Tracker!$C88="",NA(),Tracker!$C$7)</f>
@@ -26906,7 +27086,7 @@
       </c>
       <c r="C78" s="31" t="n">
         <f aca="false">IF(Tracker!$C89="",NA(),IF(A78&lt;Tracker!$J$6,NA(),IF(A78=Tracker!$J$6,Tracker!$H89,Tracker!$F89)))</f>
-        <v>97379.2</v>
+        <v>41093.87</v>
       </c>
       <c r="D78" s="31" t="n">
         <f aca="false">IF(Tracker!$C89="",NA(),Tracker!$C$7)</f>
@@ -26931,7 +27111,7 @@
       </c>
       <c r="C79" s="31" t="n">
         <f aca="false">IF(Tracker!$C90="",NA(),IF(A79&lt;Tracker!$J$6,NA(),IF(A79=Tracker!$J$6,Tracker!$H90,Tracker!$F90)))</f>
-        <v>100300.58</v>
+        <v>42326.69</v>
       </c>
       <c r="D79" s="31" t="n">
         <f aca="false">IF(Tracker!$C90="",NA(),Tracker!$C$7)</f>
@@ -26954,13 +27134,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G91),Tracker!$H91,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C80" s="33" t="e">
+      <c r="C80" s="31" t="n">
         <f aca="false">IF(Tracker!$C91="",NA(),IF(A80&lt;Tracker!$J$6,NA(),IF(A80=Tracker!$J$6,Tracker!$H91,Tracker!$F91)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D80" s="33" t="e">
+        <v>43596.49</v>
+      </c>
+      <c r="D80" s="31" t="n">
         <f aca="false">IF(Tracker!$C91="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E80" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G91),N(Tracker!$G91)&gt;0),Tracker!$G91,NA())</f>
@@ -26979,13 +27159,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G92),Tracker!$H92,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C81" s="33" t="e">
+      <c r="C81" s="31" t="n">
         <f aca="false">IF(Tracker!$C92="",NA(),IF(A81&lt;Tracker!$J$6,NA(),IF(A81=Tracker!$J$6,Tracker!$H92,Tracker!$F92)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D81" s="33" t="e">
+        <v>44904.38</v>
+      </c>
+      <c r="D81" s="31" t="n">
         <f aca="false">IF(Tracker!$C92="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E81" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G92),N(Tracker!$G92)&gt;0),Tracker!$G92,NA())</f>
@@ -27004,13 +27184,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G93),Tracker!$H93,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C82" s="33" t="e">
+      <c r="C82" s="31" t="n">
         <f aca="false">IF(Tracker!$C93="",NA(),IF(A82&lt;Tracker!$J$6,NA(),IF(A82=Tracker!$J$6,Tracker!$H93,Tracker!$F93)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D82" s="33" t="e">
+        <v>46251.51</v>
+      </c>
+      <c r="D82" s="31" t="n">
         <f aca="false">IF(Tracker!$C93="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E82" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G93),N(Tracker!$G93)&gt;0),Tracker!$G93,NA())</f>
@@ -27029,13 +27209,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G94),Tracker!$H94,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C83" s="33" t="e">
+      <c r="C83" s="31" t="n">
         <f aca="false">IF(Tracker!$C94="",NA(),IF(A83&lt;Tracker!$J$6,NA(),IF(A83=Tracker!$J$6,Tracker!$H94,Tracker!$F94)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D83" s="33" t="e">
+        <v>47639.06</v>
+      </c>
+      <c r="D83" s="31" t="n">
         <f aca="false">IF(Tracker!$C94="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E83" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G94),N(Tracker!$G94)&gt;0),Tracker!$G94,NA())</f>
@@ -27054,13 +27234,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G95),Tracker!$H95,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C84" s="33" t="e">
+      <c r="C84" s="31" t="n">
         <f aca="false">IF(Tracker!$C95="",NA(),IF(A84&lt;Tracker!$J$6,NA(),IF(A84=Tracker!$J$6,Tracker!$H95,Tracker!$F95)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D84" s="33" t="e">
+        <v>49068.23</v>
+      </c>
+      <c r="D84" s="31" t="n">
         <f aca="false">IF(Tracker!$C95="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E84" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G95),N(Tracker!$G95)&gt;0),Tracker!$G95,NA())</f>
@@ -27079,13 +27259,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G96),Tracker!$H96,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C85" s="33" t="e">
+      <c r="C85" s="31" t="n">
         <f aca="false">IF(Tracker!$C96="",NA(),IF(A85&lt;Tracker!$J$6,NA(),IF(A85=Tracker!$J$6,Tracker!$H96,Tracker!$F96)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D85" s="33" t="e">
+        <v>50540.28</v>
+      </c>
+      <c r="D85" s="31" t="n">
         <f aca="false">IF(Tracker!$C96="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E85" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G96),N(Tracker!$G96)&gt;0),Tracker!$G96,NA())</f>
@@ -27104,13 +27284,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G97),Tracker!$H97,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C86" s="33" t="e">
+      <c r="C86" s="31" t="n">
         <f aca="false">IF(Tracker!$C97="",NA(),IF(A86&lt;Tracker!$J$6,NA(),IF(A86=Tracker!$J$6,Tracker!$H97,Tracker!$F97)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D86" s="33" t="e">
+        <v>52056.49</v>
+      </c>
+      <c r="D86" s="31" t="n">
         <f aca="false">IF(Tracker!$C97="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E86" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G97),N(Tracker!$G97)&gt;0),Tracker!$G97,NA())</f>
@@ -27129,13 +27309,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G98),Tracker!$H98,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C87" s="33" t="e">
+      <c r="C87" s="31" t="n">
         <f aca="false">IF(Tracker!$C98="",NA(),IF(A87&lt;Tracker!$J$6,NA(),IF(A87=Tracker!$J$6,Tracker!$H98,Tracker!$F98)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D87" s="33" t="e">
+        <v>53618.18</v>
+      </c>
+      <c r="D87" s="31" t="n">
         <f aca="false">IF(Tracker!$C98="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E87" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G98),N(Tracker!$G98)&gt;0),Tracker!$G98,NA())</f>
@@ -27154,13 +27334,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G99),Tracker!$H99,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C88" s="33" t="e">
+      <c r="C88" s="31" t="n">
         <f aca="false">IF(Tracker!$C99="",NA(),IF(A88&lt;Tracker!$J$6,NA(),IF(A88=Tracker!$J$6,Tracker!$H99,Tracker!$F99)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D88" s="33" t="e">
+        <v>55226.73</v>
+      </c>
+      <c r="D88" s="31" t="n">
         <f aca="false">IF(Tracker!$C99="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E88" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G99),N(Tracker!$G99)&gt;0),Tracker!$G99,NA())</f>
@@ -27179,13 +27359,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G100),Tracker!$H100,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C89" s="33" t="e">
+      <c r="C89" s="31" t="n">
         <f aca="false">IF(Tracker!$C100="",NA(),IF(A89&lt;Tracker!$J$6,NA(),IF(A89=Tracker!$J$6,Tracker!$H100,Tracker!$F100)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D89" s="33" t="e">
+        <v>56883.53</v>
+      </c>
+      <c r="D89" s="31" t="n">
         <f aca="false">IF(Tracker!$C100="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E89" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G100),N(Tracker!$G100)&gt;0),Tracker!$G100,NA())</f>
@@ -27204,13 +27384,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G101),Tracker!$H101,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C90" s="33" t="e">
+      <c r="C90" s="31" t="n">
         <f aca="false">IF(Tracker!$C101="",NA(),IF(A90&lt;Tracker!$J$6,NA(),IF(A90=Tracker!$J$6,Tracker!$H101,Tracker!$F101)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D90" s="33" t="e">
+        <v>58590.04</v>
+      </c>
+      <c r="D90" s="31" t="n">
         <f aca="false">IF(Tracker!$C101="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E90" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G101),N(Tracker!$G101)&gt;0),Tracker!$G101,NA())</f>
@@ -27229,13 +27409,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G102),Tracker!$H102,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C91" s="33" t="e">
+      <c r="C91" s="31" t="n">
         <f aca="false">IF(Tracker!$C102="",NA(),IF(A91&lt;Tracker!$J$6,NA(),IF(A91=Tracker!$J$6,Tracker!$H102,Tracker!$F102)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D91" s="33" t="e">
+        <v>60347.74</v>
+      </c>
+      <c r="D91" s="31" t="n">
         <f aca="false">IF(Tracker!$C102="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E91" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G102),N(Tracker!$G102)&gt;0),Tracker!$G102,NA())</f>
@@ -27254,13 +27434,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G103),Tracker!$H103,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C92" s="33" t="e">
+      <c r="C92" s="31" t="n">
         <f aca="false">IF(Tracker!$C103="",NA(),IF(A92&lt;Tracker!$J$6,NA(),IF(A92=Tracker!$J$6,Tracker!$H103,Tracker!$F103)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D92" s="33" t="e">
+        <v>62158.17</v>
+      </c>
+      <c r="D92" s="31" t="n">
         <f aca="false">IF(Tracker!$C103="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E92" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G103),N(Tracker!$G103)&gt;0),Tracker!$G103,NA())</f>
@@ -27279,13 +27459,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G104),Tracker!$H104,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C93" s="33" t="e">
+      <c r="C93" s="31" t="n">
         <f aca="false">IF(Tracker!$C104="",NA(),IF(A93&lt;Tracker!$J$6,NA(),IF(A93=Tracker!$J$6,Tracker!$H104,Tracker!$F104)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D93" s="33" t="e">
+        <v>64022.92</v>
+      </c>
+      <c r="D93" s="31" t="n">
         <f aca="false">IF(Tracker!$C104="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E93" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G104),N(Tracker!$G104)&gt;0),Tracker!$G104,NA())</f>
@@ -27304,13 +27484,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G105),Tracker!$H105,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C94" s="33" t="e">
+      <c r="C94" s="31" t="n">
         <f aca="false">IF(Tracker!$C105="",NA(),IF(A94&lt;Tracker!$J$6,NA(),IF(A94=Tracker!$J$6,Tracker!$H105,Tracker!$F105)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D94" s="33" t="e">
+        <v>65943.61</v>
+      </c>
+      <c r="D94" s="31" t="n">
         <f aca="false">IF(Tracker!$C105="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E94" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G105),N(Tracker!$G105)&gt;0),Tracker!$G105,NA())</f>
@@ -27329,13 +27509,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G106),Tracker!$H106,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C95" s="33" t="e">
+      <c r="C95" s="31" t="n">
         <f aca="false">IF(Tracker!$C106="",NA(),IF(A95&lt;Tracker!$J$6,NA(),IF(A95=Tracker!$J$6,Tracker!$H106,Tracker!$F106)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D95" s="33" t="e">
+        <v>67921.92</v>
+      </c>
+      <c r="D95" s="31" t="n">
         <f aca="false">IF(Tracker!$C106="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E95" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G106),N(Tracker!$G106)&gt;0),Tracker!$G106,NA())</f>
@@ -27354,13 +27534,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G107),Tracker!$H107,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C96" s="33" t="e">
+      <c r="C96" s="31" t="n">
         <f aca="false">IF(Tracker!$C107="",NA(),IF(A96&lt;Tracker!$J$6,NA(),IF(A96=Tracker!$J$6,Tracker!$H107,Tracker!$F107)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D96" s="33" t="e">
+        <v>69959.58</v>
+      </c>
+      <c r="D96" s="31" t="n">
         <f aca="false">IF(Tracker!$C107="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E96" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G107),N(Tracker!$G107)&gt;0),Tracker!$G107,NA())</f>
@@ -27379,13 +27559,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G108),Tracker!$H108,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C97" s="33" t="e">
+      <c r="C97" s="31" t="n">
         <f aca="false">IF(Tracker!$C108="",NA(),IF(A97&lt;Tracker!$J$6,NA(),IF(A97=Tracker!$J$6,Tracker!$H108,Tracker!$F108)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D97" s="33" t="e">
+        <v>72058.37</v>
+      </c>
+      <c r="D97" s="31" t="n">
         <f aca="false">IF(Tracker!$C108="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E97" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G108),N(Tracker!$G108)&gt;0),Tracker!$G108,NA())</f>
@@ -27404,13 +27584,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G109),Tracker!$H109,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C98" s="33" t="e">
+      <c r="C98" s="31" t="n">
         <f aca="false">IF(Tracker!$C109="",NA(),IF(A98&lt;Tracker!$J$6,NA(),IF(A98=Tracker!$J$6,Tracker!$H109,Tracker!$F109)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D98" s="33" t="e">
+        <v>74220.12</v>
+      </c>
+      <c r="D98" s="31" t="n">
         <f aca="false">IF(Tracker!$C109="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E98" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G109),N(Tracker!$G109)&gt;0),Tracker!$G109,NA())</f>
@@ -27429,13 +27609,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G110),Tracker!$H110,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C99" s="33" t="e">
+      <c r="C99" s="31" t="n">
         <f aca="false">IF(Tracker!$C110="",NA(),IF(A99&lt;Tracker!$J$6,NA(),IF(A99=Tracker!$J$6,Tracker!$H110,Tracker!$F110)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D99" s="33" t="e">
+        <v>76446.72</v>
+      </c>
+      <c r="D99" s="31" t="n">
         <f aca="false">IF(Tracker!$C110="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E99" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G110),N(Tracker!$G110)&gt;0),Tracker!$G110,NA())</f>
@@ -27454,13 +27634,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G111),Tracker!$H111,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C100" s="33" t="e">
+      <c r="C100" s="31" t="n">
         <f aca="false">IF(Tracker!$C111="",NA(),IF(A100&lt;Tracker!$J$6,NA(),IF(A100=Tracker!$J$6,Tracker!$H111,Tracker!$F111)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D100" s="33" t="e">
+        <v>78740.12</v>
+      </c>
+      <c r="D100" s="31" t="n">
         <f aca="false">IF(Tracker!$C111="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E100" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G111),N(Tracker!$G111)&gt;0),Tracker!$G111,NA())</f>
@@ -27479,13 +27659,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G112),Tracker!$H112,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C101" s="33" t="e">
+      <c r="C101" s="31" t="n">
         <f aca="false">IF(Tracker!$C112="",NA(),IF(A101&lt;Tracker!$J$6,NA(),IF(A101=Tracker!$J$6,Tracker!$H112,Tracker!$F112)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D101" s="33" t="e">
+        <v>81102.32</v>
+      </c>
+      <c r="D101" s="31" t="n">
         <f aca="false">IF(Tracker!$C112="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E101" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G112),N(Tracker!$G112)&gt;0),Tracker!$G112,NA())</f>
@@ -27504,13 +27684,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G113),Tracker!$H113,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C102" s="33" t="e">
+      <c r="C102" s="31" t="n">
         <f aca="false">IF(Tracker!$C113="",NA(),IF(A102&lt;Tracker!$J$6,NA(),IF(A102=Tracker!$J$6,Tracker!$H113,Tracker!$F113)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D102" s="33" t="e">
+        <v>83535.39</v>
+      </c>
+      <c r="D102" s="31" t="n">
         <f aca="false">IF(Tracker!$C113="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E102" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G113),N(Tracker!$G113)&gt;0),Tracker!$G113,NA())</f>
@@ -27529,13 +27709,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G114),Tracker!$H114,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C103" s="33" t="e">
+      <c r="C103" s="31" t="n">
         <f aca="false">IF(Tracker!$C114="",NA(),IF(A103&lt;Tracker!$J$6,NA(),IF(A103=Tracker!$J$6,Tracker!$H114,Tracker!$F114)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D103" s="33" t="e">
+        <v>86041.45</v>
+      </c>
+      <c r="D103" s="31" t="n">
         <f aca="false">IF(Tracker!$C114="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E103" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G114),N(Tracker!$G114)&gt;0),Tracker!$G114,NA())</f>
@@ -27554,13 +27734,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G115),Tracker!$H115,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C104" s="33" t="e">
+      <c r="C104" s="31" t="n">
         <f aca="false">IF(Tracker!$C115="",NA(),IF(A104&lt;Tracker!$J$6,NA(),IF(A104=Tracker!$J$6,Tracker!$H115,Tracker!$F115)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D104" s="33" t="e">
+        <v>88622.69</v>
+      </c>
+      <c r="D104" s="31" t="n">
         <f aca="false">IF(Tracker!$C115="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E104" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G115),N(Tracker!$G115)&gt;0),Tracker!$G115,NA())</f>
@@ -27579,13 +27759,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G116),Tracker!$H116,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C105" s="33" t="e">
+      <c r="C105" s="31" t="n">
         <f aca="false">IF(Tracker!$C116="",NA(),IF(A105&lt;Tracker!$J$6,NA(),IF(A105=Tracker!$J$6,Tracker!$H116,Tracker!$F116)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D105" s="33" t="e">
+        <v>91281.37</v>
+      </c>
+      <c r="D105" s="31" t="n">
         <f aca="false">IF(Tracker!$C116="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E105" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G116),N(Tracker!$G116)&gt;0),Tracker!$G116,NA())</f>
@@ -27604,13 +27784,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G117),Tracker!$H117,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C106" s="33" t="e">
+      <c r="C106" s="31" t="n">
         <f aca="false">IF(Tracker!$C117="",NA(),IF(A106&lt;Tracker!$J$6,NA(),IF(A106=Tracker!$J$6,Tracker!$H117,Tracker!$F117)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D106" s="33" t="e">
+        <v>94019.81</v>
+      </c>
+      <c r="D106" s="31" t="n">
         <f aca="false">IF(Tracker!$C117="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E106" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G117),N(Tracker!$G117)&gt;0),Tracker!$G117,NA())</f>
@@ -27629,13 +27809,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G118),Tracker!$H118,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C107" s="33" t="e">
+      <c r="C107" s="31" t="n">
         <f aca="false">IF(Tracker!$C118="",NA(),IF(A107&lt;Tracker!$J$6,NA(),IF(A107=Tracker!$J$6,Tracker!$H118,Tracker!$F118)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D107" s="33" t="e">
+        <v>96840.4</v>
+      </c>
+      <c r="D107" s="31" t="n">
         <f aca="false">IF(Tracker!$C118="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E107" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G118),N(Tracker!$G118)&gt;0),Tracker!$G118,NA())</f>
@@ -27654,13 +27834,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G119),Tracker!$H119,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C108" s="33" t="e">
+      <c r="C108" s="31" t="n">
         <f aca="false">IF(Tracker!$C119="",NA(),IF(A108&lt;Tracker!$J$6,NA(),IF(A108=Tracker!$J$6,Tracker!$H119,Tracker!$F119)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D108" s="33" t="e">
+        <v>99745.61</v>
+      </c>
+      <c r="D108" s="31" t="n">
         <f aca="false">IF(Tracker!$C119="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E108" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G119),N(Tracker!$G119)&gt;0),Tracker!$G119,NA())</f>
@@ -27679,13 +27859,13 @@
         <f aca="false">IF(ISNUMBER(Tracker!$G120),Tracker!$H120,NA())</f>
         <v>#N/A</v>
       </c>
-      <c r="C109" s="33" t="e">
+      <c r="C109" s="31" t="n">
         <f aca="false">IF(Tracker!$C120="",NA(),IF(A109&lt;Tracker!$J$6,NA(),IF(A109=Tracker!$J$6,Tracker!$H120,Tracker!$F120)))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D109" s="33" t="e">
+        <v>102737.98</v>
+      </c>
+      <c r="D109" s="31" t="n">
         <f aca="false">IF(Tracker!$C120="",NA(),Tracker!$C$7)</f>
-        <v>#N/A</v>
+        <v>100000</v>
       </c>
       <c r="E109" s="33" t="e">
         <f aca="false">IF(AND(ISNUMBER(Tracker!$G120),N(Tracker!$G120)&gt;0),Tracker!$G120,NA())</f>

--- a/Trading_PnL_Tracker.xlsx
+++ b/Trading_PnL_Tracker.xlsx
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
   <si>
     <t xml:space="preserve">Live summary of the Tracker sheet — enter results there, not here. Figures marked * are projections that assume every daily profit target is met; they are illustrations, not guarantees.</t>
   </si>
@@ -351,6 +351,18 @@
   </si>
   <si>
     <t xml:space="preserve">   • The table stops at the first day whose projected (or actual) close reaches the goal, and extends automatically after losses (up to 500 days).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sync with the website dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • On the website, "Download Excel" gives you this file filled with everything saved there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • "Import from Excel" on the website reads this file's Closing Balance, Done?, Notes, Settings and NSE Holidays, and replaces the website's data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • They don't update each other live. Type in one place, then move the data across with those buttons.</t>
   </si>
   <si>
     <t xml:space="preserve">Other notes</t>
@@ -3359,11 +3371,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71873509"/>
-        <c:axId val="29867929"/>
+        <c:axId val="89161003"/>
+        <c:axId val="26325666"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71873509"/>
+        <c:axId val="89161003"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3429,7 +3441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29867929"/>
+        <c:crossAx val="26325666"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3437,7 +3449,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29867929"/>
+        <c:axId val="26325666"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3513,7 +3525,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71873509"/>
+        <c:crossAx val="89161003"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4644,11 +4656,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="100"/>
-        <c:axId val="25250192"/>
-        <c:axId val="36325388"/>
+        <c:axId val="28709444"/>
+        <c:axId val="4003282"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25250192"/>
+        <c:axId val="28709444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4714,7 +4726,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36325388"/>
+        <c:crossAx val="4003282"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4722,7 +4734,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36325388"/>
+        <c:axId val="4003282"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4798,7 +4810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25250192"/>
+        <c:crossAx val="28709444"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5444,7 +5456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1DF01534-C5DE-4079-9CE2-48A9ACE0ADD2}</x14:id>
+          <x14:id>{DCCF2CDD-89E7-417B-824B-BF3E469097F4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5481,7 +5493,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1DF01534-C5DE-4079-9CE2-48A9ACE0ADD2}">
+          <x14:cfRule type="dataBar" id="{DCCF2CDD-89E7-417B-824B-BF3E469097F4}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -24300,7 +24312,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93FCA3E9-B7B4-4178-8D8C-F0A8175D346B}</x14:id>
+          <x14:id>{39EFEA56-12AE-4D78-A16A-D4A8DB88DAA7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24331,7 +24343,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93FCA3E9-B7B4-4178-8D8C-F0A8175D346B}">
+          <x14:cfRule type="dataBar" id="{39EFEA56-12AE-4D78-A16A-D4A8DB88DAA7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -25025,7 +25037,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -25139,23 +25151,46 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="45"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="48" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="47" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="47" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="47" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -25182,19 +25217,19 @@
         <v>31</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" s="49" t="s">
         <v>25</v>
       </c>
       <c r="E1" s="49" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F1" s="49" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
